--- a/data/freight/HARPEX.xlsx
+++ b/data/freight/HARPEX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B5BDCE-9395-4A03-A26D-81FE6F4A43B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BCCEB8-BBDE-4D64-B4F2-C31E622C0F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31605" yWindow="1950" windowWidth="21600" windowHeight="10875" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
   <sheets>
     <sheet name="HARPEX" sheetId="1" r:id="rId1"/>
@@ -199,9 +199,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -219,7 +219,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2752,6 +2752,9 @@
                 <c:pt idx="827">
                   <c:v>46171</c:v>
                 </c:pt>
+                <c:pt idx="828">
+                  <c:v>46178</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4601,6 +4604,9 @@
                   <c:v>2321</c:v>
                 </c:pt>
                 <c:pt idx="827">
+                  <c:v>2322.1999999999998</c:v>
+                </c:pt>
+                <c:pt idx="828">
                   <c:v>2322.1999999999998</c:v>
                 </c:pt>
               </c:numCache>
@@ -4702,7 +4708,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -5415,9 +5421,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5455,7 +5461,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5561,7 +5567,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5703,7 +5709,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5711,17 +5717,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
-  <dimension ref="A1:P829"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P830"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.36328125" style="16" customWidth="1"/>
     <col min="4" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.36328125" style="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -5769,7 +5775,7 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>40383</v>
       </c>
@@ -5780,7 +5786,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>40390</v>
       </c>
@@ -5791,7 +5797,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>40397</v>
       </c>
@@ -5802,7 +5808,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>40404</v>
       </c>
@@ -5813,7 +5819,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>40411</v>
       </c>
@@ -5824,7 +5830,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>40418</v>
       </c>
@@ -5835,7 +5841,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>40425</v>
       </c>
@@ -5846,7 +5852,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>40432</v>
       </c>
@@ -5857,7 +5863,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>40439</v>
       </c>
@@ -5868,7 +5874,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>40446</v>
       </c>
@@ -5879,7 +5885,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>40453</v>
       </c>
@@ -5890,7 +5896,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>40460</v>
       </c>
@@ -5901,7 +5907,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>40467</v>
       </c>
@@ -5912,7 +5918,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>40474</v>
       </c>
@@ -5923,7 +5929,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>40481</v>
       </c>
@@ -5934,7 +5940,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>40488</v>
       </c>
@@ -5945,7 +5951,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>40495</v>
       </c>
@@ -5956,7 +5962,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>40502</v>
       </c>
@@ -5967,7 +5973,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>40509</v>
       </c>
@@ -5978,7 +5984,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>40516</v>
       </c>
@@ -5989,7 +5995,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>40523</v>
       </c>
@@ -6000,7 +6006,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>40530</v>
       </c>
@@ -6011,7 +6017,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>40537</v>
       </c>
@@ -6022,7 +6028,7 @@
         <v>679.37</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>40544</v>
       </c>
@@ -6033,7 +6039,7 @@
         <v>696.35</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>40551</v>
       </c>
@@ -6044,7 +6050,7 @@
         <v>706.3</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>40558</v>
       </c>
@@ -6055,7 +6061,7 @@
         <v>719.55</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>40565</v>
       </c>
@@ -6066,7 +6072,7 @@
         <v>747.31</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>40572</v>
       </c>
@@ -6077,7 +6083,7 @@
         <v>764.29</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>40579</v>
       </c>
@@ -6088,7 +6094,7 @@
         <v>782.1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>40586</v>
       </c>
@@ -6099,7 +6105,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>40593</v>
       </c>
@@ -6110,7 +6116,7 @@
         <v>849.63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>40600</v>
       </c>
@@ -6121,7 +6127,7 @@
         <v>861.23</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>40607</v>
       </c>
@@ -6132,7 +6138,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>40614</v>
       </c>
@@ -6143,7 +6149,7 @@
         <v>879.04</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>40621</v>
       </c>
@@ -6154,7 +6160,7 @@
         <v>882.35</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>40628</v>
       </c>
@@ -6165,7 +6171,7 @@
         <v>900.99</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>40635</v>
       </c>
@@ -6176,7 +6182,7 @@
         <v>892.29</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>40642</v>
       </c>
@@ -6187,7 +6193,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>40649</v>
       </c>
@@ -6198,7 +6204,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>40656</v>
       </c>
@@ -6209,7 +6215,7 @@
         <v>879.87</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>40663</v>
       </c>
@@ -6220,7 +6226,7 @@
         <v>875.72</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>40670</v>
       </c>
@@ -6231,7 +6237,7 @@
         <v>874.48</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>40677</v>
       </c>
@@ -6242,7 +6248,7 @@
         <v>877.38</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>40684</v>
       </c>
@@ -6253,7 +6259,7 @@
         <v>876.14</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>40691</v>
       </c>
@@ -6264,7 +6270,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>40698</v>
       </c>
@@ -6275,7 +6281,7 @@
         <v>865.37</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>40705</v>
       </c>
@@ -6286,7 +6292,7 @@
         <v>856.67</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>40712</v>
       </c>
@@ -6297,7 +6303,7 @@
         <v>847.14</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>40719</v>
       </c>
@@ -6308,7 +6314,7 @@
         <v>831.4</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>40726</v>
       </c>
@@ -6319,7 +6325,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>40733</v>
       </c>
@@ -6330,7 +6336,7 @@
         <v>808.62</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>40740</v>
       </c>
@@ -6341,7 +6347,7 @@
         <v>775.06</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>40747</v>
       </c>
@@ -6352,7 +6358,7 @@
         <v>741.51</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>40754</v>
       </c>
@@ -6363,7 +6369,7 @@
         <v>719.97</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>40761</v>
       </c>
@@ -6374,7 +6380,7 @@
         <v>709.2</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>40768</v>
       </c>
@@ -6385,7 +6391,7 @@
         <v>671.91</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>40775</v>
       </c>
@@ -6396,7 +6402,7 @@
         <v>666.11</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>40782</v>
       </c>
@@ -6407,7 +6413,7 @@
         <v>657.83</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>40789</v>
       </c>
@@ -6418,7 +6424,7 @@
         <v>630.9</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>40796</v>
       </c>
@@ -6429,7 +6435,7 @@
         <v>621.38</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>40803</v>
       </c>
@@ -6440,7 +6446,7 @@
         <v>616.4</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>40810</v>
       </c>
@@ -6451,7 +6457,7 @@
         <v>555.1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>40817</v>
       </c>
@@ -6462,7 +6468,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>40824</v>
       </c>
@@ -6473,7 +6479,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>40831</v>
       </c>
@@ -6484,7 +6490,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>40838</v>
       </c>
@@ -6495,7 +6501,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>40845</v>
       </c>
@@ -6506,7 +6512,7 @@
         <v>445.32</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>40852</v>
       </c>
@@ -6517,7 +6523,7 @@
         <v>438.28</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>40859</v>
       </c>
@@ -6528,7 +6534,7 @@
         <v>437.45</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>40866</v>
       </c>
@@ -6539,7 +6545,7 @@
         <v>420.05</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>40873</v>
       </c>
@@ -6550,7 +6556,7 @@
         <v>417.98</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>40880</v>
       </c>
@@ -6561,7 +6567,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>40887</v>
       </c>
@@ -6572,7 +6578,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>40894</v>
       </c>
@@ -6583,7 +6589,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>40901</v>
       </c>
@@ -6594,7 +6600,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>40908</v>
       </c>
@@ -6605,7 +6611,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>40915</v>
       </c>
@@ -6616,7 +6622,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>40922</v>
       </c>
@@ -6627,7 +6633,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>40929</v>
       </c>
@@ -6638,7 +6644,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>40936</v>
       </c>
@@ -6649,7 +6655,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>40942</v>
       </c>
@@ -6660,7 +6666,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>40943</v>
       </c>
@@ -6671,7 +6677,7 @@
         <v>389.81</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>40950</v>
       </c>
@@ -6682,7 +6688,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>40957</v>
       </c>
@@ -6693,7 +6699,7 @@
         <v>375.31</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>40964</v>
       </c>
@@ -6704,7 +6710,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>40978</v>
       </c>
@@ -6715,7 +6721,7 @@
         <v>384.84</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>40985</v>
       </c>
@@ -6726,7 +6732,7 @@
         <v>393.12</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>40992</v>
       </c>
@@ -6737,7 +6743,7 @@
         <v>396.02</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>40999</v>
       </c>
@@ -6748,7 +6754,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>41006</v>
       </c>
@@ -6759,7 +6765,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>41013</v>
       </c>
@@ -6770,7 +6776,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>41020</v>
       </c>
@@ -6781,7 +6787,7 @@
         <v>416.32</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>41027</v>
       </c>
@@ -6792,7 +6798,7 @@
         <v>428.33</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>41034</v>
       </c>
@@ -6803,7 +6809,7 @@
         <v>440.35</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>41041</v>
       </c>
@@ -6814,7 +6820,7 @@
         <v>444.9</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>41048</v>
       </c>
@@ -6825,7 +6831,7 @@
         <v>457.33</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>41055</v>
       </c>
@@ -6836,7 +6842,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>41062</v>
       </c>
@@ -6847,7 +6853,7 @@
         <v>456.92</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>41069</v>
       </c>
@@ -6858,7 +6864,7 @@
         <v>451.12</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>41076</v>
       </c>
@@ -6869,7 +6875,7 @@
         <v>446.98</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>41083</v>
       </c>
@@ -6880,7 +6886,7 @@
         <v>437.86</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>41090</v>
       </c>
@@ -6891,7 +6897,7 @@
         <v>434.96</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>41097</v>
       </c>
@@ -6902,7 +6908,7 @@
         <v>430.41</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>41104</v>
       </c>
@@ -6913,7 +6919,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>41111</v>
       </c>
@@ -6924,7 +6930,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>41118</v>
       </c>
@@ -6935,7 +6941,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>41125</v>
       </c>
@@ -6946,7 +6952,7 @@
         <v>399.75</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>41132</v>
       </c>
@@ -6957,7 +6963,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>41139</v>
       </c>
@@ -6968,7 +6974,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>41146</v>
       </c>
@@ -6979,7 +6985,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>41153</v>
       </c>
@@ -6990,7 +6996,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>41160</v>
       </c>
@@ -7001,7 +7007,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>41167</v>
       </c>
@@ -7012,7 +7018,7 @@
         <v>386.08</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>41174</v>
       </c>
@@ -7023,7 +7029,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>41181</v>
       </c>
@@ -7034,7 +7040,7 @@
         <v>377.8</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>41188</v>
       </c>
@@ -7045,7 +7051,7 @@
         <v>373.65</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>41195</v>
       </c>
@@ -7056,7 +7062,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>41202</v>
       </c>
@@ -7067,7 +7073,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>41209</v>
       </c>
@@ -7078,7 +7084,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>41216</v>
       </c>
@@ -7089,7 +7095,7 @@
         <v>367.44</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>41223</v>
       </c>
@@ -7100,7 +7106,7 @@
         <v>366.61</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>41230</v>
       </c>
@@ -7111,7 +7117,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>41237</v>
       </c>
@@ -7122,7 +7128,7 @@
         <v>362.88</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>41244</v>
       </c>
@@ -7133,7 +7139,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>41251</v>
       </c>
@@ -7144,7 +7150,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>41258</v>
       </c>
@@ -7155,7 +7161,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>41265</v>
       </c>
@@ -7166,7 +7172,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>41272</v>
       </c>
@@ -7177,7 +7183,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>41279</v>
       </c>
@@ -7188,7 +7194,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>41286</v>
       </c>
@@ -7199,7 +7205,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>41293</v>
       </c>
@@ -7210,7 +7216,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>41300</v>
       </c>
@@ -7221,7 +7227,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>41307</v>
       </c>
@@ -7232,7 +7238,7 @@
         <v>366.2</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>41314</v>
       </c>
@@ -7243,7 +7249,7 @@
         <v>369.93</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>41321</v>
       </c>
@@ -7254,7 +7260,7 @@
         <v>372.41</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>41328</v>
       </c>
@@ -7265,7 +7271,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>41335</v>
       </c>
@@ -7276,7 +7282,7 @@
         <v>376.97</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>41342</v>
       </c>
@@ -7287,7 +7293,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>41349</v>
       </c>
@@ -7298,7 +7304,7 @@
         <v>382.35</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>41356</v>
       </c>
@@ -7309,7 +7315,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>41363</v>
       </c>
@@ -7320,7 +7326,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>41370</v>
       </c>
@@ -7331,7 +7337,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>41377</v>
       </c>
@@ -7342,7 +7348,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>41384</v>
       </c>
@@ -7353,7 +7359,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>41391</v>
       </c>
@@ -7364,7 +7370,7 @@
         <v>395.61</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>41398</v>
       </c>
@@ -7375,7 +7381,7 @@
         <v>396.85</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>41405</v>
       </c>
@@ -7386,7 +7392,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>41412</v>
       </c>
@@ -7397,7 +7403,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>41419</v>
       </c>
@@ -7408,7 +7414,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>41426</v>
       </c>
@@ -7419,7 +7425,7 @@
         <v>401.41</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>41433</v>
       </c>
@@ -7430,7 +7436,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>41440</v>
       </c>
@@ -7441,7 +7447,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>41447</v>
       </c>
@@ -7452,7 +7458,7 @@
         <v>400.58</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>41454</v>
       </c>
@@ -7463,7 +7469,7 @@
         <v>401.82</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>41461</v>
       </c>
@@ -7474,7 +7480,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>41468</v>
       </c>
@@ -7485,7 +7491,7 @@
         <v>398.51</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>41475</v>
       </c>
@@ -7496,7 +7502,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>41482</v>
       </c>
@@ -7507,7 +7513,7 @@
         <v>400.99</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>41489</v>
       </c>
@@ -7518,7 +7524,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>41496</v>
       </c>
@@ -7529,7 +7535,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>41503</v>
       </c>
@@ -7540,7 +7546,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>41510</v>
       </c>
@@ -7551,7 +7557,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>41517</v>
       </c>
@@ -7562,7 +7568,7 @@
         <v>404.72</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>41524</v>
       </c>
@@ -7573,7 +7579,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>41531</v>
       </c>
@@ -7584,7 +7590,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>41538</v>
       </c>
@@ -7595,7 +7601,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>41545</v>
       </c>
@@ -7606,7 +7612,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>41552</v>
       </c>
@@ -7617,7 +7623,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>41559</v>
       </c>
@@ -7628,7 +7634,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>41566</v>
       </c>
@@ -7639,7 +7645,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>41573</v>
       </c>
@@ -7650,7 +7656,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>41580</v>
       </c>
@@ -7661,7 +7667,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>41587</v>
       </c>
@@ -7672,7 +7678,7 @@
         <v>398.92</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>41594</v>
       </c>
@@ -7683,7 +7689,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>41601</v>
       </c>
@@ -7694,7 +7700,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>41608</v>
       </c>
@@ -7705,7 +7711,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>41615</v>
       </c>
@@ -7716,7 +7722,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>41622</v>
       </c>
@@ -7727,7 +7733,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>41629</v>
       </c>
@@ -7738,7 +7744,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>41636</v>
       </c>
@@ -7749,7 +7755,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>41643</v>
       </c>
@@ -7760,7 +7766,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>41650</v>
       </c>
@@ -7771,7 +7777,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>41657</v>
       </c>
@@ -7782,7 +7788,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>41664</v>
       </c>
@@ -7793,7 +7799,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>41671</v>
       </c>
@@ -7804,7 +7810,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>41678</v>
       </c>
@@ -7815,7 +7821,7 @@
         <v>387.74</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>41685</v>
       </c>
@@ -7826,7 +7832,7 @@
         <v>386.91</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>41692</v>
       </c>
@@ -7837,7 +7843,7 @@
         <v>385.25</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>41699</v>
       </c>
@@ -7848,7 +7854,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>41706</v>
       </c>
@@ -7859,7 +7865,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>41713</v>
       </c>
@@ -7870,7 +7876,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>41720</v>
       </c>
@@ -7881,7 +7887,7 @@
         <v>380.7</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>41727</v>
       </c>
@@ -7892,7 +7898,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>41734</v>
       </c>
@@ -7903,7 +7909,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>41741</v>
       </c>
@@ -7914,7 +7920,7 @@
         <v>386.5</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>41748</v>
       </c>
@@ -7925,7 +7931,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>41755</v>
       </c>
@@ -7936,7 +7942,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>41762</v>
       </c>
@@ -7947,7 +7953,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>41769</v>
       </c>
@@ -7958,7 +7964,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>41776</v>
       </c>
@@ -7969,7 +7975,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>41783</v>
       </c>
@@ -7980,7 +7986,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>41790</v>
       </c>
@@ -7991,7 +7997,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>41797</v>
       </c>
@@ -8002,7 +8008,7 @@
         <v>406.79</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>41804</v>
       </c>
@@ -8013,7 +8019,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>41811</v>
       </c>
@@ -8024,7 +8030,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>41818</v>
       </c>
@@ -8035,7 +8041,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>41825</v>
       </c>
@@ -8046,7 +8052,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>41832</v>
       </c>
@@ -8057,7 +8063,7 @@
         <v>409.28</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>41839</v>
       </c>
@@ -8068,7 +8074,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>41846</v>
       </c>
@@ -8079,7 +8085,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>41853</v>
       </c>
@@ -8090,7 +8096,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>41860</v>
       </c>
@@ -8101,7 +8107,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>41867</v>
       </c>
@@ -8112,7 +8118,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>41874</v>
       </c>
@@ -8123,7 +8129,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>41881</v>
       </c>
@@ -8134,7 +8140,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>41888</v>
       </c>
@@ -8145,7 +8151,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>41895</v>
       </c>
@@ -8156,7 +8162,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>41902</v>
       </c>
@@ -8167,7 +8173,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>41909</v>
       </c>
@@ -8178,7 +8184,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>41916</v>
       </c>
@@ -8189,7 +8195,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>41923</v>
       </c>
@@ -8200,7 +8206,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>41930</v>
       </c>
@@ -8211,7 +8217,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>41937</v>
       </c>
@@ -8222,7 +8228,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>41944</v>
       </c>
@@ -8233,7 +8239,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>41951</v>
       </c>
@@ -8244,7 +8250,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>41958</v>
       </c>
@@ -8255,7 +8261,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>41965</v>
       </c>
@@ -8266,7 +8272,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>41972</v>
       </c>
@@ -8277,7 +8283,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>41979</v>
       </c>
@@ -8288,7 +8294,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>41986</v>
       </c>
@@ -8299,7 +8305,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>41993</v>
       </c>
@@ -8310,7 +8316,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>42000</v>
       </c>
@@ -8321,7 +8327,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>42007</v>
       </c>
@@ -8332,7 +8338,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>42014</v>
       </c>
@@ -8343,7 +8349,7 @@
         <v>435.38</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>42021</v>
       </c>
@@ -8354,7 +8360,7 @@
         <v>441.59</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>42028</v>
       </c>
@@ -8365,7 +8371,7 @@
         <v>455.26</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>42035</v>
       </c>
@@ -8376,7 +8382,7 @@
         <v>461.47</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>42042</v>
       </c>
@@ -8387,7 +8393,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>42049</v>
       </c>
@@ -8398,7 +8404,7 @@
         <v>483.84</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>42056</v>
       </c>
@@ -8409,7 +8415,7 @@
         <v>494.2</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>42063</v>
       </c>
@@ -8420,7 +8426,7 @@
         <v>496.27</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
         <v>42070</v>
       </c>
@@ -8431,7 +8437,7 @@
         <v>502.49</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A244" s="1">
         <v>42077</v>
       </c>
@@ -8442,7 +8448,7 @@
         <v>504.14</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A245" s="1">
         <v>42084</v>
       </c>
@@ -8453,7 +8459,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
         <v>42091</v>
       </c>
@@ -8464,7 +8470,7 @@
         <v>561.72</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
         <v>42098</v>
       </c>
@@ -8475,7 +8481,7 @@
         <v>596.11</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A248" s="1">
         <v>42105</v>
       </c>
@@ -8486,7 +8492,7 @@
         <v>614.75</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A249" s="1">
         <v>42112</v>
       </c>
@@ -8497,7 +8503,7 @@
         <v>612.67999999999995</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A250" s="1">
         <v>42119</v>
       </c>
@@ -8508,7 +8514,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A251" s="1">
         <v>42126</v>
       </c>
@@ -8519,7 +8525,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
         <v>42133</v>
       </c>
@@ -8530,7 +8536,7 @@
         <v>626.76</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>42140</v>
       </c>
@@ -8541,7 +8547,7 @@
         <v>640.02</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>42147</v>
       </c>
@@ -8552,7 +8558,7 @@
         <v>642.91999999999996</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A255" s="1">
         <v>42154</v>
       </c>
@@ -8563,7 +8569,7 @@
         <v>644.57000000000005</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A256" s="1">
         <v>42161</v>
       </c>
@@ -8574,7 +8580,7 @@
         <v>643.74</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A257" s="1">
         <v>42168</v>
       </c>
@@ -8585,7 +8591,7 @@
         <v>645.82000000000005</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A258" s="1">
         <v>42175</v>
       </c>
@@ -8596,7 +8602,7 @@
         <v>639.6</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A259" s="1">
         <v>42182</v>
       </c>
@@ -8607,7 +8613,7 @@
         <v>633.39</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A260" s="1">
         <v>42189</v>
       </c>
@@ -8618,7 +8624,7 @@
         <v>630.07000000000005</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A261" s="1">
         <v>42196</v>
       </c>
@@ -8629,7 +8635,7 @@
         <v>620.13</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A262" s="1">
         <v>42203</v>
       </c>
@@ -8640,7 +8646,7 @@
         <v>617.65</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A263" s="1">
         <v>42210</v>
       </c>
@@ -8651,7 +8657,7 @@
         <v>600.25</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A264" s="1">
         <v>42217</v>
       </c>
@@ -8662,7 +8668,7 @@
         <v>577.04999999999995</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A265" s="1">
         <v>42224</v>
       </c>
@@ -8673,7 +8679,7 @@
         <v>560.07000000000005</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A266" s="1">
         <v>42231</v>
       </c>
@@ -8684,7 +8690,7 @@
         <v>558.82000000000005</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A267" s="1">
         <v>42238</v>
       </c>
@@ -8695,7 +8701,7 @@
         <v>550.12</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A268" s="1">
         <v>42245</v>
       </c>
@@ -8706,7 +8712,7 @@
         <v>545.98</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A269" s="1">
         <v>42252</v>
       </c>
@@ -8717,7 +8723,7 @@
         <v>541.01</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A270" s="1">
         <v>42259</v>
       </c>
@@ -8728,7 +8734,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A271" s="1">
         <v>42266</v>
       </c>
@@ -8739,7 +8745,7 @@
         <v>512.84</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A272" s="1">
         <v>42273</v>
       </c>
@@ -8750,7 +8756,7 @@
         <v>491.3</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A273" s="1">
         <v>42280</v>
       </c>
@@ -8761,7 +8767,7 @@
         <v>477.22</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A274" s="1">
         <v>42287</v>
       </c>
@@ -8772,7 +8778,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A275" s="1">
         <v>42294</v>
       </c>
@@ -8783,7 +8789,7 @@
         <v>438.69</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A276" s="1">
         <v>42301</v>
       </c>
@@ -8794,7 +8800,7 @@
         <v>415.08</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A277" s="1">
         <v>42308</v>
       </c>
@@ -8805,7 +8811,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A278" s="1">
         <v>42315</v>
       </c>
@@ -8816,7 +8822,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A279" s="1">
         <v>42322</v>
       </c>
@@ -8827,7 +8833,7 @@
         <v>388.98</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A280" s="1">
         <v>42329</v>
       </c>
@@ -8838,7 +8844,7 @@
         <v>385.67</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A281" s="1">
         <v>42336</v>
       </c>
@@ -8849,7 +8855,7 @@
         <v>380.28</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A282" s="1">
         <v>42343</v>
       </c>
@@ -8860,7 +8866,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A283" s="1">
         <v>42350</v>
       </c>
@@ -8871,7 +8877,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A284" s="1">
         <v>42357</v>
       </c>
@@ -8882,7 +8888,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A285" s="1">
         <v>42364</v>
       </c>
@@ -8893,7 +8899,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A286" s="1">
         <v>42371</v>
       </c>
@@ -8904,7 +8910,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A287" s="1">
         <v>42378</v>
       </c>
@@ -8915,7 +8921,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A288" s="1">
         <v>42385</v>
       </c>
@@ -8926,7 +8932,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A289" s="1">
         <v>42392</v>
       </c>
@@ -8937,7 +8943,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A290" s="1">
         <v>42399</v>
       </c>
@@ -8948,7 +8954,7 @@
         <v>363.71</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A291" s="1">
         <v>42406</v>
       </c>
@@ -8959,7 +8965,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A292" s="1">
         <v>42413</v>
       </c>
@@ -8970,7 +8976,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A293" s="1">
         <v>42420</v>
       </c>
@@ -8981,7 +8987,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A294" s="1">
         <v>42427</v>
       </c>
@@ -8992,7 +8998,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A295" s="1">
         <v>42434</v>
       </c>
@@ -9003,7 +9009,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A296" s="1">
         <v>42441</v>
       </c>
@@ -9014,7 +9020,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A297" s="1">
         <v>42448</v>
       </c>
@@ -9025,7 +9031,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A298" s="1">
         <v>42455</v>
       </c>
@@ -9036,7 +9042,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A299" s="1">
         <v>42462</v>
       </c>
@@ -9047,7 +9053,7 @@
         <v>362.47</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A300" s="1">
         <v>42469</v>
       </c>
@@ -9058,7 +9064,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A301" s="1">
         <v>42476</v>
       </c>
@@ -9069,7 +9075,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A302" s="1">
         <v>42483</v>
       </c>
@@ -9080,7 +9086,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A303" s="1">
         <v>42490</v>
       </c>
@@ -9091,7 +9097,7 @@
         <v>358.74</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A304" s="1">
         <v>42497</v>
       </c>
@@ -9102,7 +9108,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A305" s="1">
         <v>42504</v>
       </c>
@@ -9113,7 +9119,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A306" s="1">
         <v>42511</v>
       </c>
@@ -9124,7 +9130,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A307" s="1">
         <v>42518</v>
       </c>
@@ -9135,7 +9141,7 @@
         <v>356.67</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A308" s="1">
         <v>42525</v>
       </c>
@@ -9146,7 +9152,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A309" s="1">
         <v>42532</v>
       </c>
@@ -9157,7 +9163,7 @@
         <v>354.6</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A310" s="1">
         <v>42539</v>
       </c>
@@ -9168,7 +9174,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A311" s="1">
         <v>42546</v>
       </c>
@@ -9179,7 +9185,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A312" s="1">
         <v>42553</v>
       </c>
@@ -9190,7 +9196,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A313" s="1">
         <v>42560</v>
       </c>
@@ -9201,7 +9207,7 @@
         <v>348.8</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A314" s="1">
         <v>42567</v>
       </c>
@@ -9212,7 +9218,7 @@
         <v>347.56</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A315" s="1">
         <v>42574</v>
       </c>
@@ -9223,7 +9229,7 @@
         <v>345.9</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A316" s="1">
         <v>42581</v>
       </c>
@@ -9234,7 +9240,7 @@
         <v>345.07</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A317" s="1">
         <v>42588</v>
       </c>
@@ -9245,7 +9251,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A318" s="1">
         <v>42595</v>
       </c>
@@ -9256,7 +9262,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A319" s="1">
         <v>42602</v>
       </c>
@@ -9267,7 +9273,7 @@
         <v>341.76</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A320" s="1">
         <v>42609</v>
       </c>
@@ -9278,7 +9284,7 @@
         <v>337.2</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A321" s="1">
         <v>42616</v>
       </c>
@@ -9289,7 +9295,7 @@
         <v>331.4</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A322" s="1">
         <v>42623</v>
       </c>
@@ -9300,7 +9306,7 @@
         <v>330.99</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A323" s="1">
         <v>42630</v>
       </c>
@@ -9311,7 +9317,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A324" s="1">
         <v>42637</v>
       </c>
@@ -9322,7 +9328,7 @@
         <v>328.09</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A325" s="1">
         <v>42644</v>
       </c>
@@ -9333,7 +9339,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A326" s="1">
         <v>42651</v>
       </c>
@@ -9344,7 +9350,7 @@
         <v>326.01</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A327" s="1">
         <v>42658</v>
       </c>
@@ -9355,7 +9361,7 @@
         <v>324.77</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A328" s="1">
         <v>42665</v>
       </c>
@@ -9366,7 +9372,7 @@
         <v>322.7</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A329" s="1">
         <v>42672</v>
       </c>
@@ -9377,7 +9383,7 @@
         <v>319.39</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A330" s="1">
         <v>42679</v>
       </c>
@@ -9388,7 +9394,7 @@
         <v>318.56</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A331" s="1">
         <v>42686</v>
       </c>
@@ -9399,7 +9405,7 @@
         <v>317.32</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A332" s="1">
         <v>42693</v>
       </c>
@@ -9410,7 +9416,7 @@
         <v>316.49</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A333" s="1">
         <v>42700</v>
       </c>
@@ -9421,7 +9427,7 @@
         <v>316.07</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A334" s="1">
         <v>42707</v>
       </c>
@@ -9432,7 +9438,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A335" s="1">
         <v>42714</v>
       </c>
@@ -9443,7 +9449,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A336" s="1">
         <v>42721</v>
       </c>
@@ -9454,7 +9460,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A337" s="1">
         <v>42728</v>
       </c>
@@ -9465,7 +9471,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A338" s="1">
         <v>42735</v>
       </c>
@@ -9476,7 +9482,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A339" s="1">
         <v>42742</v>
       </c>
@@ -9487,7 +9493,7 @@
         <v>316.39</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A340" s="1">
         <v>42749</v>
       </c>
@@ -9498,7 +9504,7 @@
         <v>319.07</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A341" s="1">
         <v>42756</v>
       </c>
@@ -9509,7 +9515,7 @@
         <v>320.56</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A342" s="1">
         <v>42763</v>
       </c>
@@ -9520,7 +9526,7 @@
         <v>322.35000000000002</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A343" s="1">
         <v>42770</v>
       </c>
@@ -9531,7 +9537,7 @@
         <v>323.83999999999997</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A344" s="1">
         <v>42777</v>
       </c>
@@ -9542,7 +9548,7 @@
         <v>325.33</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A345" s="1">
         <v>42784</v>
       </c>
@@ -9553,7 +9559,7 @@
         <v>330.4</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A346" s="1">
         <v>42791</v>
       </c>
@@ -9564,7 +9570,7 @@
         <v>343.52</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A347" s="1">
         <v>42798</v>
       </c>
@@ -9575,7 +9581,7 @@
         <v>351.87</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A348" s="1">
         <v>42805</v>
       </c>
@@ -9586,7 +9592,7 @@
         <v>389.44</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A349" s="1">
         <v>42812</v>
       </c>
@@ -9597,7 +9603,7 @@
         <v>404.35</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A350" s="1">
         <v>42819</v>
       </c>
@@ -9608,7 +9614,7 @@
         <v>438.94</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A351" s="1">
         <v>42826</v>
       </c>
@@ -9619,7 +9625,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A352" s="1">
         <v>42833</v>
       </c>
@@ -9630,7 +9636,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A353" s="1">
         <v>42840</v>
       </c>
@@ -9641,7 +9647,7 @@
         <v>516.77</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A354" s="1">
         <v>42847</v>
       </c>
@@ -9652,7 +9658,7 @@
         <v>522.14</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A355" s="1">
         <v>42854</v>
       </c>
@@ -9663,7 +9669,7 @@
         <v>523.33000000000004</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A356" s="1">
         <v>42861</v>
       </c>
@@ -9674,7 +9680,7 @@
         <v>533.47</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A357" s="1">
         <v>42868</v>
       </c>
@@ -9685,7 +9691,7 @@
         <v>533.16999999999996</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A358" s="1">
         <v>42875</v>
       </c>
@@ -9696,7 +9702,7 @@
         <v>500.37</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A359" s="1">
         <v>42882</v>
       </c>
@@ -9707,7 +9713,7 @@
         <v>483.97</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A360" s="1">
         <v>42889</v>
       </c>
@@ -9718,7 +9724,7 @@
         <v>458.92</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A361" s="1">
         <v>42896</v>
       </c>
@@ -9729,7 +9735,7 @@
         <v>443.72</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A362" s="1">
         <v>42903</v>
       </c>
@@ -9740,7 +9746,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A363" s="1">
         <v>42910</v>
       </c>
@@ -9751,7 +9757,7 @@
         <v>438.35</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A364" s="1">
         <v>42917</v>
       </c>
@@ -9762,7 +9768,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A365" s="1">
         <v>42924</v>
       </c>
@@ -9773,7 +9779,7 @@
         <v>435.96</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A366" s="1">
         <v>42931</v>
       </c>
@@ -9784,7 +9790,7 @@
         <v>445.8</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A367" s="1">
         <v>42938</v>
       </c>
@@ -9795,7 +9801,7 @@
         <v>470.25</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A368" s="1">
         <v>42945</v>
       </c>
@@ -9806,7 +9812,7 @@
         <v>472.04</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A369" s="1">
         <v>42952</v>
       </c>
@@ -9817,7 +9823,7 @@
         <v>481.88</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A370" s="1">
         <v>42959</v>
       </c>
@@ -9828,7 +9834,7 @@
         <v>486.66</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A371" s="1">
         <v>42966</v>
       </c>
@@ -9839,7 +9845,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A372" s="1">
         <v>42973</v>
       </c>
@@ -9850,7 +9856,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A373" s="1">
         <v>42980</v>
       </c>
@@ -9861,7 +9867,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A374" s="1">
         <v>42987</v>
       </c>
@@ -9872,7 +9878,7 @@
         <v>515.88</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A375" s="1">
         <v>42994</v>
       </c>
@@ -9883,7 +9889,7 @@
         <v>517.07000000000005</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A376" s="1">
         <v>43001</v>
       </c>
@@ -9894,7 +9900,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A377" s="1">
         <v>43008</v>
       </c>
@@ -9905,7 +9911,7 @@
         <v>506.34</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A378" s="1">
         <v>43015</v>
       </c>
@@ -9916,7 +9922,7 @@
         <v>507.53</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A379" s="1">
         <v>43022</v>
       </c>
@@ -9927,7 +9933,7 @@
         <v>505.14</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A380" s="1">
         <v>43029</v>
       </c>
@@ -9938,7 +9944,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A381" s="1">
         <v>43036</v>
       </c>
@@ -9949,7 +9955,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A382" s="1">
         <v>43043</v>
       </c>
@@ -9960,7 +9966,7 @@
         <v>473.24</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A383" s="1">
         <v>43050</v>
       </c>
@@ -9971,7 +9977,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A384" s="1">
         <v>43057</v>
       </c>
@@ -9982,7 +9988,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A385" s="1">
         <v>43064</v>
       </c>
@@ -9993,7 +9999,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A386" s="1">
         <v>43071</v>
       </c>
@@ -10004,7 +10010,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A387" s="1">
         <v>43078</v>
       </c>
@@ -10015,7 +10021,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A388" s="1">
         <v>43085</v>
       </c>
@@ -10026,7 +10032,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A389" s="1">
         <v>43092</v>
       </c>
@@ -10037,7 +10043,7 @@
         <v>482.78</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A390" s="1">
         <v>43099</v>
       </c>
@@ -10048,7 +10054,7 @@
         <v>483.08</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A391" s="1">
         <v>43106</v>
       </c>
@@ -10059,7 +10065,7 @@
         <v>485.16</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A392" s="1">
         <v>43113</v>
       </c>
@@ -10070,7 +10076,7 @@
         <v>489.34</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A393" s="1">
         <v>43120</v>
       </c>
@@ -10081,7 +10087,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A394" s="1">
         <v>43127</v>
       </c>
@@ -10092,7 +10098,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A395" s="1">
         <v>43134</v>
       </c>
@@ -10103,7 +10109,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A396" s="1">
         <v>43141</v>
       </c>
@@ -10114,7 +10120,7 @@
         <v>520.35</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A397" s="1">
         <v>43148</v>
       </c>
@@ -10125,7 +10131,7 @@
         <v>526.02</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A398" s="1">
         <v>43155</v>
       </c>
@@ -10136,7 +10142,7 @@
         <v>542.41999999999996</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A399" s="1">
         <v>43162</v>
       </c>
@@ -10147,7 +10153,7 @@
         <v>548.98</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A400" s="1">
         <v>43169</v>
       </c>
@@ -10158,7 +10164,7 @@
         <v>579.69000000000005</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A401" s="1">
         <v>43176</v>
       </c>
@@ -10169,7 +10175,7 @@
         <v>597.88</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A402" s="1">
         <v>43183</v>
       </c>
@@ -10180,7 +10186,7 @@
         <v>635.16</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A403" s="1">
         <v>43190</v>
       </c>
@@ -10191,7 +10197,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A404" s="1">
         <v>43197</v>
       </c>
@@ -10202,7 +10208,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A405" s="1">
         <v>43204</v>
       </c>
@@ -10213,7 +10219,7 @@
         <v>642.61</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A406" s="1">
         <v>43211</v>
       </c>
@@ -10224,7 +10230,7 @@
         <v>646.19000000000005</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A407" s="1">
         <v>43218</v>
       </c>
@@ -10235,7 +10241,7 @@
         <v>652.45000000000005</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A408" s="1">
         <v>43225</v>
       </c>
@@ -10246,7 +10252,7 @@
         <v>653.64</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A409" s="1">
         <v>43232</v>
       </c>
@@ -10257,7 +10263,7 @@
         <v>656.63</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A410" s="1">
         <v>43239</v>
       </c>
@@ -10268,7 +10274,7 @@
         <v>661.1</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A411" s="1">
         <v>43245</v>
       </c>
@@ -10279,7 +10285,7 @@
         <v>670.64</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A412" s="1">
         <v>43252</v>
       </c>
@@ -10290,7 +10296,7 @@
         <v>673.62</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A413" s="1">
         <v>43259</v>
       </c>
@@ -10301,7 +10307,7 @@
         <v>676.61</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A414" s="1">
         <v>43266</v>
       </c>
@@ -10312,7 +10318,7 @@
         <v>678.1</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A415" s="1">
         <v>43273</v>
       </c>
@@ -10323,7 +10329,7 @@
         <v>676.9</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A416" s="1">
         <v>43280</v>
       </c>
@@ -10334,7 +10340,7 @@
         <v>672.73</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A417" s="1">
         <v>43287</v>
       </c>
@@ -10345,7 +10351,7 @@
         <v>668.26</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A418" s="1">
         <v>43294</v>
       </c>
@@ -10356,7 +10362,7 @@
         <v>652.15</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A419" s="1">
         <v>43301</v>
       </c>
@@ -10367,7 +10373,7 @@
         <v>628.6</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A420" s="1">
         <v>43308</v>
       </c>
@@ -10378,7 +10384,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A421" s="1">
         <v>43315</v>
       </c>
@@ -10389,7 +10395,7 @@
         <v>594.6</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A422" s="1">
         <v>43322</v>
       </c>
@@ -10400,7 +10406,7 @@
         <v>584.16999999999996</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A423" s="1">
         <v>43329</v>
       </c>
@@ -10411,7 +10417,7 @@
         <v>582.97</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A424" s="1">
         <v>43336</v>
       </c>
@@ -10422,7 +10428,7 @@
         <v>577.01</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A425" s="1">
         <v>43343</v>
       </c>
@@ -10433,7 +10439,7 @@
         <v>568.05999999999995</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A426" s="1">
         <v>43350</v>
       </c>
@@ -10444,7 +10450,7 @@
         <v>550.77</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A427" s="1">
         <v>43357</v>
       </c>
@@ -10455,7 +10461,7 @@
         <v>548.08000000000004</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A428" s="1">
         <v>43364</v>
       </c>
@@ -10466,7 +10472,7 @@
         <v>538.54</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A429" s="1">
         <v>43371</v>
       </c>
@@ -10477,7 +10483,7 @@
         <v>534.37</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A430" s="1">
         <v>43378</v>
       </c>
@@ -10488,7 +10494,7 @@
         <v>532.28</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A431" s="1">
         <v>43385</v>
       </c>
@@ -10499,7 +10505,7 @@
         <v>524.23</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A432" s="1">
         <v>43392</v>
       </c>
@@ -10510,7 +10516,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A433" s="1">
         <v>43399</v>
       </c>
@@ -10521,7 +10527,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A434" s="1">
         <v>43406</v>
       </c>
@@ -10532,7 +10538,7 @@
         <v>503.06</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A435" s="1">
         <v>43413</v>
       </c>
@@ -10543,7 +10549,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A436" s="1">
         <v>43420</v>
       </c>
@@ -10554,7 +10560,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A437" s="1">
         <v>43427</v>
       </c>
@@ -10565,7 +10571,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A438" s="1">
         <v>43434</v>
       </c>
@@ -10576,7 +10582,7 @@
         <v>502.16</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A439" s="1">
         <v>43441</v>
       </c>
@@ -10587,7 +10593,7 @@
         <v>498.58</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A440" s="1">
         <v>43448</v>
       </c>
@@ -10598,7 +10604,7 @@
         <v>495.6</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A441" s="1">
         <v>43455</v>
       </c>
@@ -10609,7 +10615,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A442" s="1">
         <v>43462</v>
       </c>
@@ -10620,7 +10626,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A443" s="1">
         <v>43469</v>
       </c>
@@ -10631,7 +10637,7 @@
         <v>485.46</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A444" s="1">
         <v>43476</v>
       </c>
@@ -10642,7 +10648,7 @@
         <v>478.01</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A445" s="1">
         <v>43483</v>
       </c>
@@ -10653,7 +10659,7 @@
         <v>474.43</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A446" s="1">
         <v>43490</v>
       </c>
@@ -10664,7 +10670,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A447" s="1">
         <v>43497</v>
       </c>
@@ -10675,7 +10681,7 @@
         <v>492.02</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A448" s="1">
         <v>43504</v>
       </c>
@@ -10686,7 +10692,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A449" s="1">
         <v>43511</v>
       </c>
@@ -10697,7 +10703,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A450" s="1">
         <v>43518</v>
       </c>
@@ -10708,7 +10714,7 @@
         <v>502.46</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A451" s="1">
         <v>43525</v>
       </c>
@@ -10719,7 +10725,7 @@
         <v>527.80999999999995</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A452" s="1">
         <v>43532</v>
       </c>
@@ -10730,7 +10736,7 @@
         <v>543.01</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A453" s="1">
         <v>43539</v>
       </c>
@@ -10741,7 +10747,7 @@
         <v>552.55999999999995</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A454" s="1">
         <v>43546</v>
       </c>
@@ -10752,7 +10758,7 @@
         <v>560.61</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A455" s="1">
         <v>43553</v>
       </c>
@@ -10763,7 +10769,7 @@
         <v>565.67999999999995</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A456" s="1">
         <v>43560</v>
       </c>
@@ -10774,7 +10780,7 @@
         <v>576.11</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A457" s="1">
         <v>43567</v>
       </c>
@@ -10785,7 +10791,7 @@
         <v>581.48</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A458" s="1">
         <v>43574</v>
       </c>
@@ -10796,7 +10802,7 @@
         <v>585.05999999999995</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A459" s="1">
         <v>43581</v>
       </c>
@@ -10807,7 +10813,7 @@
         <v>585.66</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A460" s="1">
         <v>43588</v>
       </c>
@@ -10818,7 +10824,7 @@
         <v>586.25</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A461" s="1">
         <v>43595</v>
       </c>
@@ -10829,7 +10835,7 @@
         <v>586.85</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A462" s="1">
         <v>43602</v>
       </c>
@@ -10840,7 +10846,7 @@
         <v>596.09</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A463" s="1">
         <v>43609</v>
       </c>
@@ -10851,7 +10857,7 @@
         <v>599.08000000000004</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A464" s="1">
         <v>43616</v>
       </c>
@@ -10862,7 +10868,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A465" s="1">
         <v>43623</v>
       </c>
@@ -10873,7 +10879,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A466" s="1">
         <v>43630</v>
       </c>
@@ -10884,7 +10890,7 @@
         <v>603.85</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A467" s="1">
         <v>43637</v>
       </c>
@@ -10895,7 +10901,7 @@
         <v>603.54999999999995</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A468" s="1">
         <v>43644</v>
       </c>
@@ -10906,7 +10912,7 @@
         <v>611.6</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A469" s="1">
         <v>43651</v>
       </c>
@@ -10917,7 +10923,7 @@
         <v>618.76</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A470" s="1">
         <v>43658</v>
       </c>
@@ -10928,7 +10934,7 @@
         <v>629.19000000000005</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A471" s="1">
         <v>43665</v>
       </c>
@@ -10939,7 +10945,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A472" s="1">
         <v>43672</v>
       </c>
@@ -10950,7 +10956,7 @@
         <v>666.77</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A473" s="1">
         <v>43679</v>
       </c>
@@ -10961,7 +10967,7 @@
         <v>670.94</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A474" s="1">
         <v>43686</v>
       </c>
@@ -10972,7 +10978,7 @@
         <v>681.97</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A475" s="1">
         <v>43693</v>
       </c>
@@ -10983,7 +10989,7 @@
         <v>690.02</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A476" s="1">
         <v>43700</v>
       </c>
@@ -10994,7 +11000,7 @@
         <v>696.88</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A477" s="1">
         <v>43707</v>
       </c>
@@ -11005,7 +11011,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A478" s="1">
         <v>43714</v>
       </c>
@@ -11016,7 +11022,7 @@
         <v>718.65</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A479" s="1">
         <v>43721</v>
       </c>
@@ -11027,7 +11033,7 @@
         <v>723.42</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A480" s="1">
         <v>43728</v>
       </c>
@@ -11038,7 +11044,7 @@
         <v>724.62</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A481" s="1">
         <v>43735</v>
       </c>
@@ -11049,7 +11055,7 @@
         <v>726.4</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A482" s="1">
         <v>43742</v>
       </c>
@@ -11060,7 +11066,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A483" s="1">
         <v>43749</v>
       </c>
@@ -11071,7 +11077,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A484" s="1">
         <v>43756</v>
       </c>
@@ -11082,7 +11088,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A485" s="1">
         <v>43763</v>
       </c>
@@ -11093,7 +11099,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A486" s="1">
         <v>43770</v>
       </c>
@@ -11104,7 +11110,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A487" s="1">
         <v>43777</v>
       </c>
@@ -11115,7 +11121,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A488" s="1">
         <v>43784</v>
       </c>
@@ -11126,7 +11132,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A489" s="1">
         <v>43791</v>
       </c>
@@ -11137,7 +11143,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A490" s="1">
         <v>43798</v>
       </c>
@@ -11148,7 +11154,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A491" s="1">
         <v>43805</v>
       </c>
@@ -11159,7 +11165,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A492" s="1">
         <v>43812</v>
       </c>
@@ -11170,7 +11176,7 @@
         <v>715.67</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A493" s="1">
         <v>43819</v>
       </c>
@@ -11181,7 +11187,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A494" s="1">
         <v>43826</v>
       </c>
@@ -11192,7 +11198,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A495" s="1">
         <v>43833</v>
       </c>
@@ -11203,7 +11209,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A496" s="1">
         <v>43840</v>
       </c>
@@ -11214,7 +11220,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A497" s="1">
         <v>43847</v>
       </c>
@@ -11225,7 +11231,7 @@
         <v>711.49</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A498" s="1">
         <v>43854</v>
       </c>
@@ -11236,7 +11242,7 @@
         <v>708.51</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A499" s="1">
         <v>43861</v>
       </c>
@@ -11247,7 +11253,7 @@
         <v>705.53</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A500" s="1">
         <v>43868</v>
       </c>
@@ -11258,7 +11264,7 @@
         <v>701.95</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A501" s="1">
         <v>43875</v>
       </c>
@@ -11269,7 +11275,7 @@
         <v>691.52</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A502" s="1">
         <v>43882</v>
       </c>
@@ -11280,7 +11286,7 @@
         <v>680.48</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A503" s="1">
         <v>43889</v>
       </c>
@@ -11291,7 +11297,7 @@
         <v>668.85</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A504" s="1">
         <v>43896</v>
       </c>
@@ -11302,7 +11308,7 @@
         <v>651.26</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A505" s="1">
         <v>43903</v>
       </c>
@@ -11313,7 +11319,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A506" s="1">
         <v>43910</v>
       </c>
@@ -11324,7 +11330,7 @@
         <v>631.58000000000004</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A507" s="1">
         <v>43917</v>
       </c>
@@ -11335,7 +11341,7 @@
         <v>616.07000000000005</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A508" s="1">
         <v>43924</v>
       </c>
@@ -11346,7 +11352,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A509" s="1">
         <v>43931</v>
       </c>
@@ -11357,7 +11363,7 @@
         <v>601.46</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A510" s="1">
         <v>43938</v>
       </c>
@@ -11368,7 +11374,7 @@
         <v>572.83000000000004</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A511" s="1">
         <v>43945</v>
       </c>
@@ -11379,7 +11385,7 @@
         <v>549.87</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A512" s="1">
         <v>43952</v>
       </c>
@@ -11390,7 +11396,7 @@
         <v>528.70000000000005</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A513" s="1">
         <v>43959</v>
       </c>
@@ -11401,7 +11407,7 @@
         <v>507.83</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A514" s="1">
         <v>43966</v>
       </c>
@@ -11412,7 +11418,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A515" s="1">
         <v>43973</v>
       </c>
@@ -11423,7 +11429,7 @@
         <v>479.2</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A516" s="1">
         <v>43980</v>
       </c>
@@ -11434,7 +11440,7 @@
         <v>452.36</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A517" s="1">
         <v>43987</v>
       </c>
@@ -11445,7 +11451,7 @@
         <v>434.17</v>
       </c>
     </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A518" s="1">
         <v>43994</v>
       </c>
@@ -11456,7 +11462,7 @@
         <v>412.11</v>
       </c>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A519" s="1">
         <v>44001</v>
       </c>
@@ -11467,7 +11473,7 @@
         <v>418.96</v>
       </c>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A520" s="1">
         <v>44008</v>
       </c>
@@ -11478,7 +11484,7 @@
         <v>431.79</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A521" s="1">
         <v>44015</v>
       </c>
@@ -11489,7 +11495,7 @@
         <v>439.84</v>
       </c>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A522" s="1">
         <v>44022</v>
       </c>
@@ -11500,7 +11506,7 @@
         <v>444.91</v>
       </c>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A523" s="1">
         <v>44029</v>
       </c>
@@ -11511,7 +11517,7 @@
         <v>463.1</v>
       </c>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A524" s="1">
         <v>44036</v>
       </c>
@@ -11522,7 +11528,7 @@
         <v>484.87</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A525" s="1">
         <v>44043</v>
       </c>
@@ -11533,7 +11539,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A526" s="1">
         <v>44050</v>
       </c>
@@ -11544,7 +11550,7 @@
         <v>556.13</v>
       </c>
     </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A527" s="1">
         <v>44057</v>
       </c>
@@ -11555,7 +11561,7 @@
         <v>596.69000000000005</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A528" s="1">
         <v>44064</v>
       </c>
@@ -11566,7 +11572,7 @@
         <v>627.11</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A529" s="1">
         <v>44071</v>
       </c>
@@ -11577,7 +11583,7 @@
         <v>665.87</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A530" s="1">
         <v>44078</v>
       </c>
@@ -11588,7 +11594,7 @@
         <v>671.83</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A531" s="1">
         <v>44085</v>
       </c>
@@ -11599,7 +11605,7 @@
         <v>678.4</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A532" s="1">
         <v>44092</v>
       </c>
@@ -11610,7 +11616,7 @@
         <v>691.81</v>
       </c>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A533" s="1">
         <v>44099</v>
       </c>
@@ -11621,7 +11627,7 @@
         <v>703.74</v>
       </c>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A534" s="1">
         <v>44106</v>
       </c>
@@ -11632,7 +11638,7 @@
         <v>714.77</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A535" s="1">
         <v>44113</v>
       </c>
@@ -11643,7 +11649,7 @@
         <v>754.14</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A536" s="1">
         <v>44120</v>
       </c>
@@ -11654,7 +11660,7 @@
         <v>783.96</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A537" s="1">
         <v>44127</v>
       </c>
@@ -11665,7 +11671,7 @@
         <v>820.04</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A538" s="1">
         <v>44134</v>
       </c>
@@ -11676,7 +11682,7 @@
         <v>881.17</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A539" s="1">
         <v>44141</v>
       </c>
@@ -11687,7 +11693,7 @@
         <v>910.09</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A540" s="1">
         <v>44148</v>
       </c>
@@ -11698,7 +11704,7 @@
         <v>947.07</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A541" s="1">
         <v>44155</v>
       </c>
@@ -11709,7 +11715,7 @@
         <v>978.68</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A542" s="1">
         <v>44162</v>
       </c>
@@ -11720,7 +11726,7 @@
         <v>1009.39</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A543" s="1">
         <v>44169</v>
       </c>
@@ -11731,7 +11737,7 @@
         <v>1016.25</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A544" s="1">
         <v>44176</v>
       </c>
@@ -11742,7 +11748,7 @@
         <v>1020.13</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A545" s="1">
         <v>44183</v>
       </c>
@@ -11753,7 +11759,7 @@
         <v>1032.06</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A546" s="1">
         <v>44190</v>
       </c>
@@ -11764,7 +11770,7 @@
         <v>1036.23</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A547" s="1">
         <v>44197</v>
       </c>
@@ -11775,7 +11781,7 @@
         <v>1038.02</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A548" s="1">
         <v>44204</v>
       </c>
@@ -11786,7 +11792,7 @@
         <v>1069.6300000000001</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A549" s="1">
         <v>44211</v>
       </c>
@@ -11797,7 +11803,7 @@
         <v>1094.3800000000001</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A550" s="1">
         <v>44218</v>
       </c>
@@ -11808,7 +11814,7 @@
         <v>1112.8699999999999</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A551" s="1">
         <v>44225</v>
       </c>
@@ -11819,7 +11825,7 @@
         <v>1154.32</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A552" s="1">
         <v>44232</v>
       </c>
@@ -11830,7 +11836,7 @@
         <v>1202.03</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A553" s="1">
         <v>44239</v>
       </c>
@@ -11841,7 +11847,7 @@
         <v>1228.27</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A554" s="1">
         <v>44246</v>
       </c>
@@ -11852,7 +11858,7 @@
         <v>1262.26</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A555" s="1">
         <v>44253</v>
       </c>
@@ -11863,7 +11869,7 @@
         <v>1278.3599999999999</v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A556" s="1">
         <v>44260</v>
       </c>
@@ -11874,7 +11880,7 @@
         <v>1323.39</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A557" s="1">
         <v>44267</v>
       </c>
@@ -11885,7 +11891,7 @@
         <v>1387.21</v>
       </c>
     </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A558" s="1">
         <v>44274</v>
       </c>
@@ -11896,7 +11902,7 @@
         <v>1442.97</v>
       </c>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A559" s="1">
         <v>44281</v>
       </c>
@@ -11907,7 +11913,7 @@
         <v>1454.3</v>
       </c>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A560" s="1">
         <v>44288</v>
       </c>
@@ -11918,7 +11924,7 @@
         <v>1492.47</v>
       </c>
     </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A561" s="1">
         <v>44295</v>
       </c>
@@ -11929,7 +11935,7 @@
         <v>1559.56</v>
       </c>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A562" s="1">
         <v>44302</v>
       </c>
@@ -11940,7 +11946,7 @@
         <v>1650.51</v>
       </c>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A563" s="1">
         <v>44309</v>
       </c>
@@ -11951,7 +11957,7 @@
         <v>1680.33</v>
       </c>
     </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A564" s="1">
         <v>44316</v>
       </c>
@@ -11962,7 +11968,7 @@
         <v>1707.47</v>
       </c>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A565" s="1">
         <v>44323</v>
       </c>
@@ -11973,7 +11979,7 @@
         <v>1777.25</v>
       </c>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A566" s="1">
         <v>44330</v>
       </c>
@@ -11984,7 +11990,7 @@
         <v>1837.48</v>
       </c>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A567" s="1">
         <v>44337</v>
       </c>
@@ -11995,7 +12001,7 @@
         <v>1890.86</v>
       </c>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A568" s="1">
         <v>44344</v>
       </c>
@@ -12006,7 +12012,7 @@
         <v>1940.66</v>
       </c>
     </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A569" s="1">
         <v>44351</v>
       </c>
@@ -12017,7 +12023,7 @@
         <v>1986.58</v>
       </c>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A570" s="1">
         <v>44358</v>
       </c>
@@ -12028,7 +12034,7 @@
         <v>2033.69</v>
       </c>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A571" s="1">
         <v>44365</v>
       </c>
@@ -12039,7 +12045,7 @@
         <v>2117.19</v>
       </c>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A572" s="1">
         <v>44372</v>
       </c>
@@ -12050,7 +12056,7 @@
         <v>2212.31</v>
       </c>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A573" s="1">
         <v>44379</v>
       </c>
@@ -12061,7 +12067,7 @@
         <v>2406.44</v>
       </c>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A574" s="1">
         <v>44386</v>
       </c>
@@ -12072,7 +12078,7 @@
         <v>2695.69</v>
       </c>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A575" s="1">
         <v>44393</v>
       </c>
@@ -12083,7 +12089,7 @@
         <v>3023.7</v>
       </c>
     </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A576" s="1">
         <v>44400</v>
       </c>
@@ -12094,7 +12100,7 @@
         <v>3142.98</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A577" s="1">
         <v>44407</v>
       </c>
@@ -12105,7 +12111,7 @@
         <v>3301.03</v>
       </c>
     </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A578" s="1">
         <v>44414</v>
       </c>
@@ -12116,7 +12122,7 @@
         <v>3548.53</v>
       </c>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A579" s="1">
         <v>44421</v>
       </c>
@@ -12127,7 +12133,7 @@
         <v>3554.49</v>
       </c>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A580" s="1">
         <v>44428</v>
       </c>
@@ -12138,7 +12144,7 @@
         <v>3560.46</v>
       </c>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A581" s="1">
         <v>44435</v>
       </c>
@@ -12149,7 +12155,7 @@
         <v>3599.22</v>
       </c>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A582" s="1">
         <v>44442</v>
       </c>
@@ -12160,7 +12166,7 @@
         <v>3694.64</v>
       </c>
     </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A583" s="1">
         <v>44449</v>
       </c>
@@ -12171,7 +12177,7 @@
         <v>3822.87</v>
       </c>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A584" s="1">
         <v>44456</v>
       </c>
@@ -12182,7 +12188,7 @@
         <v>3928.73</v>
       </c>
     </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A585" s="1">
         <v>44463</v>
       </c>
@@ -12193,7 +12199,7 @@
         <v>3980.91</v>
       </c>
     </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A586" s="1">
         <v>44470</v>
       </c>
@@ -12204,7 +12210,7 @@
         <v>3989.86</v>
       </c>
     </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A587" s="1">
         <v>44477</v>
       </c>
@@ -12215,7 +12221,7 @@
         <v>3995.82</v>
       </c>
     </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A588" s="1">
         <v>44484</v>
       </c>
@@ -12226,7 +12232,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A589" s="1">
         <v>44491</v>
       </c>
@@ -12237,7 +12243,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A590" s="1">
         <v>44498</v>
       </c>
@@ -12248,7 +12254,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A591" s="1">
         <v>44505</v>
       </c>
@@ -12259,7 +12265,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A592" s="1">
         <v>44512</v>
       </c>
@@ -12270,7 +12276,7 @@
         <v>3852.69</v>
       </c>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" s="1">
         <v>44519</v>
       </c>
@@ -12278,7 +12284,7 @@
         <v>44519</v>
       </c>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" s="1">
         <v>44526</v>
       </c>
@@ -12286,7 +12292,7 @@
         <v>44526</v>
       </c>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" s="1">
         <v>44533</v>
       </c>
@@ -12294,7 +12300,7 @@
         <v>44533</v>
       </c>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" s="1">
         <v>44540</v>
       </c>
@@ -12302,7 +12308,7 @@
         <v>44540</v>
       </c>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" s="1">
         <v>44547</v>
       </c>
@@ -12310,7 +12316,7 @@
         <v>44547</v>
       </c>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" s="1">
         <v>44554</v>
       </c>
@@ -12318,7 +12324,7 @@
         <v>44554</v>
       </c>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" s="1">
         <v>44561</v>
       </c>
@@ -12326,7 +12332,7 @@
         <v>44561</v>
       </c>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" s="1">
         <v>44568</v>
       </c>
@@ -12334,7 +12340,7 @@
         <v>44568</v>
       </c>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" s="1">
         <v>44575</v>
       </c>
@@ -12342,7 +12348,7 @@
         <v>44575</v>
       </c>
     </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" s="1">
         <v>44582</v>
       </c>
@@ -12350,7 +12356,7 @@
         <v>44582</v>
       </c>
     </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" s="1">
         <v>44589</v>
       </c>
@@ -12358,7 +12364,7 @@
         <v>44589</v>
       </c>
     </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" s="1">
         <v>44596</v>
       </c>
@@ -12366,7 +12372,7 @@
         <v>44596</v>
       </c>
     </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" s="1">
         <v>44603</v>
       </c>
@@ -12374,7 +12380,7 @@
         <v>44603</v>
       </c>
     </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" s="1">
         <v>44610</v>
       </c>
@@ -12382,7 +12388,7 @@
         <v>44610</v>
       </c>
     </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" s="1">
         <v>44617</v>
       </c>
@@ -12390,7 +12396,7 @@
         <v>44617</v>
       </c>
     </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" s="1">
         <v>44624</v>
       </c>
@@ -12398,7 +12404,7 @@
         <v>44624</v>
       </c>
     </row>
-    <row r="609" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" s="1">
         <v>44631</v>
       </c>
@@ -12406,7 +12412,7 @@
         <v>44631</v>
       </c>
     </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" s="1">
         <v>44638</v>
       </c>
@@ -12414,7 +12420,7 @@
         <v>44638</v>
       </c>
     </row>
-    <row r="611" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" s="1">
         <v>44645</v>
       </c>
@@ -12422,7 +12428,7 @@
         <v>44645</v>
       </c>
     </row>
-    <row r="612" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" s="1">
         <v>44652</v>
       </c>
@@ -12430,7 +12436,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="613" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" s="1">
         <v>44659</v>
       </c>
@@ -12438,7 +12444,7 @@
         <v>44659</v>
       </c>
     </row>
-    <row r="614" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" s="1">
         <v>44666</v>
       </c>
@@ -12446,7 +12452,7 @@
         <v>44666</v>
       </c>
     </row>
-    <row r="615" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" s="1">
         <v>44673</v>
       </c>
@@ -12454,7 +12460,7 @@
         <v>44673</v>
       </c>
     </row>
-    <row r="616" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" s="1">
         <v>44680</v>
       </c>
@@ -12462,7 +12468,7 @@
         <v>44680</v>
       </c>
     </row>
-    <row r="617" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" s="1">
         <v>44687</v>
       </c>
@@ -12470,7 +12476,7 @@
         <v>44687</v>
       </c>
     </row>
-    <row r="618" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" s="1">
         <v>44694</v>
       </c>
@@ -12478,7 +12484,7 @@
         <v>44694</v>
       </c>
     </row>
-    <row r="619" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" s="1">
         <v>44701</v>
       </c>
@@ -12486,7 +12492,7 @@
         <v>44701</v>
       </c>
     </row>
-    <row r="620" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" s="1">
         <v>44708</v>
       </c>
@@ -12494,7 +12500,7 @@
         <v>44708</v>
       </c>
     </row>
-    <row r="621" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" s="1">
         <v>44715</v>
       </c>
@@ -12502,7 +12508,7 @@
         <v>44715</v>
       </c>
     </row>
-    <row r="622" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" s="1">
         <v>44722</v>
       </c>
@@ -12510,7 +12516,7 @@
         <v>44722</v>
       </c>
     </row>
-    <row r="623" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" s="1">
         <v>44729</v>
       </c>
@@ -12518,7 +12524,7 @@
         <v>44729</v>
       </c>
     </row>
-    <row r="624" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" s="1">
         <v>44736</v>
       </c>
@@ -12526,7 +12532,7 @@
         <v>44736</v>
       </c>
     </row>
-    <row r="625" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" s="1">
         <v>44743</v>
       </c>
@@ -12534,7 +12540,7 @@
         <v>44743</v>
       </c>
     </row>
-    <row r="626" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" s="1">
         <v>44750</v>
       </c>
@@ -12542,7 +12548,7 @@
         <v>44750</v>
       </c>
     </row>
-    <row r="627" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" s="1">
         <v>44757</v>
       </c>
@@ -12550,7 +12556,7 @@
         <v>44757</v>
       </c>
     </row>
-    <row r="628" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" s="1">
         <v>44764</v>
       </c>
@@ -12558,7 +12564,7 @@
         <v>44764</v>
       </c>
     </row>
-    <row r="629" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" s="1">
         <v>44771</v>
       </c>
@@ -12566,7 +12572,7 @@
         <v>44771</v>
       </c>
     </row>
-    <row r="630" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" s="1">
         <v>44778</v>
       </c>
@@ -12574,7 +12580,7 @@
         <v>44778</v>
       </c>
     </row>
-    <row r="631" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" s="1">
         <v>44785</v>
       </c>
@@ -12582,7 +12588,7 @@
         <v>44785</v>
       </c>
     </row>
-    <row r="632" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" s="1">
         <v>44792</v>
       </c>
@@ -12590,7 +12596,7 @@
         <v>44792</v>
       </c>
     </row>
-    <row r="633" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" s="1">
         <v>44799</v>
       </c>
@@ -12598,7 +12604,7 @@
         <v>44799</v>
       </c>
     </row>
-    <row r="634" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" s="1">
         <v>44806</v>
       </c>
@@ -12606,7 +12612,7 @@
         <v>44806</v>
       </c>
     </row>
-    <row r="635" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" s="1">
         <v>44813</v>
       </c>
@@ -12614,7 +12620,7 @@
         <v>44813</v>
       </c>
     </row>
-    <row r="636" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" s="1">
         <v>44820</v>
       </c>
@@ -12622,7 +12628,7 @@
         <v>44820</v>
       </c>
     </row>
-    <row r="637" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" s="1">
         <v>44827</v>
       </c>
@@ -12630,7 +12636,7 @@
         <v>44827</v>
       </c>
     </row>
-    <row r="638" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638" s="1">
         <v>44834</v>
       </c>
@@ -12638,7 +12644,7 @@
         <v>44834</v>
       </c>
     </row>
-    <row r="639" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" s="1">
         <v>44841</v>
       </c>
@@ -12646,7 +12652,7 @@
         <v>44841</v>
       </c>
     </row>
-    <row r="640" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" s="1">
         <v>44848</v>
       </c>
@@ -12654,7 +12660,7 @@
         <v>44848</v>
       </c>
     </row>
-    <row r="641" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" s="1">
         <v>44855</v>
       </c>
@@ -12662,7 +12668,7 @@
         <v>44855</v>
       </c>
     </row>
-    <row r="642" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" s="1">
         <v>44862</v>
       </c>
@@ -12670,7 +12676,7 @@
         <v>44862</v>
       </c>
     </row>
-    <row r="643" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643" s="1">
         <v>44869</v>
       </c>
@@ -12678,7 +12684,7 @@
         <v>44869</v>
       </c>
     </row>
-    <row r="644" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" s="1">
         <v>44876</v>
       </c>
@@ -12686,7 +12692,7 @@
         <v>44876</v>
       </c>
     </row>
-    <row r="645" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" s="1">
         <v>44883</v>
       </c>
@@ -12694,7 +12700,7 @@
         <v>44883</v>
       </c>
     </row>
-    <row r="646" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" s="1">
         <v>44890</v>
       </c>
@@ -12702,7 +12708,7 @@
         <v>44890</v>
       </c>
     </row>
-    <row r="647" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" s="1">
         <v>44897</v>
       </c>
@@ -12710,7 +12716,7 @@
         <v>44897</v>
       </c>
     </row>
-    <row r="648" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" s="1">
         <v>44904</v>
       </c>
@@ -12718,7 +12724,7 @@
         <v>44904</v>
       </c>
     </row>
-    <row r="649" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" s="1">
         <v>44911</v>
       </c>
@@ -12726,7 +12732,7 @@
         <v>44911</v>
       </c>
     </row>
-    <row r="650" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" s="1">
         <v>44918</v>
       </c>
@@ -12734,7 +12740,7 @@
         <v>44918</v>
       </c>
     </row>
-    <row r="651" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" s="1">
         <v>44925</v>
       </c>
@@ -12742,7 +12748,7 @@
         <v>44925</v>
       </c>
     </row>
-    <row r="652" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" s="1">
         <v>44932</v>
       </c>
@@ -12750,7 +12756,7 @@
         <v>44932</v>
       </c>
     </row>
-    <row r="653" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" s="1">
         <v>44939</v>
       </c>
@@ -12758,7 +12764,7 @@
         <v>44939</v>
       </c>
     </row>
-    <row r="654" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654" s="1">
         <v>44946</v>
       </c>
@@ -12766,7 +12772,7 @@
         <v>44946</v>
       </c>
     </row>
-    <row r="655" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655" s="1">
         <v>44953</v>
       </c>
@@ -12774,7 +12780,7 @@
         <v>44953</v>
       </c>
     </row>
-    <row r="656" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656" s="1">
         <v>44960</v>
       </c>
@@ -12782,7 +12788,7 @@
         <v>44960</v>
       </c>
     </row>
-    <row r="657" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A657" s="1">
         <v>44967</v>
       </c>
@@ -12790,7 +12796,7 @@
         <v>44967</v>
       </c>
     </row>
-    <row r="658" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658" s="1">
         <v>44974</v>
       </c>
@@ -12798,7 +12804,7 @@
         <v>44974</v>
       </c>
     </row>
-    <row r="659" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659" s="1">
         <v>44981</v>
       </c>
@@ -12806,7 +12812,7 @@
         <v>44981</v>
       </c>
     </row>
-    <row r="660" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" s="1">
         <v>44988</v>
       </c>
@@ -12814,7 +12820,7 @@
         <v>44988</v>
       </c>
     </row>
-    <row r="661" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A661" s="1">
         <v>44995</v>
       </c>
@@ -12822,7 +12828,7 @@
         <v>44995</v>
       </c>
     </row>
-    <row r="662" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A662" s="1">
         <v>45002</v>
       </c>
@@ -12830,7 +12836,7 @@
         <v>45002</v>
       </c>
     </row>
-    <row r="663" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663" s="1">
         <v>45009</v>
       </c>
@@ -12838,7 +12844,7 @@
         <v>45009</v>
       </c>
     </row>
-    <row r="664" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664" s="1">
         <v>45016</v>
       </c>
@@ -12846,7 +12852,7 @@
         <v>45016</v>
       </c>
     </row>
-    <row r="665" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A665" s="1">
         <v>45023</v>
       </c>
@@ -12854,7 +12860,7 @@
         <v>45023</v>
       </c>
     </row>
-    <row r="666" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A666" s="1">
         <v>45030</v>
       </c>
@@ -12862,7 +12868,7 @@
         <v>45030</v>
       </c>
     </row>
-    <row r="667" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A667" s="1">
         <v>45037</v>
       </c>
@@ -12870,7 +12876,7 @@
         <v>45037</v>
       </c>
     </row>
-    <row r="668" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A668" s="1">
         <v>45044</v>
       </c>
@@ -12878,7 +12884,7 @@
         <v>45044</v>
       </c>
     </row>
-    <row r="669" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A669" s="1">
         <v>45051</v>
       </c>
@@ -12886,7 +12892,7 @@
         <v>45051</v>
       </c>
     </row>
-    <row r="670" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A670" s="1">
         <v>45058</v>
       </c>
@@ -12894,7 +12900,7 @@
         <v>45058</v>
       </c>
     </row>
-    <row r="671" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671" s="1">
         <v>45065</v>
       </c>
@@ -12902,7 +12908,7 @@
         <v>45065</v>
       </c>
     </row>
-    <row r="672" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A672" s="1">
         <v>45072</v>
       </c>
@@ -12910,7 +12916,7 @@
         <v>45072</v>
       </c>
     </row>
-    <row r="673" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A673" s="1">
         <v>45079</v>
       </c>
@@ -12918,7 +12924,7 @@
         <v>45079</v>
       </c>
     </row>
-    <row r="674" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674" s="1">
         <v>45086</v>
       </c>
@@ -12926,7 +12932,7 @@
         <v>45086</v>
       </c>
     </row>
-    <row r="675" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A675" s="1">
         <v>45093</v>
       </c>
@@ -12934,7 +12940,7 @@
         <v>45093</v>
       </c>
     </row>
-    <row r="676" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A676" s="1">
         <v>45100</v>
       </c>
@@ -12942,7 +12948,7 @@
         <v>45100</v>
       </c>
     </row>
-    <row r="677" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A677" s="1">
         <v>45107</v>
       </c>
@@ -12950,7 +12956,7 @@
         <v>45107</v>
       </c>
     </row>
-    <row r="678" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A678" s="1">
         <v>45114</v>
       </c>
@@ -12958,7 +12964,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="679" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A679" s="1">
         <v>45121</v>
       </c>
@@ -12966,7 +12972,7 @@
         <v>45121</v>
       </c>
     </row>
-    <row r="680" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A680" s="1">
         <v>45128</v>
       </c>
@@ -12974,7 +12980,7 @@
         <v>45128</v>
       </c>
     </row>
-    <row r="681" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A681" s="1">
         <v>45135</v>
       </c>
@@ -12982,7 +12988,7 @@
         <v>45135</v>
       </c>
     </row>
-    <row r="682" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A682" s="1">
         <v>45142</v>
       </c>
@@ -12990,7 +12996,7 @@
         <v>45142</v>
       </c>
     </row>
-    <row r="683" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A683" s="1">
         <v>45149</v>
       </c>
@@ -12998,7 +13004,7 @@
         <v>45149</v>
       </c>
     </row>
-    <row r="684" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A684" s="1">
         <v>45156</v>
       </c>
@@ -13006,7 +13012,7 @@
         <v>45156</v>
       </c>
     </row>
-    <row r="685" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A685" s="1">
         <v>45163</v>
       </c>
@@ -13014,7 +13020,7 @@
         <v>45163</v>
       </c>
     </row>
-    <row r="686" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686" s="1">
         <v>45170</v>
       </c>
@@ -13022,7 +13028,7 @@
         <v>45170</v>
       </c>
     </row>
-    <row r="687" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A687" s="1">
         <v>45177</v>
       </c>
@@ -13030,7 +13036,7 @@
         <v>45177</v>
       </c>
     </row>
-    <row r="688" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A688" s="1">
         <v>45184</v>
       </c>
@@ -13038,7 +13044,7 @@
         <v>45184</v>
       </c>
     </row>
-    <row r="689" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A689" s="1">
         <v>45191</v>
       </c>
@@ -13046,7 +13052,7 @@
         <v>45191</v>
       </c>
     </row>
-    <row r="690" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A690" s="1">
         <v>45198</v>
       </c>
@@ -13054,7 +13060,7 @@
         <v>45198</v>
       </c>
     </row>
-    <row r="691" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A691" s="1">
         <v>45205</v>
       </c>
@@ -13062,7 +13068,7 @@
         <v>45205</v>
       </c>
     </row>
-    <row r="692" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A692" s="1">
         <v>45212</v>
       </c>
@@ -13070,7 +13076,7 @@
         <v>45212</v>
       </c>
     </row>
-    <row r="693" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A693" s="1">
         <v>45219</v>
       </c>
@@ -13078,7 +13084,7 @@
         <v>45219</v>
       </c>
     </row>
-    <row r="694" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A694" s="1">
         <v>45226</v>
       </c>
@@ -13086,7 +13092,7 @@
         <v>45226</v>
       </c>
     </row>
-    <row r="695" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A695" s="1">
         <v>45233</v>
       </c>
@@ -13094,7 +13100,7 @@
         <v>45233</v>
       </c>
     </row>
-    <row r="696" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A696" s="1">
         <v>45240</v>
       </c>
@@ -13102,7 +13108,7 @@
         <v>45240</v>
       </c>
     </row>
-    <row r="697" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A697" s="1">
         <v>45247</v>
       </c>
@@ -13110,7 +13116,7 @@
         <v>45247</v>
       </c>
     </row>
-    <row r="698" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A698" s="1">
         <v>45254</v>
       </c>
@@ -13118,7 +13124,7 @@
         <v>45254</v>
       </c>
     </row>
-    <row r="699" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A699" s="1">
         <v>45261</v>
       </c>
@@ -13126,7 +13132,7 @@
         <v>45261</v>
       </c>
     </row>
-    <row r="700" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A700" s="1">
         <v>45268</v>
       </c>
@@ -13134,7 +13140,7 @@
         <v>45268</v>
       </c>
     </row>
-    <row r="701" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A701" s="1">
         <v>45275</v>
       </c>
@@ -13142,7 +13148,7 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="702" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A702" s="1">
         <v>45282</v>
       </c>
@@ -13150,7 +13156,7 @@
         <v>45282</v>
       </c>
     </row>
-    <row r="703" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A703" s="1">
         <v>45289</v>
       </c>
@@ -13158,7 +13164,7 @@
         <v>45289</v>
       </c>
     </row>
-    <row r="704" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A704" s="1">
         <v>45296</v>
       </c>
@@ -13166,7 +13172,7 @@
         <v>45296</v>
       </c>
     </row>
-    <row r="705" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A705" s="1">
         <v>45303</v>
       </c>
@@ -13174,7 +13180,7 @@
         <v>45303</v>
       </c>
     </row>
-    <row r="706" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A706" s="1">
         <v>45310</v>
       </c>
@@ -13182,7 +13188,7 @@
         <v>45310</v>
       </c>
     </row>
-    <row r="707" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A707" s="1">
         <v>45317</v>
       </c>
@@ -13190,7 +13196,7 @@
         <v>45317</v>
       </c>
     </row>
-    <row r="708" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A708" s="1">
         <v>45324</v>
       </c>
@@ -13198,7 +13204,7 @@
         <v>45324</v>
       </c>
     </row>
-    <row r="709" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A709" s="1">
         <v>45331</v>
       </c>
@@ -13206,7 +13212,7 @@
         <v>45331</v>
       </c>
     </row>
-    <row r="710" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A710" s="1">
         <v>45338</v>
       </c>
@@ -13214,7 +13220,7 @@
         <v>45338</v>
       </c>
     </row>
-    <row r="711" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A711" s="1">
         <v>45345</v>
       </c>
@@ -13222,7 +13228,7 @@
         <v>45345</v>
       </c>
     </row>
-    <row r="712" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712" s="1">
         <v>45352</v>
       </c>
@@ -13230,7 +13236,7 @@
         <v>45352</v>
       </c>
     </row>
-    <row r="713" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A713" s="1">
         <v>45359</v>
       </c>
@@ -13238,7 +13244,7 @@
         <v>45359</v>
       </c>
     </row>
-    <row r="714" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A714" s="1">
         <v>45366</v>
       </c>
@@ -13246,7 +13252,7 @@
         <v>45366</v>
       </c>
     </row>
-    <row r="715" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A715" s="1">
         <v>45373</v>
       </c>
@@ -13254,7 +13260,7 @@
         <v>45373</v>
       </c>
     </row>
-    <row r="716" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A716" s="1">
         <v>45380</v>
       </c>
@@ -13262,7 +13268,7 @@
         <v>45380</v>
       </c>
     </row>
-    <row r="717" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A717" s="1">
         <v>45387</v>
       </c>
@@ -13270,7 +13276,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="718" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A718" s="1">
         <v>45394</v>
       </c>
@@ -13278,7 +13284,7 @@
         <v>45394</v>
       </c>
     </row>
-    <row r="719" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A719" s="1">
         <v>45401</v>
       </c>
@@ -13286,7 +13292,7 @@
         <v>45401</v>
       </c>
     </row>
-    <row r="720" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A720" s="1">
         <v>45408</v>
       </c>
@@ -13294,7 +13300,7 @@
         <v>45408</v>
       </c>
     </row>
-    <row r="721" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A721" s="1">
         <v>45415</v>
       </c>
@@ -13302,7 +13308,7 @@
         <v>45415</v>
       </c>
     </row>
-    <row r="722" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A722" s="1">
         <v>45422</v>
       </c>
@@ -13310,7 +13316,7 @@
         <v>45422</v>
       </c>
     </row>
-    <row r="723" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A723" s="1">
         <v>45429</v>
       </c>
@@ -13318,7 +13324,7 @@
         <v>45429</v>
       </c>
     </row>
-    <row r="724" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A724" s="1">
         <v>45436</v>
       </c>
@@ -13326,7 +13332,7 @@
         <v>45436</v>
       </c>
     </row>
-    <row r="725" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A725" s="1">
         <v>45443</v>
       </c>
@@ -13334,7 +13340,7 @@
         <v>45443</v>
       </c>
     </row>
-    <row r="726" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A726" s="1">
         <v>45450</v>
       </c>
@@ -13342,7 +13348,7 @@
         <v>45450</v>
       </c>
     </row>
-    <row r="727" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A727" s="1">
         <v>45457</v>
       </c>
@@ -13350,7 +13356,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="728" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A728" s="1">
         <v>45464</v>
       </c>
@@ -13358,7 +13364,7 @@
         <v>45464</v>
       </c>
     </row>
-    <row r="729" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A729" s="1">
         <v>45471</v>
       </c>
@@ -13366,7 +13372,7 @@
         <v>45471</v>
       </c>
     </row>
-    <row r="730" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A730" s="1">
         <v>45478</v>
       </c>
@@ -13374,7 +13380,7 @@
         <v>45478</v>
       </c>
     </row>
-    <row r="731" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A731" s="1">
         <v>45485</v>
       </c>
@@ -13382,7 +13388,7 @@
         <v>45485</v>
       </c>
     </row>
-    <row r="732" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A732" s="1">
         <v>45492</v>
       </c>
@@ -13390,7 +13396,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="733" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A733" s="1">
         <v>45499</v>
       </c>
@@ -13398,7 +13404,7 @@
         <v>45499</v>
       </c>
     </row>
-    <row r="734" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A734" s="1">
         <v>45506</v>
       </c>
@@ -13406,7 +13412,7 @@
         <v>45506</v>
       </c>
     </row>
-    <row r="735" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A735" s="1">
         <v>45513</v>
       </c>
@@ -13414,7 +13420,7 @@
         <v>45513</v>
       </c>
     </row>
-    <row r="736" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A736" s="1">
         <v>45520</v>
       </c>
@@ -13422,7 +13428,7 @@
         <v>45520</v>
       </c>
     </row>
-    <row r="737" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A737" s="1">
         <v>45527</v>
       </c>
@@ -13430,7 +13436,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="738" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" s="1">
         <v>45534</v>
       </c>
@@ -13438,7 +13444,7 @@
         <v>45534</v>
       </c>
     </row>
-    <row r="739" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A739" s="1">
         <v>45541</v>
       </c>
@@ -13446,7 +13452,7 @@
         <v>45541</v>
       </c>
     </row>
-    <row r="740" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A740" s="1">
         <v>45548</v>
       </c>
@@ -13454,7 +13460,7 @@
         <v>45548</v>
       </c>
     </row>
-    <row r="741" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A741" s="1">
         <v>45555</v>
       </c>
@@ -13462,7 +13468,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="742" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A742" s="1">
         <v>45562</v>
       </c>
@@ -13470,7 +13476,7 @@
         <v>45562</v>
       </c>
     </row>
-    <row r="743" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A743" s="1">
         <v>45569</v>
       </c>
@@ -13478,7 +13484,7 @@
         <v>45569</v>
       </c>
     </row>
-    <row r="744" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A744" s="1">
         <v>45576</v>
       </c>
@@ -13486,7 +13492,7 @@
         <v>45576</v>
       </c>
     </row>
-    <row r="745" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A745" s="1">
         <v>45583</v>
       </c>
@@ -13494,7 +13500,7 @@
         <v>45583</v>
       </c>
     </row>
-    <row r="746" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A746" s="1">
         <v>45590</v>
       </c>
@@ -13502,7 +13508,7 @@
         <v>45590</v>
       </c>
     </row>
-    <row r="747" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A747" s="1">
         <v>45597</v>
       </c>
@@ -13510,7 +13516,7 @@
         <v>45597</v>
       </c>
     </row>
-    <row r="748" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A748" s="1">
         <v>45604</v>
       </c>
@@ -13518,7 +13524,7 @@
         <v>45604</v>
       </c>
     </row>
-    <row r="749" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A749" s="1">
         <v>45611</v>
       </c>
@@ -13526,7 +13532,7 @@
         <v>45611</v>
       </c>
     </row>
-    <row r="750" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A750" s="1">
         <v>45618</v>
       </c>
@@ -13534,7 +13540,7 @@
         <v>45618</v>
       </c>
     </row>
-    <row r="751" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A751" s="1">
         <v>45625</v>
       </c>
@@ -13542,7 +13548,7 @@
         <v>45625</v>
       </c>
     </row>
-    <row r="752" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A752" s="1">
         <v>45632</v>
       </c>
@@ -13550,7 +13556,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="753" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A753" s="1">
         <v>45639</v>
       </c>
@@ -13558,7 +13564,7 @@
         <v>45639</v>
       </c>
     </row>
-    <row r="754" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A754" s="1">
         <v>45646</v>
       </c>
@@ -13566,7 +13572,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="755" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A755" s="1">
         <v>45653</v>
       </c>
@@ -13574,7 +13580,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="756" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A756" s="1">
         <v>45660</v>
       </c>
@@ -13582,7 +13588,7 @@
         <v>45660</v>
       </c>
     </row>
-    <row r="757" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A757" s="1">
         <v>45667</v>
       </c>
@@ -13590,7 +13596,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="758" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A758" s="1">
         <v>45674</v>
       </c>
@@ -13598,7 +13604,7 @@
         <v>45674</v>
       </c>
     </row>
-    <row r="759" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A759" s="1">
         <v>45681</v>
       </c>
@@ -13606,7 +13612,7 @@
         <v>45681</v>
       </c>
     </row>
-    <row r="760" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A760" s="1">
         <v>45688</v>
       </c>
@@ -13614,7 +13620,7 @@
         <v>45688</v>
       </c>
     </row>
-    <row r="761" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A761" s="1">
         <v>45695</v>
       </c>
@@ -13622,7 +13628,7 @@
         <v>45695</v>
       </c>
     </row>
-    <row r="762" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A762" s="1">
         <v>45702</v>
       </c>
@@ -13630,7 +13636,7 @@
         <v>45702</v>
       </c>
     </row>
-    <row r="763" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A763" s="1">
         <v>45709</v>
       </c>
@@ -13638,7 +13644,7 @@
         <v>45709</v>
       </c>
     </row>
-    <row r="764" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A764" s="1">
         <v>45716</v>
       </c>
@@ -13646,7 +13652,7 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="765" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A765" s="1">
         <v>45723</v>
       </c>
@@ -13654,7 +13660,7 @@
         <v>45723</v>
       </c>
     </row>
-    <row r="766" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A766" s="1">
         <v>45730</v>
       </c>
@@ -13662,7 +13668,7 @@
         <v>45730</v>
       </c>
     </row>
-    <row r="767" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A767" s="1">
         <v>45737</v>
       </c>
@@ -13670,7 +13676,7 @@
         <v>45737</v>
       </c>
     </row>
-    <row r="768" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A768" s="1">
         <v>45744</v>
       </c>
@@ -13678,7 +13684,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="769" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A769" s="1">
         <v>45751</v>
       </c>
@@ -13686,7 +13692,7 @@
         <v>45751</v>
       </c>
     </row>
-    <row r="770" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A770" s="1">
         <v>45758</v>
       </c>
@@ -13694,7 +13700,7 @@
         <v>45758</v>
       </c>
     </row>
-    <row r="771" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A771" s="1">
         <v>45765</v>
       </c>
@@ -13702,7 +13708,7 @@
         <v>45765</v>
       </c>
     </row>
-    <row r="772" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A772" s="1">
         <v>45772</v>
       </c>
@@ -13710,7 +13716,7 @@
         <v>45772</v>
       </c>
     </row>
-    <row r="773" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A773" s="1">
         <v>45779</v>
       </c>
@@ -13718,7 +13724,7 @@
         <v>45779</v>
       </c>
     </row>
-    <row r="774" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A774" s="1">
         <v>45786</v>
       </c>
@@ -13726,7 +13732,7 @@
         <v>45786</v>
       </c>
     </row>
-    <row r="775" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A775" s="1">
         <v>45793</v>
       </c>
@@ -13734,7 +13740,7 @@
         <v>45793</v>
       </c>
     </row>
-    <row r="776" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A776" s="1">
         <v>45800</v>
       </c>
@@ -13742,7 +13748,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="777" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A777" s="1">
         <v>45807</v>
       </c>
@@ -13750,7 +13756,7 @@
         <v>45807</v>
       </c>
     </row>
-    <row r="778" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A778" s="1">
         <v>45814</v>
       </c>
@@ -13758,7 +13764,7 @@
         <v>45814</v>
       </c>
     </row>
-    <row r="779" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A779" s="1">
         <v>45821</v>
       </c>
@@ -13766,7 +13772,7 @@
         <v>45821</v>
       </c>
     </row>
-    <row r="780" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A780" s="1">
         <v>45828</v>
       </c>
@@ -13774,7 +13780,7 @@
         <v>45828</v>
       </c>
     </row>
-    <row r="781" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A781" s="1">
         <v>45835</v>
       </c>
@@ -13782,7 +13788,7 @@
         <v>45835</v>
       </c>
     </row>
-    <row r="782" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A782" s="1">
         <v>45842</v>
       </c>
@@ -13790,7 +13796,7 @@
         <v>45842</v>
       </c>
     </row>
-    <row r="783" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A783" s="1">
         <v>45849</v>
       </c>
@@ -13798,7 +13804,7 @@
         <v>45849</v>
       </c>
     </row>
-    <row r="784" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A784" s="1">
         <v>45856</v>
       </c>
@@ -13806,7 +13812,7 @@
         <v>45856</v>
       </c>
     </row>
-    <row r="785" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A785" s="1">
         <v>45863</v>
       </c>
@@ -13814,7 +13820,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="786" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A786" s="1">
         <v>45870</v>
       </c>
@@ -13822,7 +13828,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="787" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A787" s="1">
         <v>45877</v>
       </c>
@@ -13830,7 +13836,7 @@
         <v>45877</v>
       </c>
     </row>
-    <row r="788" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A788" s="1">
         <v>45884</v>
       </c>
@@ -13838,7 +13844,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="789" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A789" s="1">
         <v>45891</v>
       </c>
@@ -13846,7 +13852,7 @@
         <v>45891</v>
       </c>
     </row>
-    <row r="790" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A790" s="1">
         <v>45898</v>
       </c>
@@ -13854,7 +13860,7 @@
         <v>45898</v>
       </c>
     </row>
-    <row r="791" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A791" s="1">
         <v>45905</v>
       </c>
@@ -13862,7 +13868,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="792" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A792" s="1">
         <v>45912</v>
       </c>
@@ -13870,7 +13876,7 @@
         <v>45912</v>
       </c>
     </row>
-    <row r="793" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A793" s="1">
         <v>45919</v>
       </c>
@@ -13878,7 +13884,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="794" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A794" s="1">
         <v>45926</v>
       </c>
@@ -13886,7 +13892,7 @@
         <v>45926</v>
       </c>
     </row>
-    <row r="795" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A795" s="1">
         <v>45933</v>
       </c>
@@ -13894,7 +13900,7 @@
         <v>45933</v>
       </c>
     </row>
-    <row r="796" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A796" s="1">
         <v>45940</v>
       </c>
@@ -13902,7 +13908,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="797" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A797" s="1">
         <v>45947</v>
       </c>
@@ -13910,7 +13916,7 @@
         <v>45947</v>
       </c>
     </row>
-    <row r="798" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A798" s="1">
         <v>45954</v>
       </c>
@@ -13918,7 +13924,7 @@
         <v>45954</v>
       </c>
     </row>
-    <row r="799" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A799" s="1">
         <v>45961</v>
       </c>
@@ -13926,7 +13932,7 @@
         <v>45961</v>
       </c>
     </row>
-    <row r="800" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A800" s="1">
         <v>45968</v>
       </c>
@@ -13934,7 +13940,7 @@
         <v>45968</v>
       </c>
     </row>
-    <row r="801" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A801" s="1">
         <v>45975</v>
       </c>
@@ -13942,7 +13948,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="802" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A802" s="1">
         <v>45982</v>
       </c>
@@ -13950,7 +13956,7 @@
         <v>45982</v>
       </c>
     </row>
-    <row r="803" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A803" s="1">
         <v>45989</v>
       </c>
@@ -13958,7 +13964,7 @@
         <v>45989</v>
       </c>
     </row>
-    <row r="804" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A804" s="1">
         <v>45996</v>
       </c>
@@ -13966,7 +13972,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="805" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A805" s="1">
         <v>46003</v>
       </c>
@@ -13974,7 +13980,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="806" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A806" s="1">
         <v>46010</v>
       </c>
@@ -13982,7 +13988,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="807" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A807" s="1">
         <v>46017</v>
       </c>
@@ -14005,7 +14011,7 @@
       <c r="N807" s="10"/>
       <c r="O807" s="10"/>
     </row>
-    <row r="808" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A808" s="1">
         <v>46024</v>
       </c>
@@ -14048,7 +14054,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="809" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A809" s="1">
         <v>46031</v>
       </c>
@@ -14091,7 +14097,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="810" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A810" s="1">
         <v>46038</v>
       </c>
@@ -14134,7 +14140,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="811" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A811" s="1">
         <v>46045</v>
       </c>
@@ -14177,7 +14183,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="812" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A812" s="1">
         <v>46052</v>
       </c>
@@ -14220,7 +14226,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="813" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A813" s="1">
         <v>46059</v>
       </c>
@@ -14263,7 +14269,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="814" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A814" s="1">
         <v>46066</v>
       </c>
@@ -14306,7 +14312,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="815" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A815" s="1">
         <v>46073</v>
       </c>
@@ -14349,7 +14355,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="816" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A816" s="1">
         <v>46080</v>
       </c>
@@ -14392,7 +14398,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="817" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A817" s="1">
         <v>46087</v>
       </c>
@@ -14435,7 +14441,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="818" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A818" s="1">
         <v>46094</v>
       </c>
@@ -14478,7 +14484,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="819" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A819" s="1">
         <v>46101</v>
       </c>
@@ -14521,7 +14527,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="820" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A820" s="1">
         <v>46108</v>
       </c>
@@ -14564,7 +14570,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="821" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A821" s="1">
         <v>46115</v>
       </c>
@@ -14607,7 +14613,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="822" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A822" s="1">
         <v>46122</v>
       </c>
@@ -14630,7 +14636,7 @@
       <c r="N822" s="3"/>
       <c r="O822" s="3"/>
     </row>
-    <row r="823" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A823" s="1">
         <v>46129</v>
       </c>
@@ -14653,7 +14659,7 @@
       <c r="N823" s="3"/>
       <c r="O823" s="3"/>
     </row>
-    <row r="824" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A824" s="1">
         <v>46136</v>
       </c>
@@ -14676,7 +14682,7 @@
       <c r="N824" s="3"/>
       <c r="O824" s="3"/>
     </row>
-    <row r="825" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A825" s="1">
         <v>46143</v>
       </c>
@@ -14719,7 +14725,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="826" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A826" s="1">
         <v>46150</v>
       </c>
@@ -14762,7 +14768,7 @@
         <v>76000</v>
       </c>
     </row>
-    <row r="827" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A827" s="1">
         <v>46157</v>
       </c>
@@ -14805,7 +14811,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="828" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A828" s="1">
         <v>46164</v>
       </c>
@@ -14848,7 +14854,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="829" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A829" s="1">
         <v>46171</v>
       </c>
@@ -14888,6 +14894,47 @@
         <v>71000</v>
       </c>
       <c r="O829" s="4">
+        <v>78000</v>
+      </c>
+    </row>
+    <row r="830" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A830" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B830" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E830" s="13">
+        <v>2322.1999999999998</v>
+      </c>
+      <c r="F830" s="4">
+        <v>11250</v>
+      </c>
+      <c r="G830" s="4">
+        <v>17750</v>
+      </c>
+      <c r="H830" s="4">
+        <v>28500</v>
+      </c>
+      <c r="I830" s="4">
+        <v>33500</v>
+      </c>
+      <c r="J830" s="4">
+        <v>38000</v>
+      </c>
+      <c r="K830" s="4">
+        <v>40000</v>
+      </c>
+      <c r="L830" s="4">
+        <v>46000</v>
+      </c>
+      <c r="M830" s="4">
+        <v>57000</v>
+      </c>
+      <c r="N830" s="4">
+        <v>71000</v>
+      </c>
+      <c r="O830" s="4">
         <v>78000</v>
       </c>
     </row>
@@ -14899,7 +14946,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02768588-2FF0-42C1-8A18-87D4CAFE9D17}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -14909,12 +14956,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A6084AF-43C5-4F58-881A-79CFC1D1F25A}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="8" t="s">
         <v>15</v>
       </c>
@@ -14922,7 +14969,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B3" s="8" t="s">
         <v>17</v>
       </c>

--- a/data/freight/HARPEX.xlsx
+++ b/data/freight/HARPEX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BCCEB8-BBDE-4D64-B4F2-C31E622C0F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F501396-EA6A-2847-B447-BE3968F1B2A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
+    <workbookView xWindow="25700" yWindow="3980" windowWidth="23260" windowHeight="14860" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
   <sheets>
     <sheet name="HARPEX" sheetId="1" r:id="rId1"/>
@@ -2755,6 +2755,9 @@
                 <c:pt idx="828">
                   <c:v>46178</c:v>
                 </c:pt>
+                <c:pt idx="829">
+                  <c:v>46185</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4537,17 +4540,26 @@
                 <c:pt idx="590">
                   <c:v>3852.69</c:v>
                 </c:pt>
+                <c:pt idx="726">
+                  <c:v>1627.4</c:v>
+                </c:pt>
+                <c:pt idx="778">
+                  <c:v>2158.19</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>2158.19</c:v>
+                </c:pt>
                 <c:pt idx="805">
                   <c:v>2180.56</c:v>
                 </c:pt>
                 <c:pt idx="806">
-                  <c:v>2182</c:v>
+                  <c:v>2182.0500000000002</c:v>
                 </c:pt>
                 <c:pt idx="807">
-                  <c:v>2182</c:v>
+                  <c:v>2182.0500000000002</c:v>
                 </c:pt>
                 <c:pt idx="808">
-                  <c:v>2182</c:v>
+                  <c:v>2182.0500000000002</c:v>
                 </c:pt>
                 <c:pt idx="809">
                   <c:v>2184</c:v>
@@ -4608,6 +4620,9 @@
                 </c:pt>
                 <c:pt idx="828">
                   <c:v>2322.1999999999998</c:v>
+                </c:pt>
+                <c:pt idx="829">
+                  <c:v>2323.69</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5717,17 +5732,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
-  <dimension ref="A1:P830"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:P831"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.36328125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="16" customWidth="1"/>
     <col min="4" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="15" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -5775,7 +5791,7 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>40383</v>
       </c>
@@ -5786,7 +5802,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>40390</v>
       </c>
@@ -5797,7 +5813,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>40397</v>
       </c>
@@ -5808,7 +5824,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>40404</v>
       </c>
@@ -5819,7 +5835,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>40411</v>
       </c>
@@ -5830,7 +5846,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>40418</v>
       </c>
@@ -5841,7 +5857,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>40425</v>
       </c>
@@ -5852,7 +5868,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>40432</v>
       </c>
@@ -5863,7 +5879,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>40439</v>
       </c>
@@ -5874,7 +5890,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>40446</v>
       </c>
@@ -5885,7 +5901,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>40453</v>
       </c>
@@ -5896,7 +5912,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>40460</v>
       </c>
@@ -5907,7 +5923,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>40467</v>
       </c>
@@ -5918,7 +5934,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>40474</v>
       </c>
@@ -5929,7 +5945,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>40481</v>
       </c>
@@ -5940,7 +5956,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>40488</v>
       </c>
@@ -5951,7 +5967,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>40495</v>
       </c>
@@ -5962,7 +5978,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>40502</v>
       </c>
@@ -5973,7 +5989,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>40509</v>
       </c>
@@ -5984,7 +6000,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>40516</v>
       </c>
@@ -5995,7 +6011,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>40523</v>
       </c>
@@ -6006,7 +6022,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>40530</v>
       </c>
@@ -6017,7 +6033,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>40537</v>
       </c>
@@ -6028,7 +6044,7 @@
         <v>679.37</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>40544</v>
       </c>
@@ -6039,7 +6055,7 @@
         <v>696.35</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>40551</v>
       </c>
@@ -6050,7 +6066,7 @@
         <v>706.3</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>40558</v>
       </c>
@@ -6061,7 +6077,7 @@
         <v>719.55</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>40565</v>
       </c>
@@ -6072,7 +6088,7 @@
         <v>747.31</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>40572</v>
       </c>
@@ -6083,7 +6099,7 @@
         <v>764.29</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>40579</v>
       </c>
@@ -6094,7 +6110,7 @@
         <v>782.1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>40586</v>
       </c>
@@ -6105,7 +6121,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>40593</v>
       </c>
@@ -6116,7 +6132,7 @@
         <v>849.63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>40600</v>
       </c>
@@ -6127,7 +6143,7 @@
         <v>861.23</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>40607</v>
       </c>
@@ -6138,7 +6154,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>40614</v>
       </c>
@@ -6149,7 +6165,7 @@
         <v>879.04</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>40621</v>
       </c>
@@ -6160,7 +6176,7 @@
         <v>882.35</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>40628</v>
       </c>
@@ -6171,7 +6187,7 @@
         <v>900.99</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>40635</v>
       </c>
@@ -6182,7 +6198,7 @@
         <v>892.29</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>40642</v>
       </c>
@@ -6193,7 +6209,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>40649</v>
       </c>
@@ -6204,7 +6220,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>40656</v>
       </c>
@@ -6215,7 +6231,7 @@
         <v>879.87</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>40663</v>
       </c>
@@ -6226,7 +6242,7 @@
         <v>875.72</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>40670</v>
       </c>
@@ -6237,7 +6253,7 @@
         <v>874.48</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>40677</v>
       </c>
@@ -6248,7 +6264,7 @@
         <v>877.38</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>40684</v>
       </c>
@@ -6259,7 +6275,7 @@
         <v>876.14</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>40691</v>
       </c>
@@ -6270,7 +6286,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>40698</v>
       </c>
@@ -6281,7 +6297,7 @@
         <v>865.37</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>40705</v>
       </c>
@@ -6292,7 +6308,7 @@
         <v>856.67</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>40712</v>
       </c>
@@ -6303,7 +6319,7 @@
         <v>847.14</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>40719</v>
       </c>
@@ -6314,7 +6330,7 @@
         <v>831.4</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>40726</v>
       </c>
@@ -6325,7 +6341,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>40733</v>
       </c>
@@ -6336,7 +6352,7 @@
         <v>808.62</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>40740</v>
       </c>
@@ -6347,7 +6363,7 @@
         <v>775.06</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>40747</v>
       </c>
@@ -6358,7 +6374,7 @@
         <v>741.51</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>40754</v>
       </c>
@@ -6369,7 +6385,7 @@
         <v>719.97</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>40761</v>
       </c>
@@ -6380,7 +6396,7 @@
         <v>709.2</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>40768</v>
       </c>
@@ -6391,7 +6407,7 @@
         <v>671.91</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>40775</v>
       </c>
@@ -6402,7 +6418,7 @@
         <v>666.11</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>40782</v>
       </c>
@@ -6413,7 +6429,7 @@
         <v>657.83</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>40789</v>
       </c>
@@ -6424,7 +6440,7 @@
         <v>630.9</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>40796</v>
       </c>
@@ -6435,7 +6451,7 @@
         <v>621.38</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>40803</v>
       </c>
@@ -6446,7 +6462,7 @@
         <v>616.4</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>40810</v>
       </c>
@@ -6457,7 +6473,7 @@
         <v>555.1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>40817</v>
       </c>
@@ -6468,7 +6484,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>40824</v>
       </c>
@@ -6479,7 +6495,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>40831</v>
       </c>
@@ -6490,7 +6506,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>40838</v>
       </c>
@@ -6501,7 +6517,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>40845</v>
       </c>
@@ -6512,7 +6528,7 @@
         <v>445.32</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>40852</v>
       </c>
@@ -6523,7 +6539,7 @@
         <v>438.28</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>40859</v>
       </c>
@@ -6534,7 +6550,7 @@
         <v>437.45</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>40866</v>
       </c>
@@ -6545,7 +6561,7 @@
         <v>420.05</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>40873</v>
       </c>
@@ -6556,7 +6572,7 @@
         <v>417.98</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>40880</v>
       </c>
@@ -6567,7 +6583,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>40887</v>
       </c>
@@ -6578,7 +6594,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>40894</v>
       </c>
@@ -6589,7 +6605,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>40901</v>
       </c>
@@ -6600,7 +6616,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>40908</v>
       </c>
@@ -6611,7 +6627,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>40915</v>
       </c>
@@ -6622,7 +6638,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>40922</v>
       </c>
@@ -6633,7 +6649,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>40929</v>
       </c>
@@ -6644,7 +6660,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>40936</v>
       </c>
@@ -6655,7 +6671,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>40942</v>
       </c>
@@ -6666,7 +6682,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>40943</v>
       </c>
@@ -6677,7 +6693,7 @@
         <v>389.81</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>40950</v>
       </c>
@@ -6688,7 +6704,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>40957</v>
       </c>
@@ -6699,7 +6715,7 @@
         <v>375.31</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>40964</v>
       </c>
@@ -6710,7 +6726,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>40978</v>
       </c>
@@ -6721,7 +6737,7 @@
         <v>384.84</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>40985</v>
       </c>
@@ -6732,7 +6748,7 @@
         <v>393.12</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>40992</v>
       </c>
@@ -6743,7 +6759,7 @@
         <v>396.02</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>40999</v>
       </c>
@@ -6754,7 +6770,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>41006</v>
       </c>
@@ -6765,7 +6781,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>41013</v>
       </c>
@@ -6776,7 +6792,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>41020</v>
       </c>
@@ -6787,7 +6803,7 @@
         <v>416.32</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>41027</v>
       </c>
@@ -6798,7 +6814,7 @@
         <v>428.33</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>41034</v>
       </c>
@@ -6809,7 +6825,7 @@
         <v>440.35</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>41041</v>
       </c>
@@ -6820,7 +6836,7 @@
         <v>444.9</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>41048</v>
       </c>
@@ -6831,7 +6847,7 @@
         <v>457.33</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>41055</v>
       </c>
@@ -6842,7 +6858,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>41062</v>
       </c>
@@ -6853,7 +6869,7 @@
         <v>456.92</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>41069</v>
       </c>
@@ -6864,7 +6880,7 @@
         <v>451.12</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>41076</v>
       </c>
@@ -6875,7 +6891,7 @@
         <v>446.98</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>41083</v>
       </c>
@@ -6886,7 +6902,7 @@
         <v>437.86</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>41090</v>
       </c>
@@ -6897,7 +6913,7 @@
         <v>434.96</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>41097</v>
       </c>
@@ -6908,7 +6924,7 @@
         <v>430.41</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>41104</v>
       </c>
@@ -6919,7 +6935,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>41111</v>
       </c>
@@ -6930,7 +6946,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>41118</v>
       </c>
@@ -6941,7 +6957,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>41125</v>
       </c>
@@ -6952,7 +6968,7 @@
         <v>399.75</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>41132</v>
       </c>
@@ -6963,7 +6979,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>41139</v>
       </c>
@@ -6974,7 +6990,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>41146</v>
       </c>
@@ -6985,7 +7001,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>41153</v>
       </c>
@@ -6996,7 +7012,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>41160</v>
       </c>
@@ -7007,7 +7023,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>41167</v>
       </c>
@@ -7018,7 +7034,7 @@
         <v>386.08</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>41174</v>
       </c>
@@ -7029,7 +7045,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>41181</v>
       </c>
@@ -7040,7 +7056,7 @@
         <v>377.8</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>41188</v>
       </c>
@@ -7051,7 +7067,7 @@
         <v>373.65</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>41195</v>
       </c>
@@ -7062,7 +7078,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>41202</v>
       </c>
@@ -7073,7 +7089,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>41209</v>
       </c>
@@ -7084,7 +7100,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>41216</v>
       </c>
@@ -7095,7 +7111,7 @@
         <v>367.44</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>41223</v>
       </c>
@@ -7106,7 +7122,7 @@
         <v>366.61</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>41230</v>
       </c>
@@ -7117,7 +7133,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>41237</v>
       </c>
@@ -7128,7 +7144,7 @@
         <v>362.88</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>41244</v>
       </c>
@@ -7139,7 +7155,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>41251</v>
       </c>
@@ -7150,7 +7166,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>41258</v>
       </c>
@@ -7161,7 +7177,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>41265</v>
       </c>
@@ -7172,7 +7188,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>41272</v>
       </c>
@@ -7183,7 +7199,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>41279</v>
       </c>
@@ -7194,7 +7210,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>41286</v>
       </c>
@@ -7205,7 +7221,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>41293</v>
       </c>
@@ -7216,7 +7232,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>41300</v>
       </c>
@@ -7227,7 +7243,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>41307</v>
       </c>
@@ -7238,7 +7254,7 @@
         <v>366.2</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>41314</v>
       </c>
@@ -7249,7 +7265,7 @@
         <v>369.93</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>41321</v>
       </c>
@@ -7260,7 +7276,7 @@
         <v>372.41</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>41328</v>
       </c>
@@ -7271,7 +7287,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>41335</v>
       </c>
@@ -7282,7 +7298,7 @@
         <v>376.97</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>41342</v>
       </c>
@@ -7293,7 +7309,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>41349</v>
       </c>
@@ -7304,7 +7320,7 @@
         <v>382.35</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>41356</v>
       </c>
@@ -7315,7 +7331,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>41363</v>
       </c>
@@ -7326,7 +7342,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>41370</v>
       </c>
@@ -7337,7 +7353,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>41377</v>
       </c>
@@ -7348,7 +7364,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>41384</v>
       </c>
@@ -7359,7 +7375,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>41391</v>
       </c>
@@ -7370,7 +7386,7 @@
         <v>395.61</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>41398</v>
       </c>
@@ -7381,7 +7397,7 @@
         <v>396.85</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>41405</v>
       </c>
@@ -7392,7 +7408,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>41412</v>
       </c>
@@ -7403,7 +7419,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>41419</v>
       </c>
@@ -7414,7 +7430,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>41426</v>
       </c>
@@ -7425,7 +7441,7 @@
         <v>401.41</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>41433</v>
       </c>
@@ -7436,7 +7452,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>41440</v>
       </c>
@@ -7447,7 +7463,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>41447</v>
       </c>
@@ -7458,7 +7474,7 @@
         <v>400.58</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>41454</v>
       </c>
@@ -7469,7 +7485,7 @@
         <v>401.82</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>41461</v>
       </c>
@@ -7480,7 +7496,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>41468</v>
       </c>
@@ -7491,7 +7507,7 @@
         <v>398.51</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>41475</v>
       </c>
@@ -7502,7 +7518,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>41482</v>
       </c>
@@ -7513,7 +7529,7 @@
         <v>400.99</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>41489</v>
       </c>
@@ -7524,7 +7540,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>41496</v>
       </c>
@@ -7535,7 +7551,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>41503</v>
       </c>
@@ -7546,7 +7562,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>41510</v>
       </c>
@@ -7557,7 +7573,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>41517</v>
       </c>
@@ -7568,7 +7584,7 @@
         <v>404.72</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>41524</v>
       </c>
@@ -7579,7 +7595,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>41531</v>
       </c>
@@ -7590,7 +7606,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>41538</v>
       </c>
@@ -7601,7 +7617,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>41545</v>
       </c>
@@ -7612,7 +7628,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>41552</v>
       </c>
@@ -7623,7 +7639,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>41559</v>
       </c>
@@ -7634,7 +7650,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>41566</v>
       </c>
@@ -7645,7 +7661,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>41573</v>
       </c>
@@ -7656,7 +7672,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>41580</v>
       </c>
@@ -7667,7 +7683,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>41587</v>
       </c>
@@ -7678,7 +7694,7 @@
         <v>398.92</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>41594</v>
       </c>
@@ -7689,7 +7705,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>41601</v>
       </c>
@@ -7700,7 +7716,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>41608</v>
       </c>
@@ -7711,7 +7727,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>41615</v>
       </c>
@@ -7722,7 +7738,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>41622</v>
       </c>
@@ -7733,7 +7749,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>41629</v>
       </c>
@@ -7744,7 +7760,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>41636</v>
       </c>
@@ -7755,7 +7771,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>41643</v>
       </c>
@@ -7766,7 +7782,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>41650</v>
       </c>
@@ -7777,7 +7793,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>41657</v>
       </c>
@@ -7788,7 +7804,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>41664</v>
       </c>
@@ -7799,7 +7815,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>41671</v>
       </c>
@@ -7810,7 +7826,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>41678</v>
       </c>
@@ -7821,7 +7837,7 @@
         <v>387.74</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>41685</v>
       </c>
@@ -7832,7 +7848,7 @@
         <v>386.91</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>41692</v>
       </c>
@@ -7843,7 +7859,7 @@
         <v>385.25</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>41699</v>
       </c>
@@ -7854,7 +7870,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>41706</v>
       </c>
@@ -7865,7 +7881,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>41713</v>
       </c>
@@ -7876,7 +7892,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>41720</v>
       </c>
@@ -7887,7 +7903,7 @@
         <v>380.7</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>41727</v>
       </c>
@@ -7898,7 +7914,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>41734</v>
       </c>
@@ -7909,7 +7925,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>41741</v>
       </c>
@@ -7920,7 +7936,7 @@
         <v>386.5</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>41748</v>
       </c>
@@ -7931,7 +7947,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>41755</v>
       </c>
@@ -7942,7 +7958,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>41762</v>
       </c>
@@ -7953,7 +7969,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>41769</v>
       </c>
@@ -7964,7 +7980,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>41776</v>
       </c>
@@ -7975,7 +7991,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>41783</v>
       </c>
@@ -7986,7 +8002,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>41790</v>
       </c>
@@ -7997,7 +8013,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>41797</v>
       </c>
@@ -8008,7 +8024,7 @@
         <v>406.79</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>41804</v>
       </c>
@@ -8019,7 +8035,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>41811</v>
       </c>
@@ -8030,7 +8046,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>41818</v>
       </c>
@@ -8041,7 +8057,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>41825</v>
       </c>
@@ -8052,7 +8068,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <v>41832</v>
       </c>
@@ -8063,7 +8079,7 @@
         <v>409.28</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <v>41839</v>
       </c>
@@ -8074,7 +8090,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <v>41846</v>
       </c>
@@ -8085,7 +8101,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>41853</v>
       </c>
@@ -8096,7 +8112,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>41860</v>
       </c>
@@ -8107,7 +8123,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>41867</v>
       </c>
@@ -8118,7 +8134,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>41874</v>
       </c>
@@ -8129,7 +8145,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>41881</v>
       </c>
@@ -8140,7 +8156,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>41888</v>
       </c>
@@ -8151,7 +8167,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>41895</v>
       </c>
@@ -8162,7 +8178,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>41902</v>
       </c>
@@ -8173,7 +8189,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>41909</v>
       </c>
@@ -8184,7 +8200,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>41916</v>
       </c>
@@ -8195,7 +8211,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>41923</v>
       </c>
@@ -8206,7 +8222,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>41930</v>
       </c>
@@ -8217,7 +8233,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>41937</v>
       </c>
@@ -8228,7 +8244,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>41944</v>
       </c>
@@ -8239,7 +8255,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>41951</v>
       </c>
@@ -8250,7 +8266,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>41958</v>
       </c>
@@ -8261,7 +8277,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>41965</v>
       </c>
@@ -8272,7 +8288,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>41972</v>
       </c>
@@ -8283,7 +8299,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>41979</v>
       </c>
@@ -8294,7 +8310,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>41986</v>
       </c>
@@ -8305,7 +8321,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>41993</v>
       </c>
@@ -8316,7 +8332,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>42000</v>
       </c>
@@ -8327,7 +8343,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>42007</v>
       </c>
@@ -8338,7 +8354,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>42014</v>
       </c>
@@ -8349,7 +8365,7 @@
         <v>435.38</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>42021</v>
       </c>
@@ -8360,7 +8376,7 @@
         <v>441.59</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <v>42028</v>
       </c>
@@ -8371,7 +8387,7 @@
         <v>455.26</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <v>42035</v>
       </c>
@@ -8382,7 +8398,7 @@
         <v>461.47</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <v>42042</v>
       </c>
@@ -8393,7 +8409,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <v>42049</v>
       </c>
@@ -8404,7 +8420,7 @@
         <v>483.84</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <v>42056</v>
       </c>
@@ -8415,7 +8431,7 @@
         <v>494.2</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>42063</v>
       </c>
@@ -8426,7 +8442,7 @@
         <v>496.27</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <v>42070</v>
       </c>
@@ -8437,7 +8453,7 @@
         <v>502.49</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>42077</v>
       </c>
@@ -8448,7 +8464,7 @@
         <v>504.14</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>42084</v>
       </c>
@@ -8459,7 +8475,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>42091</v>
       </c>
@@ -8470,7 +8486,7 @@
         <v>561.72</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <v>42098</v>
       </c>
@@ -8481,7 +8497,7 @@
         <v>596.11</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>42105</v>
       </c>
@@ -8492,7 +8508,7 @@
         <v>614.75</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>42112</v>
       </c>
@@ -8503,7 +8519,7 @@
         <v>612.67999999999995</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>42119</v>
       </c>
@@ -8514,7 +8530,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>42126</v>
       </c>
@@ -8525,7 +8541,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>42133</v>
       </c>
@@ -8536,7 +8552,7 @@
         <v>626.76</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>42140</v>
       </c>
@@ -8547,7 +8563,7 @@
         <v>640.02</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>42147</v>
       </c>
@@ -8558,7 +8574,7 @@
         <v>642.91999999999996</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>42154</v>
       </c>
@@ -8569,7 +8585,7 @@
         <v>644.57000000000005</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <v>42161</v>
       </c>
@@ -8580,7 +8596,7 @@
         <v>643.74</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>42168</v>
       </c>
@@ -8591,7 +8607,7 @@
         <v>645.82000000000005</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <v>42175</v>
       </c>
@@ -8602,7 +8618,7 @@
         <v>639.6</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>42182</v>
       </c>
@@ -8613,7 +8629,7 @@
         <v>633.39</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>42189</v>
       </c>
@@ -8624,7 +8640,7 @@
         <v>630.07000000000005</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>42196</v>
       </c>
@@ -8635,7 +8651,7 @@
         <v>620.13</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>42203</v>
       </c>
@@ -8646,7 +8662,7 @@
         <v>617.65</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>42210</v>
       </c>
@@ -8657,7 +8673,7 @@
         <v>600.25</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>42217</v>
       </c>
@@ -8668,7 +8684,7 @@
         <v>577.04999999999995</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>42224</v>
       </c>
@@ -8679,7 +8695,7 @@
         <v>560.07000000000005</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>42231</v>
       </c>
@@ -8690,7 +8706,7 @@
         <v>558.82000000000005</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>42238</v>
       </c>
@@ -8701,7 +8717,7 @@
         <v>550.12</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>42245</v>
       </c>
@@ -8712,7 +8728,7 @@
         <v>545.98</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>42252</v>
       </c>
@@ -8723,7 +8739,7 @@
         <v>541.01</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>42259</v>
       </c>
@@ -8734,7 +8750,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>42266</v>
       </c>
@@ -8745,7 +8761,7 @@
         <v>512.84</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>42273</v>
       </c>
@@ -8756,7 +8772,7 @@
         <v>491.3</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>42280</v>
       </c>
@@ -8767,7 +8783,7 @@
         <v>477.22</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>42287</v>
       </c>
@@ -8778,7 +8794,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>42294</v>
       </c>
@@ -8789,7 +8805,7 @@
         <v>438.69</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <v>42301</v>
       </c>
@@ -8800,7 +8816,7 @@
         <v>415.08</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <v>42308</v>
       </c>
@@ -8811,7 +8827,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>42315</v>
       </c>
@@ -8822,7 +8838,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>42322</v>
       </c>
@@ -8833,7 +8849,7 @@
         <v>388.98</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>42329</v>
       </c>
@@ -8844,7 +8860,7 @@
         <v>385.67</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>42336</v>
       </c>
@@ -8855,7 +8871,7 @@
         <v>380.28</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>42343</v>
       </c>
@@ -8866,7 +8882,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>42350</v>
       </c>
@@ -8877,7 +8893,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>42357</v>
       </c>
@@ -8888,7 +8904,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>42364</v>
       </c>
@@ -8899,7 +8915,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>42371</v>
       </c>
@@ -8910,7 +8926,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>42378</v>
       </c>
@@ -8921,7 +8937,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>42385</v>
       </c>
@@ -8932,7 +8948,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>42392</v>
       </c>
@@ -8943,7 +8959,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>42399</v>
       </c>
@@ -8954,7 +8970,7 @@
         <v>363.71</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>42406</v>
       </c>
@@ -8965,7 +8981,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>42413</v>
       </c>
@@ -8976,7 +8992,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>42420</v>
       </c>
@@ -8987,7 +9003,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>42427</v>
       </c>
@@ -8998,7 +9014,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>42434</v>
       </c>
@@ -9009,7 +9025,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>42441</v>
       </c>
@@ -9020,7 +9036,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>42448</v>
       </c>
@@ -9031,7 +9047,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>42455</v>
       </c>
@@ -9042,7 +9058,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>42462</v>
       </c>
@@ -9053,7 +9069,7 @@
         <v>362.47</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>42469</v>
       </c>
@@ -9064,7 +9080,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>42476</v>
       </c>
@@ -9075,7 +9091,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>42483</v>
       </c>
@@ -9086,7 +9102,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
         <v>42490</v>
       </c>
@@ -9097,7 +9113,7 @@
         <v>358.74</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
         <v>42497</v>
       </c>
@@ -9108,7 +9124,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
         <v>42504</v>
       </c>
@@ -9119,7 +9135,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
         <v>42511</v>
       </c>
@@ -9130,7 +9146,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
         <v>42518</v>
       </c>
@@ -9141,7 +9157,7 @@
         <v>356.67</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A308" s="1">
         <v>42525</v>
       </c>
@@ -9152,7 +9168,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A309" s="1">
         <v>42532</v>
       </c>
@@ -9163,7 +9179,7 @@
         <v>354.6</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A310" s="1">
         <v>42539</v>
       </c>
@@ -9174,7 +9190,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A311" s="1">
         <v>42546</v>
       </c>
@@ -9185,7 +9201,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A312" s="1">
         <v>42553</v>
       </c>
@@ -9196,7 +9212,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A313" s="1">
         <v>42560</v>
       </c>
@@ -9207,7 +9223,7 @@
         <v>348.8</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A314" s="1">
         <v>42567</v>
       </c>
@@ -9218,7 +9234,7 @@
         <v>347.56</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A315" s="1">
         <v>42574</v>
       </c>
@@ -9229,7 +9245,7 @@
         <v>345.9</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A316" s="1">
         <v>42581</v>
       </c>
@@ -9240,7 +9256,7 @@
         <v>345.07</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A317" s="1">
         <v>42588</v>
       </c>
@@ -9251,7 +9267,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A318" s="1">
         <v>42595</v>
       </c>
@@ -9262,7 +9278,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A319" s="1">
         <v>42602</v>
       </c>
@@ -9273,7 +9289,7 @@
         <v>341.76</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A320" s="1">
         <v>42609</v>
       </c>
@@ -9284,7 +9300,7 @@
         <v>337.2</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A321" s="1">
         <v>42616</v>
       </c>
@@ -9295,7 +9311,7 @@
         <v>331.4</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A322" s="1">
         <v>42623</v>
       </c>
@@ -9306,7 +9322,7 @@
         <v>330.99</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A323" s="1">
         <v>42630</v>
       </c>
@@ -9317,7 +9333,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
         <v>42637</v>
       </c>
@@ -9328,7 +9344,7 @@
         <v>328.09</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
         <v>42644</v>
       </c>
@@ -9339,7 +9355,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A326" s="1">
         <v>42651</v>
       </c>
@@ -9350,7 +9366,7 @@
         <v>326.01</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A327" s="1">
         <v>42658</v>
       </c>
@@ -9361,7 +9377,7 @@
         <v>324.77</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
         <v>42665</v>
       </c>
@@ -9372,7 +9388,7 @@
         <v>322.7</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A329" s="1">
         <v>42672</v>
       </c>
@@ -9383,7 +9399,7 @@
         <v>319.39</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A330" s="1">
         <v>42679</v>
       </c>
@@ -9394,7 +9410,7 @@
         <v>318.56</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A331" s="1">
         <v>42686</v>
       </c>
@@ -9405,7 +9421,7 @@
         <v>317.32</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A332" s="1">
         <v>42693</v>
       </c>
@@ -9416,7 +9432,7 @@
         <v>316.49</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A333" s="1">
         <v>42700</v>
       </c>
@@ -9427,7 +9443,7 @@
         <v>316.07</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A334" s="1">
         <v>42707</v>
       </c>
@@ -9438,7 +9454,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A335" s="1">
         <v>42714</v>
       </c>
@@ -9449,7 +9465,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A336" s="1">
         <v>42721</v>
       </c>
@@ -9460,7 +9476,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A337" s="1">
         <v>42728</v>
       </c>
@@ -9471,7 +9487,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A338" s="1">
         <v>42735</v>
       </c>
@@ -9482,7 +9498,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A339" s="1">
         <v>42742</v>
       </c>
@@ -9493,7 +9509,7 @@
         <v>316.39</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A340" s="1">
         <v>42749</v>
       </c>
@@ -9504,7 +9520,7 @@
         <v>319.07</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A341" s="1">
         <v>42756</v>
       </c>
@@ -9515,7 +9531,7 @@
         <v>320.56</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A342" s="1">
         <v>42763</v>
       </c>
@@ -9526,7 +9542,7 @@
         <v>322.35000000000002</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A343" s="1">
         <v>42770</v>
       </c>
@@ -9537,7 +9553,7 @@
         <v>323.83999999999997</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A344" s="1">
         <v>42777</v>
       </c>
@@ -9548,7 +9564,7 @@
         <v>325.33</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A345" s="1">
         <v>42784</v>
       </c>
@@ -9559,7 +9575,7 @@
         <v>330.4</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A346" s="1">
         <v>42791</v>
       </c>
@@ -9570,7 +9586,7 @@
         <v>343.52</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A347" s="1">
         <v>42798</v>
       </c>
@@ -9581,7 +9597,7 @@
         <v>351.87</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A348" s="1">
         <v>42805</v>
       </c>
@@ -9592,7 +9608,7 @@
         <v>389.44</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A349" s="1">
         <v>42812</v>
       </c>
@@ -9603,7 +9619,7 @@
         <v>404.35</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A350" s="1">
         <v>42819</v>
       </c>
@@ -9614,7 +9630,7 @@
         <v>438.94</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A351" s="1">
         <v>42826</v>
       </c>
@@ -9625,7 +9641,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A352" s="1">
         <v>42833</v>
       </c>
@@ -9636,7 +9652,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A353" s="1">
         <v>42840</v>
       </c>
@@ -9647,7 +9663,7 @@
         <v>516.77</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A354" s="1">
         <v>42847</v>
       </c>
@@ -9658,7 +9674,7 @@
         <v>522.14</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A355" s="1">
         <v>42854</v>
       </c>
@@ -9669,7 +9685,7 @@
         <v>523.33000000000004</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A356" s="1">
         <v>42861</v>
       </c>
@@ -9680,7 +9696,7 @@
         <v>533.47</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A357" s="1">
         <v>42868</v>
       </c>
@@ -9691,7 +9707,7 @@
         <v>533.16999999999996</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A358" s="1">
         <v>42875</v>
       </c>
@@ -9702,7 +9718,7 @@
         <v>500.37</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A359" s="1">
         <v>42882</v>
       </c>
@@ -9713,7 +9729,7 @@
         <v>483.97</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A360" s="1">
         <v>42889</v>
       </c>
@@ -9724,7 +9740,7 @@
         <v>458.92</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A361" s="1">
         <v>42896</v>
       </c>
@@ -9735,7 +9751,7 @@
         <v>443.72</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A362" s="1">
         <v>42903</v>
       </c>
@@ -9746,7 +9762,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A363" s="1">
         <v>42910</v>
       </c>
@@ -9757,7 +9773,7 @@
         <v>438.35</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A364" s="1">
         <v>42917</v>
       </c>
@@ -9768,7 +9784,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A365" s="1">
         <v>42924</v>
       </c>
@@ -9779,7 +9795,7 @@
         <v>435.96</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A366" s="1">
         <v>42931</v>
       </c>
@@ -9790,7 +9806,7 @@
         <v>445.8</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A367" s="1">
         <v>42938</v>
       </c>
@@ -9801,7 +9817,7 @@
         <v>470.25</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A368" s="1">
         <v>42945</v>
       </c>
@@ -9812,7 +9828,7 @@
         <v>472.04</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A369" s="1">
         <v>42952</v>
       </c>
@@ -9823,7 +9839,7 @@
         <v>481.88</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A370" s="1">
         <v>42959</v>
       </c>
@@ -9834,7 +9850,7 @@
         <v>486.66</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A371" s="1">
         <v>42966</v>
       </c>
@@ -9845,7 +9861,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A372" s="1">
         <v>42973</v>
       </c>
@@ -9856,7 +9872,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A373" s="1">
         <v>42980</v>
       </c>
@@ -9867,7 +9883,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A374" s="1">
         <v>42987</v>
       </c>
@@ -9878,7 +9894,7 @@
         <v>515.88</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A375" s="1">
         <v>42994</v>
       </c>
@@ -9889,7 +9905,7 @@
         <v>517.07000000000005</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A376" s="1">
         <v>43001</v>
       </c>
@@ -9900,7 +9916,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A377" s="1">
         <v>43008</v>
       </c>
@@ -9911,7 +9927,7 @@
         <v>506.34</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A378" s="1">
         <v>43015</v>
       </c>
@@ -9922,7 +9938,7 @@
         <v>507.53</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A379" s="1">
         <v>43022</v>
       </c>
@@ -9933,7 +9949,7 @@
         <v>505.14</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A380" s="1">
         <v>43029</v>
       </c>
@@ -9944,7 +9960,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A381" s="1">
         <v>43036</v>
       </c>
@@ -9955,7 +9971,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A382" s="1">
         <v>43043</v>
       </c>
@@ -9966,7 +9982,7 @@
         <v>473.24</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A383" s="1">
         <v>43050</v>
       </c>
@@ -9977,7 +9993,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A384" s="1">
         <v>43057</v>
       </c>
@@ -9988,7 +10004,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A385" s="1">
         <v>43064</v>
       </c>
@@ -9999,7 +10015,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A386" s="1">
         <v>43071</v>
       </c>
@@ -10010,7 +10026,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A387" s="1">
         <v>43078</v>
       </c>
@@ -10021,7 +10037,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A388" s="1">
         <v>43085</v>
       </c>
@@ -10032,7 +10048,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A389" s="1">
         <v>43092</v>
       </c>
@@ -10043,7 +10059,7 @@
         <v>482.78</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A390" s="1">
         <v>43099</v>
       </c>
@@ -10054,7 +10070,7 @@
         <v>483.08</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A391" s="1">
         <v>43106</v>
       </c>
@@ -10065,7 +10081,7 @@
         <v>485.16</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A392" s="1">
         <v>43113</v>
       </c>
@@ -10076,7 +10092,7 @@
         <v>489.34</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A393" s="1">
         <v>43120</v>
       </c>
@@ -10087,7 +10103,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A394" s="1">
         <v>43127</v>
       </c>
@@ -10098,7 +10114,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A395" s="1">
         <v>43134</v>
       </c>
@@ -10109,7 +10125,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A396" s="1">
         <v>43141</v>
       </c>
@@ -10120,7 +10136,7 @@
         <v>520.35</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A397" s="1">
         <v>43148</v>
       </c>
@@ -10131,7 +10147,7 @@
         <v>526.02</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A398" s="1">
         <v>43155</v>
       </c>
@@ -10142,7 +10158,7 @@
         <v>542.41999999999996</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A399" s="1">
         <v>43162</v>
       </c>
@@ -10153,7 +10169,7 @@
         <v>548.98</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A400" s="1">
         <v>43169</v>
       </c>
@@ -10164,7 +10180,7 @@
         <v>579.69000000000005</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A401" s="1">
         <v>43176</v>
       </c>
@@ -10175,7 +10191,7 @@
         <v>597.88</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A402" s="1">
         <v>43183</v>
       </c>
@@ -10186,7 +10202,7 @@
         <v>635.16</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A403" s="1">
         <v>43190</v>
       </c>
@@ -10197,7 +10213,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A404" s="1">
         <v>43197</v>
       </c>
@@ -10208,7 +10224,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A405" s="1">
         <v>43204</v>
       </c>
@@ -10219,7 +10235,7 @@
         <v>642.61</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A406" s="1">
         <v>43211</v>
       </c>
@@ -10230,7 +10246,7 @@
         <v>646.19000000000005</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A407" s="1">
         <v>43218</v>
       </c>
@@ -10241,7 +10257,7 @@
         <v>652.45000000000005</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A408" s="1">
         <v>43225</v>
       </c>
@@ -10252,7 +10268,7 @@
         <v>653.64</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A409" s="1">
         <v>43232</v>
       </c>
@@ -10263,7 +10279,7 @@
         <v>656.63</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A410" s="1">
         <v>43239</v>
       </c>
@@ -10274,7 +10290,7 @@
         <v>661.1</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A411" s="1">
         <v>43245</v>
       </c>
@@ -10285,7 +10301,7 @@
         <v>670.64</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A412" s="1">
         <v>43252</v>
       </c>
@@ -10296,7 +10312,7 @@
         <v>673.62</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A413" s="1">
         <v>43259</v>
       </c>
@@ -10307,7 +10323,7 @@
         <v>676.61</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A414" s="1">
         <v>43266</v>
       </c>
@@ -10318,7 +10334,7 @@
         <v>678.1</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A415" s="1">
         <v>43273</v>
       </c>
@@ -10329,7 +10345,7 @@
         <v>676.9</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A416" s="1">
         <v>43280</v>
       </c>
@@ -10340,7 +10356,7 @@
         <v>672.73</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A417" s="1">
         <v>43287</v>
       </c>
@@ -10351,7 +10367,7 @@
         <v>668.26</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A418" s="1">
         <v>43294</v>
       </c>
@@ -10362,7 +10378,7 @@
         <v>652.15</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A419" s="1">
         <v>43301</v>
       </c>
@@ -10373,7 +10389,7 @@
         <v>628.6</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A420" s="1">
         <v>43308</v>
       </c>
@@ -10384,7 +10400,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A421" s="1">
         <v>43315</v>
       </c>
@@ -10395,7 +10411,7 @@
         <v>594.6</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A422" s="1">
         <v>43322</v>
       </c>
@@ -10406,7 +10422,7 @@
         <v>584.16999999999996</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A423" s="1">
         <v>43329</v>
       </c>
@@ -10417,7 +10433,7 @@
         <v>582.97</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A424" s="1">
         <v>43336</v>
       </c>
@@ -10428,7 +10444,7 @@
         <v>577.01</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A425" s="1">
         <v>43343</v>
       </c>
@@ -10439,7 +10455,7 @@
         <v>568.05999999999995</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A426" s="1">
         <v>43350</v>
       </c>
@@ -10450,7 +10466,7 @@
         <v>550.77</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A427" s="1">
         <v>43357</v>
       </c>
@@ -10461,7 +10477,7 @@
         <v>548.08000000000004</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A428" s="1">
         <v>43364</v>
       </c>
@@ -10472,7 +10488,7 @@
         <v>538.54</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A429" s="1">
         <v>43371</v>
       </c>
@@ -10483,7 +10499,7 @@
         <v>534.37</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A430" s="1">
         <v>43378</v>
       </c>
@@ -10494,7 +10510,7 @@
         <v>532.28</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A431" s="1">
         <v>43385</v>
       </c>
@@ -10505,7 +10521,7 @@
         <v>524.23</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A432" s="1">
         <v>43392</v>
       </c>
@@ -10516,7 +10532,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A433" s="1">
         <v>43399</v>
       </c>
@@ -10527,7 +10543,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A434" s="1">
         <v>43406</v>
       </c>
@@ -10538,7 +10554,7 @@
         <v>503.06</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A435" s="1">
         <v>43413</v>
       </c>
@@ -10549,7 +10565,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A436" s="1">
         <v>43420</v>
       </c>
@@ -10560,7 +10576,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A437" s="1">
         <v>43427</v>
       </c>
@@ -10571,7 +10587,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A438" s="1">
         <v>43434</v>
       </c>
@@ -10582,7 +10598,7 @@
         <v>502.16</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A439" s="1">
         <v>43441</v>
       </c>
@@ -10593,7 +10609,7 @@
         <v>498.58</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A440" s="1">
         <v>43448</v>
       </c>
@@ -10604,7 +10620,7 @@
         <v>495.6</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A441" s="1">
         <v>43455</v>
       </c>
@@ -10615,7 +10631,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A442" s="1">
         <v>43462</v>
       </c>
@@ -10626,7 +10642,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A443" s="1">
         <v>43469</v>
       </c>
@@ -10637,7 +10653,7 @@
         <v>485.46</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A444" s="1">
         <v>43476</v>
       </c>
@@ -10648,7 +10664,7 @@
         <v>478.01</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A445" s="1">
         <v>43483</v>
       </c>
@@ -10659,7 +10675,7 @@
         <v>474.43</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A446" s="1">
         <v>43490</v>
       </c>
@@ -10670,7 +10686,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A447" s="1">
         <v>43497</v>
       </c>
@@ -10681,7 +10697,7 @@
         <v>492.02</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A448" s="1">
         <v>43504</v>
       </c>
@@ -10692,7 +10708,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A449" s="1">
         <v>43511</v>
       </c>
@@ -10703,7 +10719,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A450" s="1">
         <v>43518</v>
       </c>
@@ -10714,7 +10730,7 @@
         <v>502.46</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A451" s="1">
         <v>43525</v>
       </c>
@@ -10725,7 +10741,7 @@
         <v>527.80999999999995</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A452" s="1">
         <v>43532</v>
       </c>
@@ -10736,7 +10752,7 @@
         <v>543.01</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A453" s="1">
         <v>43539</v>
       </c>
@@ -10747,7 +10763,7 @@
         <v>552.55999999999995</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A454" s="1">
         <v>43546</v>
       </c>
@@ -10758,7 +10774,7 @@
         <v>560.61</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A455" s="1">
         <v>43553</v>
       </c>
@@ -10769,7 +10785,7 @@
         <v>565.67999999999995</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A456" s="1">
         <v>43560</v>
       </c>
@@ -10780,7 +10796,7 @@
         <v>576.11</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A457" s="1">
         <v>43567</v>
       </c>
@@ -10791,7 +10807,7 @@
         <v>581.48</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A458" s="1">
         <v>43574</v>
       </c>
@@ -10802,7 +10818,7 @@
         <v>585.05999999999995</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A459" s="1">
         <v>43581</v>
       </c>
@@ -10813,7 +10829,7 @@
         <v>585.66</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A460" s="1">
         <v>43588</v>
       </c>
@@ -10824,7 +10840,7 @@
         <v>586.25</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A461" s="1">
         <v>43595</v>
       </c>
@@ -10835,7 +10851,7 @@
         <v>586.85</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A462" s="1">
         <v>43602</v>
       </c>
@@ -10846,7 +10862,7 @@
         <v>596.09</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A463" s="1">
         <v>43609</v>
       </c>
@@ -10857,7 +10873,7 @@
         <v>599.08000000000004</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A464" s="1">
         <v>43616</v>
       </c>
@@ -10868,7 +10884,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A465" s="1">
         <v>43623</v>
       </c>
@@ -10879,7 +10895,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A466" s="1">
         <v>43630</v>
       </c>
@@ -10890,7 +10906,7 @@
         <v>603.85</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A467" s="1">
         <v>43637</v>
       </c>
@@ -10901,7 +10917,7 @@
         <v>603.54999999999995</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A468" s="1">
         <v>43644</v>
       </c>
@@ -10912,7 +10928,7 @@
         <v>611.6</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A469" s="1">
         <v>43651</v>
       </c>
@@ -10923,7 +10939,7 @@
         <v>618.76</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A470" s="1">
         <v>43658</v>
       </c>
@@ -10934,7 +10950,7 @@
         <v>629.19000000000005</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A471" s="1">
         <v>43665</v>
       </c>
@@ -10945,7 +10961,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A472" s="1">
         <v>43672</v>
       </c>
@@ -10956,7 +10972,7 @@
         <v>666.77</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A473" s="1">
         <v>43679</v>
       </c>
@@ -10967,7 +10983,7 @@
         <v>670.94</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A474" s="1">
         <v>43686</v>
       </c>
@@ -10978,7 +10994,7 @@
         <v>681.97</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A475" s="1">
         <v>43693</v>
       </c>
@@ -10989,7 +11005,7 @@
         <v>690.02</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A476" s="1">
         <v>43700</v>
       </c>
@@ -11000,7 +11016,7 @@
         <v>696.88</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A477" s="1">
         <v>43707</v>
       </c>
@@ -11011,7 +11027,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A478" s="1">
         <v>43714</v>
       </c>
@@ -11022,7 +11038,7 @@
         <v>718.65</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A479" s="1">
         <v>43721</v>
       </c>
@@ -11033,7 +11049,7 @@
         <v>723.42</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A480" s="1">
         <v>43728</v>
       </c>
@@ -11044,7 +11060,7 @@
         <v>724.62</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A481" s="1">
         <v>43735</v>
       </c>
@@ -11055,7 +11071,7 @@
         <v>726.4</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A482" s="1">
         <v>43742</v>
       </c>
@@ -11066,7 +11082,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A483" s="1">
         <v>43749</v>
       </c>
@@ -11077,7 +11093,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A484" s="1">
         <v>43756</v>
       </c>
@@ -11088,7 +11104,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A485" s="1">
         <v>43763</v>
       </c>
@@ -11099,7 +11115,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A486" s="1">
         <v>43770</v>
       </c>
@@ -11110,7 +11126,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A487" s="1">
         <v>43777</v>
       </c>
@@ -11121,7 +11137,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A488" s="1">
         <v>43784</v>
       </c>
@@ -11132,7 +11148,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A489" s="1">
         <v>43791</v>
       </c>
@@ -11143,7 +11159,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A490" s="1">
         <v>43798</v>
       </c>
@@ -11154,7 +11170,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A491" s="1">
         <v>43805</v>
       </c>
@@ -11165,7 +11181,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A492" s="1">
         <v>43812</v>
       </c>
@@ -11176,7 +11192,7 @@
         <v>715.67</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A493" s="1">
         <v>43819</v>
       </c>
@@ -11187,7 +11203,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A494" s="1">
         <v>43826</v>
       </c>
@@ -11198,7 +11214,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A495" s="1">
         <v>43833</v>
       </c>
@@ -11209,7 +11225,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A496" s="1">
         <v>43840</v>
       </c>
@@ -11220,7 +11236,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A497" s="1">
         <v>43847</v>
       </c>
@@ -11231,7 +11247,7 @@
         <v>711.49</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A498" s="1">
         <v>43854</v>
       </c>
@@ -11242,7 +11258,7 @@
         <v>708.51</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A499" s="1">
         <v>43861</v>
       </c>
@@ -11253,7 +11269,7 @@
         <v>705.53</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A500" s="1">
         <v>43868</v>
       </c>
@@ -11264,7 +11280,7 @@
         <v>701.95</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A501" s="1">
         <v>43875</v>
       </c>
@@ -11275,7 +11291,7 @@
         <v>691.52</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A502" s="1">
         <v>43882</v>
       </c>
@@ -11286,7 +11302,7 @@
         <v>680.48</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A503" s="1">
         <v>43889</v>
       </c>
@@ -11297,7 +11313,7 @@
         <v>668.85</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A504" s="1">
         <v>43896</v>
       </c>
@@ -11308,7 +11324,7 @@
         <v>651.26</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A505" s="1">
         <v>43903</v>
       </c>
@@ -11319,7 +11335,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A506" s="1">
         <v>43910</v>
       </c>
@@ -11330,7 +11346,7 @@
         <v>631.58000000000004</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A507" s="1">
         <v>43917</v>
       </c>
@@ -11341,7 +11357,7 @@
         <v>616.07000000000005</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A508" s="1">
         <v>43924</v>
       </c>
@@ -11352,7 +11368,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A509" s="1">
         <v>43931</v>
       </c>
@@ -11363,7 +11379,7 @@
         <v>601.46</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A510" s="1">
         <v>43938</v>
       </c>
@@ -11374,7 +11390,7 @@
         <v>572.83000000000004</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A511" s="1">
         <v>43945</v>
       </c>
@@ -11385,7 +11401,7 @@
         <v>549.87</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A512" s="1">
         <v>43952</v>
       </c>
@@ -11396,7 +11412,7 @@
         <v>528.70000000000005</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A513" s="1">
         <v>43959</v>
       </c>
@@ -11407,7 +11423,7 @@
         <v>507.83</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A514" s="1">
         <v>43966</v>
       </c>
@@ -11418,7 +11434,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A515" s="1">
         <v>43973</v>
       </c>
@@ -11429,7 +11445,7 @@
         <v>479.2</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A516" s="1">
         <v>43980</v>
       </c>
@@ -11440,7 +11456,7 @@
         <v>452.36</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A517" s="1">
         <v>43987</v>
       </c>
@@ -11451,7 +11467,7 @@
         <v>434.17</v>
       </c>
     </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A518" s="1">
         <v>43994</v>
       </c>
@@ -11462,7 +11478,7 @@
         <v>412.11</v>
       </c>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A519" s="1">
         <v>44001</v>
       </c>
@@ -11473,7 +11489,7 @@
         <v>418.96</v>
       </c>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A520" s="1">
         <v>44008</v>
       </c>
@@ -11484,7 +11500,7 @@
         <v>431.79</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A521" s="1">
         <v>44015</v>
       </c>
@@ -11495,7 +11511,7 @@
         <v>439.84</v>
       </c>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A522" s="1">
         <v>44022</v>
       </c>
@@ -11506,7 +11522,7 @@
         <v>444.91</v>
       </c>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A523" s="1">
         <v>44029</v>
       </c>
@@ -11517,7 +11533,7 @@
         <v>463.1</v>
       </c>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A524" s="1">
         <v>44036</v>
       </c>
@@ -11528,7 +11544,7 @@
         <v>484.87</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A525" s="1">
         <v>44043</v>
       </c>
@@ -11539,7 +11555,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A526" s="1">
         <v>44050</v>
       </c>
@@ -11550,7 +11566,7 @@
         <v>556.13</v>
       </c>
     </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A527" s="1">
         <v>44057</v>
       </c>
@@ -11561,7 +11577,7 @@
         <v>596.69000000000005</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A528" s="1">
         <v>44064</v>
       </c>
@@ -11572,7 +11588,7 @@
         <v>627.11</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A529" s="1">
         <v>44071</v>
       </c>
@@ -11583,7 +11599,7 @@
         <v>665.87</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A530" s="1">
         <v>44078</v>
       </c>
@@ -11594,7 +11610,7 @@
         <v>671.83</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A531" s="1">
         <v>44085</v>
       </c>
@@ -11605,7 +11621,7 @@
         <v>678.4</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A532" s="1">
         <v>44092</v>
       </c>
@@ -11616,7 +11632,7 @@
         <v>691.81</v>
       </c>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A533" s="1">
         <v>44099</v>
       </c>
@@ -11627,7 +11643,7 @@
         <v>703.74</v>
       </c>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A534" s="1">
         <v>44106</v>
       </c>
@@ -11638,7 +11654,7 @@
         <v>714.77</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A535" s="1">
         <v>44113</v>
       </c>
@@ -11649,7 +11665,7 @@
         <v>754.14</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A536" s="1">
         <v>44120</v>
       </c>
@@ -11660,7 +11676,7 @@
         <v>783.96</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A537" s="1">
         <v>44127</v>
       </c>
@@ -11671,7 +11687,7 @@
         <v>820.04</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A538" s="1">
         <v>44134</v>
       </c>
@@ -11682,7 +11698,7 @@
         <v>881.17</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A539" s="1">
         <v>44141</v>
       </c>
@@ -11693,7 +11709,7 @@
         <v>910.09</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A540" s="1">
         <v>44148</v>
       </c>
@@ -11704,7 +11720,7 @@
         <v>947.07</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A541" s="1">
         <v>44155</v>
       </c>
@@ -11715,7 +11731,7 @@
         <v>978.68</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A542" s="1">
         <v>44162</v>
       </c>
@@ -11726,7 +11742,7 @@
         <v>1009.39</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A543" s="1">
         <v>44169</v>
       </c>
@@ -11737,7 +11753,7 @@
         <v>1016.25</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A544" s="1">
         <v>44176</v>
       </c>
@@ -11748,7 +11764,7 @@
         <v>1020.13</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A545" s="1">
         <v>44183</v>
       </c>
@@ -11759,7 +11775,7 @@
         <v>1032.06</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A546" s="1">
         <v>44190</v>
       </c>
@@ -11770,7 +11786,7 @@
         <v>1036.23</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A547" s="1">
         <v>44197</v>
       </c>
@@ -11781,7 +11797,7 @@
         <v>1038.02</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A548" s="1">
         <v>44204</v>
       </c>
@@ -11792,7 +11808,7 @@
         <v>1069.6300000000001</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A549" s="1">
         <v>44211</v>
       </c>
@@ -11803,7 +11819,7 @@
         <v>1094.3800000000001</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A550" s="1">
         <v>44218</v>
       </c>
@@ -11814,7 +11830,7 @@
         <v>1112.8699999999999</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A551" s="1">
         <v>44225</v>
       </c>
@@ -11825,7 +11841,7 @@
         <v>1154.32</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A552" s="1">
         <v>44232</v>
       </c>
@@ -11836,7 +11852,7 @@
         <v>1202.03</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A553" s="1">
         <v>44239</v>
       </c>
@@ -11847,7 +11863,7 @@
         <v>1228.27</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A554" s="1">
         <v>44246</v>
       </c>
@@ -11858,7 +11874,7 @@
         <v>1262.26</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A555" s="1">
         <v>44253</v>
       </c>
@@ -11869,7 +11885,7 @@
         <v>1278.3599999999999</v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A556" s="1">
         <v>44260</v>
       </c>
@@ -11880,7 +11896,7 @@
         <v>1323.39</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A557" s="1">
         <v>44267</v>
       </c>
@@ -11891,7 +11907,7 @@
         <v>1387.21</v>
       </c>
     </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A558" s="1">
         <v>44274</v>
       </c>
@@ -11902,7 +11918,7 @@
         <v>1442.97</v>
       </c>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A559" s="1">
         <v>44281</v>
       </c>
@@ -11913,7 +11929,7 @@
         <v>1454.3</v>
       </c>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A560" s="1">
         <v>44288</v>
       </c>
@@ -11924,7 +11940,7 @@
         <v>1492.47</v>
       </c>
     </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A561" s="1">
         <v>44295</v>
       </c>
@@ -11935,7 +11951,7 @@
         <v>1559.56</v>
       </c>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A562" s="1">
         <v>44302</v>
       </c>
@@ -11946,7 +11962,7 @@
         <v>1650.51</v>
       </c>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A563" s="1">
         <v>44309</v>
       </c>
@@ -11957,7 +11973,7 @@
         <v>1680.33</v>
       </c>
     </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A564" s="1">
         <v>44316</v>
       </c>
@@ -11968,7 +11984,7 @@
         <v>1707.47</v>
       </c>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A565" s="1">
         <v>44323</v>
       </c>
@@ -11979,7 +11995,7 @@
         <v>1777.25</v>
       </c>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A566" s="1">
         <v>44330</v>
       </c>
@@ -11990,7 +12006,7 @@
         <v>1837.48</v>
       </c>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A567" s="1">
         <v>44337</v>
       </c>
@@ -12001,7 +12017,7 @@
         <v>1890.86</v>
       </c>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A568" s="1">
         <v>44344</v>
       </c>
@@ -12012,7 +12028,7 @@
         <v>1940.66</v>
       </c>
     </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A569" s="1">
         <v>44351</v>
       </c>
@@ -12023,7 +12039,7 @@
         <v>1986.58</v>
       </c>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A570" s="1">
         <v>44358</v>
       </c>
@@ -12034,7 +12050,7 @@
         <v>2033.69</v>
       </c>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A571" s="1">
         <v>44365</v>
       </c>
@@ -12045,7 +12061,7 @@
         <v>2117.19</v>
       </c>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A572" s="1">
         <v>44372</v>
       </c>
@@ -12056,7 +12072,7 @@
         <v>2212.31</v>
       </c>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A573" s="1">
         <v>44379</v>
       </c>
@@ -12067,7 +12083,7 @@
         <v>2406.44</v>
       </c>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A574" s="1">
         <v>44386</v>
       </c>
@@ -12078,7 +12094,7 @@
         <v>2695.69</v>
       </c>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A575" s="1">
         <v>44393</v>
       </c>
@@ -12089,7 +12105,7 @@
         <v>3023.7</v>
       </c>
     </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A576" s="1">
         <v>44400</v>
       </c>
@@ -12100,7 +12116,7 @@
         <v>3142.98</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A577" s="1">
         <v>44407</v>
       </c>
@@ -12111,7 +12127,7 @@
         <v>3301.03</v>
       </c>
     </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A578" s="1">
         <v>44414</v>
       </c>
@@ -12122,7 +12138,7 @@
         <v>3548.53</v>
       </c>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A579" s="1">
         <v>44421</v>
       </c>
@@ -12133,7 +12149,7 @@
         <v>3554.49</v>
       </c>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A580" s="1">
         <v>44428</v>
       </c>
@@ -12144,7 +12160,7 @@
         <v>3560.46</v>
       </c>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A581" s="1">
         <v>44435</v>
       </c>
@@ -12155,7 +12171,7 @@
         <v>3599.22</v>
       </c>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A582" s="1">
         <v>44442</v>
       </c>
@@ -12166,7 +12182,7 @@
         <v>3694.64</v>
       </c>
     </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A583" s="1">
         <v>44449</v>
       </c>
@@ -12177,7 +12193,7 @@
         <v>3822.87</v>
       </c>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A584" s="1">
         <v>44456</v>
       </c>
@@ -12188,7 +12204,7 @@
         <v>3928.73</v>
       </c>
     </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A585" s="1">
         <v>44463</v>
       </c>
@@ -12199,7 +12215,7 @@
         <v>3980.91</v>
       </c>
     </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A586" s="1">
         <v>44470</v>
       </c>
@@ -12210,7 +12226,7 @@
         <v>3989.86</v>
       </c>
     </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A587" s="1">
         <v>44477</v>
       </c>
@@ -12221,7 +12237,7 @@
         <v>3995.82</v>
       </c>
     </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A588" s="1">
         <v>44484</v>
       </c>
@@ -12232,7 +12248,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A589" s="1">
         <v>44491</v>
       </c>
@@ -12243,7 +12259,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A590" s="1">
         <v>44498</v>
       </c>
@@ -12254,7 +12270,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A591" s="1">
         <v>44505</v>
       </c>
@@ -12265,7 +12281,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A592" s="1">
         <v>44512</v>
       </c>
@@ -12276,7 +12292,7 @@
         <v>3852.69</v>
       </c>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A593" s="1">
         <v>44519</v>
       </c>
@@ -12284,7 +12300,7 @@
         <v>44519</v>
       </c>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A594" s="1">
         <v>44526</v>
       </c>
@@ -12292,7 +12308,7 @@
         <v>44526</v>
       </c>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A595" s="1">
         <v>44533</v>
       </c>
@@ -12300,7 +12316,7 @@
         <v>44533</v>
       </c>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A596" s="1">
         <v>44540</v>
       </c>
@@ -12308,7 +12324,7 @@
         <v>44540</v>
       </c>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A597" s="1">
         <v>44547</v>
       </c>
@@ -12316,7 +12332,7 @@
         <v>44547</v>
       </c>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A598" s="1">
         <v>44554</v>
       </c>
@@ -12324,7 +12340,7 @@
         <v>44554</v>
       </c>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A599" s="1">
         <v>44561</v>
       </c>
@@ -12332,7 +12348,7 @@
         <v>44561</v>
       </c>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A600" s="1">
         <v>44568</v>
       </c>
@@ -12340,7 +12356,7 @@
         <v>44568</v>
       </c>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A601" s="1">
         <v>44575</v>
       </c>
@@ -12348,7 +12364,7 @@
         <v>44575</v>
       </c>
     </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A602" s="1">
         <v>44582</v>
       </c>
@@ -12356,7 +12372,7 @@
         <v>44582</v>
       </c>
     </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A603" s="1">
         <v>44589</v>
       </c>
@@ -12364,7 +12380,7 @@
         <v>44589</v>
       </c>
     </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A604" s="1">
         <v>44596</v>
       </c>
@@ -12372,7 +12388,7 @@
         <v>44596</v>
       </c>
     </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A605" s="1">
         <v>44603</v>
       </c>
@@ -12380,7 +12396,7 @@
         <v>44603</v>
       </c>
     </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A606" s="1">
         <v>44610</v>
       </c>
@@ -12388,7 +12404,7 @@
         <v>44610</v>
       </c>
     </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A607" s="1">
         <v>44617</v>
       </c>
@@ -12396,7 +12412,7 @@
         <v>44617</v>
       </c>
     </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A608" s="1">
         <v>44624</v>
       </c>
@@ -12404,7 +12420,7 @@
         <v>44624</v>
       </c>
     </row>
-    <row r="609" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A609" s="1">
         <v>44631</v>
       </c>
@@ -12412,7 +12428,7 @@
         <v>44631</v>
       </c>
     </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A610" s="1">
         <v>44638</v>
       </c>
@@ -12420,7 +12436,7 @@
         <v>44638</v>
       </c>
     </row>
-    <row r="611" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A611" s="1">
         <v>44645</v>
       </c>
@@ -12428,7 +12444,7 @@
         <v>44645</v>
       </c>
     </row>
-    <row r="612" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A612" s="1">
         <v>44652</v>
       </c>
@@ -12436,7 +12452,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="613" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A613" s="1">
         <v>44659</v>
       </c>
@@ -12444,7 +12460,7 @@
         <v>44659</v>
       </c>
     </row>
-    <row r="614" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A614" s="1">
         <v>44666</v>
       </c>
@@ -12452,7 +12468,7 @@
         <v>44666</v>
       </c>
     </row>
-    <row r="615" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A615" s="1">
         <v>44673</v>
       </c>
@@ -12460,7 +12476,7 @@
         <v>44673</v>
       </c>
     </row>
-    <row r="616" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A616" s="1">
         <v>44680</v>
       </c>
@@ -12468,7 +12484,7 @@
         <v>44680</v>
       </c>
     </row>
-    <row r="617" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A617" s="1">
         <v>44687</v>
       </c>
@@ -12476,7 +12492,7 @@
         <v>44687</v>
       </c>
     </row>
-    <row r="618" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A618" s="1">
         <v>44694</v>
       </c>
@@ -12484,7 +12500,7 @@
         <v>44694</v>
       </c>
     </row>
-    <row r="619" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A619" s="1">
         <v>44701</v>
       </c>
@@ -12492,7 +12508,7 @@
         <v>44701</v>
       </c>
     </row>
-    <row r="620" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A620" s="1">
         <v>44708</v>
       </c>
@@ -12500,7 +12516,7 @@
         <v>44708</v>
       </c>
     </row>
-    <row r="621" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A621" s="1">
         <v>44715</v>
       </c>
@@ -12508,7 +12524,7 @@
         <v>44715</v>
       </c>
     </row>
-    <row r="622" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A622" s="1">
         <v>44722</v>
       </c>
@@ -12516,7 +12532,7 @@
         <v>44722</v>
       </c>
     </row>
-    <row r="623" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A623" s="1">
         <v>44729</v>
       </c>
@@ -12524,7 +12540,7 @@
         <v>44729</v>
       </c>
     </row>
-    <row r="624" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A624" s="1">
         <v>44736</v>
       </c>
@@ -12532,7 +12548,7 @@
         <v>44736</v>
       </c>
     </row>
-    <row r="625" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A625" s="1">
         <v>44743</v>
       </c>
@@ -12540,7 +12556,7 @@
         <v>44743</v>
       </c>
     </row>
-    <row r="626" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A626" s="1">
         <v>44750</v>
       </c>
@@ -12548,7 +12564,7 @@
         <v>44750</v>
       </c>
     </row>
-    <row r="627" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A627" s="1">
         <v>44757</v>
       </c>
@@ -12556,7 +12572,7 @@
         <v>44757</v>
       </c>
     </row>
-    <row r="628" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A628" s="1">
         <v>44764</v>
       </c>
@@ -12564,7 +12580,7 @@
         <v>44764</v>
       </c>
     </row>
-    <row r="629" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A629" s="1">
         <v>44771</v>
       </c>
@@ -12572,7 +12588,7 @@
         <v>44771</v>
       </c>
     </row>
-    <row r="630" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A630" s="1">
         <v>44778</v>
       </c>
@@ -12580,7 +12596,7 @@
         <v>44778</v>
       </c>
     </row>
-    <row r="631" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A631" s="1">
         <v>44785</v>
       </c>
@@ -12588,7 +12604,7 @@
         <v>44785</v>
       </c>
     </row>
-    <row r="632" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A632" s="1">
         <v>44792</v>
       </c>
@@ -12596,7 +12612,7 @@
         <v>44792</v>
       </c>
     </row>
-    <row r="633" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A633" s="1">
         <v>44799</v>
       </c>
@@ -12604,7 +12620,7 @@
         <v>44799</v>
       </c>
     </row>
-    <row r="634" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A634" s="1">
         <v>44806</v>
       </c>
@@ -12612,7 +12628,7 @@
         <v>44806</v>
       </c>
     </row>
-    <row r="635" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A635" s="1">
         <v>44813</v>
       </c>
@@ -12620,7 +12636,7 @@
         <v>44813</v>
       </c>
     </row>
-    <row r="636" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A636" s="1">
         <v>44820</v>
       </c>
@@ -12628,7 +12644,7 @@
         <v>44820</v>
       </c>
     </row>
-    <row r="637" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A637" s="1">
         <v>44827</v>
       </c>
@@ -12636,7 +12652,7 @@
         <v>44827</v>
       </c>
     </row>
-    <row r="638" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A638" s="1">
         <v>44834</v>
       </c>
@@ -12644,7 +12660,7 @@
         <v>44834</v>
       </c>
     </row>
-    <row r="639" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A639" s="1">
         <v>44841</v>
       </c>
@@ -12652,7 +12668,7 @@
         <v>44841</v>
       </c>
     </row>
-    <row r="640" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A640" s="1">
         <v>44848</v>
       </c>
@@ -12660,7 +12676,7 @@
         <v>44848</v>
       </c>
     </row>
-    <row r="641" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A641" s="1">
         <v>44855</v>
       </c>
@@ -12668,7 +12684,7 @@
         <v>44855</v>
       </c>
     </row>
-    <row r="642" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A642" s="1">
         <v>44862</v>
       </c>
@@ -12676,7 +12692,7 @@
         <v>44862</v>
       </c>
     </row>
-    <row r="643" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A643" s="1">
         <v>44869</v>
       </c>
@@ -12684,7 +12700,7 @@
         <v>44869</v>
       </c>
     </row>
-    <row r="644" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A644" s="1">
         <v>44876</v>
       </c>
@@ -12692,7 +12708,7 @@
         <v>44876</v>
       </c>
     </row>
-    <row r="645" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A645" s="1">
         <v>44883</v>
       </c>
@@ -12700,7 +12716,7 @@
         <v>44883</v>
       </c>
     </row>
-    <row r="646" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A646" s="1">
         <v>44890</v>
       </c>
@@ -12708,7 +12724,7 @@
         <v>44890</v>
       </c>
     </row>
-    <row r="647" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A647" s="1">
         <v>44897</v>
       </c>
@@ -12716,7 +12732,7 @@
         <v>44897</v>
       </c>
     </row>
-    <row r="648" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A648" s="1">
         <v>44904</v>
       </c>
@@ -12724,7 +12740,7 @@
         <v>44904</v>
       </c>
     </row>
-    <row r="649" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A649" s="1">
         <v>44911</v>
       </c>
@@ -12732,7 +12748,7 @@
         <v>44911</v>
       </c>
     </row>
-    <row r="650" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A650" s="1">
         <v>44918</v>
       </c>
@@ -12740,7 +12756,7 @@
         <v>44918</v>
       </c>
     </row>
-    <row r="651" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A651" s="1">
         <v>44925</v>
       </c>
@@ -12748,7 +12764,7 @@
         <v>44925</v>
       </c>
     </row>
-    <row r="652" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A652" s="1">
         <v>44932</v>
       </c>
@@ -12756,7 +12772,7 @@
         <v>44932</v>
       </c>
     </row>
-    <row r="653" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A653" s="1">
         <v>44939</v>
       </c>
@@ -12764,7 +12780,7 @@
         <v>44939</v>
       </c>
     </row>
-    <row r="654" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A654" s="1">
         <v>44946</v>
       </c>
@@ -12772,7 +12788,7 @@
         <v>44946</v>
       </c>
     </row>
-    <row r="655" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A655" s="1">
         <v>44953</v>
       </c>
@@ -12780,7 +12796,7 @@
         <v>44953</v>
       </c>
     </row>
-    <row r="656" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A656" s="1">
         <v>44960</v>
       </c>
@@ -12788,7 +12804,7 @@
         <v>44960</v>
       </c>
     </row>
-    <row r="657" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A657" s="1">
         <v>44967</v>
       </c>
@@ -12796,7 +12812,7 @@
         <v>44967</v>
       </c>
     </row>
-    <row r="658" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A658" s="1">
         <v>44974</v>
       </c>
@@ -12804,7 +12820,7 @@
         <v>44974</v>
       </c>
     </row>
-    <row r="659" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A659" s="1">
         <v>44981</v>
       </c>
@@ -12812,7 +12828,7 @@
         <v>44981</v>
       </c>
     </row>
-    <row r="660" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A660" s="1">
         <v>44988</v>
       </c>
@@ -12820,7 +12836,7 @@
         <v>44988</v>
       </c>
     </row>
-    <row r="661" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A661" s="1">
         <v>44995</v>
       </c>
@@ -12828,7 +12844,7 @@
         <v>44995</v>
       </c>
     </row>
-    <row r="662" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A662" s="1">
         <v>45002</v>
       </c>
@@ -12836,7 +12852,7 @@
         <v>45002</v>
       </c>
     </row>
-    <row r="663" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A663" s="1">
         <v>45009</v>
       </c>
@@ -12844,7 +12860,7 @@
         <v>45009</v>
       </c>
     </row>
-    <row r="664" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A664" s="1">
         <v>45016</v>
       </c>
@@ -12852,7 +12868,7 @@
         <v>45016</v>
       </c>
     </row>
-    <row r="665" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A665" s="1">
         <v>45023</v>
       </c>
@@ -12860,7 +12876,7 @@
         <v>45023</v>
       </c>
     </row>
-    <row r="666" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A666" s="1">
         <v>45030</v>
       </c>
@@ -12868,7 +12884,7 @@
         <v>45030</v>
       </c>
     </row>
-    <row r="667" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A667" s="1">
         <v>45037</v>
       </c>
@@ -12876,7 +12892,7 @@
         <v>45037</v>
       </c>
     </row>
-    <row r="668" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A668" s="1">
         <v>45044</v>
       </c>
@@ -12884,7 +12900,7 @@
         <v>45044</v>
       </c>
     </row>
-    <row r="669" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A669" s="1">
         <v>45051</v>
       </c>
@@ -12892,7 +12908,7 @@
         <v>45051</v>
       </c>
     </row>
-    <row r="670" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A670" s="1">
         <v>45058</v>
       </c>
@@ -12900,7 +12916,7 @@
         <v>45058</v>
       </c>
     </row>
-    <row r="671" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A671" s="1">
         <v>45065</v>
       </c>
@@ -12908,7 +12924,7 @@
         <v>45065</v>
       </c>
     </row>
-    <row r="672" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A672" s="1">
         <v>45072</v>
       </c>
@@ -12916,7 +12932,7 @@
         <v>45072</v>
       </c>
     </row>
-    <row r="673" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A673" s="1">
         <v>45079</v>
       </c>
@@ -12924,7 +12940,7 @@
         <v>45079</v>
       </c>
     </row>
-    <row r="674" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A674" s="1">
         <v>45086</v>
       </c>
@@ -12932,7 +12948,7 @@
         <v>45086</v>
       </c>
     </row>
-    <row r="675" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A675" s="1">
         <v>45093</v>
       </c>
@@ -12940,7 +12956,7 @@
         <v>45093</v>
       </c>
     </row>
-    <row r="676" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A676" s="1">
         <v>45100</v>
       </c>
@@ -12948,7 +12964,7 @@
         <v>45100</v>
       </c>
     </row>
-    <row r="677" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A677" s="1">
         <v>45107</v>
       </c>
@@ -12956,7 +12972,7 @@
         <v>45107</v>
       </c>
     </row>
-    <row r="678" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A678" s="1">
         <v>45114</v>
       </c>
@@ -12964,7 +12980,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="679" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A679" s="1">
         <v>45121</v>
       </c>
@@ -12972,7 +12988,7 @@
         <v>45121</v>
       </c>
     </row>
-    <row r="680" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A680" s="1">
         <v>45128</v>
       </c>
@@ -12980,7 +12996,7 @@
         <v>45128</v>
       </c>
     </row>
-    <row r="681" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A681" s="1">
         <v>45135</v>
       </c>
@@ -12988,7 +13004,7 @@
         <v>45135</v>
       </c>
     </row>
-    <row r="682" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A682" s="1">
         <v>45142</v>
       </c>
@@ -12996,7 +13012,7 @@
         <v>45142</v>
       </c>
     </row>
-    <row r="683" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A683" s="1">
         <v>45149</v>
       </c>
@@ -13004,7 +13020,7 @@
         <v>45149</v>
       </c>
     </row>
-    <row r="684" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A684" s="1">
         <v>45156</v>
       </c>
@@ -13012,7 +13028,7 @@
         <v>45156</v>
       </c>
     </row>
-    <row r="685" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A685" s="1">
         <v>45163</v>
       </c>
@@ -13020,7 +13036,7 @@
         <v>45163</v>
       </c>
     </row>
-    <row r="686" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A686" s="1">
         <v>45170</v>
       </c>
@@ -13028,7 +13044,7 @@
         <v>45170</v>
       </c>
     </row>
-    <row r="687" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A687" s="1">
         <v>45177</v>
       </c>
@@ -13036,7 +13052,7 @@
         <v>45177</v>
       </c>
     </row>
-    <row r="688" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A688" s="1">
         <v>45184</v>
       </c>
@@ -13044,7 +13060,7 @@
         <v>45184</v>
       </c>
     </row>
-    <row r="689" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A689" s="1">
         <v>45191</v>
       </c>
@@ -13052,7 +13068,7 @@
         <v>45191</v>
       </c>
     </row>
-    <row r="690" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A690" s="1">
         <v>45198</v>
       </c>
@@ -13060,7 +13076,7 @@
         <v>45198</v>
       </c>
     </row>
-    <row r="691" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A691" s="1">
         <v>45205</v>
       </c>
@@ -13068,7 +13084,7 @@
         <v>45205</v>
       </c>
     </row>
-    <row r="692" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A692" s="1">
         <v>45212</v>
       </c>
@@ -13076,7 +13092,7 @@
         <v>45212</v>
       </c>
     </row>
-    <row r="693" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A693" s="1">
         <v>45219</v>
       </c>
@@ -13084,7 +13100,7 @@
         <v>45219</v>
       </c>
     </row>
-    <row r="694" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A694" s="1">
         <v>45226</v>
       </c>
@@ -13092,7 +13108,7 @@
         <v>45226</v>
       </c>
     </row>
-    <row r="695" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A695" s="1">
         <v>45233</v>
       </c>
@@ -13100,7 +13116,7 @@
         <v>45233</v>
       </c>
     </row>
-    <row r="696" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A696" s="1">
         <v>45240</v>
       </c>
@@ -13108,7 +13124,7 @@
         <v>45240</v>
       </c>
     </row>
-    <row r="697" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A697" s="1">
         <v>45247</v>
       </c>
@@ -13116,7 +13132,7 @@
         <v>45247</v>
       </c>
     </row>
-    <row r="698" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A698" s="1">
         <v>45254</v>
       </c>
@@ -13124,7 +13140,7 @@
         <v>45254</v>
       </c>
     </row>
-    <row r="699" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A699" s="1">
         <v>45261</v>
       </c>
@@ -13132,7 +13148,7 @@
         <v>45261</v>
       </c>
     </row>
-    <row r="700" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A700" s="1">
         <v>45268</v>
       </c>
@@ -13140,7 +13156,7 @@
         <v>45268</v>
       </c>
     </row>
-    <row r="701" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A701" s="1">
         <v>45275</v>
       </c>
@@ -13148,7 +13164,7 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="702" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A702" s="1">
         <v>45282</v>
       </c>
@@ -13156,7 +13172,7 @@
         <v>45282</v>
       </c>
     </row>
-    <row r="703" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A703" s="1">
         <v>45289</v>
       </c>
@@ -13164,7 +13180,7 @@
         <v>45289</v>
       </c>
     </row>
-    <row r="704" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A704" s="1">
         <v>45296</v>
       </c>
@@ -13172,7 +13188,7 @@
         <v>45296</v>
       </c>
     </row>
-    <row r="705" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A705" s="1">
         <v>45303</v>
       </c>
@@ -13180,7 +13196,7 @@
         <v>45303</v>
       </c>
     </row>
-    <row r="706" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A706" s="1">
         <v>45310</v>
       </c>
@@ -13188,7 +13204,7 @@
         <v>45310</v>
       </c>
     </row>
-    <row r="707" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A707" s="1">
         <v>45317</v>
       </c>
@@ -13196,7 +13212,7 @@
         <v>45317</v>
       </c>
     </row>
-    <row r="708" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A708" s="1">
         <v>45324</v>
       </c>
@@ -13204,7 +13220,7 @@
         <v>45324</v>
       </c>
     </row>
-    <row r="709" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A709" s="1">
         <v>45331</v>
       </c>
@@ -13212,7 +13228,7 @@
         <v>45331</v>
       </c>
     </row>
-    <row r="710" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A710" s="1">
         <v>45338</v>
       </c>
@@ -13220,7 +13236,7 @@
         <v>45338</v>
       </c>
     </row>
-    <row r="711" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A711" s="1">
         <v>45345</v>
       </c>
@@ -13228,7 +13244,7 @@
         <v>45345</v>
       </c>
     </row>
-    <row r="712" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A712" s="1">
         <v>45352</v>
       </c>
@@ -13236,7 +13252,7 @@
         <v>45352</v>
       </c>
     </row>
-    <row r="713" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A713" s="1">
         <v>45359</v>
       </c>
@@ -13244,7 +13260,7 @@
         <v>45359</v>
       </c>
     </row>
-    <row r="714" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A714" s="1">
         <v>45366</v>
       </c>
@@ -13252,7 +13268,7 @@
         <v>45366</v>
       </c>
     </row>
-    <row r="715" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A715" s="1">
         <v>45373</v>
       </c>
@@ -13260,7 +13276,7 @@
         <v>45373</v>
       </c>
     </row>
-    <row r="716" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A716" s="1">
         <v>45380</v>
       </c>
@@ -13268,7 +13284,7 @@
         <v>45380</v>
       </c>
     </row>
-    <row r="717" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A717" s="1">
         <v>45387</v>
       </c>
@@ -13276,7 +13292,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="718" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A718" s="1">
         <v>45394</v>
       </c>
@@ -13284,7 +13300,7 @@
         <v>45394</v>
       </c>
     </row>
-    <row r="719" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A719" s="1">
         <v>45401</v>
       </c>
@@ -13292,7 +13308,7 @@
         <v>45401</v>
       </c>
     </row>
-    <row r="720" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A720" s="1">
         <v>45408</v>
       </c>
@@ -13300,7 +13316,7 @@
         <v>45408</v>
       </c>
     </row>
-    <row r="721" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A721" s="1">
         <v>45415</v>
       </c>
@@ -13308,7 +13324,7 @@
         <v>45415</v>
       </c>
     </row>
-    <row r="722" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A722" s="1">
         <v>45422</v>
       </c>
@@ -13316,7 +13332,7 @@
         <v>45422</v>
       </c>
     </row>
-    <row r="723" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A723" s="1">
         <v>45429</v>
       </c>
@@ -13324,7 +13340,7 @@
         <v>45429</v>
       </c>
     </row>
-    <row r="724" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A724" s="1">
         <v>45436</v>
       </c>
@@ -13332,7 +13348,7 @@
         <v>45436</v>
       </c>
     </row>
-    <row r="725" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A725" s="1">
         <v>45443</v>
       </c>
@@ -13340,7 +13356,7 @@
         <v>45443</v>
       </c>
     </row>
-    <row r="726" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A726" s="1">
         <v>45450</v>
       </c>
@@ -13348,7 +13364,7 @@
         <v>45450</v>
       </c>
     </row>
-    <row r="727" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A727" s="1">
         <v>45457</v>
       </c>
@@ -13356,15 +13372,18 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="728" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A728" s="1">
         <v>45464</v>
       </c>
       <c r="B728" s="1">
         <v>45464</v>
       </c>
-    </row>
-    <row r="729" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="E728" s="13">
+        <v>1627.4</v>
+      </c>
+    </row>
+    <row r="729" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A729" s="1">
         <v>45471</v>
       </c>
@@ -13372,7 +13391,7 @@
         <v>45471</v>
       </c>
     </row>
-    <row r="730" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A730" s="1">
         <v>45478</v>
       </c>
@@ -13380,7 +13399,7 @@
         <v>45478</v>
       </c>
     </row>
-    <row r="731" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A731" s="1">
         <v>45485</v>
       </c>
@@ -13388,7 +13407,7 @@
         <v>45485</v>
       </c>
     </row>
-    <row r="732" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A732" s="1">
         <v>45492</v>
       </c>
@@ -13396,7 +13415,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="733" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A733" s="1">
         <v>45499</v>
       </c>
@@ -13404,7 +13423,7 @@
         <v>45499</v>
       </c>
     </row>
-    <row r="734" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A734" s="1">
         <v>45506</v>
       </c>
@@ -13412,7 +13431,7 @@
         <v>45506</v>
       </c>
     </row>
-    <row r="735" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A735" s="1">
         <v>45513</v>
       </c>
@@ -13420,7 +13439,7 @@
         <v>45513</v>
       </c>
     </row>
-    <row r="736" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A736" s="1">
         <v>45520</v>
       </c>
@@ -13428,7 +13447,7 @@
         <v>45520</v>
       </c>
     </row>
-    <row r="737" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A737" s="1">
         <v>45527</v>
       </c>
@@ -13436,7 +13455,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="738" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A738" s="1">
         <v>45534</v>
       </c>
@@ -13444,7 +13463,7 @@
         <v>45534</v>
       </c>
     </row>
-    <row r="739" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A739" s="1">
         <v>45541</v>
       </c>
@@ -13452,7 +13471,7 @@
         <v>45541</v>
       </c>
     </row>
-    <row r="740" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A740" s="1">
         <v>45548</v>
       </c>
@@ -13460,7 +13479,7 @@
         <v>45548</v>
       </c>
     </row>
-    <row r="741" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A741" s="1">
         <v>45555</v>
       </c>
@@ -13468,7 +13487,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="742" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A742" s="1">
         <v>45562</v>
       </c>
@@ -13476,7 +13495,7 @@
         <v>45562</v>
       </c>
     </row>
-    <row r="743" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A743" s="1">
         <v>45569</v>
       </c>
@@ -13484,7 +13503,7 @@
         <v>45569</v>
       </c>
     </row>
-    <row r="744" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A744" s="1">
         <v>45576</v>
       </c>
@@ -13492,7 +13511,7 @@
         <v>45576</v>
       </c>
     </row>
-    <row r="745" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A745" s="1">
         <v>45583</v>
       </c>
@@ -13500,7 +13519,7 @@
         <v>45583</v>
       </c>
     </row>
-    <row r="746" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A746" s="1">
         <v>45590</v>
       </c>
@@ -13508,7 +13527,7 @@
         <v>45590</v>
       </c>
     </row>
-    <row r="747" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A747" s="1">
         <v>45597</v>
       </c>
@@ -13516,7 +13535,7 @@
         <v>45597</v>
       </c>
     </row>
-    <row r="748" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A748" s="1">
         <v>45604</v>
       </c>
@@ -13524,7 +13543,7 @@
         <v>45604</v>
       </c>
     </row>
-    <row r="749" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A749" s="1">
         <v>45611</v>
       </c>
@@ -13532,7 +13551,7 @@
         <v>45611</v>
       </c>
     </row>
-    <row r="750" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A750" s="1">
         <v>45618</v>
       </c>
@@ -13540,7 +13559,7 @@
         <v>45618</v>
       </c>
     </row>
-    <row r="751" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A751" s="1">
         <v>45625</v>
       </c>
@@ -13548,7 +13567,7 @@
         <v>45625</v>
       </c>
     </row>
-    <row r="752" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A752" s="1">
         <v>45632</v>
       </c>
@@ -13556,7 +13575,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="753" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A753" s="1">
         <v>45639</v>
       </c>
@@ -13564,7 +13583,7 @@
         <v>45639</v>
       </c>
     </row>
-    <row r="754" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A754" s="1">
         <v>45646</v>
       </c>
@@ -13572,7 +13591,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="755" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A755" s="1">
         <v>45653</v>
       </c>
@@ -13580,7 +13599,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="756" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A756" s="1">
         <v>45660</v>
       </c>
@@ -13588,7 +13607,7 @@
         <v>45660</v>
       </c>
     </row>
-    <row r="757" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A757" s="1">
         <v>45667</v>
       </c>
@@ -13596,7 +13615,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="758" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A758" s="1">
         <v>45674</v>
       </c>
@@ -13604,7 +13623,7 @@
         <v>45674</v>
       </c>
     </row>
-    <row r="759" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A759" s="1">
         <v>45681</v>
       </c>
@@ -13612,7 +13631,7 @@
         <v>45681</v>
       </c>
     </row>
-    <row r="760" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A760" s="1">
         <v>45688</v>
       </c>
@@ -13620,7 +13639,7 @@
         <v>45688</v>
       </c>
     </row>
-    <row r="761" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A761" s="1">
         <v>45695</v>
       </c>
@@ -13628,7 +13647,7 @@
         <v>45695</v>
       </c>
     </row>
-    <row r="762" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A762" s="1">
         <v>45702</v>
       </c>
@@ -13636,7 +13655,7 @@
         <v>45702</v>
       </c>
     </row>
-    <row r="763" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A763" s="1">
         <v>45709</v>
       </c>
@@ -13644,7 +13663,7 @@
         <v>45709</v>
       </c>
     </row>
-    <row r="764" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A764" s="1">
         <v>45716</v>
       </c>
@@ -13652,7 +13671,7 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="765" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A765" s="1">
         <v>45723</v>
       </c>
@@ -13660,7 +13679,7 @@
         <v>45723</v>
       </c>
     </row>
-    <row r="766" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A766" s="1">
         <v>45730</v>
       </c>
@@ -13668,7 +13687,7 @@
         <v>45730</v>
       </c>
     </row>
-    <row r="767" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A767" s="1">
         <v>45737</v>
       </c>
@@ -13676,7 +13695,7 @@
         <v>45737</v>
       </c>
     </row>
-    <row r="768" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A768" s="1">
         <v>45744</v>
       </c>
@@ -13684,7 +13703,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="769" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A769" s="1">
         <v>45751</v>
       </c>
@@ -13692,7 +13711,7 @@
         <v>45751</v>
       </c>
     </row>
-    <row r="770" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A770" s="1">
         <v>45758</v>
       </c>
@@ -13700,7 +13719,7 @@
         <v>45758</v>
       </c>
     </row>
-    <row r="771" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A771" s="1">
         <v>45765</v>
       </c>
@@ -13708,7 +13727,7 @@
         <v>45765</v>
       </c>
     </row>
-    <row r="772" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A772" s="1">
         <v>45772</v>
       </c>
@@ -13716,7 +13735,7 @@
         <v>45772</v>
       </c>
     </row>
-    <row r="773" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A773" s="1">
         <v>45779</v>
       </c>
@@ -13724,7 +13743,7 @@
         <v>45779</v>
       </c>
     </row>
-    <row r="774" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A774" s="1">
         <v>45786</v>
       </c>
@@ -13732,7 +13751,7 @@
         <v>45786</v>
       </c>
     </row>
-    <row r="775" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A775" s="1">
         <v>45793</v>
       </c>
@@ -13740,7 +13759,7 @@
         <v>45793</v>
       </c>
     </row>
-    <row r="776" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A776" s="1">
         <v>45800</v>
       </c>
@@ -13748,7 +13767,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="777" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A777" s="1">
         <v>45807</v>
       </c>
@@ -13756,7 +13775,7 @@
         <v>45807</v>
       </c>
     </row>
-    <row r="778" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A778" s="1">
         <v>45814</v>
       </c>
@@ -13764,7 +13783,7 @@
         <v>45814</v>
       </c>
     </row>
-    <row r="779" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A779" s="1">
         <v>45821</v>
       </c>
@@ -13772,23 +13791,29 @@
         <v>45821</v>
       </c>
     </row>
-    <row r="780" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A780" s="1">
         <v>45828</v>
       </c>
       <c r="B780" s="1">
         <v>45828</v>
       </c>
-    </row>
-    <row r="781" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="E780" s="13">
+        <v>2158.19</v>
+      </c>
+    </row>
+    <row r="781" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A781" s="1">
         <v>45835</v>
       </c>
       <c r="B781" s="1">
         <v>45835</v>
       </c>
-    </row>
-    <row r="782" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="E781" s="13">
+        <v>2158.19</v>
+      </c>
+    </row>
+    <row r="782" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A782" s="1">
         <v>45842</v>
       </c>
@@ -13796,7 +13821,7 @@
         <v>45842</v>
       </c>
     </row>
-    <row r="783" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A783" s="1">
         <v>45849</v>
       </c>
@@ -13804,7 +13829,7 @@
         <v>45849</v>
       </c>
     </row>
-    <row r="784" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A784" s="1">
         <v>45856</v>
       </c>
@@ -13812,7 +13837,7 @@
         <v>45856</v>
       </c>
     </row>
-    <row r="785" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A785" s="1">
         <v>45863</v>
       </c>
@@ -13820,7 +13845,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="786" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A786" s="1">
         <v>45870</v>
       </c>
@@ -13828,7 +13853,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="787" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A787" s="1">
         <v>45877</v>
       </c>
@@ -13836,7 +13861,7 @@
         <v>45877</v>
       </c>
     </row>
-    <row r="788" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A788" s="1">
         <v>45884</v>
       </c>
@@ -13844,7 +13869,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="789" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A789" s="1">
         <v>45891</v>
       </c>
@@ -13852,7 +13877,7 @@
         <v>45891</v>
       </c>
     </row>
-    <row r="790" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A790" s="1">
         <v>45898</v>
       </c>
@@ -13860,7 +13885,7 @@
         <v>45898</v>
       </c>
     </row>
-    <row r="791" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A791" s="1">
         <v>45905</v>
       </c>
@@ -13868,7 +13893,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="792" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A792" s="1">
         <v>45912</v>
       </c>
@@ -13876,7 +13901,7 @@
         <v>45912</v>
       </c>
     </row>
-    <row r="793" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A793" s="1">
         <v>45919</v>
       </c>
@@ -13884,7 +13909,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="794" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A794" s="1">
         <v>45926</v>
       </c>
@@ -13892,7 +13917,7 @@
         <v>45926</v>
       </c>
     </row>
-    <row r="795" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A795" s="1">
         <v>45933</v>
       </c>
@@ -13900,7 +13925,7 @@
         <v>45933</v>
       </c>
     </row>
-    <row r="796" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A796" s="1">
         <v>45940</v>
       </c>
@@ -13908,7 +13933,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="797" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A797" s="1">
         <v>45947</v>
       </c>
@@ -13916,7 +13941,7 @@
         <v>45947</v>
       </c>
     </row>
-    <row r="798" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A798" s="1">
         <v>45954</v>
       </c>
@@ -13924,7 +13949,7 @@
         <v>45954</v>
       </c>
     </row>
-    <row r="799" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A799" s="1">
         <v>45961</v>
       </c>
@@ -13932,7 +13957,7 @@
         <v>45961</v>
       </c>
     </row>
-    <row r="800" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A800" s="1">
         <v>45968</v>
       </c>
@@ -13940,7 +13965,7 @@
         <v>45968</v>
       </c>
     </row>
-    <row r="801" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A801" s="1">
         <v>45975</v>
       </c>
@@ -13948,7 +13973,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="802" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A802" s="1">
         <v>45982</v>
       </c>
@@ -13956,7 +13981,7 @@
         <v>45982</v>
       </c>
     </row>
-    <row r="803" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A803" s="1">
         <v>45989</v>
       </c>
@@ -13964,7 +13989,7 @@
         <v>45989</v>
       </c>
     </row>
-    <row r="804" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A804" s="1">
         <v>45996</v>
       </c>
@@ -13972,7 +13997,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="805" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A805" s="1">
         <v>46003</v>
       </c>
@@ -13980,7 +14005,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="806" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A806" s="1">
         <v>46010</v>
       </c>
@@ -13988,7 +14013,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="807" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A807" s="1">
         <v>46017</v>
       </c>
@@ -14011,7 +14036,7 @@
       <c r="N807" s="10"/>
       <c r="O807" s="10"/>
     </row>
-    <row r="808" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A808" s="1">
         <v>46024</v>
       </c>
@@ -14021,7 +14046,7 @@
       <c r="C808" s="2"/>
       <c r="D808" s="2"/>
       <c r="E808" s="15">
-        <v>2182</v>
+        <v>2182.0500000000002</v>
       </c>
       <c r="F808" s="3">
         <v>10250</v>
@@ -14054,7 +14079,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="809" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A809" s="1">
         <v>46031</v>
       </c>
@@ -14064,7 +14089,7 @@
       <c r="C809" s="2"/>
       <c r="D809" s="2"/>
       <c r="E809" s="15">
-        <v>2182</v>
+        <v>2182.0500000000002</v>
       </c>
       <c r="F809" s="3">
         <v>10250</v>
@@ -14097,7 +14122,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="810" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A810" s="1">
         <v>46038</v>
       </c>
@@ -14107,7 +14132,7 @@
       <c r="C810" s="2"/>
       <c r="D810" s="2"/>
       <c r="E810" s="15">
-        <v>2182</v>
+        <v>2182.0500000000002</v>
       </c>
       <c r="F810" s="3">
         <v>10250</v>
@@ -14140,7 +14165,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="811" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A811" s="1">
         <v>46045</v>
       </c>
@@ -14183,7 +14208,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="812" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A812" s="1">
         <v>46052</v>
       </c>
@@ -14226,7 +14251,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="813" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A813" s="1">
         <v>46059</v>
       </c>
@@ -14269,7 +14294,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="814" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A814" s="1">
         <v>46066</v>
       </c>
@@ -14312,7 +14337,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="815" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A815" s="1">
         <v>46073</v>
       </c>
@@ -14355,7 +14380,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="816" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A816" s="1">
         <v>46080</v>
       </c>
@@ -14398,7 +14423,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="817" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A817" s="1">
         <v>46087</v>
       </c>
@@ -14441,7 +14466,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="818" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A818" s="1">
         <v>46094</v>
       </c>
@@ -14484,7 +14509,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="819" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A819" s="1">
         <v>46101</v>
       </c>
@@ -14527,7 +14552,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="820" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A820" s="1">
         <v>46108</v>
       </c>
@@ -14570,7 +14595,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="821" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A821" s="1">
         <v>46115</v>
       </c>
@@ -14613,7 +14638,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="822" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A822" s="1">
         <v>46122</v>
       </c>
@@ -14636,7 +14661,7 @@
       <c r="N822" s="3"/>
       <c r="O822" s="3"/>
     </row>
-    <row r="823" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A823" s="1">
         <v>46129</v>
       </c>
@@ -14659,7 +14684,7 @@
       <c r="N823" s="3"/>
       <c r="O823" s="3"/>
     </row>
-    <row r="824" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A824" s="1">
         <v>46136</v>
       </c>
@@ -14682,7 +14707,7 @@
       <c r="N824" s="3"/>
       <c r="O824" s="3"/>
     </row>
-    <row r="825" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A825" s="1">
         <v>46143</v>
       </c>
@@ -14725,7 +14750,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="826" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A826" s="1">
         <v>46150</v>
       </c>
@@ -14768,7 +14793,7 @@
         <v>76000</v>
       </c>
     </row>
-    <row r="827" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A827" s="1">
         <v>46157</v>
       </c>
@@ -14811,7 +14836,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="828" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A828" s="1">
         <v>46164</v>
       </c>
@@ -14854,7 +14879,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="829" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A829" s="1">
         <v>46171</v>
       </c>
@@ -14897,7 +14922,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="830" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A830" s="1">
         <v>46178</v>
       </c>
@@ -14935,6 +14960,47 @@
         <v>71000</v>
       </c>
       <c r="O830" s="4">
+        <v>78000</v>
+      </c>
+    </row>
+    <row r="831" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A831" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B831" s="1">
+        <v>46185</v>
+      </c>
+      <c r="E831" s="13">
+        <v>2323.69</v>
+      </c>
+      <c r="F831" s="4">
+        <v>11250</v>
+      </c>
+      <c r="G831" s="4">
+        <v>17750</v>
+      </c>
+      <c r="H831" s="4">
+        <v>29000</v>
+      </c>
+      <c r="I831" s="4">
+        <v>33500</v>
+      </c>
+      <c r="J831" s="4">
+        <v>38000</v>
+      </c>
+      <c r="K831" s="4">
+        <v>40000</v>
+      </c>
+      <c r="L831" s="4">
+        <v>46000</v>
+      </c>
+      <c r="M831" s="4">
+        <v>57000</v>
+      </c>
+      <c r="N831" s="4">
+        <v>71000</v>
+      </c>
+      <c r="O831" s="4">
         <v>78000</v>
       </c>
     </row>
@@ -14946,7 +15012,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02768588-2FF0-42C1-8A18-87D4CAFE9D17}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -14956,12 +15022,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A6084AF-43C5-4F58-881A-79CFC1D1F25A}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" s="8" t="s">
         <v>15</v>
       </c>
@@ -14969,7 +15035,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" s="8" t="s">
         <v>17</v>
       </c>

--- a/data/freight/HARPEX.xlsx
+++ b/data/freight/HARPEX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/freight/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F501396-EA6A-2847-B447-BE3968F1B2A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79912C2-376B-407D-AA79-1D81338721C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25700" yWindow="3980" windowWidth="23260" windowHeight="14860" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
   <sheets>
     <sheet name="HARPEX" sheetId="1" r:id="rId1"/>
@@ -199,9 +199,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -219,7 +219,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2758,6 +2758,9 @@
                 <c:pt idx="829">
                   <c:v>46185</c:v>
                 </c:pt>
+                <c:pt idx="830">
+                  <c:v>46192</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4623,6 +4626,9 @@
                 </c:pt>
                 <c:pt idx="829">
                   <c:v>2323.69</c:v>
+                </c:pt>
+                <c:pt idx="830">
+                  <c:v>2326.67</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5436,9 +5442,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5476,7 +5482,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5582,7 +5588,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5724,7 +5730,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5732,18 +5738,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
-  <dimension ref="A1:P831"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:P832"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" style="16" customWidth="1"/>
     <col min="4" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="15" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="15" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -5791,7 +5797,7 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>40383</v>
       </c>
@@ -5802,7 +5808,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>40390</v>
       </c>
@@ -5813,7 +5819,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>40397</v>
       </c>
@@ -5824,7 +5830,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>40404</v>
       </c>
@@ -5835,7 +5841,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>40411</v>
       </c>
@@ -5846,7 +5852,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>40418</v>
       </c>
@@ -5857,7 +5863,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>40425</v>
       </c>
@@ -5868,7 +5874,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>40432</v>
       </c>
@@ -5879,7 +5885,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>40439</v>
       </c>
@@ -5890,7 +5896,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>40446</v>
       </c>
@@ -5901,7 +5907,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>40453</v>
       </c>
@@ -5912,7 +5918,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>40460</v>
       </c>
@@ -5923,7 +5929,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>40467</v>
       </c>
@@ -5934,7 +5940,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>40474</v>
       </c>
@@ -5945,7 +5951,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>40481</v>
       </c>
@@ -5956,7 +5962,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>40488</v>
       </c>
@@ -5967,7 +5973,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>40495</v>
       </c>
@@ -5978,7 +5984,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>40502</v>
       </c>
@@ -5989,7 +5995,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>40509</v>
       </c>
@@ -6000,7 +6006,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>40516</v>
       </c>
@@ -6011,7 +6017,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>40523</v>
       </c>
@@ -6022,7 +6028,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>40530</v>
       </c>
@@ -6033,7 +6039,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>40537</v>
       </c>
@@ -6044,7 +6050,7 @@
         <v>679.37</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>40544</v>
       </c>
@@ -6055,7 +6061,7 @@
         <v>696.35</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>40551</v>
       </c>
@@ -6066,7 +6072,7 @@
         <v>706.3</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>40558</v>
       </c>
@@ -6077,7 +6083,7 @@
         <v>719.55</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>40565</v>
       </c>
@@ -6088,7 +6094,7 @@
         <v>747.31</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>40572</v>
       </c>
@@ -6099,7 +6105,7 @@
         <v>764.29</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>40579</v>
       </c>
@@ -6110,7 +6116,7 @@
         <v>782.1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>40586</v>
       </c>
@@ -6121,7 +6127,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>40593</v>
       </c>
@@ -6132,7 +6138,7 @@
         <v>849.63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>40600</v>
       </c>
@@ -6143,7 +6149,7 @@
         <v>861.23</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>40607</v>
       </c>
@@ -6154,7 +6160,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>40614</v>
       </c>
@@ -6165,7 +6171,7 @@
         <v>879.04</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>40621</v>
       </c>
@@ -6176,7 +6182,7 @@
         <v>882.35</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>40628</v>
       </c>
@@ -6187,7 +6193,7 @@
         <v>900.99</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>40635</v>
       </c>
@@ -6198,7 +6204,7 @@
         <v>892.29</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>40642</v>
       </c>
@@ -6209,7 +6215,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>40649</v>
       </c>
@@ -6220,7 +6226,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>40656</v>
       </c>
@@ -6231,7 +6237,7 @@
         <v>879.87</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40663</v>
       </c>
@@ -6242,7 +6248,7 @@
         <v>875.72</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>40670</v>
       </c>
@@ -6253,7 +6259,7 @@
         <v>874.48</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>40677</v>
       </c>
@@ -6264,7 +6270,7 @@
         <v>877.38</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>40684</v>
       </c>
@@ -6275,7 +6281,7 @@
         <v>876.14</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>40691</v>
       </c>
@@ -6286,7 +6292,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>40698</v>
       </c>
@@ -6297,7 +6303,7 @@
         <v>865.37</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>40705</v>
       </c>
@@ -6308,7 +6314,7 @@
         <v>856.67</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>40712</v>
       </c>
@@ -6319,7 +6325,7 @@
         <v>847.14</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>40719</v>
       </c>
@@ -6330,7 +6336,7 @@
         <v>831.4</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>40726</v>
       </c>
@@ -6341,7 +6347,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>40733</v>
       </c>
@@ -6352,7 +6358,7 @@
         <v>808.62</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>40740</v>
       </c>
@@ -6363,7 +6369,7 @@
         <v>775.06</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>40747</v>
       </c>
@@ -6374,7 +6380,7 @@
         <v>741.51</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>40754</v>
       </c>
@@ -6385,7 +6391,7 @@
         <v>719.97</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>40761</v>
       </c>
@@ -6396,7 +6402,7 @@
         <v>709.2</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>40768</v>
       </c>
@@ -6407,7 +6413,7 @@
         <v>671.91</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>40775</v>
       </c>
@@ -6418,7 +6424,7 @@
         <v>666.11</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>40782</v>
       </c>
@@ -6429,7 +6435,7 @@
         <v>657.83</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>40789</v>
       </c>
@@ -6440,7 +6446,7 @@
         <v>630.9</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>40796</v>
       </c>
@@ -6451,7 +6457,7 @@
         <v>621.38</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>40803</v>
       </c>
@@ -6462,7 +6468,7 @@
         <v>616.4</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>40810</v>
       </c>
@@ -6473,7 +6479,7 @@
         <v>555.1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>40817</v>
       </c>
@@ -6484,7 +6490,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>40824</v>
       </c>
@@ -6495,7 +6501,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>40831</v>
       </c>
@@ -6506,7 +6512,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>40838</v>
       </c>
@@ -6517,7 +6523,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>40845</v>
       </c>
@@ -6528,7 +6534,7 @@
         <v>445.32</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>40852</v>
       </c>
@@ -6539,7 +6545,7 @@
         <v>438.28</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>40859</v>
       </c>
@@ -6550,7 +6556,7 @@
         <v>437.45</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>40866</v>
       </c>
@@ -6561,7 +6567,7 @@
         <v>420.05</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>40873</v>
       </c>
@@ -6572,7 +6578,7 @@
         <v>417.98</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>40880</v>
       </c>
@@ -6583,7 +6589,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>40887</v>
       </c>
@@ -6594,7 +6600,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>40894</v>
       </c>
@@ -6605,7 +6611,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>40901</v>
       </c>
@@ -6616,7 +6622,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>40908</v>
       </c>
@@ -6627,7 +6633,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>40915</v>
       </c>
@@ -6638,7 +6644,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>40922</v>
       </c>
@@ -6649,7 +6655,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>40929</v>
       </c>
@@ -6660,7 +6666,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>40936</v>
       </c>
@@ -6671,7 +6677,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>40942</v>
       </c>
@@ -6682,7 +6688,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>40943</v>
       </c>
@@ -6693,7 +6699,7 @@
         <v>389.81</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>40950</v>
       </c>
@@ -6704,7 +6710,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>40957</v>
       </c>
@@ -6715,7 +6721,7 @@
         <v>375.31</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>40964</v>
       </c>
@@ -6726,7 +6732,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>40978</v>
       </c>
@@ -6737,7 +6743,7 @@
         <v>384.84</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>40985</v>
       </c>
@@ -6748,7 +6754,7 @@
         <v>393.12</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>40992</v>
       </c>
@@ -6759,7 +6765,7 @@
         <v>396.02</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>40999</v>
       </c>
@@ -6770,7 +6776,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>41006</v>
       </c>
@@ -6781,7 +6787,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>41013</v>
       </c>
@@ -6792,7 +6798,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>41020</v>
       </c>
@@ -6803,7 +6809,7 @@
         <v>416.32</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>41027</v>
       </c>
@@ -6814,7 +6820,7 @@
         <v>428.33</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>41034</v>
       </c>
@@ -6825,7 +6831,7 @@
         <v>440.35</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>41041</v>
       </c>
@@ -6836,7 +6842,7 @@
         <v>444.9</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>41048</v>
       </c>
@@ -6847,7 +6853,7 @@
         <v>457.33</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>41055</v>
       </c>
@@ -6858,7 +6864,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>41062</v>
       </c>
@@ -6869,7 +6875,7 @@
         <v>456.92</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>41069</v>
       </c>
@@ -6880,7 +6886,7 @@
         <v>451.12</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>41076</v>
       </c>
@@ -6891,7 +6897,7 @@
         <v>446.98</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>41083</v>
       </c>
@@ -6902,7 +6908,7 @@
         <v>437.86</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>41090</v>
       </c>
@@ -6913,7 +6919,7 @@
         <v>434.96</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>41097</v>
       </c>
@@ -6924,7 +6930,7 @@
         <v>430.41</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>41104</v>
       </c>
@@ -6935,7 +6941,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>41111</v>
       </c>
@@ -6946,7 +6952,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>41118</v>
       </c>
@@ -6957,7 +6963,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>41125</v>
       </c>
@@ -6968,7 +6974,7 @@
         <v>399.75</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>41132</v>
       </c>
@@ -6979,7 +6985,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>41139</v>
       </c>
@@ -6990,7 +6996,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>41146</v>
       </c>
@@ -7001,7 +7007,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>41153</v>
       </c>
@@ -7012,7 +7018,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>41160</v>
       </c>
@@ -7023,7 +7029,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>41167</v>
       </c>
@@ -7034,7 +7040,7 @@
         <v>386.08</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>41174</v>
       </c>
@@ -7045,7 +7051,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>41181</v>
       </c>
@@ -7056,7 +7062,7 @@
         <v>377.8</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>41188</v>
       </c>
@@ -7067,7 +7073,7 @@
         <v>373.65</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>41195</v>
       </c>
@@ -7078,7 +7084,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>41202</v>
       </c>
@@ -7089,7 +7095,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>41209</v>
       </c>
@@ -7100,7 +7106,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>41216</v>
       </c>
@@ -7111,7 +7117,7 @@
         <v>367.44</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>41223</v>
       </c>
@@ -7122,7 +7128,7 @@
         <v>366.61</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>41230</v>
       </c>
@@ -7133,7 +7139,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>41237</v>
       </c>
@@ -7144,7 +7150,7 @@
         <v>362.88</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>41244</v>
       </c>
@@ -7155,7 +7161,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>41251</v>
       </c>
@@ -7166,7 +7172,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>41258</v>
       </c>
@@ -7177,7 +7183,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>41265</v>
       </c>
@@ -7188,7 +7194,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>41272</v>
       </c>
@@ -7199,7 +7205,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>41279</v>
       </c>
@@ -7210,7 +7216,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>41286</v>
       </c>
@@ -7221,7 +7227,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>41293</v>
       </c>
@@ -7232,7 +7238,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>41300</v>
       </c>
@@ -7243,7 +7249,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>41307</v>
       </c>
@@ -7254,7 +7260,7 @@
         <v>366.2</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>41314</v>
       </c>
@@ -7265,7 +7271,7 @@
         <v>369.93</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>41321</v>
       </c>
@@ -7276,7 +7282,7 @@
         <v>372.41</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>41328</v>
       </c>
@@ -7287,7 +7293,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>41335</v>
       </c>
@@ -7298,7 +7304,7 @@
         <v>376.97</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>41342</v>
       </c>
@@ -7309,7 +7315,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>41349</v>
       </c>
@@ -7320,7 +7326,7 @@
         <v>382.35</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>41356</v>
       </c>
@@ -7331,7 +7337,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>41363</v>
       </c>
@@ -7342,7 +7348,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>41370</v>
       </c>
@@ -7353,7 +7359,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>41377</v>
       </c>
@@ -7364,7 +7370,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>41384</v>
       </c>
@@ -7375,7 +7381,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>41391</v>
       </c>
@@ -7386,7 +7392,7 @@
         <v>395.61</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>41398</v>
       </c>
@@ -7397,7 +7403,7 @@
         <v>396.85</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>41405</v>
       </c>
@@ -7408,7 +7414,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>41412</v>
       </c>
@@ -7419,7 +7425,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>41419</v>
       </c>
@@ -7430,7 +7436,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>41426</v>
       </c>
@@ -7441,7 +7447,7 @@
         <v>401.41</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>41433</v>
       </c>
@@ -7452,7 +7458,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>41440</v>
       </c>
@@ -7463,7 +7469,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>41447</v>
       </c>
@@ -7474,7 +7480,7 @@
         <v>400.58</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>41454</v>
       </c>
@@ -7485,7 +7491,7 @@
         <v>401.82</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>41461</v>
       </c>
@@ -7496,7 +7502,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>41468</v>
       </c>
@@ -7507,7 +7513,7 @@
         <v>398.51</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>41475</v>
       </c>
@@ -7518,7 +7524,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>41482</v>
       </c>
@@ -7529,7 +7535,7 @@
         <v>400.99</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>41489</v>
       </c>
@@ -7540,7 +7546,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>41496</v>
       </c>
@@ -7551,7 +7557,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>41503</v>
       </c>
@@ -7562,7 +7568,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>41510</v>
       </c>
@@ -7573,7 +7579,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>41517</v>
       </c>
@@ -7584,7 +7590,7 @@
         <v>404.72</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>41524</v>
       </c>
@@ -7595,7 +7601,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>41531</v>
       </c>
@@ -7606,7 +7612,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>41538</v>
       </c>
@@ -7617,7 +7623,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>41545</v>
       </c>
@@ -7628,7 +7634,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>41552</v>
       </c>
@@ -7639,7 +7645,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>41559</v>
       </c>
@@ -7650,7 +7656,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>41566</v>
       </c>
@@ -7661,7 +7667,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>41573</v>
       </c>
@@ -7672,7 +7678,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>41580</v>
       </c>
@@ -7683,7 +7689,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>41587</v>
       </c>
@@ -7694,7 +7700,7 @@
         <v>398.92</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>41594</v>
       </c>
@@ -7705,7 +7711,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>41601</v>
       </c>
@@ -7716,7 +7722,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>41608</v>
       </c>
@@ -7727,7 +7733,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>41615</v>
       </c>
@@ -7738,7 +7744,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>41622</v>
       </c>
@@ -7749,7 +7755,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>41629</v>
       </c>
@@ -7760,7 +7766,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>41636</v>
       </c>
@@ -7771,7 +7777,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>41643</v>
       </c>
@@ -7782,7 +7788,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>41650</v>
       </c>
@@ -7793,7 +7799,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>41657</v>
       </c>
@@ -7804,7 +7810,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>41664</v>
       </c>
@@ -7815,7 +7821,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>41671</v>
       </c>
@@ -7826,7 +7832,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>41678</v>
       </c>
@@ -7837,7 +7843,7 @@
         <v>387.74</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>41685</v>
       </c>
@@ -7848,7 +7854,7 @@
         <v>386.91</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>41692</v>
       </c>
@@ -7859,7 +7865,7 @@
         <v>385.25</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>41699</v>
       </c>
@@ -7870,7 +7876,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>41706</v>
       </c>
@@ -7881,7 +7887,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>41713</v>
       </c>
@@ -7892,7 +7898,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>41720</v>
       </c>
@@ -7903,7 +7909,7 @@
         <v>380.7</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>41727</v>
       </c>
@@ -7914,7 +7920,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>41734</v>
       </c>
@@ -7925,7 +7931,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>41741</v>
       </c>
@@ -7936,7 +7942,7 @@
         <v>386.5</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>41748</v>
       </c>
@@ -7947,7 +7953,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>41755</v>
       </c>
@@ -7958,7 +7964,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>41762</v>
       </c>
@@ -7969,7 +7975,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>41769</v>
       </c>
@@ -7980,7 +7986,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>41776</v>
       </c>
@@ -7991,7 +7997,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>41783</v>
       </c>
@@ -8002,7 +8008,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>41790</v>
       </c>
@@ -8013,7 +8019,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>41797</v>
       </c>
@@ -8024,7 +8030,7 @@
         <v>406.79</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>41804</v>
       </c>
@@ -8035,7 +8041,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>41811</v>
       </c>
@@ -8046,7 +8052,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>41818</v>
       </c>
@@ -8057,7 +8063,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>41825</v>
       </c>
@@ -8068,7 +8074,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>41832</v>
       </c>
@@ -8079,7 +8085,7 @@
         <v>409.28</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>41839</v>
       </c>
@@ -8090,7 +8096,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>41846</v>
       </c>
@@ -8101,7 +8107,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>41853</v>
       </c>
@@ -8112,7 +8118,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>41860</v>
       </c>
@@ -8123,7 +8129,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>41867</v>
       </c>
@@ -8134,7 +8140,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>41874</v>
       </c>
@@ -8145,7 +8151,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>41881</v>
       </c>
@@ -8156,7 +8162,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>41888</v>
       </c>
@@ -8167,7 +8173,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>41895</v>
       </c>
@@ -8178,7 +8184,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>41902</v>
       </c>
@@ -8189,7 +8195,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>41909</v>
       </c>
@@ -8200,7 +8206,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>41916</v>
       </c>
@@ -8211,7 +8217,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>41923</v>
       </c>
@@ -8222,7 +8228,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>41930</v>
       </c>
@@ -8233,7 +8239,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>41937</v>
       </c>
@@ -8244,7 +8250,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>41944</v>
       </c>
@@ -8255,7 +8261,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>41951</v>
       </c>
@@ -8266,7 +8272,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>41958</v>
       </c>
@@ -8277,7 +8283,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>41965</v>
       </c>
@@ -8288,7 +8294,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>41972</v>
       </c>
@@ -8299,7 +8305,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>41979</v>
       </c>
@@ -8310,7 +8316,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>41986</v>
       </c>
@@ -8321,7 +8327,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>41993</v>
       </c>
@@ -8332,7 +8338,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>42000</v>
       </c>
@@ -8343,7 +8349,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>42007</v>
       </c>
@@ -8354,7 +8360,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>42014</v>
       </c>
@@ -8365,7 +8371,7 @@
         <v>435.38</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>42021</v>
       </c>
@@ -8376,7 +8382,7 @@
         <v>441.59</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>42028</v>
       </c>
@@ -8387,7 +8393,7 @@
         <v>455.26</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>42035</v>
       </c>
@@ -8398,7 +8404,7 @@
         <v>461.47</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>42042</v>
       </c>
@@ -8409,7 +8415,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>42049</v>
       </c>
@@ -8420,7 +8426,7 @@
         <v>483.84</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>42056</v>
       </c>
@@ -8431,7 +8437,7 @@
         <v>494.2</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>42063</v>
       </c>
@@ -8442,7 +8448,7 @@
         <v>496.27</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>42070</v>
       </c>
@@ -8453,7 +8459,7 @@
         <v>502.49</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>42077</v>
       </c>
@@ -8464,7 +8470,7 @@
         <v>504.14</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>42084</v>
       </c>
@@ -8475,7 +8481,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>42091</v>
       </c>
@@ -8486,7 +8492,7 @@
         <v>561.72</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>42098</v>
       </c>
@@ -8497,7 +8503,7 @@
         <v>596.11</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>42105</v>
       </c>
@@ -8508,7 +8514,7 @@
         <v>614.75</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>42112</v>
       </c>
@@ -8519,7 +8525,7 @@
         <v>612.67999999999995</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>42119</v>
       </c>
@@ -8530,7 +8536,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>42126</v>
       </c>
@@ -8541,7 +8547,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>42133</v>
       </c>
@@ -8552,7 +8558,7 @@
         <v>626.76</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>42140</v>
       </c>
@@ -8563,7 +8569,7 @@
         <v>640.02</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>42147</v>
       </c>
@@ -8574,7 +8580,7 @@
         <v>642.91999999999996</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>42154</v>
       </c>
@@ -8585,7 +8591,7 @@
         <v>644.57000000000005</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>42161</v>
       </c>
@@ -8596,7 +8602,7 @@
         <v>643.74</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>42168</v>
       </c>
@@ -8607,7 +8613,7 @@
         <v>645.82000000000005</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>42175</v>
       </c>
@@ -8618,7 +8624,7 @@
         <v>639.6</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>42182</v>
       </c>
@@ -8629,7 +8635,7 @@
         <v>633.39</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>42189</v>
       </c>
@@ -8640,7 +8646,7 @@
         <v>630.07000000000005</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>42196</v>
       </c>
@@ -8651,7 +8657,7 @@
         <v>620.13</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>42203</v>
       </c>
@@ -8662,7 +8668,7 @@
         <v>617.65</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>42210</v>
       </c>
@@ -8673,7 +8679,7 @@
         <v>600.25</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>42217</v>
       </c>
@@ -8684,7 +8690,7 @@
         <v>577.04999999999995</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>42224</v>
       </c>
@@ -8695,7 +8701,7 @@
         <v>560.07000000000005</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>42231</v>
       </c>
@@ -8706,7 +8712,7 @@
         <v>558.82000000000005</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>42238</v>
       </c>
@@ -8717,7 +8723,7 @@
         <v>550.12</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>42245</v>
       </c>
@@ -8728,7 +8734,7 @@
         <v>545.98</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>42252</v>
       </c>
@@ -8739,7 +8745,7 @@
         <v>541.01</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>42259</v>
       </c>
@@ -8750,7 +8756,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>42266</v>
       </c>
@@ -8761,7 +8767,7 @@
         <v>512.84</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>42273</v>
       </c>
@@ -8772,7 +8778,7 @@
         <v>491.3</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>42280</v>
       </c>
@@ -8783,7 +8789,7 @@
         <v>477.22</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>42287</v>
       </c>
@@ -8794,7 +8800,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>42294</v>
       </c>
@@ -8805,7 +8811,7 @@
         <v>438.69</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>42301</v>
       </c>
@@ -8816,7 +8822,7 @@
         <v>415.08</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>42308</v>
       </c>
@@ -8827,7 +8833,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>42315</v>
       </c>
@@ -8838,7 +8844,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>42322</v>
       </c>
@@ -8849,7 +8855,7 @@
         <v>388.98</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>42329</v>
       </c>
@@ -8860,7 +8866,7 @@
         <v>385.67</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>42336</v>
       </c>
@@ -8871,7 +8877,7 @@
         <v>380.28</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>42343</v>
       </c>
@@ -8882,7 +8888,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>42350</v>
       </c>
@@ -8893,7 +8899,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>42357</v>
       </c>
@@ -8904,7 +8910,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>42364</v>
       </c>
@@ -8915,7 +8921,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>42371</v>
       </c>
@@ -8926,7 +8932,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>42378</v>
       </c>
@@ -8937,7 +8943,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>42385</v>
       </c>
@@ -8948,7 +8954,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>42392</v>
       </c>
@@ -8959,7 +8965,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>42399</v>
       </c>
@@ -8970,7 +8976,7 @@
         <v>363.71</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>42406</v>
       </c>
@@ -8981,7 +8987,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>42413</v>
       </c>
@@ -8992,7 +8998,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>42420</v>
       </c>
@@ -9003,7 +9009,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>42427</v>
       </c>
@@ -9014,7 +9020,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>42434</v>
       </c>
@@ -9025,7 +9031,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>42441</v>
       </c>
@@ -9036,7 +9042,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>42448</v>
       </c>
@@ -9047,7 +9053,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>42455</v>
       </c>
@@ -9058,7 +9064,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>42462</v>
       </c>
@@ -9069,7 +9075,7 @@
         <v>362.47</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>42469</v>
       </c>
@@ -9080,7 +9086,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>42476</v>
       </c>
@@ -9091,7 +9097,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>42483</v>
       </c>
@@ -9102,7 +9108,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>42490</v>
       </c>
@@ -9113,7 +9119,7 @@
         <v>358.74</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>42497</v>
       </c>
@@ -9124,7 +9130,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>42504</v>
       </c>
@@ -9135,7 +9141,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>42511</v>
       </c>
@@ -9146,7 +9152,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>42518</v>
       </c>
@@ -9157,7 +9163,7 @@
         <v>356.67</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>42525</v>
       </c>
@@ -9168,7 +9174,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>42532</v>
       </c>
@@ -9179,7 +9185,7 @@
         <v>354.6</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>42539</v>
       </c>
@@ -9190,7 +9196,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>42546</v>
       </c>
@@ -9201,7 +9207,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>42553</v>
       </c>
@@ -9212,7 +9218,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>42560</v>
       </c>
@@ -9223,7 +9229,7 @@
         <v>348.8</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>42567</v>
       </c>
@@ -9234,7 +9240,7 @@
         <v>347.56</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>42574</v>
       </c>
@@ -9245,7 +9251,7 @@
         <v>345.9</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>42581</v>
       </c>
@@ -9256,7 +9262,7 @@
         <v>345.07</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>42588</v>
       </c>
@@ -9267,7 +9273,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>42595</v>
       </c>
@@ -9278,7 +9284,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>42602</v>
       </c>
@@ -9289,7 +9295,7 @@
         <v>341.76</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>42609</v>
       </c>
@@ -9300,7 +9306,7 @@
         <v>337.2</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>42616</v>
       </c>
@@ -9311,7 +9317,7 @@
         <v>331.4</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>42623</v>
       </c>
@@ -9322,7 +9328,7 @@
         <v>330.99</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
         <v>42630</v>
       </c>
@@ -9333,7 +9339,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>42637</v>
       </c>
@@ -9344,7 +9350,7 @@
         <v>328.09</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>42644</v>
       </c>
@@ -9355,7 +9361,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>42651</v>
       </c>
@@ -9366,7 +9372,7 @@
         <v>326.01</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>42658</v>
       </c>
@@ -9377,7 +9383,7 @@
         <v>324.77</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>42665</v>
       </c>
@@ -9388,7 +9394,7 @@
         <v>322.7</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>42672</v>
       </c>
@@ -9399,7 +9405,7 @@
         <v>319.39</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>42679</v>
       </c>
@@ -9410,7 +9416,7 @@
         <v>318.56</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>42686</v>
       </c>
@@ -9421,7 +9427,7 @@
         <v>317.32</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>42693</v>
       </c>
@@ -9432,7 +9438,7 @@
         <v>316.49</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>42700</v>
       </c>
@@ -9443,7 +9449,7 @@
         <v>316.07</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>42707</v>
       </c>
@@ -9454,7 +9460,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>42714</v>
       </c>
@@ -9465,7 +9471,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>42721</v>
       </c>
@@ -9476,7 +9482,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>42728</v>
       </c>
@@ -9487,7 +9493,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>42735</v>
       </c>
@@ -9498,7 +9504,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>42742</v>
       </c>
@@ -9509,7 +9515,7 @@
         <v>316.39</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>42749</v>
       </c>
@@ -9520,7 +9526,7 @@
         <v>319.07</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>42756</v>
       </c>
@@ -9531,7 +9537,7 @@
         <v>320.56</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>42763</v>
       </c>
@@ -9542,7 +9548,7 @@
         <v>322.35000000000002</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
         <v>42770</v>
       </c>
@@ -9553,7 +9559,7 @@
         <v>323.83999999999997</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
         <v>42777</v>
       </c>
@@ -9564,7 +9570,7 @@
         <v>325.33</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>42784</v>
       </c>
@@ -9575,7 +9581,7 @@
         <v>330.4</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>42791</v>
       </c>
@@ -9586,7 +9592,7 @@
         <v>343.52</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
         <v>42798</v>
       </c>
@@ -9597,7 +9603,7 @@
         <v>351.87</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
         <v>42805</v>
       </c>
@@ -9608,7 +9614,7 @@
         <v>389.44</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>42812</v>
       </c>
@@ -9619,7 +9625,7 @@
         <v>404.35</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>42819</v>
       </c>
@@ -9630,7 +9636,7 @@
         <v>438.94</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>42826</v>
       </c>
@@ -9641,7 +9647,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>42833</v>
       </c>
@@ -9652,7 +9658,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>42840</v>
       </c>
@@ -9663,7 +9669,7 @@
         <v>516.77</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>42847</v>
       </c>
@@ -9674,7 +9680,7 @@
         <v>522.14</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>42854</v>
       </c>
@@ -9685,7 +9691,7 @@
         <v>523.33000000000004</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>42861</v>
       </c>
@@ -9696,7 +9702,7 @@
         <v>533.47</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>42868</v>
       </c>
@@ -9707,7 +9713,7 @@
         <v>533.16999999999996</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>42875</v>
       </c>
@@ -9718,7 +9724,7 @@
         <v>500.37</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>42882</v>
       </c>
@@ -9729,7 +9735,7 @@
         <v>483.97</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>42889</v>
       </c>
@@ -9740,7 +9746,7 @@
         <v>458.92</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>42896</v>
       </c>
@@ -9751,7 +9757,7 @@
         <v>443.72</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>42903</v>
       </c>
@@ -9762,7 +9768,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>42910</v>
       </c>
@@ -9773,7 +9779,7 @@
         <v>438.35</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
         <v>42917</v>
       </c>
@@ -9784,7 +9790,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365" s="1">
         <v>42924</v>
       </c>
@@ -9795,7 +9801,7 @@
         <v>435.96</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>42931</v>
       </c>
@@ -9806,7 +9812,7 @@
         <v>445.8</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>42938</v>
       </c>
@@ -9817,7 +9823,7 @@
         <v>470.25</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>42945</v>
       </c>
@@ -9828,7 +9834,7 @@
         <v>472.04</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A369" s="1">
         <v>42952</v>
       </c>
@@ -9839,7 +9845,7 @@
         <v>481.88</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A370" s="1">
         <v>42959</v>
       </c>
@@ -9850,7 +9856,7 @@
         <v>486.66</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
         <v>42966</v>
       </c>
@@ -9861,7 +9867,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>42973</v>
       </c>
@@ -9872,7 +9878,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A373" s="1">
         <v>42980</v>
       </c>
@@ -9883,7 +9889,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A374" s="1">
         <v>42987</v>
       </c>
@@ -9894,7 +9900,7 @@
         <v>515.88</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>42994</v>
       </c>
@@ -9905,7 +9911,7 @@
         <v>517.07000000000005</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>43001</v>
       </c>
@@ -9916,7 +9922,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>43008</v>
       </c>
@@ -9927,7 +9933,7 @@
         <v>506.34</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>43015</v>
       </c>
@@ -9938,7 +9944,7 @@
         <v>507.53</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>43022</v>
       </c>
@@ -9949,7 +9955,7 @@
         <v>505.14</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>43029</v>
       </c>
@@ -9960,7 +9966,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>43036</v>
       </c>
@@ -9971,7 +9977,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>43043</v>
       </c>
@@ -9982,7 +9988,7 @@
         <v>473.24</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383" s="1">
         <v>43050</v>
       </c>
@@ -9993,7 +9999,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A384" s="1">
         <v>43057</v>
       </c>
@@ -10004,7 +10010,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385" s="1">
         <v>43064</v>
       </c>
@@ -10015,7 +10021,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
         <v>43071</v>
       </c>
@@ -10026,7 +10032,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387" s="1">
         <v>43078</v>
       </c>
@@ -10037,7 +10043,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" s="1">
         <v>43085</v>
       </c>
@@ -10048,7 +10054,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A389" s="1">
         <v>43092</v>
       </c>
@@ -10059,7 +10065,7 @@
         <v>482.78</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A390" s="1">
         <v>43099</v>
       </c>
@@ -10070,7 +10076,7 @@
         <v>483.08</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391" s="1">
         <v>43106</v>
       </c>
@@ -10081,7 +10087,7 @@
         <v>485.16</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392" s="1">
         <v>43113</v>
       </c>
@@ -10092,7 +10098,7 @@
         <v>489.34</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393" s="1">
         <v>43120</v>
       </c>
@@ -10103,7 +10109,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394" s="1">
         <v>43127</v>
       </c>
@@ -10114,7 +10120,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395" s="1">
         <v>43134</v>
       </c>
@@ -10125,7 +10131,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396" s="1">
         <v>43141</v>
       </c>
@@ -10136,7 +10142,7 @@
         <v>520.35</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397" s="1">
         <v>43148</v>
       </c>
@@ -10147,7 +10153,7 @@
         <v>526.02</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398" s="1">
         <v>43155</v>
       </c>
@@ -10158,7 +10164,7 @@
         <v>542.41999999999996</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A399" s="1">
         <v>43162</v>
       </c>
@@ -10169,7 +10175,7 @@
         <v>548.98</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
         <v>43169</v>
       </c>
@@ -10180,7 +10186,7 @@
         <v>579.69000000000005</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>43176</v>
       </c>
@@ -10191,7 +10197,7 @@
         <v>597.88</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>43183</v>
       </c>
@@ -10202,7 +10208,7 @@
         <v>635.16</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>43190</v>
       </c>
@@ -10213,7 +10219,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
         <v>43197</v>
       </c>
@@ -10224,7 +10230,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>43204</v>
       </c>
@@ -10235,7 +10241,7 @@
         <v>642.61</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A406" s="1">
         <v>43211</v>
       </c>
@@ -10246,7 +10252,7 @@
         <v>646.19000000000005</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407" s="1">
         <v>43218</v>
       </c>
@@ -10257,7 +10263,7 @@
         <v>652.45000000000005</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A408" s="1">
         <v>43225</v>
       </c>
@@ -10268,7 +10274,7 @@
         <v>653.64</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409" s="1">
         <v>43232</v>
       </c>
@@ -10279,7 +10285,7 @@
         <v>656.63</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>43239</v>
       </c>
@@ -10290,7 +10296,7 @@
         <v>661.1</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>43245</v>
       </c>
@@ -10301,7 +10307,7 @@
         <v>670.64</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412" s="1">
         <v>43252</v>
       </c>
@@ -10312,7 +10318,7 @@
         <v>673.62</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413" s="1">
         <v>43259</v>
       </c>
@@ -10323,7 +10329,7 @@
         <v>676.61</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A414" s="1">
         <v>43266</v>
       </c>
@@ -10334,7 +10340,7 @@
         <v>678.1</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A415" s="1">
         <v>43273</v>
       </c>
@@ -10345,7 +10351,7 @@
         <v>676.9</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A416" s="1">
         <v>43280</v>
       </c>
@@ -10356,7 +10362,7 @@
         <v>672.73</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417" s="1">
         <v>43287</v>
       </c>
@@ -10367,7 +10373,7 @@
         <v>668.26</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418" s="1">
         <v>43294</v>
       </c>
@@ -10378,7 +10384,7 @@
         <v>652.15</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419" s="1">
         <v>43301</v>
       </c>
@@ -10389,7 +10395,7 @@
         <v>628.6</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420" s="1">
         <v>43308</v>
       </c>
@@ -10400,7 +10406,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A421" s="1">
         <v>43315</v>
       </c>
@@ -10411,7 +10417,7 @@
         <v>594.6</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422" s="1">
         <v>43322</v>
       </c>
@@ -10422,7 +10428,7 @@
         <v>584.16999999999996</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423" s="1">
         <v>43329</v>
       </c>
@@ -10433,7 +10439,7 @@
         <v>582.97</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424" s="1">
         <v>43336</v>
       </c>
@@ -10444,7 +10450,7 @@
         <v>577.01</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425" s="1">
         <v>43343</v>
       </c>
@@ -10455,7 +10461,7 @@
         <v>568.05999999999995</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A426" s="1">
         <v>43350</v>
       </c>
@@ -10466,7 +10472,7 @@
         <v>550.77</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427" s="1">
         <v>43357</v>
       </c>
@@ -10477,7 +10483,7 @@
         <v>548.08000000000004</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428" s="1">
         <v>43364</v>
       </c>
@@ -10488,7 +10494,7 @@
         <v>538.54</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429" s="1">
         <v>43371</v>
       </c>
@@ -10499,7 +10505,7 @@
         <v>534.37</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" s="1">
         <v>43378</v>
       </c>
@@ -10510,7 +10516,7 @@
         <v>532.28</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431" s="1">
         <v>43385</v>
       </c>
@@ -10521,7 +10527,7 @@
         <v>524.23</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432" s="1">
         <v>43392</v>
       </c>
@@ -10532,7 +10538,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" s="1">
         <v>43399</v>
       </c>
@@ -10543,7 +10549,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434" s="1">
         <v>43406</v>
       </c>
@@ -10554,7 +10560,7 @@
         <v>503.06</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435" s="1">
         <v>43413</v>
       </c>
@@ -10565,7 +10571,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436" s="1">
         <v>43420</v>
       </c>
@@ -10576,7 +10582,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A437" s="1">
         <v>43427</v>
       </c>
@@ -10587,7 +10593,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438" s="1">
         <v>43434</v>
       </c>
@@ -10598,7 +10604,7 @@
         <v>502.16</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A439" s="1">
         <v>43441</v>
       </c>
@@ -10609,7 +10615,7 @@
         <v>498.58</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440" s="1">
         <v>43448</v>
       </c>
@@ -10620,7 +10626,7 @@
         <v>495.6</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441" s="1">
         <v>43455</v>
       </c>
@@ -10631,7 +10637,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442" s="1">
         <v>43462</v>
       </c>
@@ -10642,7 +10648,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443" s="1">
         <v>43469</v>
       </c>
@@ -10653,7 +10659,7 @@
         <v>485.46</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444" s="1">
         <v>43476</v>
       </c>
@@ -10664,7 +10670,7 @@
         <v>478.01</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445" s="1">
         <v>43483</v>
       </c>
@@ -10675,7 +10681,7 @@
         <v>474.43</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A446" s="1">
         <v>43490</v>
       </c>
@@ -10686,7 +10692,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447" s="1">
         <v>43497</v>
       </c>
@@ -10697,7 +10703,7 @@
         <v>492.02</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448" s="1">
         <v>43504</v>
       </c>
@@ -10708,7 +10714,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A449" s="1">
         <v>43511</v>
       </c>
@@ -10719,7 +10725,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A450" s="1">
         <v>43518</v>
       </c>
@@ -10730,7 +10736,7 @@
         <v>502.46</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A451" s="1">
         <v>43525</v>
       </c>
@@ -10741,7 +10747,7 @@
         <v>527.80999999999995</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452" s="1">
         <v>43532</v>
       </c>
@@ -10752,7 +10758,7 @@
         <v>543.01</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A453" s="1">
         <v>43539</v>
       </c>
@@ -10763,7 +10769,7 @@
         <v>552.55999999999995</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A454" s="1">
         <v>43546</v>
       </c>
@@ -10774,7 +10780,7 @@
         <v>560.61</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455" s="1">
         <v>43553</v>
       </c>
@@ -10785,7 +10791,7 @@
         <v>565.67999999999995</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456" s="1">
         <v>43560</v>
       </c>
@@ -10796,7 +10802,7 @@
         <v>576.11</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457" s="1">
         <v>43567</v>
       </c>
@@ -10807,7 +10813,7 @@
         <v>581.48</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A458" s="1">
         <v>43574</v>
       </c>
@@ -10818,7 +10824,7 @@
         <v>585.05999999999995</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A459" s="1">
         <v>43581</v>
       </c>
@@ -10829,7 +10835,7 @@
         <v>585.66</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A460" s="1">
         <v>43588</v>
       </c>
@@ -10840,7 +10846,7 @@
         <v>586.25</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A461" s="1">
         <v>43595</v>
       </c>
@@ -10851,7 +10857,7 @@
         <v>586.85</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A462" s="1">
         <v>43602</v>
       </c>
@@ -10862,7 +10868,7 @@
         <v>596.09</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A463" s="1">
         <v>43609</v>
       </c>
@@ -10873,7 +10879,7 @@
         <v>599.08000000000004</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A464" s="1">
         <v>43616</v>
       </c>
@@ -10884,7 +10890,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465" s="1">
         <v>43623</v>
       </c>
@@ -10895,7 +10901,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466" s="1">
         <v>43630</v>
       </c>
@@ -10906,7 +10912,7 @@
         <v>603.85</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A467" s="1">
         <v>43637</v>
       </c>
@@ -10917,7 +10923,7 @@
         <v>603.54999999999995</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A468" s="1">
         <v>43644</v>
       </c>
@@ -10928,7 +10934,7 @@
         <v>611.6</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A469" s="1">
         <v>43651</v>
       </c>
@@ -10939,7 +10945,7 @@
         <v>618.76</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A470" s="1">
         <v>43658</v>
       </c>
@@ -10950,7 +10956,7 @@
         <v>629.19000000000005</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A471" s="1">
         <v>43665</v>
       </c>
@@ -10961,7 +10967,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A472" s="1">
         <v>43672</v>
       </c>
@@ -10972,7 +10978,7 @@
         <v>666.77</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A473" s="1">
         <v>43679</v>
       </c>
@@ -10983,7 +10989,7 @@
         <v>670.94</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474" s="1">
         <v>43686</v>
       </c>
@@ -10994,7 +11000,7 @@
         <v>681.97</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A475" s="1">
         <v>43693</v>
       </c>
@@ -11005,7 +11011,7 @@
         <v>690.02</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A476" s="1">
         <v>43700</v>
       </c>
@@ -11016,7 +11022,7 @@
         <v>696.88</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A477" s="1">
         <v>43707</v>
       </c>
@@ -11027,7 +11033,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A478" s="1">
         <v>43714</v>
       </c>
@@ -11038,7 +11044,7 @@
         <v>718.65</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A479" s="1">
         <v>43721</v>
       </c>
@@ -11049,7 +11055,7 @@
         <v>723.42</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A480" s="1">
         <v>43728</v>
       </c>
@@ -11060,7 +11066,7 @@
         <v>724.62</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A481" s="1">
         <v>43735</v>
       </c>
@@ -11071,7 +11077,7 @@
         <v>726.4</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A482" s="1">
         <v>43742</v>
       </c>
@@ -11082,7 +11088,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483" s="1">
         <v>43749</v>
       </c>
@@ -11093,7 +11099,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A484" s="1">
         <v>43756</v>
       </c>
@@ -11104,7 +11110,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A485" s="1">
         <v>43763</v>
       </c>
@@ -11115,7 +11121,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486" s="1">
         <v>43770</v>
       </c>
@@ -11126,7 +11132,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A487" s="1">
         <v>43777</v>
       </c>
@@ -11137,7 +11143,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A488" s="1">
         <v>43784</v>
       </c>
@@ -11148,7 +11154,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A489" s="1">
         <v>43791</v>
       </c>
@@ -11159,7 +11165,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A490" s="1">
         <v>43798</v>
       </c>
@@ -11170,7 +11176,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A491" s="1">
         <v>43805</v>
       </c>
@@ -11181,7 +11187,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A492" s="1">
         <v>43812</v>
       </c>
@@ -11192,7 +11198,7 @@
         <v>715.67</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A493" s="1">
         <v>43819</v>
       </c>
@@ -11203,7 +11209,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A494" s="1">
         <v>43826</v>
       </c>
@@ -11214,7 +11220,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A495" s="1">
         <v>43833</v>
       </c>
@@ -11225,7 +11231,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A496" s="1">
         <v>43840</v>
       </c>
@@ -11236,7 +11242,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A497" s="1">
         <v>43847</v>
       </c>
@@ -11247,7 +11253,7 @@
         <v>711.49</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A498" s="1">
         <v>43854</v>
       </c>
@@ -11258,7 +11264,7 @@
         <v>708.51</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A499" s="1">
         <v>43861</v>
       </c>
@@ -11269,7 +11275,7 @@
         <v>705.53</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A500" s="1">
         <v>43868</v>
       </c>
@@ -11280,7 +11286,7 @@
         <v>701.95</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A501" s="1">
         <v>43875</v>
       </c>
@@ -11291,7 +11297,7 @@
         <v>691.52</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A502" s="1">
         <v>43882</v>
       </c>
@@ -11302,7 +11308,7 @@
         <v>680.48</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A503" s="1">
         <v>43889</v>
       </c>
@@ -11313,7 +11319,7 @@
         <v>668.85</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A504" s="1">
         <v>43896</v>
       </c>
@@ -11324,7 +11330,7 @@
         <v>651.26</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A505" s="1">
         <v>43903</v>
       </c>
@@ -11335,7 +11341,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A506" s="1">
         <v>43910</v>
       </c>
@@ -11346,7 +11352,7 @@
         <v>631.58000000000004</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A507" s="1">
         <v>43917</v>
       </c>
@@ -11357,7 +11363,7 @@
         <v>616.07000000000005</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A508" s="1">
         <v>43924</v>
       </c>
@@ -11368,7 +11374,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A509" s="1">
         <v>43931</v>
       </c>
@@ -11379,7 +11385,7 @@
         <v>601.46</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A510" s="1">
         <v>43938</v>
       </c>
@@ -11390,7 +11396,7 @@
         <v>572.83000000000004</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A511" s="1">
         <v>43945</v>
       </c>
@@ -11401,7 +11407,7 @@
         <v>549.87</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A512" s="1">
         <v>43952</v>
       </c>
@@ -11412,7 +11418,7 @@
         <v>528.70000000000005</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A513" s="1">
         <v>43959</v>
       </c>
@@ -11423,7 +11429,7 @@
         <v>507.83</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A514" s="1">
         <v>43966</v>
       </c>
@@ -11434,7 +11440,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A515" s="1">
         <v>43973</v>
       </c>
@@ -11445,7 +11451,7 @@
         <v>479.2</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A516" s="1">
         <v>43980</v>
       </c>
@@ -11456,7 +11462,7 @@
         <v>452.36</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A517" s="1">
         <v>43987</v>
       </c>
@@ -11467,7 +11473,7 @@
         <v>434.17</v>
       </c>
     </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A518" s="1">
         <v>43994</v>
       </c>
@@ -11478,7 +11484,7 @@
         <v>412.11</v>
       </c>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A519" s="1">
         <v>44001</v>
       </c>
@@ -11489,7 +11495,7 @@
         <v>418.96</v>
       </c>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A520" s="1">
         <v>44008</v>
       </c>
@@ -11500,7 +11506,7 @@
         <v>431.79</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A521" s="1">
         <v>44015</v>
       </c>
@@ -11511,7 +11517,7 @@
         <v>439.84</v>
       </c>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A522" s="1">
         <v>44022</v>
       </c>
@@ -11522,7 +11528,7 @@
         <v>444.91</v>
       </c>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A523" s="1">
         <v>44029</v>
       </c>
@@ -11533,7 +11539,7 @@
         <v>463.1</v>
       </c>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A524" s="1">
         <v>44036</v>
       </c>
@@ -11544,7 +11550,7 @@
         <v>484.87</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A525" s="1">
         <v>44043</v>
       </c>
@@ -11555,7 +11561,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A526" s="1">
         <v>44050</v>
       </c>
@@ -11566,7 +11572,7 @@
         <v>556.13</v>
       </c>
     </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A527" s="1">
         <v>44057</v>
       </c>
@@ -11577,7 +11583,7 @@
         <v>596.69000000000005</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A528" s="1">
         <v>44064</v>
       </c>
@@ -11588,7 +11594,7 @@
         <v>627.11</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A529" s="1">
         <v>44071</v>
       </c>
@@ -11599,7 +11605,7 @@
         <v>665.87</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A530" s="1">
         <v>44078</v>
       </c>
@@ -11610,7 +11616,7 @@
         <v>671.83</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A531" s="1">
         <v>44085</v>
       </c>
@@ -11621,7 +11627,7 @@
         <v>678.4</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A532" s="1">
         <v>44092</v>
       </c>
@@ -11632,7 +11638,7 @@
         <v>691.81</v>
       </c>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A533" s="1">
         <v>44099</v>
       </c>
@@ -11643,7 +11649,7 @@
         <v>703.74</v>
       </c>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A534" s="1">
         <v>44106</v>
       </c>
@@ -11654,7 +11660,7 @@
         <v>714.77</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A535" s="1">
         <v>44113</v>
       </c>
@@ -11665,7 +11671,7 @@
         <v>754.14</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A536" s="1">
         <v>44120</v>
       </c>
@@ -11676,7 +11682,7 @@
         <v>783.96</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A537" s="1">
         <v>44127</v>
       </c>
@@ -11687,7 +11693,7 @@
         <v>820.04</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A538" s="1">
         <v>44134</v>
       </c>
@@ -11698,7 +11704,7 @@
         <v>881.17</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A539" s="1">
         <v>44141</v>
       </c>
@@ -11709,7 +11715,7 @@
         <v>910.09</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A540" s="1">
         <v>44148</v>
       </c>
@@ -11720,7 +11726,7 @@
         <v>947.07</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A541" s="1">
         <v>44155</v>
       </c>
@@ -11731,7 +11737,7 @@
         <v>978.68</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A542" s="1">
         <v>44162</v>
       </c>
@@ -11742,7 +11748,7 @@
         <v>1009.39</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A543" s="1">
         <v>44169</v>
       </c>
@@ -11753,7 +11759,7 @@
         <v>1016.25</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A544" s="1">
         <v>44176</v>
       </c>
@@ -11764,7 +11770,7 @@
         <v>1020.13</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A545" s="1">
         <v>44183</v>
       </c>
@@ -11775,7 +11781,7 @@
         <v>1032.06</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A546" s="1">
         <v>44190</v>
       </c>
@@ -11786,7 +11792,7 @@
         <v>1036.23</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A547" s="1">
         <v>44197</v>
       </c>
@@ -11797,7 +11803,7 @@
         <v>1038.02</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A548" s="1">
         <v>44204</v>
       </c>
@@ -11808,7 +11814,7 @@
         <v>1069.6300000000001</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A549" s="1">
         <v>44211</v>
       </c>
@@ -11819,7 +11825,7 @@
         <v>1094.3800000000001</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A550" s="1">
         <v>44218</v>
       </c>
@@ -11830,7 +11836,7 @@
         <v>1112.8699999999999</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A551" s="1">
         <v>44225</v>
       </c>
@@ -11841,7 +11847,7 @@
         <v>1154.32</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A552" s="1">
         <v>44232</v>
       </c>
@@ -11852,7 +11858,7 @@
         <v>1202.03</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A553" s="1">
         <v>44239</v>
       </c>
@@ -11863,7 +11869,7 @@
         <v>1228.27</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A554" s="1">
         <v>44246</v>
       </c>
@@ -11874,7 +11880,7 @@
         <v>1262.26</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A555" s="1">
         <v>44253</v>
       </c>
@@ -11885,7 +11891,7 @@
         <v>1278.3599999999999</v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A556" s="1">
         <v>44260</v>
       </c>
@@ -11896,7 +11902,7 @@
         <v>1323.39</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A557" s="1">
         <v>44267</v>
       </c>
@@ -11907,7 +11913,7 @@
         <v>1387.21</v>
       </c>
     </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A558" s="1">
         <v>44274</v>
       </c>
@@ -11918,7 +11924,7 @@
         <v>1442.97</v>
       </c>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A559" s="1">
         <v>44281</v>
       </c>
@@ -11929,7 +11935,7 @@
         <v>1454.3</v>
       </c>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A560" s="1">
         <v>44288</v>
       </c>
@@ -11940,7 +11946,7 @@
         <v>1492.47</v>
       </c>
     </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A561" s="1">
         <v>44295</v>
       </c>
@@ -11951,7 +11957,7 @@
         <v>1559.56</v>
       </c>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A562" s="1">
         <v>44302</v>
       </c>
@@ -11962,7 +11968,7 @@
         <v>1650.51</v>
       </c>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A563" s="1">
         <v>44309</v>
       </c>
@@ -11973,7 +11979,7 @@
         <v>1680.33</v>
       </c>
     </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A564" s="1">
         <v>44316</v>
       </c>
@@ -11984,7 +11990,7 @@
         <v>1707.47</v>
       </c>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A565" s="1">
         <v>44323</v>
       </c>
@@ -11995,7 +12001,7 @@
         <v>1777.25</v>
       </c>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A566" s="1">
         <v>44330</v>
       </c>
@@ -12006,7 +12012,7 @@
         <v>1837.48</v>
       </c>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A567" s="1">
         <v>44337</v>
       </c>
@@ -12017,7 +12023,7 @@
         <v>1890.86</v>
       </c>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A568" s="1">
         <v>44344</v>
       </c>
@@ -12028,7 +12034,7 @@
         <v>1940.66</v>
       </c>
     </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A569" s="1">
         <v>44351</v>
       </c>
@@ -12039,7 +12045,7 @@
         <v>1986.58</v>
       </c>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A570" s="1">
         <v>44358</v>
       </c>
@@ -12050,7 +12056,7 @@
         <v>2033.69</v>
       </c>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A571" s="1">
         <v>44365</v>
       </c>
@@ -12061,7 +12067,7 @@
         <v>2117.19</v>
       </c>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A572" s="1">
         <v>44372</v>
       </c>
@@ -12072,7 +12078,7 @@
         <v>2212.31</v>
       </c>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A573" s="1">
         <v>44379</v>
       </c>
@@ -12083,7 +12089,7 @@
         <v>2406.44</v>
       </c>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A574" s="1">
         <v>44386</v>
       </c>
@@ -12094,7 +12100,7 @@
         <v>2695.69</v>
       </c>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A575" s="1">
         <v>44393</v>
       </c>
@@ -12105,7 +12111,7 @@
         <v>3023.7</v>
       </c>
     </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A576" s="1">
         <v>44400</v>
       </c>
@@ -12116,7 +12122,7 @@
         <v>3142.98</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A577" s="1">
         <v>44407</v>
       </c>
@@ -12127,7 +12133,7 @@
         <v>3301.03</v>
       </c>
     </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A578" s="1">
         <v>44414</v>
       </c>
@@ -12138,7 +12144,7 @@
         <v>3548.53</v>
       </c>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A579" s="1">
         <v>44421</v>
       </c>
@@ -12149,7 +12155,7 @@
         <v>3554.49</v>
       </c>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A580" s="1">
         <v>44428</v>
       </c>
@@ -12160,7 +12166,7 @@
         <v>3560.46</v>
       </c>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A581" s="1">
         <v>44435</v>
       </c>
@@ -12171,7 +12177,7 @@
         <v>3599.22</v>
       </c>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A582" s="1">
         <v>44442</v>
       </c>
@@ -12182,7 +12188,7 @@
         <v>3694.64</v>
       </c>
     </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A583" s="1">
         <v>44449</v>
       </c>
@@ -12193,7 +12199,7 @@
         <v>3822.87</v>
       </c>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A584" s="1">
         <v>44456</v>
       </c>
@@ -12204,7 +12210,7 @@
         <v>3928.73</v>
       </c>
     </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A585" s="1">
         <v>44463</v>
       </c>
@@ -12215,7 +12221,7 @@
         <v>3980.91</v>
       </c>
     </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A586" s="1">
         <v>44470</v>
       </c>
@@ -12226,7 +12232,7 @@
         <v>3989.86</v>
       </c>
     </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A587" s="1">
         <v>44477</v>
       </c>
@@ -12237,7 +12243,7 @@
         <v>3995.82</v>
       </c>
     </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A588" s="1">
         <v>44484</v>
       </c>
@@ -12248,7 +12254,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A589" s="1">
         <v>44491</v>
       </c>
@@ -12259,7 +12265,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A590" s="1">
         <v>44498</v>
       </c>
@@ -12270,7 +12276,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A591" s="1">
         <v>44505</v>
       </c>
@@ -12281,7 +12287,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A592" s="1">
         <v>44512</v>
       </c>
@@ -12292,7 +12298,7 @@
         <v>3852.69</v>
       </c>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A593" s="1">
         <v>44519</v>
       </c>
@@ -12300,7 +12306,7 @@
         <v>44519</v>
       </c>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A594" s="1">
         <v>44526</v>
       </c>
@@ -12308,7 +12314,7 @@
         <v>44526</v>
       </c>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A595" s="1">
         <v>44533</v>
       </c>
@@ -12316,7 +12322,7 @@
         <v>44533</v>
       </c>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A596" s="1">
         <v>44540</v>
       </c>
@@ -12324,7 +12330,7 @@
         <v>44540</v>
       </c>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A597" s="1">
         <v>44547</v>
       </c>
@@ -12332,7 +12338,7 @@
         <v>44547</v>
       </c>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A598" s="1">
         <v>44554</v>
       </c>
@@ -12340,7 +12346,7 @@
         <v>44554</v>
       </c>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A599" s="1">
         <v>44561</v>
       </c>
@@ -12348,7 +12354,7 @@
         <v>44561</v>
       </c>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A600" s="1">
         <v>44568</v>
       </c>
@@ -12356,7 +12362,7 @@
         <v>44568</v>
       </c>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A601" s="1">
         <v>44575</v>
       </c>
@@ -12364,7 +12370,7 @@
         <v>44575</v>
       </c>
     </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A602" s="1">
         <v>44582</v>
       </c>
@@ -12372,7 +12378,7 @@
         <v>44582</v>
       </c>
     </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A603" s="1">
         <v>44589</v>
       </c>
@@ -12380,7 +12386,7 @@
         <v>44589</v>
       </c>
     </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A604" s="1">
         <v>44596</v>
       </c>
@@ -12388,7 +12394,7 @@
         <v>44596</v>
       </c>
     </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A605" s="1">
         <v>44603</v>
       </c>
@@ -12396,7 +12402,7 @@
         <v>44603</v>
       </c>
     </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A606" s="1">
         <v>44610</v>
       </c>
@@ -12404,7 +12410,7 @@
         <v>44610</v>
       </c>
     </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A607" s="1">
         <v>44617</v>
       </c>
@@ -12412,7 +12418,7 @@
         <v>44617</v>
       </c>
     </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A608" s="1">
         <v>44624</v>
       </c>
@@ -12420,7 +12426,7 @@
         <v>44624</v>
       </c>
     </row>
-    <row r="609" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A609" s="1">
         <v>44631</v>
       </c>
@@ -12428,7 +12434,7 @@
         <v>44631</v>
       </c>
     </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A610" s="1">
         <v>44638</v>
       </c>
@@ -12436,7 +12442,7 @@
         <v>44638</v>
       </c>
     </row>
-    <row r="611" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A611" s="1">
         <v>44645</v>
       </c>
@@ -12444,7 +12450,7 @@
         <v>44645</v>
       </c>
     </row>
-    <row r="612" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A612" s="1">
         <v>44652</v>
       </c>
@@ -12452,7 +12458,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="613" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A613" s="1">
         <v>44659</v>
       </c>
@@ -12460,7 +12466,7 @@
         <v>44659</v>
       </c>
     </row>
-    <row r="614" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A614" s="1">
         <v>44666</v>
       </c>
@@ -12468,7 +12474,7 @@
         <v>44666</v>
       </c>
     </row>
-    <row r="615" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A615" s="1">
         <v>44673</v>
       </c>
@@ -12476,7 +12482,7 @@
         <v>44673</v>
       </c>
     </row>
-    <row r="616" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A616" s="1">
         <v>44680</v>
       </c>
@@ -12484,7 +12490,7 @@
         <v>44680</v>
       </c>
     </row>
-    <row r="617" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A617" s="1">
         <v>44687</v>
       </c>
@@ -12492,7 +12498,7 @@
         <v>44687</v>
       </c>
     </row>
-    <row r="618" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A618" s="1">
         <v>44694</v>
       </c>
@@ -12500,7 +12506,7 @@
         <v>44694</v>
       </c>
     </row>
-    <row r="619" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A619" s="1">
         <v>44701</v>
       </c>
@@ -12508,7 +12514,7 @@
         <v>44701</v>
       </c>
     </row>
-    <row r="620" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A620" s="1">
         <v>44708</v>
       </c>
@@ -12516,7 +12522,7 @@
         <v>44708</v>
       </c>
     </row>
-    <row r="621" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A621" s="1">
         <v>44715</v>
       </c>
@@ -12524,7 +12530,7 @@
         <v>44715</v>
       </c>
     </row>
-    <row r="622" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A622" s="1">
         <v>44722</v>
       </c>
@@ -12532,7 +12538,7 @@
         <v>44722</v>
       </c>
     </row>
-    <row r="623" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A623" s="1">
         <v>44729</v>
       </c>
@@ -12540,7 +12546,7 @@
         <v>44729</v>
       </c>
     </row>
-    <row r="624" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A624" s="1">
         <v>44736</v>
       </c>
@@ -12548,7 +12554,7 @@
         <v>44736</v>
       </c>
     </row>
-    <row r="625" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A625" s="1">
         <v>44743</v>
       </c>
@@ -12556,7 +12562,7 @@
         <v>44743</v>
       </c>
     </row>
-    <row r="626" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A626" s="1">
         <v>44750</v>
       </c>
@@ -12564,7 +12570,7 @@
         <v>44750</v>
       </c>
     </row>
-    <row r="627" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A627" s="1">
         <v>44757</v>
       </c>
@@ -12572,7 +12578,7 @@
         <v>44757</v>
       </c>
     </row>
-    <row r="628" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A628" s="1">
         <v>44764</v>
       </c>
@@ -12580,7 +12586,7 @@
         <v>44764</v>
       </c>
     </row>
-    <row r="629" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A629" s="1">
         <v>44771</v>
       </c>
@@ -12588,7 +12594,7 @@
         <v>44771</v>
       </c>
     </row>
-    <row r="630" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A630" s="1">
         <v>44778</v>
       </c>
@@ -12596,7 +12602,7 @@
         <v>44778</v>
       </c>
     </row>
-    <row r="631" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A631" s="1">
         <v>44785</v>
       </c>
@@ -12604,7 +12610,7 @@
         <v>44785</v>
       </c>
     </row>
-    <row r="632" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A632" s="1">
         <v>44792</v>
       </c>
@@ -12612,7 +12618,7 @@
         <v>44792</v>
       </c>
     </row>
-    <row r="633" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A633" s="1">
         <v>44799</v>
       </c>
@@ -12620,7 +12626,7 @@
         <v>44799</v>
       </c>
     </row>
-    <row r="634" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A634" s="1">
         <v>44806</v>
       </c>
@@ -12628,7 +12634,7 @@
         <v>44806</v>
       </c>
     </row>
-    <row r="635" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A635" s="1">
         <v>44813</v>
       </c>
@@ -12636,7 +12642,7 @@
         <v>44813</v>
       </c>
     </row>
-    <row r="636" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A636" s="1">
         <v>44820</v>
       </c>
@@ -12644,7 +12650,7 @@
         <v>44820</v>
       </c>
     </row>
-    <row r="637" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A637" s="1">
         <v>44827</v>
       </c>
@@ -12652,7 +12658,7 @@
         <v>44827</v>
       </c>
     </row>
-    <row r="638" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A638" s="1">
         <v>44834</v>
       </c>
@@ -12660,7 +12666,7 @@
         <v>44834</v>
       </c>
     </row>
-    <row r="639" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A639" s="1">
         <v>44841</v>
       </c>
@@ -12668,7 +12674,7 @@
         <v>44841</v>
       </c>
     </row>
-    <row r="640" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A640" s="1">
         <v>44848</v>
       </c>
@@ -12676,7 +12682,7 @@
         <v>44848</v>
       </c>
     </row>
-    <row r="641" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A641" s="1">
         <v>44855</v>
       </c>
@@ -12684,7 +12690,7 @@
         <v>44855</v>
       </c>
     </row>
-    <row r="642" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A642" s="1">
         <v>44862</v>
       </c>
@@ -12692,7 +12698,7 @@
         <v>44862</v>
       </c>
     </row>
-    <row r="643" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A643" s="1">
         <v>44869</v>
       </c>
@@ -12700,7 +12706,7 @@
         <v>44869</v>
       </c>
     </row>
-    <row r="644" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A644" s="1">
         <v>44876</v>
       </c>
@@ -12708,7 +12714,7 @@
         <v>44876</v>
       </c>
     </row>
-    <row r="645" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A645" s="1">
         <v>44883</v>
       </c>
@@ -12716,7 +12722,7 @@
         <v>44883</v>
       </c>
     </row>
-    <row r="646" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A646" s="1">
         <v>44890</v>
       </c>
@@ -12724,7 +12730,7 @@
         <v>44890</v>
       </c>
     </row>
-    <row r="647" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A647" s="1">
         <v>44897</v>
       </c>
@@ -12732,7 +12738,7 @@
         <v>44897</v>
       </c>
     </row>
-    <row r="648" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A648" s="1">
         <v>44904</v>
       </c>
@@ -12740,7 +12746,7 @@
         <v>44904</v>
       </c>
     </row>
-    <row r="649" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A649" s="1">
         <v>44911</v>
       </c>
@@ -12748,7 +12754,7 @@
         <v>44911</v>
       </c>
     </row>
-    <row r="650" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A650" s="1">
         <v>44918</v>
       </c>
@@ -12756,7 +12762,7 @@
         <v>44918</v>
       </c>
     </row>
-    <row r="651" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A651" s="1">
         <v>44925</v>
       </c>
@@ -12764,7 +12770,7 @@
         <v>44925</v>
       </c>
     </row>
-    <row r="652" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A652" s="1">
         <v>44932</v>
       </c>
@@ -12772,7 +12778,7 @@
         <v>44932</v>
       </c>
     </row>
-    <row r="653" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A653" s="1">
         <v>44939</v>
       </c>
@@ -12780,7 +12786,7 @@
         <v>44939</v>
       </c>
     </row>
-    <row r="654" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A654" s="1">
         <v>44946</v>
       </c>
@@ -12788,7 +12794,7 @@
         <v>44946</v>
       </c>
     </row>
-    <row r="655" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A655" s="1">
         <v>44953</v>
       </c>
@@ -12796,7 +12802,7 @@
         <v>44953</v>
       </c>
     </row>
-    <row r="656" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A656" s="1">
         <v>44960</v>
       </c>
@@ -12804,7 +12810,7 @@
         <v>44960</v>
       </c>
     </row>
-    <row r="657" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A657" s="1">
         <v>44967</v>
       </c>
@@ -12812,7 +12818,7 @@
         <v>44967</v>
       </c>
     </row>
-    <row r="658" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A658" s="1">
         <v>44974</v>
       </c>
@@ -12820,7 +12826,7 @@
         <v>44974</v>
       </c>
     </row>
-    <row r="659" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A659" s="1">
         <v>44981</v>
       </c>
@@ -12828,7 +12834,7 @@
         <v>44981</v>
       </c>
     </row>
-    <row r="660" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A660" s="1">
         <v>44988</v>
       </c>
@@ -12836,7 +12842,7 @@
         <v>44988</v>
       </c>
     </row>
-    <row r="661" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A661" s="1">
         <v>44995</v>
       </c>
@@ -12844,7 +12850,7 @@
         <v>44995</v>
       </c>
     </row>
-    <row r="662" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A662" s="1">
         <v>45002</v>
       </c>
@@ -12852,7 +12858,7 @@
         <v>45002</v>
       </c>
     </row>
-    <row r="663" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A663" s="1">
         <v>45009</v>
       </c>
@@ -12860,7 +12866,7 @@
         <v>45009</v>
       </c>
     </row>
-    <row r="664" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A664" s="1">
         <v>45016</v>
       </c>
@@ -12868,7 +12874,7 @@
         <v>45016</v>
       </c>
     </row>
-    <row r="665" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A665" s="1">
         <v>45023</v>
       </c>
@@ -12876,7 +12882,7 @@
         <v>45023</v>
       </c>
     </row>
-    <row r="666" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A666" s="1">
         <v>45030</v>
       </c>
@@ -12884,7 +12890,7 @@
         <v>45030</v>
       </c>
     </row>
-    <row r="667" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A667" s="1">
         <v>45037</v>
       </c>
@@ -12892,7 +12898,7 @@
         <v>45037</v>
       </c>
     </row>
-    <row r="668" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A668" s="1">
         <v>45044</v>
       </c>
@@ -12900,7 +12906,7 @@
         <v>45044</v>
       </c>
     </row>
-    <row r="669" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A669" s="1">
         <v>45051</v>
       </c>
@@ -12908,7 +12914,7 @@
         <v>45051</v>
       </c>
     </row>
-    <row r="670" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A670" s="1">
         <v>45058</v>
       </c>
@@ -12916,7 +12922,7 @@
         <v>45058</v>
       </c>
     </row>
-    <row r="671" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A671" s="1">
         <v>45065</v>
       </c>
@@ -12924,7 +12930,7 @@
         <v>45065</v>
       </c>
     </row>
-    <row r="672" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A672" s="1">
         <v>45072</v>
       </c>
@@ -12932,7 +12938,7 @@
         <v>45072</v>
       </c>
     </row>
-    <row r="673" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A673" s="1">
         <v>45079</v>
       </c>
@@ -12940,7 +12946,7 @@
         <v>45079</v>
       </c>
     </row>
-    <row r="674" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A674" s="1">
         <v>45086</v>
       </c>
@@ -12948,7 +12954,7 @@
         <v>45086</v>
       </c>
     </row>
-    <row r="675" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A675" s="1">
         <v>45093</v>
       </c>
@@ -12956,7 +12962,7 @@
         <v>45093</v>
       </c>
     </row>
-    <row r="676" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A676" s="1">
         <v>45100</v>
       </c>
@@ -12964,7 +12970,7 @@
         <v>45100</v>
       </c>
     </row>
-    <row r="677" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A677" s="1">
         <v>45107</v>
       </c>
@@ -12972,7 +12978,7 @@
         <v>45107</v>
       </c>
     </row>
-    <row r="678" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A678" s="1">
         <v>45114</v>
       </c>
@@ -12980,7 +12986,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="679" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A679" s="1">
         <v>45121</v>
       </c>
@@ -12988,7 +12994,7 @@
         <v>45121</v>
       </c>
     </row>
-    <row r="680" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A680" s="1">
         <v>45128</v>
       </c>
@@ -12996,7 +13002,7 @@
         <v>45128</v>
       </c>
     </row>
-    <row r="681" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A681" s="1">
         <v>45135</v>
       </c>
@@ -13004,7 +13010,7 @@
         <v>45135</v>
       </c>
     </row>
-    <row r="682" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A682" s="1">
         <v>45142</v>
       </c>
@@ -13012,7 +13018,7 @@
         <v>45142</v>
       </c>
     </row>
-    <row r="683" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A683" s="1">
         <v>45149</v>
       </c>
@@ -13020,7 +13026,7 @@
         <v>45149</v>
       </c>
     </row>
-    <row r="684" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A684" s="1">
         <v>45156</v>
       </c>
@@ -13028,7 +13034,7 @@
         <v>45156</v>
       </c>
     </row>
-    <row r="685" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A685" s="1">
         <v>45163</v>
       </c>
@@ -13036,7 +13042,7 @@
         <v>45163</v>
       </c>
     </row>
-    <row r="686" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A686" s="1">
         <v>45170</v>
       </c>
@@ -13044,7 +13050,7 @@
         <v>45170</v>
       </c>
     </row>
-    <row r="687" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A687" s="1">
         <v>45177</v>
       </c>
@@ -13052,7 +13058,7 @@
         <v>45177</v>
       </c>
     </row>
-    <row r="688" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A688" s="1">
         <v>45184</v>
       </c>
@@ -13060,7 +13066,7 @@
         <v>45184</v>
       </c>
     </row>
-    <row r="689" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A689" s="1">
         <v>45191</v>
       </c>
@@ -13068,7 +13074,7 @@
         <v>45191</v>
       </c>
     </row>
-    <row r="690" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A690" s="1">
         <v>45198</v>
       </c>
@@ -13076,7 +13082,7 @@
         <v>45198</v>
       </c>
     </row>
-    <row r="691" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A691" s="1">
         <v>45205</v>
       </c>
@@ -13084,7 +13090,7 @@
         <v>45205</v>
       </c>
     </row>
-    <row r="692" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A692" s="1">
         <v>45212</v>
       </c>
@@ -13092,7 +13098,7 @@
         <v>45212</v>
       </c>
     </row>
-    <row r="693" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A693" s="1">
         <v>45219</v>
       </c>
@@ -13100,7 +13106,7 @@
         <v>45219</v>
       </c>
     </row>
-    <row r="694" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A694" s="1">
         <v>45226</v>
       </c>
@@ -13108,7 +13114,7 @@
         <v>45226</v>
       </c>
     </row>
-    <row r="695" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A695" s="1">
         <v>45233</v>
       </c>
@@ -13116,7 +13122,7 @@
         <v>45233</v>
       </c>
     </row>
-    <row r="696" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A696" s="1">
         <v>45240</v>
       </c>
@@ -13124,7 +13130,7 @@
         <v>45240</v>
       </c>
     </row>
-    <row r="697" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A697" s="1">
         <v>45247</v>
       </c>
@@ -13132,7 +13138,7 @@
         <v>45247</v>
       </c>
     </row>
-    <row r="698" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A698" s="1">
         <v>45254</v>
       </c>
@@ -13140,7 +13146,7 @@
         <v>45254</v>
       </c>
     </row>
-    <row r="699" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A699" s="1">
         <v>45261</v>
       </c>
@@ -13148,7 +13154,7 @@
         <v>45261</v>
       </c>
     </row>
-    <row r="700" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A700" s="1">
         <v>45268</v>
       </c>
@@ -13156,7 +13162,7 @@
         <v>45268</v>
       </c>
     </row>
-    <row r="701" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A701" s="1">
         <v>45275</v>
       </c>
@@ -13164,7 +13170,7 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="702" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A702" s="1">
         <v>45282</v>
       </c>
@@ -13172,7 +13178,7 @@
         <v>45282</v>
       </c>
     </row>
-    <row r="703" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A703" s="1">
         <v>45289</v>
       </c>
@@ -13180,7 +13186,7 @@
         <v>45289</v>
       </c>
     </row>
-    <row r="704" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A704" s="1">
         <v>45296</v>
       </c>
@@ -13188,7 +13194,7 @@
         <v>45296</v>
       </c>
     </row>
-    <row r="705" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A705" s="1">
         <v>45303</v>
       </c>
@@ -13196,7 +13202,7 @@
         <v>45303</v>
       </c>
     </row>
-    <row r="706" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A706" s="1">
         <v>45310</v>
       </c>
@@ -13204,7 +13210,7 @@
         <v>45310</v>
       </c>
     </row>
-    <row r="707" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A707" s="1">
         <v>45317</v>
       </c>
@@ -13212,7 +13218,7 @@
         <v>45317</v>
       </c>
     </row>
-    <row r="708" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A708" s="1">
         <v>45324</v>
       </c>
@@ -13220,7 +13226,7 @@
         <v>45324</v>
       </c>
     </row>
-    <row r="709" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A709" s="1">
         <v>45331</v>
       </c>
@@ -13228,7 +13234,7 @@
         <v>45331</v>
       </c>
     </row>
-    <row r="710" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A710" s="1">
         <v>45338</v>
       </c>
@@ -13236,7 +13242,7 @@
         <v>45338</v>
       </c>
     </row>
-    <row r="711" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A711" s="1">
         <v>45345</v>
       </c>
@@ -13244,7 +13250,7 @@
         <v>45345</v>
       </c>
     </row>
-    <row r="712" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A712" s="1">
         <v>45352</v>
       </c>
@@ -13252,7 +13258,7 @@
         <v>45352</v>
       </c>
     </row>
-    <row r="713" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A713" s="1">
         <v>45359</v>
       </c>
@@ -13260,7 +13266,7 @@
         <v>45359</v>
       </c>
     </row>
-    <row r="714" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A714" s="1">
         <v>45366</v>
       </c>
@@ -13268,7 +13274,7 @@
         <v>45366</v>
       </c>
     </row>
-    <row r="715" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A715" s="1">
         <v>45373</v>
       </c>
@@ -13276,7 +13282,7 @@
         <v>45373</v>
       </c>
     </row>
-    <row r="716" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A716" s="1">
         <v>45380</v>
       </c>
@@ -13284,7 +13290,7 @@
         <v>45380</v>
       </c>
     </row>
-    <row r="717" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A717" s="1">
         <v>45387</v>
       </c>
@@ -13292,7 +13298,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="718" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A718" s="1">
         <v>45394</v>
       </c>
@@ -13300,7 +13306,7 @@
         <v>45394</v>
       </c>
     </row>
-    <row r="719" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A719" s="1">
         <v>45401</v>
       </c>
@@ -13308,7 +13314,7 @@
         <v>45401</v>
       </c>
     </row>
-    <row r="720" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A720" s="1">
         <v>45408</v>
       </c>
@@ -13316,7 +13322,7 @@
         <v>45408</v>
       </c>
     </row>
-    <row r="721" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A721" s="1">
         <v>45415</v>
       </c>
@@ -13324,7 +13330,7 @@
         <v>45415</v>
       </c>
     </row>
-    <row r="722" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A722" s="1">
         <v>45422</v>
       </c>
@@ -13332,7 +13338,7 @@
         <v>45422</v>
       </c>
     </row>
-    <row r="723" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A723" s="1">
         <v>45429</v>
       </c>
@@ -13340,7 +13346,7 @@
         <v>45429</v>
       </c>
     </row>
-    <row r="724" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A724" s="1">
         <v>45436</v>
       </c>
@@ -13348,7 +13354,7 @@
         <v>45436</v>
       </c>
     </row>
-    <row r="725" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A725" s="1">
         <v>45443</v>
       </c>
@@ -13356,7 +13362,7 @@
         <v>45443</v>
       </c>
     </row>
-    <row r="726" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A726" s="1">
         <v>45450</v>
       </c>
@@ -13364,7 +13370,7 @@
         <v>45450</v>
       </c>
     </row>
-    <row r="727" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A727" s="1">
         <v>45457</v>
       </c>
@@ -13372,7 +13378,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="728" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A728" s="1">
         <v>45464</v>
       </c>
@@ -13383,7 +13389,7 @@
         <v>1627.4</v>
       </c>
     </row>
-    <row r="729" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A729" s="1">
         <v>45471</v>
       </c>
@@ -13391,7 +13397,7 @@
         <v>45471</v>
       </c>
     </row>
-    <row r="730" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A730" s="1">
         <v>45478</v>
       </c>
@@ -13399,7 +13405,7 @@
         <v>45478</v>
       </c>
     </row>
-    <row r="731" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A731" s="1">
         <v>45485</v>
       </c>
@@ -13407,7 +13413,7 @@
         <v>45485</v>
       </c>
     </row>
-    <row r="732" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A732" s="1">
         <v>45492</v>
       </c>
@@ -13415,7 +13421,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="733" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A733" s="1">
         <v>45499</v>
       </c>
@@ -13423,7 +13429,7 @@
         <v>45499</v>
       </c>
     </row>
-    <row r="734" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A734" s="1">
         <v>45506</v>
       </c>
@@ -13431,7 +13437,7 @@
         <v>45506</v>
       </c>
     </row>
-    <row r="735" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A735" s="1">
         <v>45513</v>
       </c>
@@ -13439,7 +13445,7 @@
         <v>45513</v>
       </c>
     </row>
-    <row r="736" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A736" s="1">
         <v>45520</v>
       </c>
@@ -13447,7 +13453,7 @@
         <v>45520</v>
       </c>
     </row>
-    <row r="737" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A737" s="1">
         <v>45527</v>
       </c>
@@ -13455,7 +13461,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="738" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A738" s="1">
         <v>45534</v>
       </c>
@@ -13463,7 +13469,7 @@
         <v>45534</v>
       </c>
     </row>
-    <row r="739" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A739" s="1">
         <v>45541</v>
       </c>
@@ -13471,7 +13477,7 @@
         <v>45541</v>
       </c>
     </row>
-    <row r="740" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A740" s="1">
         <v>45548</v>
       </c>
@@ -13479,7 +13485,7 @@
         <v>45548</v>
       </c>
     </row>
-    <row r="741" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A741" s="1">
         <v>45555</v>
       </c>
@@ -13487,7 +13493,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="742" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A742" s="1">
         <v>45562</v>
       </c>
@@ -13495,7 +13501,7 @@
         <v>45562</v>
       </c>
     </row>
-    <row r="743" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A743" s="1">
         <v>45569</v>
       </c>
@@ -13503,7 +13509,7 @@
         <v>45569</v>
       </c>
     </row>
-    <row r="744" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A744" s="1">
         <v>45576</v>
       </c>
@@ -13511,7 +13517,7 @@
         <v>45576</v>
       </c>
     </row>
-    <row r="745" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A745" s="1">
         <v>45583</v>
       </c>
@@ -13519,7 +13525,7 @@
         <v>45583</v>
       </c>
     </row>
-    <row r="746" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A746" s="1">
         <v>45590</v>
       </c>
@@ -13527,7 +13533,7 @@
         <v>45590</v>
       </c>
     </row>
-    <row r="747" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A747" s="1">
         <v>45597</v>
       </c>
@@ -13535,7 +13541,7 @@
         <v>45597</v>
       </c>
     </row>
-    <row r="748" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A748" s="1">
         <v>45604</v>
       </c>
@@ -13543,7 +13549,7 @@
         <v>45604</v>
       </c>
     </row>
-    <row r="749" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A749" s="1">
         <v>45611</v>
       </c>
@@ -13551,7 +13557,7 @@
         <v>45611</v>
       </c>
     </row>
-    <row r="750" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A750" s="1">
         <v>45618</v>
       </c>
@@ -13559,7 +13565,7 @@
         <v>45618</v>
       </c>
     </row>
-    <row r="751" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A751" s="1">
         <v>45625</v>
       </c>
@@ -13567,7 +13573,7 @@
         <v>45625</v>
       </c>
     </row>
-    <row r="752" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A752" s="1">
         <v>45632</v>
       </c>
@@ -13575,7 +13581,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="753" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A753" s="1">
         <v>45639</v>
       </c>
@@ -13583,7 +13589,7 @@
         <v>45639</v>
       </c>
     </row>
-    <row r="754" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A754" s="1">
         <v>45646</v>
       </c>
@@ -13591,7 +13597,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="755" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A755" s="1">
         <v>45653</v>
       </c>
@@ -13599,7 +13605,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="756" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A756" s="1">
         <v>45660</v>
       </c>
@@ -13607,7 +13613,7 @@
         <v>45660</v>
       </c>
     </row>
-    <row r="757" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A757" s="1">
         <v>45667</v>
       </c>
@@ -13615,7 +13621,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="758" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A758" s="1">
         <v>45674</v>
       </c>
@@ -13623,7 +13629,7 @@
         <v>45674</v>
       </c>
     </row>
-    <row r="759" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A759" s="1">
         <v>45681</v>
       </c>
@@ -13631,7 +13637,7 @@
         <v>45681</v>
       </c>
     </row>
-    <row r="760" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A760" s="1">
         <v>45688</v>
       </c>
@@ -13639,7 +13645,7 @@
         <v>45688</v>
       </c>
     </row>
-    <row r="761" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A761" s="1">
         <v>45695</v>
       </c>
@@ -13647,7 +13653,7 @@
         <v>45695</v>
       </c>
     </row>
-    <row r="762" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A762" s="1">
         <v>45702</v>
       </c>
@@ -13655,7 +13661,7 @@
         <v>45702</v>
       </c>
     </row>
-    <row r="763" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A763" s="1">
         <v>45709</v>
       </c>
@@ -13663,7 +13669,7 @@
         <v>45709</v>
       </c>
     </row>
-    <row r="764" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A764" s="1">
         <v>45716</v>
       </c>
@@ -13671,7 +13677,7 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="765" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A765" s="1">
         <v>45723</v>
       </c>
@@ -13679,7 +13685,7 @@
         <v>45723</v>
       </c>
     </row>
-    <row r="766" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A766" s="1">
         <v>45730</v>
       </c>
@@ -13687,7 +13693,7 @@
         <v>45730</v>
       </c>
     </row>
-    <row r="767" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A767" s="1">
         <v>45737</v>
       </c>
@@ -13695,7 +13701,7 @@
         <v>45737</v>
       </c>
     </row>
-    <row r="768" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A768" s="1">
         <v>45744</v>
       </c>
@@ -13703,7 +13709,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="769" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A769" s="1">
         <v>45751</v>
       </c>
@@ -13711,7 +13717,7 @@
         <v>45751</v>
       </c>
     </row>
-    <row r="770" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A770" s="1">
         <v>45758</v>
       </c>
@@ -13719,7 +13725,7 @@
         <v>45758</v>
       </c>
     </row>
-    <row r="771" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A771" s="1">
         <v>45765</v>
       </c>
@@ -13727,7 +13733,7 @@
         <v>45765</v>
       </c>
     </row>
-    <row r="772" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A772" s="1">
         <v>45772</v>
       </c>
@@ -13735,7 +13741,7 @@
         <v>45772</v>
       </c>
     </row>
-    <row r="773" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A773" s="1">
         <v>45779</v>
       </c>
@@ -13743,7 +13749,7 @@
         <v>45779</v>
       </c>
     </row>
-    <row r="774" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A774" s="1">
         <v>45786</v>
       </c>
@@ -13751,7 +13757,7 @@
         <v>45786</v>
       </c>
     </row>
-    <row r="775" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A775" s="1">
         <v>45793</v>
       </c>
@@ -13759,7 +13765,7 @@
         <v>45793</v>
       </c>
     </row>
-    <row r="776" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A776" s="1">
         <v>45800</v>
       </c>
@@ -13767,7 +13773,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="777" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A777" s="1">
         <v>45807</v>
       </c>
@@ -13775,7 +13781,7 @@
         <v>45807</v>
       </c>
     </row>
-    <row r="778" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A778" s="1">
         <v>45814</v>
       </c>
@@ -13783,7 +13789,7 @@
         <v>45814</v>
       </c>
     </row>
-    <row r="779" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A779" s="1">
         <v>45821</v>
       </c>
@@ -13791,7 +13797,7 @@
         <v>45821</v>
       </c>
     </row>
-    <row r="780" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A780" s="1">
         <v>45828</v>
       </c>
@@ -13802,7 +13808,7 @@
         <v>2158.19</v>
       </c>
     </row>
-    <row r="781" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A781" s="1">
         <v>45835</v>
       </c>
@@ -13813,7 +13819,7 @@
         <v>2158.19</v>
       </c>
     </row>
-    <row r="782" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A782" s="1">
         <v>45842</v>
       </c>
@@ -13821,7 +13827,7 @@
         <v>45842</v>
       </c>
     </row>
-    <row r="783" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A783" s="1">
         <v>45849</v>
       </c>
@@ -13829,7 +13835,7 @@
         <v>45849</v>
       </c>
     </row>
-    <row r="784" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A784" s="1">
         <v>45856</v>
       </c>
@@ -13837,7 +13843,7 @@
         <v>45856</v>
       </c>
     </row>
-    <row r="785" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A785" s="1">
         <v>45863</v>
       </c>
@@ -13845,7 +13851,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="786" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A786" s="1">
         <v>45870</v>
       </c>
@@ -13853,7 +13859,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="787" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A787" s="1">
         <v>45877</v>
       </c>
@@ -13861,7 +13867,7 @@
         <v>45877</v>
       </c>
     </row>
-    <row r="788" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A788" s="1">
         <v>45884</v>
       </c>
@@ -13869,7 +13875,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="789" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A789" s="1">
         <v>45891</v>
       </c>
@@ -13877,7 +13883,7 @@
         <v>45891</v>
       </c>
     </row>
-    <row r="790" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A790" s="1">
         <v>45898</v>
       </c>
@@ -13885,7 +13891,7 @@
         <v>45898</v>
       </c>
     </row>
-    <row r="791" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A791" s="1">
         <v>45905</v>
       </c>
@@ -13893,7 +13899,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="792" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A792" s="1">
         <v>45912</v>
       </c>
@@ -13901,7 +13907,7 @@
         <v>45912</v>
       </c>
     </row>
-    <row r="793" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A793" s="1">
         <v>45919</v>
       </c>
@@ -13909,7 +13915,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="794" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A794" s="1">
         <v>45926</v>
       </c>
@@ -13917,7 +13923,7 @@
         <v>45926</v>
       </c>
     </row>
-    <row r="795" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A795" s="1">
         <v>45933</v>
       </c>
@@ -13925,7 +13931,7 @@
         <v>45933</v>
       </c>
     </row>
-    <row r="796" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A796" s="1">
         <v>45940</v>
       </c>
@@ -13933,7 +13939,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="797" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A797" s="1">
         <v>45947</v>
       </c>
@@ -13941,7 +13947,7 @@
         <v>45947</v>
       </c>
     </row>
-    <row r="798" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A798" s="1">
         <v>45954</v>
       </c>
@@ -13949,7 +13955,7 @@
         <v>45954</v>
       </c>
     </row>
-    <row r="799" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A799" s="1">
         <v>45961</v>
       </c>
@@ -13957,7 +13963,7 @@
         <v>45961</v>
       </c>
     </row>
-    <row r="800" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A800" s="1">
         <v>45968</v>
       </c>
@@ -13965,7 +13971,7 @@
         <v>45968</v>
       </c>
     </row>
-    <row r="801" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A801" s="1">
         <v>45975</v>
       </c>
@@ -13973,7 +13979,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="802" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A802" s="1">
         <v>45982</v>
       </c>
@@ -13981,7 +13987,7 @@
         <v>45982</v>
       </c>
     </row>
-    <row r="803" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A803" s="1">
         <v>45989</v>
       </c>
@@ -13989,7 +13995,7 @@
         <v>45989</v>
       </c>
     </row>
-    <row r="804" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A804" s="1">
         <v>45996</v>
       </c>
@@ -13997,7 +14003,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="805" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A805" s="1">
         <v>46003</v>
       </c>
@@ -14005,7 +14011,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="806" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A806" s="1">
         <v>46010</v>
       </c>
@@ -14013,7 +14019,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="807" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A807" s="1">
         <v>46017</v>
       </c>
@@ -14036,7 +14042,7 @@
       <c r="N807" s="10"/>
       <c r="O807" s="10"/>
     </row>
-    <row r="808" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A808" s="1">
         <v>46024</v>
       </c>
@@ -14079,7 +14085,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="809" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A809" s="1">
         <v>46031</v>
       </c>
@@ -14122,7 +14128,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="810" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A810" s="1">
         <v>46038</v>
       </c>
@@ -14165,7 +14171,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="811" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A811" s="1">
         <v>46045</v>
       </c>
@@ -14208,7 +14214,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="812" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A812" s="1">
         <v>46052</v>
       </c>
@@ -14251,7 +14257,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="813" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A813" s="1">
         <v>46059</v>
       </c>
@@ -14294,7 +14300,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="814" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A814" s="1">
         <v>46066</v>
       </c>
@@ -14337,7 +14343,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="815" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A815" s="1">
         <v>46073</v>
       </c>
@@ -14380,7 +14386,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="816" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A816" s="1">
         <v>46080</v>
       </c>
@@ -14423,7 +14429,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="817" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A817" s="1">
         <v>46087</v>
       </c>
@@ -14466,7 +14472,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="818" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A818" s="1">
         <v>46094</v>
       </c>
@@ -14509,7 +14515,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="819" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A819" s="1">
         <v>46101</v>
       </c>
@@ -14552,7 +14558,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="820" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A820" s="1">
         <v>46108</v>
       </c>
@@ -14595,7 +14601,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="821" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A821" s="1">
         <v>46115</v>
       </c>
@@ -14638,7 +14644,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="822" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A822" s="1">
         <v>46122</v>
       </c>
@@ -14661,7 +14667,7 @@
       <c r="N822" s="3"/>
       <c r="O822" s="3"/>
     </row>
-    <row r="823" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A823" s="1">
         <v>46129</v>
       </c>
@@ -14684,7 +14690,7 @@
       <c r="N823" s="3"/>
       <c r="O823" s="3"/>
     </row>
-    <row r="824" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A824" s="1">
         <v>46136</v>
       </c>
@@ -14707,7 +14713,7 @@
       <c r="N824" s="3"/>
       <c r="O824" s="3"/>
     </row>
-    <row r="825" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A825" s="1">
         <v>46143</v>
       </c>
@@ -14750,7 +14756,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="826" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A826" s="1">
         <v>46150</v>
       </c>
@@ -14793,7 +14799,7 @@
         <v>76000</v>
       </c>
     </row>
-    <row r="827" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A827" s="1">
         <v>46157</v>
       </c>
@@ -14836,7 +14842,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="828" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A828" s="1">
         <v>46164</v>
       </c>
@@ -14879,7 +14885,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="829" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A829" s="1">
         <v>46171</v>
       </c>
@@ -14922,7 +14928,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="830" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A830" s="1">
         <v>46178</v>
       </c>
@@ -14963,7 +14969,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="831" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A831" s="1">
         <v>46185</v>
       </c>
@@ -15001,6 +15007,47 @@
         <v>71000</v>
       </c>
       <c r="O831" s="4">
+        <v>78000</v>
+      </c>
+    </row>
+    <row r="832" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A832" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B832" s="1">
+        <v>46192</v>
+      </c>
+      <c r="E832" s="13">
+        <v>2326.67</v>
+      </c>
+      <c r="F832" s="4">
+        <v>11250</v>
+      </c>
+      <c r="G832" s="4">
+        <v>17750</v>
+      </c>
+      <c r="H832" s="4">
+        <v>30000</v>
+      </c>
+      <c r="I832" s="4">
+        <v>33500</v>
+      </c>
+      <c r="J832" s="4">
+        <v>38000</v>
+      </c>
+      <c r="K832" s="4">
+        <v>40000</v>
+      </c>
+      <c r="L832" s="4">
+        <v>46000</v>
+      </c>
+      <c r="M832" s="4">
+        <v>57000</v>
+      </c>
+      <c r="N832" s="4">
+        <v>71000</v>
+      </c>
+      <c r="O832" s="4">
         <v>78000</v>
       </c>
     </row>
@@ -15012,7 +15059,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02768588-2FF0-42C1-8A18-87D4CAFE9D17}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -15022,12 +15069,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A6084AF-43C5-4F58-881A-79CFC1D1F25A}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B2" s="8" t="s">
         <v>15</v>
       </c>
@@ -15035,7 +15082,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B3" s="8" t="s">
         <v>17</v>
       </c>

--- a/data/freight/HARPEX.xlsx
+++ b/data/freight/HARPEX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79912C2-376B-407D-AA79-1D81338721C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82C67B9-2401-7145-B87A-A45AFC3761B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
+    <workbookView xWindow="25700" yWindow="3980" windowWidth="23260" windowHeight="14860" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
   <sheets>
     <sheet name="HARPEX" sheetId="1" r:id="rId1"/>
@@ -199,9 +199,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -219,7 +219,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4545,6 +4545,9 @@
                 </c:pt>
                 <c:pt idx="726">
                   <c:v>1627.4</c:v>
+                </c:pt>
+                <c:pt idx="727">
+                  <c:v>1712.39</c:v>
                 </c:pt>
                 <c:pt idx="778">
                   <c:v>2158.19</c:v>
@@ -5442,9 +5445,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5482,7 +5485,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5588,7 +5591,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5730,7 +5733,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5739,17 +5742,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
   <dimension ref="A1:P832"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" style="16" customWidth="1"/>
     <col min="4" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="15" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="15" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -5797,7 +5800,7 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>40383</v>
       </c>
@@ -5808,7 +5811,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>40390</v>
       </c>
@@ -5819,7 +5822,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>40397</v>
       </c>
@@ -5830,7 +5833,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>40404</v>
       </c>
@@ -5841,7 +5844,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>40411</v>
       </c>
@@ -5852,7 +5855,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>40418</v>
       </c>
@@ -5863,7 +5866,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>40425</v>
       </c>
@@ -5874,7 +5877,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>40432</v>
       </c>
@@ -5885,7 +5888,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>40439</v>
       </c>
@@ -5896,7 +5899,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>40446</v>
       </c>
@@ -5907,7 +5910,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>40453</v>
       </c>
@@ -5918,7 +5921,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>40460</v>
       </c>
@@ -5929,7 +5932,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>40467</v>
       </c>
@@ -5940,7 +5943,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>40474</v>
       </c>
@@ -5951,7 +5954,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>40481</v>
       </c>
@@ -5962,7 +5965,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>40488</v>
       </c>
@@ -5973,7 +5976,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>40495</v>
       </c>
@@ -5984,7 +5987,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>40502</v>
       </c>
@@ -5995,7 +5998,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>40509</v>
       </c>
@@ -6006,7 +6009,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>40516</v>
       </c>
@@ -6017,7 +6020,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>40523</v>
       </c>
@@ -6028,7 +6031,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>40530</v>
       </c>
@@ -6039,7 +6042,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>40537</v>
       </c>
@@ -6050,7 +6053,7 @@
         <v>679.37</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>40544</v>
       </c>
@@ -6061,7 +6064,7 @@
         <v>696.35</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>40551</v>
       </c>
@@ -6072,7 +6075,7 @@
         <v>706.3</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>40558</v>
       </c>
@@ -6083,7 +6086,7 @@
         <v>719.55</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>40565</v>
       </c>
@@ -6094,7 +6097,7 @@
         <v>747.31</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>40572</v>
       </c>
@@ -6105,7 +6108,7 @@
         <v>764.29</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>40579</v>
       </c>
@@ -6116,7 +6119,7 @@
         <v>782.1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>40586</v>
       </c>
@@ -6127,7 +6130,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>40593</v>
       </c>
@@ -6138,7 +6141,7 @@
         <v>849.63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>40600</v>
       </c>
@@ -6149,7 +6152,7 @@
         <v>861.23</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>40607</v>
       </c>
@@ -6160,7 +6163,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>40614</v>
       </c>
@@ -6171,7 +6174,7 @@
         <v>879.04</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>40621</v>
       </c>
@@ -6182,7 +6185,7 @@
         <v>882.35</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>40628</v>
       </c>
@@ -6193,7 +6196,7 @@
         <v>900.99</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>40635</v>
       </c>
@@ -6204,7 +6207,7 @@
         <v>892.29</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>40642</v>
       </c>
@@ -6215,7 +6218,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>40649</v>
       </c>
@@ -6226,7 +6229,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>40656</v>
       </c>
@@ -6237,7 +6240,7 @@
         <v>879.87</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>40663</v>
       </c>
@@ -6248,7 +6251,7 @@
         <v>875.72</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>40670</v>
       </c>
@@ -6259,7 +6262,7 @@
         <v>874.48</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>40677</v>
       </c>
@@ -6270,7 +6273,7 @@
         <v>877.38</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>40684</v>
       </c>
@@ -6281,7 +6284,7 @@
         <v>876.14</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>40691</v>
       </c>
@@ -6292,7 +6295,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>40698</v>
       </c>
@@ -6303,7 +6306,7 @@
         <v>865.37</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>40705</v>
       </c>
@@ -6314,7 +6317,7 @@
         <v>856.67</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>40712</v>
       </c>
@@ -6325,7 +6328,7 @@
         <v>847.14</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>40719</v>
       </c>
@@ -6336,7 +6339,7 @@
         <v>831.4</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>40726</v>
       </c>
@@ -6347,7 +6350,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>40733</v>
       </c>
@@ -6358,7 +6361,7 @@
         <v>808.62</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>40740</v>
       </c>
@@ -6369,7 +6372,7 @@
         <v>775.06</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>40747</v>
       </c>
@@ -6380,7 +6383,7 @@
         <v>741.51</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>40754</v>
       </c>
@@ -6391,7 +6394,7 @@
         <v>719.97</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>40761</v>
       </c>
@@ -6402,7 +6405,7 @@
         <v>709.2</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>40768</v>
       </c>
@@ -6413,7 +6416,7 @@
         <v>671.91</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>40775</v>
       </c>
@@ -6424,7 +6427,7 @@
         <v>666.11</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>40782</v>
       </c>
@@ -6435,7 +6438,7 @@
         <v>657.83</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>40789</v>
       </c>
@@ -6446,7 +6449,7 @@
         <v>630.9</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>40796</v>
       </c>
@@ -6457,7 +6460,7 @@
         <v>621.38</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>40803</v>
       </c>
@@ -6468,7 +6471,7 @@
         <v>616.4</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>40810</v>
       </c>
@@ -6479,7 +6482,7 @@
         <v>555.1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>40817</v>
       </c>
@@ -6490,7 +6493,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>40824</v>
       </c>
@@ -6501,7 +6504,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>40831</v>
       </c>
@@ -6512,7 +6515,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>40838</v>
       </c>
@@ -6523,7 +6526,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>40845</v>
       </c>
@@ -6534,7 +6537,7 @@
         <v>445.32</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>40852</v>
       </c>
@@ -6545,7 +6548,7 @@
         <v>438.28</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>40859</v>
       </c>
@@ -6556,7 +6559,7 @@
         <v>437.45</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>40866</v>
       </c>
@@ -6567,7 +6570,7 @@
         <v>420.05</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>40873</v>
       </c>
@@ -6578,7 +6581,7 @@
         <v>417.98</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>40880</v>
       </c>
@@ -6589,7 +6592,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>40887</v>
       </c>
@@ -6600,7 +6603,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>40894</v>
       </c>
@@ -6611,7 +6614,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>40901</v>
       </c>
@@ -6622,7 +6625,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>40908</v>
       </c>
@@ -6633,7 +6636,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>40915</v>
       </c>
@@ -6644,7 +6647,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>40922</v>
       </c>
@@ -6655,7 +6658,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>40929</v>
       </c>
@@ -6666,7 +6669,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>40936</v>
       </c>
@@ -6677,7 +6680,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>40942</v>
       </c>
@@ -6688,7 +6691,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>40943</v>
       </c>
@@ -6699,7 +6702,7 @@
         <v>389.81</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>40950</v>
       </c>
@@ -6710,7 +6713,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>40957</v>
       </c>
@@ -6721,7 +6724,7 @@
         <v>375.31</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>40964</v>
       </c>
@@ -6732,7 +6735,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>40978</v>
       </c>
@@ -6743,7 +6746,7 @@
         <v>384.84</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>40985</v>
       </c>
@@ -6754,7 +6757,7 @@
         <v>393.12</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>40992</v>
       </c>
@@ -6765,7 +6768,7 @@
         <v>396.02</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>40999</v>
       </c>
@@ -6776,7 +6779,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>41006</v>
       </c>
@@ -6787,7 +6790,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>41013</v>
       </c>
@@ -6798,7 +6801,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>41020</v>
       </c>
@@ -6809,7 +6812,7 @@
         <v>416.32</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>41027</v>
       </c>
@@ -6820,7 +6823,7 @@
         <v>428.33</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>41034</v>
       </c>
@@ -6831,7 +6834,7 @@
         <v>440.35</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>41041</v>
       </c>
@@ -6842,7 +6845,7 @@
         <v>444.9</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>41048</v>
       </c>
@@ -6853,7 +6856,7 @@
         <v>457.33</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>41055</v>
       </c>
@@ -6864,7 +6867,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>41062</v>
       </c>
@@ -6875,7 +6878,7 @@
         <v>456.92</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>41069</v>
       </c>
@@ -6886,7 +6889,7 @@
         <v>451.12</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>41076</v>
       </c>
@@ -6897,7 +6900,7 @@
         <v>446.98</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>41083</v>
       </c>
@@ -6908,7 +6911,7 @@
         <v>437.86</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>41090</v>
       </c>
@@ -6919,7 +6922,7 @@
         <v>434.96</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>41097</v>
       </c>
@@ -6930,7 +6933,7 @@
         <v>430.41</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>41104</v>
       </c>
@@ -6941,7 +6944,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>41111</v>
       </c>
@@ -6952,7 +6955,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>41118</v>
       </c>
@@ -6963,7 +6966,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>41125</v>
       </c>
@@ -6974,7 +6977,7 @@
         <v>399.75</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>41132</v>
       </c>
@@ -6985,7 +6988,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>41139</v>
       </c>
@@ -6996,7 +6999,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>41146</v>
       </c>
@@ -7007,7 +7010,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>41153</v>
       </c>
@@ -7018,7 +7021,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>41160</v>
       </c>
@@ -7029,7 +7032,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>41167</v>
       </c>
@@ -7040,7 +7043,7 @@
         <v>386.08</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>41174</v>
       </c>
@@ -7051,7 +7054,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>41181</v>
       </c>
@@ -7062,7 +7065,7 @@
         <v>377.8</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>41188</v>
       </c>
@@ -7073,7 +7076,7 @@
         <v>373.65</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>41195</v>
       </c>
@@ -7084,7 +7087,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>41202</v>
       </c>
@@ -7095,7 +7098,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>41209</v>
       </c>
@@ -7106,7 +7109,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>41216</v>
       </c>
@@ -7117,7 +7120,7 @@
         <v>367.44</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>41223</v>
       </c>
@@ -7128,7 +7131,7 @@
         <v>366.61</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>41230</v>
       </c>
@@ -7139,7 +7142,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>41237</v>
       </c>
@@ -7150,7 +7153,7 @@
         <v>362.88</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>41244</v>
       </c>
@@ -7161,7 +7164,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>41251</v>
       </c>
@@ -7172,7 +7175,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>41258</v>
       </c>
@@ -7183,7 +7186,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>41265</v>
       </c>
@@ -7194,7 +7197,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>41272</v>
       </c>
@@ -7205,7 +7208,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>41279</v>
       </c>
@@ -7216,7 +7219,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>41286</v>
       </c>
@@ -7227,7 +7230,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>41293</v>
       </c>
@@ -7238,7 +7241,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>41300</v>
       </c>
@@ -7249,7 +7252,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>41307</v>
       </c>
@@ -7260,7 +7263,7 @@
         <v>366.2</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>41314</v>
       </c>
@@ -7271,7 +7274,7 @@
         <v>369.93</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>41321</v>
       </c>
@@ -7282,7 +7285,7 @@
         <v>372.41</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>41328</v>
       </c>
@@ -7293,7 +7296,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>41335</v>
       </c>
@@ -7304,7 +7307,7 @@
         <v>376.97</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>41342</v>
       </c>
@@ -7315,7 +7318,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>41349</v>
       </c>
@@ -7326,7 +7329,7 @@
         <v>382.35</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>41356</v>
       </c>
@@ -7337,7 +7340,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>41363</v>
       </c>
@@ -7348,7 +7351,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>41370</v>
       </c>
@@ -7359,7 +7362,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>41377</v>
       </c>
@@ -7370,7 +7373,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>41384</v>
       </c>
@@ -7381,7 +7384,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>41391</v>
       </c>
@@ -7392,7 +7395,7 @@
         <v>395.61</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>41398</v>
       </c>
@@ -7403,7 +7406,7 @@
         <v>396.85</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>41405</v>
       </c>
@@ -7414,7 +7417,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>41412</v>
       </c>
@@ -7425,7 +7428,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>41419</v>
       </c>
@@ -7436,7 +7439,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>41426</v>
       </c>
@@ -7447,7 +7450,7 @@
         <v>401.41</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>41433</v>
       </c>
@@ -7458,7 +7461,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>41440</v>
       </c>
@@ -7469,7 +7472,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>41447</v>
       </c>
@@ -7480,7 +7483,7 @@
         <v>400.58</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>41454</v>
       </c>
@@ -7491,7 +7494,7 @@
         <v>401.82</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>41461</v>
       </c>
@@ -7502,7 +7505,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>41468</v>
       </c>
@@ -7513,7 +7516,7 @@
         <v>398.51</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>41475</v>
       </c>
@@ -7524,7 +7527,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>41482</v>
       </c>
@@ -7535,7 +7538,7 @@
         <v>400.99</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>41489</v>
       </c>
@@ -7546,7 +7549,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>41496</v>
       </c>
@@ -7557,7 +7560,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>41503</v>
       </c>
@@ -7568,7 +7571,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>41510</v>
       </c>
@@ -7579,7 +7582,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>41517</v>
       </c>
@@ -7590,7 +7593,7 @@
         <v>404.72</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>41524</v>
       </c>
@@ -7601,7 +7604,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>41531</v>
       </c>
@@ -7612,7 +7615,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>41538</v>
       </c>
@@ -7623,7 +7626,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>41545</v>
       </c>
@@ -7634,7 +7637,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>41552</v>
       </c>
@@ -7645,7 +7648,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>41559</v>
       </c>
@@ -7656,7 +7659,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>41566</v>
       </c>
@@ -7667,7 +7670,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>41573</v>
       </c>
@@ -7678,7 +7681,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>41580</v>
       </c>
@@ -7689,7 +7692,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>41587</v>
       </c>
@@ -7700,7 +7703,7 @@
         <v>398.92</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>41594</v>
       </c>
@@ -7711,7 +7714,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>41601</v>
       </c>
@@ -7722,7 +7725,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>41608</v>
       </c>
@@ -7733,7 +7736,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>41615</v>
       </c>
@@ -7744,7 +7747,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>41622</v>
       </c>
@@ -7755,7 +7758,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>41629</v>
       </c>
@@ -7766,7 +7769,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>41636</v>
       </c>
@@ -7777,7 +7780,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>41643</v>
       </c>
@@ -7788,7 +7791,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>41650</v>
       </c>
@@ -7799,7 +7802,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>41657</v>
       </c>
@@ -7810,7 +7813,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>41664</v>
       </c>
@@ -7821,7 +7824,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>41671</v>
       </c>
@@ -7832,7 +7835,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>41678</v>
       </c>
@@ -7843,7 +7846,7 @@
         <v>387.74</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>41685</v>
       </c>
@@ -7854,7 +7857,7 @@
         <v>386.91</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>41692</v>
       </c>
@@ -7865,7 +7868,7 @@
         <v>385.25</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>41699</v>
       </c>
@@ -7876,7 +7879,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>41706</v>
       </c>
@@ -7887,7 +7890,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>41713</v>
       </c>
@@ -7898,7 +7901,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>41720</v>
       </c>
@@ -7909,7 +7912,7 @@
         <v>380.7</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>41727</v>
       </c>
@@ -7920,7 +7923,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>41734</v>
       </c>
@@ -7931,7 +7934,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>41741</v>
       </c>
@@ -7942,7 +7945,7 @@
         <v>386.5</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>41748</v>
       </c>
@@ -7953,7 +7956,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>41755</v>
       </c>
@@ -7964,7 +7967,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>41762</v>
       </c>
@@ -7975,7 +7978,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>41769</v>
       </c>
@@ -7986,7 +7989,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>41776</v>
       </c>
@@ -7997,7 +8000,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>41783</v>
       </c>
@@ -8008,7 +8011,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>41790</v>
       </c>
@@ -8019,7 +8022,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>41797</v>
       </c>
@@ -8030,7 +8033,7 @@
         <v>406.79</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>41804</v>
       </c>
@@ -8041,7 +8044,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>41811</v>
       </c>
@@ -8052,7 +8055,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>41818</v>
       </c>
@@ -8063,7 +8066,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>41825</v>
       </c>
@@ -8074,7 +8077,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <v>41832</v>
       </c>
@@ -8085,7 +8088,7 @@
         <v>409.28</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <v>41839</v>
       </c>
@@ -8096,7 +8099,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <v>41846</v>
       </c>
@@ -8107,7 +8110,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>41853</v>
       </c>
@@ -8118,7 +8121,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>41860</v>
       </c>
@@ -8129,7 +8132,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>41867</v>
       </c>
@@ -8140,7 +8143,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>41874</v>
       </c>
@@ -8151,7 +8154,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>41881</v>
       </c>
@@ -8162,7 +8165,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>41888</v>
       </c>
@@ -8173,7 +8176,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>41895</v>
       </c>
@@ -8184,7 +8187,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>41902</v>
       </c>
@@ -8195,7 +8198,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>41909</v>
       </c>
@@ -8206,7 +8209,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>41916</v>
       </c>
@@ -8217,7 +8220,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>41923</v>
       </c>
@@ -8228,7 +8231,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>41930</v>
       </c>
@@ -8239,7 +8242,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>41937</v>
       </c>
@@ -8250,7 +8253,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>41944</v>
       </c>
@@ -8261,7 +8264,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>41951</v>
       </c>
@@ -8272,7 +8275,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>41958</v>
       </c>
@@ -8283,7 +8286,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>41965</v>
       </c>
@@ -8294,7 +8297,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>41972</v>
       </c>
@@ -8305,7 +8308,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>41979</v>
       </c>
@@ -8316,7 +8319,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>41986</v>
       </c>
@@ -8327,7 +8330,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>41993</v>
       </c>
@@ -8338,7 +8341,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>42000</v>
       </c>
@@ -8349,7 +8352,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>42007</v>
       </c>
@@ -8360,7 +8363,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>42014</v>
       </c>
@@ -8371,7 +8374,7 @@
         <v>435.38</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>42021</v>
       </c>
@@ -8382,7 +8385,7 @@
         <v>441.59</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <v>42028</v>
       </c>
@@ -8393,7 +8396,7 @@
         <v>455.26</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <v>42035</v>
       </c>
@@ -8404,7 +8407,7 @@
         <v>461.47</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <v>42042</v>
       </c>
@@ -8415,7 +8418,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <v>42049</v>
       </c>
@@ -8426,7 +8429,7 @@
         <v>483.84</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <v>42056</v>
       </c>
@@ -8437,7 +8440,7 @@
         <v>494.2</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>42063</v>
       </c>
@@ -8448,7 +8451,7 @@
         <v>496.27</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <v>42070</v>
       </c>
@@ -8459,7 +8462,7 @@
         <v>502.49</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>42077</v>
       </c>
@@ -8470,7 +8473,7 @@
         <v>504.14</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>42084</v>
       </c>
@@ -8481,7 +8484,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>42091</v>
       </c>
@@ -8492,7 +8495,7 @@
         <v>561.72</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <v>42098</v>
       </c>
@@ -8503,7 +8506,7 @@
         <v>596.11</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>42105</v>
       </c>
@@ -8514,7 +8517,7 @@
         <v>614.75</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>42112</v>
       </c>
@@ -8525,7 +8528,7 @@
         <v>612.67999999999995</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>42119</v>
       </c>
@@ -8536,7 +8539,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>42126</v>
       </c>
@@ -8547,7 +8550,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>42133</v>
       </c>
@@ -8558,7 +8561,7 @@
         <v>626.76</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>42140</v>
       </c>
@@ -8569,7 +8572,7 @@
         <v>640.02</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>42147</v>
       </c>
@@ -8580,7 +8583,7 @@
         <v>642.91999999999996</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>42154</v>
       </c>
@@ -8591,7 +8594,7 @@
         <v>644.57000000000005</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <v>42161</v>
       </c>
@@ -8602,7 +8605,7 @@
         <v>643.74</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>42168</v>
       </c>
@@ -8613,7 +8616,7 @@
         <v>645.82000000000005</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <v>42175</v>
       </c>
@@ -8624,7 +8627,7 @@
         <v>639.6</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>42182</v>
       </c>
@@ -8635,7 +8638,7 @@
         <v>633.39</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>42189</v>
       </c>
@@ -8646,7 +8649,7 @@
         <v>630.07000000000005</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>42196</v>
       </c>
@@ -8657,7 +8660,7 @@
         <v>620.13</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>42203</v>
       </c>
@@ -8668,7 +8671,7 @@
         <v>617.65</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>42210</v>
       </c>
@@ -8679,7 +8682,7 @@
         <v>600.25</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>42217</v>
       </c>
@@ -8690,7 +8693,7 @@
         <v>577.04999999999995</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>42224</v>
       </c>
@@ -8701,7 +8704,7 @@
         <v>560.07000000000005</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>42231</v>
       </c>
@@ -8712,7 +8715,7 @@
         <v>558.82000000000005</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>42238</v>
       </c>
@@ -8723,7 +8726,7 @@
         <v>550.12</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>42245</v>
       </c>
@@ -8734,7 +8737,7 @@
         <v>545.98</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>42252</v>
       </c>
@@ -8745,7 +8748,7 @@
         <v>541.01</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>42259</v>
       </c>
@@ -8756,7 +8759,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>42266</v>
       </c>
@@ -8767,7 +8770,7 @@
         <v>512.84</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>42273</v>
       </c>
@@ -8778,7 +8781,7 @@
         <v>491.3</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>42280</v>
       </c>
@@ -8789,7 +8792,7 @@
         <v>477.22</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>42287</v>
       </c>
@@ -8800,7 +8803,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>42294</v>
       </c>
@@ -8811,7 +8814,7 @@
         <v>438.69</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <v>42301</v>
       </c>
@@ -8822,7 +8825,7 @@
         <v>415.08</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <v>42308</v>
       </c>
@@ -8833,7 +8836,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>42315</v>
       </c>
@@ -8844,7 +8847,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>42322</v>
       </c>
@@ -8855,7 +8858,7 @@
         <v>388.98</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>42329</v>
       </c>
@@ -8866,7 +8869,7 @@
         <v>385.67</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>42336</v>
       </c>
@@ -8877,7 +8880,7 @@
         <v>380.28</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>42343</v>
       </c>
@@ -8888,7 +8891,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>42350</v>
       </c>
@@ -8899,7 +8902,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>42357</v>
       </c>
@@ -8910,7 +8913,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>42364</v>
       </c>
@@ -8921,7 +8924,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>42371</v>
       </c>
@@ -8932,7 +8935,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>42378</v>
       </c>
@@ -8943,7 +8946,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>42385</v>
       </c>
@@ -8954,7 +8957,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>42392</v>
       </c>
@@ -8965,7 +8968,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>42399</v>
       </c>
@@ -8976,7 +8979,7 @@
         <v>363.71</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>42406</v>
       </c>
@@ -8987,7 +8990,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>42413</v>
       </c>
@@ -8998,7 +9001,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>42420</v>
       </c>
@@ -9009,7 +9012,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>42427</v>
       </c>
@@ -9020,7 +9023,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>42434</v>
       </c>
@@ -9031,7 +9034,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>42441</v>
       </c>
@@ -9042,7 +9045,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>42448</v>
       </c>
@@ -9053,7 +9056,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>42455</v>
       </c>
@@ -9064,7 +9067,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>42462</v>
       </c>
@@ -9075,7 +9078,7 @@
         <v>362.47</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>42469</v>
       </c>
@@ -9086,7 +9089,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>42476</v>
       </c>
@@ -9097,7 +9100,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>42483</v>
       </c>
@@ -9108,7 +9111,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
         <v>42490</v>
       </c>
@@ -9119,7 +9122,7 @@
         <v>358.74</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
         <v>42497</v>
       </c>
@@ -9130,7 +9133,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
         <v>42504</v>
       </c>
@@ -9141,7 +9144,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
         <v>42511</v>
       </c>
@@ -9152,7 +9155,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
         <v>42518</v>
       </c>
@@ -9163,7 +9166,7 @@
         <v>356.67</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A308" s="1">
         <v>42525</v>
       </c>
@@ -9174,7 +9177,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A309" s="1">
         <v>42532</v>
       </c>
@@ -9185,7 +9188,7 @@
         <v>354.6</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A310" s="1">
         <v>42539</v>
       </c>
@@ -9196,7 +9199,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A311" s="1">
         <v>42546</v>
       </c>
@@ -9207,7 +9210,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A312" s="1">
         <v>42553</v>
       </c>
@@ -9218,7 +9221,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A313" s="1">
         <v>42560</v>
       </c>
@@ -9229,7 +9232,7 @@
         <v>348.8</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A314" s="1">
         <v>42567</v>
       </c>
@@ -9240,7 +9243,7 @@
         <v>347.56</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A315" s="1">
         <v>42574</v>
       </c>
@@ -9251,7 +9254,7 @@
         <v>345.9</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A316" s="1">
         <v>42581</v>
       </c>
@@ -9262,7 +9265,7 @@
         <v>345.07</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A317" s="1">
         <v>42588</v>
       </c>
@@ -9273,7 +9276,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A318" s="1">
         <v>42595</v>
       </c>
@@ -9284,7 +9287,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A319" s="1">
         <v>42602</v>
       </c>
@@ -9295,7 +9298,7 @@
         <v>341.76</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A320" s="1">
         <v>42609</v>
       </c>
@@ -9306,7 +9309,7 @@
         <v>337.2</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A321" s="1">
         <v>42616</v>
       </c>
@@ -9317,7 +9320,7 @@
         <v>331.4</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A322" s="1">
         <v>42623</v>
       </c>
@@ -9328,7 +9331,7 @@
         <v>330.99</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A323" s="1">
         <v>42630</v>
       </c>
@@ -9339,7 +9342,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
         <v>42637</v>
       </c>
@@ -9350,7 +9353,7 @@
         <v>328.09</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
         <v>42644</v>
       </c>
@@ -9361,7 +9364,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A326" s="1">
         <v>42651</v>
       </c>
@@ -9372,7 +9375,7 @@
         <v>326.01</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A327" s="1">
         <v>42658</v>
       </c>
@@ -9383,7 +9386,7 @@
         <v>324.77</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
         <v>42665</v>
       </c>
@@ -9394,7 +9397,7 @@
         <v>322.7</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A329" s="1">
         <v>42672</v>
       </c>
@@ -9405,7 +9408,7 @@
         <v>319.39</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A330" s="1">
         <v>42679</v>
       </c>
@@ -9416,7 +9419,7 @@
         <v>318.56</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A331" s="1">
         <v>42686</v>
       </c>
@@ -9427,7 +9430,7 @@
         <v>317.32</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A332" s="1">
         <v>42693</v>
       </c>
@@ -9438,7 +9441,7 @@
         <v>316.49</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A333" s="1">
         <v>42700</v>
       </c>
@@ -9449,7 +9452,7 @@
         <v>316.07</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A334" s="1">
         <v>42707</v>
       </c>
@@ -9460,7 +9463,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A335" s="1">
         <v>42714</v>
       </c>
@@ -9471,7 +9474,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A336" s="1">
         <v>42721</v>
       </c>
@@ -9482,7 +9485,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A337" s="1">
         <v>42728</v>
       </c>
@@ -9493,7 +9496,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A338" s="1">
         <v>42735</v>
       </c>
@@ -9504,7 +9507,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A339" s="1">
         <v>42742</v>
       </c>
@@ -9515,7 +9518,7 @@
         <v>316.39</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A340" s="1">
         <v>42749</v>
       </c>
@@ -9526,7 +9529,7 @@
         <v>319.07</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A341" s="1">
         <v>42756</v>
       </c>
@@ -9537,7 +9540,7 @@
         <v>320.56</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A342" s="1">
         <v>42763</v>
       </c>
@@ -9548,7 +9551,7 @@
         <v>322.35000000000002</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A343" s="1">
         <v>42770</v>
       </c>
@@ -9559,7 +9562,7 @@
         <v>323.83999999999997</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A344" s="1">
         <v>42777</v>
       </c>
@@ -9570,7 +9573,7 @@
         <v>325.33</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A345" s="1">
         <v>42784</v>
       </c>
@@ -9581,7 +9584,7 @@
         <v>330.4</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A346" s="1">
         <v>42791</v>
       </c>
@@ -9592,7 +9595,7 @@
         <v>343.52</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A347" s="1">
         <v>42798</v>
       </c>
@@ -9603,7 +9606,7 @@
         <v>351.87</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A348" s="1">
         <v>42805</v>
       </c>
@@ -9614,7 +9617,7 @@
         <v>389.44</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A349" s="1">
         <v>42812</v>
       </c>
@@ -9625,7 +9628,7 @@
         <v>404.35</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A350" s="1">
         <v>42819</v>
       </c>
@@ -9636,7 +9639,7 @@
         <v>438.94</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A351" s="1">
         <v>42826</v>
       </c>
@@ -9647,7 +9650,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A352" s="1">
         <v>42833</v>
       </c>
@@ -9658,7 +9661,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A353" s="1">
         <v>42840</v>
       </c>
@@ -9669,7 +9672,7 @@
         <v>516.77</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A354" s="1">
         <v>42847</v>
       </c>
@@ -9680,7 +9683,7 @@
         <v>522.14</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A355" s="1">
         <v>42854</v>
       </c>
@@ -9691,7 +9694,7 @@
         <v>523.33000000000004</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A356" s="1">
         <v>42861</v>
       </c>
@@ -9702,7 +9705,7 @@
         <v>533.47</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A357" s="1">
         <v>42868</v>
       </c>
@@ -9713,7 +9716,7 @@
         <v>533.16999999999996</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A358" s="1">
         <v>42875</v>
       </c>
@@ -9724,7 +9727,7 @@
         <v>500.37</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A359" s="1">
         <v>42882</v>
       </c>
@@ -9735,7 +9738,7 @@
         <v>483.97</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A360" s="1">
         <v>42889</v>
       </c>
@@ -9746,7 +9749,7 @@
         <v>458.92</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A361" s="1">
         <v>42896</v>
       </c>
@@ -9757,7 +9760,7 @@
         <v>443.72</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A362" s="1">
         <v>42903</v>
       </c>
@@ -9768,7 +9771,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A363" s="1">
         <v>42910</v>
       </c>
@@ -9779,7 +9782,7 @@
         <v>438.35</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A364" s="1">
         <v>42917</v>
       </c>
@@ -9790,7 +9793,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A365" s="1">
         <v>42924</v>
       </c>
@@ -9801,7 +9804,7 @@
         <v>435.96</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A366" s="1">
         <v>42931</v>
       </c>
@@ -9812,7 +9815,7 @@
         <v>445.8</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A367" s="1">
         <v>42938</v>
       </c>
@@ -9823,7 +9826,7 @@
         <v>470.25</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A368" s="1">
         <v>42945</v>
       </c>
@@ -9834,7 +9837,7 @@
         <v>472.04</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A369" s="1">
         <v>42952</v>
       </c>
@@ -9845,7 +9848,7 @@
         <v>481.88</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A370" s="1">
         <v>42959</v>
       </c>
@@ -9856,7 +9859,7 @@
         <v>486.66</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A371" s="1">
         <v>42966</v>
       </c>
@@ -9867,7 +9870,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A372" s="1">
         <v>42973</v>
       </c>
@@ -9878,7 +9881,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A373" s="1">
         <v>42980</v>
       </c>
@@ -9889,7 +9892,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A374" s="1">
         <v>42987</v>
       </c>
@@ -9900,7 +9903,7 @@
         <v>515.88</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A375" s="1">
         <v>42994</v>
       </c>
@@ -9911,7 +9914,7 @@
         <v>517.07000000000005</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A376" s="1">
         <v>43001</v>
       </c>
@@ -9922,7 +9925,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A377" s="1">
         <v>43008</v>
       </c>
@@ -9933,7 +9936,7 @@
         <v>506.34</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A378" s="1">
         <v>43015</v>
       </c>
@@ -9944,7 +9947,7 @@
         <v>507.53</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A379" s="1">
         <v>43022</v>
       </c>
@@ -9955,7 +9958,7 @@
         <v>505.14</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A380" s="1">
         <v>43029</v>
       </c>
@@ -9966,7 +9969,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A381" s="1">
         <v>43036</v>
       </c>
@@ -9977,7 +9980,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A382" s="1">
         <v>43043</v>
       </c>
@@ -9988,7 +9991,7 @@
         <v>473.24</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A383" s="1">
         <v>43050</v>
       </c>
@@ -9999,7 +10002,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A384" s="1">
         <v>43057</v>
       </c>
@@ -10010,7 +10013,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A385" s="1">
         <v>43064</v>
       </c>
@@ -10021,7 +10024,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A386" s="1">
         <v>43071</v>
       </c>
@@ -10032,7 +10035,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A387" s="1">
         <v>43078</v>
       </c>
@@ -10043,7 +10046,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A388" s="1">
         <v>43085</v>
       </c>
@@ -10054,7 +10057,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A389" s="1">
         <v>43092</v>
       </c>
@@ -10065,7 +10068,7 @@
         <v>482.78</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A390" s="1">
         <v>43099</v>
       </c>
@@ -10076,7 +10079,7 @@
         <v>483.08</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A391" s="1">
         <v>43106</v>
       </c>
@@ -10087,7 +10090,7 @@
         <v>485.16</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A392" s="1">
         <v>43113</v>
       </c>
@@ -10098,7 +10101,7 @@
         <v>489.34</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A393" s="1">
         <v>43120</v>
       </c>
@@ -10109,7 +10112,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A394" s="1">
         <v>43127</v>
       </c>
@@ -10120,7 +10123,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A395" s="1">
         <v>43134</v>
       </c>
@@ -10131,7 +10134,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A396" s="1">
         <v>43141</v>
       </c>
@@ -10142,7 +10145,7 @@
         <v>520.35</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A397" s="1">
         <v>43148</v>
       </c>
@@ -10153,7 +10156,7 @@
         <v>526.02</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A398" s="1">
         <v>43155</v>
       </c>
@@ -10164,7 +10167,7 @@
         <v>542.41999999999996</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A399" s="1">
         <v>43162</v>
       </c>
@@ -10175,7 +10178,7 @@
         <v>548.98</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A400" s="1">
         <v>43169</v>
       </c>
@@ -10186,7 +10189,7 @@
         <v>579.69000000000005</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A401" s="1">
         <v>43176</v>
       </c>
@@ -10197,7 +10200,7 @@
         <v>597.88</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A402" s="1">
         <v>43183</v>
       </c>
@@ -10208,7 +10211,7 @@
         <v>635.16</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A403" s="1">
         <v>43190</v>
       </c>
@@ -10219,7 +10222,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A404" s="1">
         <v>43197</v>
       </c>
@@ -10230,7 +10233,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A405" s="1">
         <v>43204</v>
       </c>
@@ -10241,7 +10244,7 @@
         <v>642.61</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A406" s="1">
         <v>43211</v>
       </c>
@@ -10252,7 +10255,7 @@
         <v>646.19000000000005</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A407" s="1">
         <v>43218</v>
       </c>
@@ -10263,7 +10266,7 @@
         <v>652.45000000000005</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A408" s="1">
         <v>43225</v>
       </c>
@@ -10274,7 +10277,7 @@
         <v>653.64</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A409" s="1">
         <v>43232</v>
       </c>
@@ -10285,7 +10288,7 @@
         <v>656.63</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A410" s="1">
         <v>43239</v>
       </c>
@@ -10296,7 +10299,7 @@
         <v>661.1</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A411" s="1">
         <v>43245</v>
       </c>
@@ -10307,7 +10310,7 @@
         <v>670.64</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A412" s="1">
         <v>43252</v>
       </c>
@@ -10318,7 +10321,7 @@
         <v>673.62</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A413" s="1">
         <v>43259</v>
       </c>
@@ -10329,7 +10332,7 @@
         <v>676.61</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A414" s="1">
         <v>43266</v>
       </c>
@@ -10340,7 +10343,7 @@
         <v>678.1</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A415" s="1">
         <v>43273</v>
       </c>
@@ -10351,7 +10354,7 @@
         <v>676.9</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A416" s="1">
         <v>43280</v>
       </c>
@@ -10362,7 +10365,7 @@
         <v>672.73</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A417" s="1">
         <v>43287</v>
       </c>
@@ -10373,7 +10376,7 @@
         <v>668.26</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A418" s="1">
         <v>43294</v>
       </c>
@@ -10384,7 +10387,7 @@
         <v>652.15</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A419" s="1">
         <v>43301</v>
       </c>
@@ -10395,7 +10398,7 @@
         <v>628.6</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A420" s="1">
         <v>43308</v>
       </c>
@@ -10406,7 +10409,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A421" s="1">
         <v>43315</v>
       </c>
@@ -10417,7 +10420,7 @@
         <v>594.6</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A422" s="1">
         <v>43322</v>
       </c>
@@ -10428,7 +10431,7 @@
         <v>584.16999999999996</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A423" s="1">
         <v>43329</v>
       </c>
@@ -10439,7 +10442,7 @@
         <v>582.97</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A424" s="1">
         <v>43336</v>
       </c>
@@ -10450,7 +10453,7 @@
         <v>577.01</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A425" s="1">
         <v>43343</v>
       </c>
@@ -10461,7 +10464,7 @@
         <v>568.05999999999995</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A426" s="1">
         <v>43350</v>
       </c>
@@ -10472,7 +10475,7 @@
         <v>550.77</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A427" s="1">
         <v>43357</v>
       </c>
@@ -10483,7 +10486,7 @@
         <v>548.08000000000004</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A428" s="1">
         <v>43364</v>
       </c>
@@ -10494,7 +10497,7 @@
         <v>538.54</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A429" s="1">
         <v>43371</v>
       </c>
@@ -10505,7 +10508,7 @@
         <v>534.37</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A430" s="1">
         <v>43378</v>
       </c>
@@ -10516,7 +10519,7 @@
         <v>532.28</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A431" s="1">
         <v>43385</v>
       </c>
@@ -10527,7 +10530,7 @@
         <v>524.23</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A432" s="1">
         <v>43392</v>
       </c>
@@ -10538,7 +10541,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A433" s="1">
         <v>43399</v>
       </c>
@@ -10549,7 +10552,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A434" s="1">
         <v>43406</v>
       </c>
@@ -10560,7 +10563,7 @@
         <v>503.06</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A435" s="1">
         <v>43413</v>
       </c>
@@ -10571,7 +10574,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A436" s="1">
         <v>43420</v>
       </c>
@@ -10582,7 +10585,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A437" s="1">
         <v>43427</v>
       </c>
@@ -10593,7 +10596,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A438" s="1">
         <v>43434</v>
       </c>
@@ -10604,7 +10607,7 @@
         <v>502.16</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A439" s="1">
         <v>43441</v>
       </c>
@@ -10615,7 +10618,7 @@
         <v>498.58</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A440" s="1">
         <v>43448</v>
       </c>
@@ -10626,7 +10629,7 @@
         <v>495.6</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A441" s="1">
         <v>43455</v>
       </c>
@@ -10637,7 +10640,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A442" s="1">
         <v>43462</v>
       </c>
@@ -10648,7 +10651,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A443" s="1">
         <v>43469</v>
       </c>
@@ -10659,7 +10662,7 @@
         <v>485.46</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A444" s="1">
         <v>43476</v>
       </c>
@@ -10670,7 +10673,7 @@
         <v>478.01</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A445" s="1">
         <v>43483</v>
       </c>
@@ -10681,7 +10684,7 @@
         <v>474.43</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A446" s="1">
         <v>43490</v>
       </c>
@@ -10692,7 +10695,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A447" s="1">
         <v>43497</v>
       </c>
@@ -10703,7 +10706,7 @@
         <v>492.02</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A448" s="1">
         <v>43504</v>
       </c>
@@ -10714,7 +10717,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A449" s="1">
         <v>43511</v>
       </c>
@@ -10725,7 +10728,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A450" s="1">
         <v>43518</v>
       </c>
@@ -10736,7 +10739,7 @@
         <v>502.46</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A451" s="1">
         <v>43525</v>
       </c>
@@ -10747,7 +10750,7 @@
         <v>527.80999999999995</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A452" s="1">
         <v>43532</v>
       </c>
@@ -10758,7 +10761,7 @@
         <v>543.01</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A453" s="1">
         <v>43539</v>
       </c>
@@ -10769,7 +10772,7 @@
         <v>552.55999999999995</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A454" s="1">
         <v>43546</v>
       </c>
@@ -10780,7 +10783,7 @@
         <v>560.61</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A455" s="1">
         <v>43553</v>
       </c>
@@ -10791,7 +10794,7 @@
         <v>565.67999999999995</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A456" s="1">
         <v>43560</v>
       </c>
@@ -10802,7 +10805,7 @@
         <v>576.11</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A457" s="1">
         <v>43567</v>
       </c>
@@ -10813,7 +10816,7 @@
         <v>581.48</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A458" s="1">
         <v>43574</v>
       </c>
@@ -10824,7 +10827,7 @@
         <v>585.05999999999995</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A459" s="1">
         <v>43581</v>
       </c>
@@ -10835,7 +10838,7 @@
         <v>585.66</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A460" s="1">
         <v>43588</v>
       </c>
@@ -10846,7 +10849,7 @@
         <v>586.25</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A461" s="1">
         <v>43595</v>
       </c>
@@ -10857,7 +10860,7 @@
         <v>586.85</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A462" s="1">
         <v>43602</v>
       </c>
@@ -10868,7 +10871,7 @@
         <v>596.09</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A463" s="1">
         <v>43609</v>
       </c>
@@ -10879,7 +10882,7 @@
         <v>599.08000000000004</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A464" s="1">
         <v>43616</v>
       </c>
@@ -10890,7 +10893,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A465" s="1">
         <v>43623</v>
       </c>
@@ -10901,7 +10904,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A466" s="1">
         <v>43630</v>
       </c>
@@ -10912,7 +10915,7 @@
         <v>603.85</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A467" s="1">
         <v>43637</v>
       </c>
@@ -10923,7 +10926,7 @@
         <v>603.54999999999995</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A468" s="1">
         <v>43644</v>
       </c>
@@ -10934,7 +10937,7 @@
         <v>611.6</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A469" s="1">
         <v>43651</v>
       </c>
@@ -10945,7 +10948,7 @@
         <v>618.76</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A470" s="1">
         <v>43658</v>
       </c>
@@ -10956,7 +10959,7 @@
         <v>629.19000000000005</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A471" s="1">
         <v>43665</v>
       </c>
@@ -10967,7 +10970,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A472" s="1">
         <v>43672</v>
       </c>
@@ -10978,7 +10981,7 @@
         <v>666.77</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A473" s="1">
         <v>43679</v>
       </c>
@@ -10989,7 +10992,7 @@
         <v>670.94</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A474" s="1">
         <v>43686</v>
       </c>
@@ -11000,7 +11003,7 @@
         <v>681.97</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A475" s="1">
         <v>43693</v>
       </c>
@@ -11011,7 +11014,7 @@
         <v>690.02</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A476" s="1">
         <v>43700</v>
       </c>
@@ -11022,7 +11025,7 @@
         <v>696.88</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A477" s="1">
         <v>43707</v>
       </c>
@@ -11033,7 +11036,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A478" s="1">
         <v>43714</v>
       </c>
@@ -11044,7 +11047,7 @@
         <v>718.65</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A479" s="1">
         <v>43721</v>
       </c>
@@ -11055,7 +11058,7 @@
         <v>723.42</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A480" s="1">
         <v>43728</v>
       </c>
@@ -11066,7 +11069,7 @@
         <v>724.62</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A481" s="1">
         <v>43735</v>
       </c>
@@ -11077,7 +11080,7 @@
         <v>726.4</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A482" s="1">
         <v>43742</v>
       </c>
@@ -11088,7 +11091,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A483" s="1">
         <v>43749</v>
       </c>
@@ -11099,7 +11102,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A484" s="1">
         <v>43756</v>
       </c>
@@ -11110,7 +11113,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A485" s="1">
         <v>43763</v>
       </c>
@@ -11121,7 +11124,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A486" s="1">
         <v>43770</v>
       </c>
@@ -11132,7 +11135,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A487" s="1">
         <v>43777</v>
       </c>
@@ -11143,7 +11146,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A488" s="1">
         <v>43784</v>
       </c>
@@ -11154,7 +11157,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A489" s="1">
         <v>43791</v>
       </c>
@@ -11165,7 +11168,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A490" s="1">
         <v>43798</v>
       </c>
@@ -11176,7 +11179,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A491" s="1">
         <v>43805</v>
       </c>
@@ -11187,7 +11190,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A492" s="1">
         <v>43812</v>
       </c>
@@ -11198,7 +11201,7 @@
         <v>715.67</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A493" s="1">
         <v>43819</v>
       </c>
@@ -11209,7 +11212,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A494" s="1">
         <v>43826</v>
       </c>
@@ -11220,7 +11223,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A495" s="1">
         <v>43833</v>
       </c>
@@ -11231,7 +11234,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A496" s="1">
         <v>43840</v>
       </c>
@@ -11242,7 +11245,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A497" s="1">
         <v>43847</v>
       </c>
@@ -11253,7 +11256,7 @@
         <v>711.49</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A498" s="1">
         <v>43854</v>
       </c>
@@ -11264,7 +11267,7 @@
         <v>708.51</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A499" s="1">
         <v>43861</v>
       </c>
@@ -11275,7 +11278,7 @@
         <v>705.53</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A500" s="1">
         <v>43868</v>
       </c>
@@ -11286,7 +11289,7 @@
         <v>701.95</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A501" s="1">
         <v>43875</v>
       </c>
@@ -11297,7 +11300,7 @@
         <v>691.52</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A502" s="1">
         <v>43882</v>
       </c>
@@ -11308,7 +11311,7 @@
         <v>680.48</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A503" s="1">
         <v>43889</v>
       </c>
@@ -11319,7 +11322,7 @@
         <v>668.85</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A504" s="1">
         <v>43896</v>
       </c>
@@ -11330,7 +11333,7 @@
         <v>651.26</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A505" s="1">
         <v>43903</v>
       </c>
@@ -11341,7 +11344,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A506" s="1">
         <v>43910</v>
       </c>
@@ -11352,7 +11355,7 @@
         <v>631.58000000000004</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A507" s="1">
         <v>43917</v>
       </c>
@@ -11363,7 +11366,7 @@
         <v>616.07000000000005</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A508" s="1">
         <v>43924</v>
       </c>
@@ -11374,7 +11377,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A509" s="1">
         <v>43931</v>
       </c>
@@ -11385,7 +11388,7 @@
         <v>601.46</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A510" s="1">
         <v>43938</v>
       </c>
@@ -11396,7 +11399,7 @@
         <v>572.83000000000004</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A511" s="1">
         <v>43945</v>
       </c>
@@ -11407,7 +11410,7 @@
         <v>549.87</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A512" s="1">
         <v>43952</v>
       </c>
@@ -11418,7 +11421,7 @@
         <v>528.70000000000005</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A513" s="1">
         <v>43959</v>
       </c>
@@ -11429,7 +11432,7 @@
         <v>507.83</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A514" s="1">
         <v>43966</v>
       </c>
@@ -11440,7 +11443,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A515" s="1">
         <v>43973</v>
       </c>
@@ -11451,7 +11454,7 @@
         <v>479.2</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A516" s="1">
         <v>43980</v>
       </c>
@@ -11462,7 +11465,7 @@
         <v>452.36</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A517" s="1">
         <v>43987</v>
       </c>
@@ -11473,7 +11476,7 @@
         <v>434.17</v>
       </c>
     </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A518" s="1">
         <v>43994</v>
       </c>
@@ -11484,7 +11487,7 @@
         <v>412.11</v>
       </c>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A519" s="1">
         <v>44001</v>
       </c>
@@ -11495,7 +11498,7 @@
         <v>418.96</v>
       </c>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A520" s="1">
         <v>44008</v>
       </c>
@@ -11506,7 +11509,7 @@
         <v>431.79</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A521" s="1">
         <v>44015</v>
       </c>
@@ -11517,7 +11520,7 @@
         <v>439.84</v>
       </c>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A522" s="1">
         <v>44022</v>
       </c>
@@ -11528,7 +11531,7 @@
         <v>444.91</v>
       </c>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A523" s="1">
         <v>44029</v>
       </c>
@@ -11539,7 +11542,7 @@
         <v>463.1</v>
       </c>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A524" s="1">
         <v>44036</v>
       </c>
@@ -11550,7 +11553,7 @@
         <v>484.87</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A525" s="1">
         <v>44043</v>
       </c>
@@ -11561,7 +11564,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A526" s="1">
         <v>44050</v>
       </c>
@@ -11572,7 +11575,7 @@
         <v>556.13</v>
       </c>
     </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A527" s="1">
         <v>44057</v>
       </c>
@@ -11583,7 +11586,7 @@
         <v>596.69000000000005</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A528" s="1">
         <v>44064</v>
       </c>
@@ -11594,7 +11597,7 @@
         <v>627.11</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A529" s="1">
         <v>44071</v>
       </c>
@@ -11605,7 +11608,7 @@
         <v>665.87</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A530" s="1">
         <v>44078</v>
       </c>
@@ -11616,7 +11619,7 @@
         <v>671.83</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A531" s="1">
         <v>44085</v>
       </c>
@@ -11627,7 +11630,7 @@
         <v>678.4</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A532" s="1">
         <v>44092</v>
       </c>
@@ -11638,7 +11641,7 @@
         <v>691.81</v>
       </c>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A533" s="1">
         <v>44099</v>
       </c>
@@ -11649,7 +11652,7 @@
         <v>703.74</v>
       </c>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A534" s="1">
         <v>44106</v>
       </c>
@@ -11660,7 +11663,7 @@
         <v>714.77</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A535" s="1">
         <v>44113</v>
       </c>
@@ -11671,7 +11674,7 @@
         <v>754.14</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A536" s="1">
         <v>44120</v>
       </c>
@@ -11682,7 +11685,7 @@
         <v>783.96</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A537" s="1">
         <v>44127</v>
       </c>
@@ -11693,7 +11696,7 @@
         <v>820.04</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A538" s="1">
         <v>44134</v>
       </c>
@@ -11704,7 +11707,7 @@
         <v>881.17</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A539" s="1">
         <v>44141</v>
       </c>
@@ -11715,7 +11718,7 @@
         <v>910.09</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A540" s="1">
         <v>44148</v>
       </c>
@@ -11726,7 +11729,7 @@
         <v>947.07</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A541" s="1">
         <v>44155</v>
       </c>
@@ -11737,7 +11740,7 @@
         <v>978.68</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A542" s="1">
         <v>44162</v>
       </c>
@@ -11748,7 +11751,7 @@
         <v>1009.39</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A543" s="1">
         <v>44169</v>
       </c>
@@ -11759,7 +11762,7 @@
         <v>1016.25</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A544" s="1">
         <v>44176</v>
       </c>
@@ -11770,7 +11773,7 @@
         <v>1020.13</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A545" s="1">
         <v>44183</v>
       </c>
@@ -11781,7 +11784,7 @@
         <v>1032.06</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A546" s="1">
         <v>44190</v>
       </c>
@@ -11792,7 +11795,7 @@
         <v>1036.23</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A547" s="1">
         <v>44197</v>
       </c>
@@ -11803,7 +11806,7 @@
         <v>1038.02</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A548" s="1">
         <v>44204</v>
       </c>
@@ -11814,7 +11817,7 @@
         <v>1069.6300000000001</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A549" s="1">
         <v>44211</v>
       </c>
@@ -11825,7 +11828,7 @@
         <v>1094.3800000000001</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A550" s="1">
         <v>44218</v>
       </c>
@@ -11836,7 +11839,7 @@
         <v>1112.8699999999999</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A551" s="1">
         <v>44225</v>
       </c>
@@ -11847,7 +11850,7 @@
         <v>1154.32</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A552" s="1">
         <v>44232</v>
       </c>
@@ -11858,7 +11861,7 @@
         <v>1202.03</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A553" s="1">
         <v>44239</v>
       </c>
@@ -11869,7 +11872,7 @@
         <v>1228.27</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A554" s="1">
         <v>44246</v>
       </c>
@@ -11880,7 +11883,7 @@
         <v>1262.26</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A555" s="1">
         <v>44253</v>
       </c>
@@ -11891,7 +11894,7 @@
         <v>1278.3599999999999</v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A556" s="1">
         <v>44260</v>
       </c>
@@ -11902,7 +11905,7 @@
         <v>1323.39</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A557" s="1">
         <v>44267</v>
       </c>
@@ -11913,7 +11916,7 @@
         <v>1387.21</v>
       </c>
     </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A558" s="1">
         <v>44274</v>
       </c>
@@ -11924,7 +11927,7 @@
         <v>1442.97</v>
       </c>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A559" s="1">
         <v>44281</v>
       </c>
@@ -11935,7 +11938,7 @@
         <v>1454.3</v>
       </c>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A560" s="1">
         <v>44288</v>
       </c>
@@ -11946,7 +11949,7 @@
         <v>1492.47</v>
       </c>
     </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A561" s="1">
         <v>44295</v>
       </c>
@@ -11957,7 +11960,7 @@
         <v>1559.56</v>
       </c>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A562" s="1">
         <v>44302</v>
       </c>
@@ -11968,7 +11971,7 @@
         <v>1650.51</v>
       </c>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A563" s="1">
         <v>44309</v>
       </c>
@@ -11979,7 +11982,7 @@
         <v>1680.33</v>
       </c>
     </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A564" s="1">
         <v>44316</v>
       </c>
@@ -11990,7 +11993,7 @@
         <v>1707.47</v>
       </c>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A565" s="1">
         <v>44323</v>
       </c>
@@ -12001,7 +12004,7 @@
         <v>1777.25</v>
       </c>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A566" s="1">
         <v>44330</v>
       </c>
@@ -12012,7 +12015,7 @@
         <v>1837.48</v>
       </c>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A567" s="1">
         <v>44337</v>
       </c>
@@ -12023,7 +12026,7 @@
         <v>1890.86</v>
       </c>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A568" s="1">
         <v>44344</v>
       </c>
@@ -12034,7 +12037,7 @@
         <v>1940.66</v>
       </c>
     </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A569" s="1">
         <v>44351</v>
       </c>
@@ -12045,7 +12048,7 @@
         <v>1986.58</v>
       </c>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A570" s="1">
         <v>44358</v>
       </c>
@@ -12056,7 +12059,7 @@
         <v>2033.69</v>
       </c>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A571" s="1">
         <v>44365</v>
       </c>
@@ -12067,7 +12070,7 @@
         <v>2117.19</v>
       </c>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A572" s="1">
         <v>44372</v>
       </c>
@@ -12078,7 +12081,7 @@
         <v>2212.31</v>
       </c>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A573" s="1">
         <v>44379</v>
       </c>
@@ -12089,7 +12092,7 @@
         <v>2406.44</v>
       </c>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A574" s="1">
         <v>44386</v>
       </c>
@@ -12100,7 +12103,7 @@
         <v>2695.69</v>
       </c>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A575" s="1">
         <v>44393</v>
       </c>
@@ -12111,7 +12114,7 @@
         <v>3023.7</v>
       </c>
     </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A576" s="1">
         <v>44400</v>
       </c>
@@ -12122,7 +12125,7 @@
         <v>3142.98</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A577" s="1">
         <v>44407</v>
       </c>
@@ -12133,7 +12136,7 @@
         <v>3301.03</v>
       </c>
     </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A578" s="1">
         <v>44414</v>
       </c>
@@ -12144,7 +12147,7 @@
         <v>3548.53</v>
       </c>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A579" s="1">
         <v>44421</v>
       </c>
@@ -12155,7 +12158,7 @@
         <v>3554.49</v>
       </c>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A580" s="1">
         <v>44428</v>
       </c>
@@ -12166,7 +12169,7 @@
         <v>3560.46</v>
       </c>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A581" s="1">
         <v>44435</v>
       </c>
@@ -12177,7 +12180,7 @@
         <v>3599.22</v>
       </c>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A582" s="1">
         <v>44442</v>
       </c>
@@ -12188,7 +12191,7 @@
         <v>3694.64</v>
       </c>
     </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A583" s="1">
         <v>44449</v>
       </c>
@@ -12199,7 +12202,7 @@
         <v>3822.87</v>
       </c>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A584" s="1">
         <v>44456</v>
       </c>
@@ -12210,7 +12213,7 @@
         <v>3928.73</v>
       </c>
     </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A585" s="1">
         <v>44463</v>
       </c>
@@ -12221,7 +12224,7 @@
         <v>3980.91</v>
       </c>
     </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A586" s="1">
         <v>44470</v>
       </c>
@@ -12232,7 +12235,7 @@
         <v>3989.86</v>
       </c>
     </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A587" s="1">
         <v>44477</v>
       </c>
@@ -12243,7 +12246,7 @@
         <v>3995.82</v>
       </c>
     </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A588" s="1">
         <v>44484</v>
       </c>
@@ -12254,7 +12257,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A589" s="1">
         <v>44491</v>
       </c>
@@ -12265,7 +12268,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A590" s="1">
         <v>44498</v>
       </c>
@@ -12276,7 +12279,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A591" s="1">
         <v>44505</v>
       </c>
@@ -12287,7 +12290,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A592" s="1">
         <v>44512</v>
       </c>
@@ -12298,7 +12301,7 @@
         <v>3852.69</v>
       </c>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A593" s="1">
         <v>44519</v>
       </c>
@@ -12306,7 +12309,7 @@
         <v>44519</v>
       </c>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A594" s="1">
         <v>44526</v>
       </c>
@@ -12314,7 +12317,7 @@
         <v>44526</v>
       </c>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A595" s="1">
         <v>44533</v>
       </c>
@@ -12322,7 +12325,7 @@
         <v>44533</v>
       </c>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A596" s="1">
         <v>44540</v>
       </c>
@@ -12330,7 +12333,7 @@
         <v>44540</v>
       </c>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A597" s="1">
         <v>44547</v>
       </c>
@@ -12338,7 +12341,7 @@
         <v>44547</v>
       </c>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A598" s="1">
         <v>44554</v>
       </c>
@@ -12346,7 +12349,7 @@
         <v>44554</v>
       </c>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A599" s="1">
         <v>44561</v>
       </c>
@@ -12354,7 +12357,7 @@
         <v>44561</v>
       </c>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A600" s="1">
         <v>44568</v>
       </c>
@@ -12362,7 +12365,7 @@
         <v>44568</v>
       </c>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A601" s="1">
         <v>44575</v>
       </c>
@@ -12370,7 +12373,7 @@
         <v>44575</v>
       </c>
     </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A602" s="1">
         <v>44582</v>
       </c>
@@ -12378,7 +12381,7 @@
         <v>44582</v>
       </c>
     </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A603" s="1">
         <v>44589</v>
       </c>
@@ -12386,7 +12389,7 @@
         <v>44589</v>
       </c>
     </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A604" s="1">
         <v>44596</v>
       </c>
@@ -12394,7 +12397,7 @@
         <v>44596</v>
       </c>
     </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A605" s="1">
         <v>44603</v>
       </c>
@@ -12402,7 +12405,7 @@
         <v>44603</v>
       </c>
     </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A606" s="1">
         <v>44610</v>
       </c>
@@ -12410,7 +12413,7 @@
         <v>44610</v>
       </c>
     </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A607" s="1">
         <v>44617</v>
       </c>
@@ -12418,7 +12421,7 @@
         <v>44617</v>
       </c>
     </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A608" s="1">
         <v>44624</v>
       </c>
@@ -12426,7 +12429,7 @@
         <v>44624</v>
       </c>
     </row>
-    <row r="609" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A609" s="1">
         <v>44631</v>
       </c>
@@ -12434,7 +12437,7 @@
         <v>44631</v>
       </c>
     </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A610" s="1">
         <v>44638</v>
       </c>
@@ -12442,7 +12445,7 @@
         <v>44638</v>
       </c>
     </row>
-    <row r="611" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A611" s="1">
         <v>44645</v>
       </c>
@@ -12450,7 +12453,7 @@
         <v>44645</v>
       </c>
     </row>
-    <row r="612" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A612" s="1">
         <v>44652</v>
       </c>
@@ -12458,7 +12461,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="613" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A613" s="1">
         <v>44659</v>
       </c>
@@ -12466,7 +12469,7 @@
         <v>44659</v>
       </c>
     </row>
-    <row r="614" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A614" s="1">
         <v>44666</v>
       </c>
@@ -12474,7 +12477,7 @@
         <v>44666</v>
       </c>
     </row>
-    <row r="615" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A615" s="1">
         <v>44673</v>
       </c>
@@ -12482,7 +12485,7 @@
         <v>44673</v>
       </c>
     </row>
-    <row r="616" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A616" s="1">
         <v>44680</v>
       </c>
@@ -12490,7 +12493,7 @@
         <v>44680</v>
       </c>
     </row>
-    <row r="617" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A617" s="1">
         <v>44687</v>
       </c>
@@ -12498,7 +12501,7 @@
         <v>44687</v>
       </c>
     </row>
-    <row r="618" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A618" s="1">
         <v>44694</v>
       </c>
@@ -12506,7 +12509,7 @@
         <v>44694</v>
       </c>
     </row>
-    <row r="619" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A619" s="1">
         <v>44701</v>
       </c>
@@ -12514,7 +12517,7 @@
         <v>44701</v>
       </c>
     </row>
-    <row r="620" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A620" s="1">
         <v>44708</v>
       </c>
@@ -12522,7 +12525,7 @@
         <v>44708</v>
       </c>
     </row>
-    <row r="621" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A621" s="1">
         <v>44715</v>
       </c>
@@ -12530,7 +12533,7 @@
         <v>44715</v>
       </c>
     </row>
-    <row r="622" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A622" s="1">
         <v>44722</v>
       </c>
@@ -12538,7 +12541,7 @@
         <v>44722</v>
       </c>
     </row>
-    <row r="623" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A623" s="1">
         <v>44729</v>
       </c>
@@ -12546,7 +12549,7 @@
         <v>44729</v>
       </c>
     </row>
-    <row r="624" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A624" s="1">
         <v>44736</v>
       </c>
@@ -12554,7 +12557,7 @@
         <v>44736</v>
       </c>
     </row>
-    <row r="625" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A625" s="1">
         <v>44743</v>
       </c>
@@ -12562,7 +12565,7 @@
         <v>44743</v>
       </c>
     </row>
-    <row r="626" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A626" s="1">
         <v>44750</v>
       </c>
@@ -12570,7 +12573,7 @@
         <v>44750</v>
       </c>
     </row>
-    <row r="627" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A627" s="1">
         <v>44757</v>
       </c>
@@ -12578,7 +12581,7 @@
         <v>44757</v>
       </c>
     </row>
-    <row r="628" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A628" s="1">
         <v>44764</v>
       </c>
@@ -12586,7 +12589,7 @@
         <v>44764</v>
       </c>
     </row>
-    <row r="629" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A629" s="1">
         <v>44771</v>
       </c>
@@ -12594,7 +12597,7 @@
         <v>44771</v>
       </c>
     </row>
-    <row r="630" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A630" s="1">
         <v>44778</v>
       </c>
@@ -12602,7 +12605,7 @@
         <v>44778</v>
       </c>
     </row>
-    <row r="631" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A631" s="1">
         <v>44785</v>
       </c>
@@ -12610,7 +12613,7 @@
         <v>44785</v>
       </c>
     </row>
-    <row r="632" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A632" s="1">
         <v>44792</v>
       </c>
@@ -12618,7 +12621,7 @@
         <v>44792</v>
       </c>
     </row>
-    <row r="633" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A633" s="1">
         <v>44799</v>
       </c>
@@ -12626,7 +12629,7 @@
         <v>44799</v>
       </c>
     </row>
-    <row r="634" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A634" s="1">
         <v>44806</v>
       </c>
@@ -12634,7 +12637,7 @@
         <v>44806</v>
       </c>
     </row>
-    <row r="635" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A635" s="1">
         <v>44813</v>
       </c>
@@ -12642,7 +12645,7 @@
         <v>44813</v>
       </c>
     </row>
-    <row r="636" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A636" s="1">
         <v>44820</v>
       </c>
@@ -12650,7 +12653,7 @@
         <v>44820</v>
       </c>
     </row>
-    <row r="637" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A637" s="1">
         <v>44827</v>
       </c>
@@ -12658,7 +12661,7 @@
         <v>44827</v>
       </c>
     </row>
-    <row r="638" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A638" s="1">
         <v>44834</v>
       </c>
@@ -12666,7 +12669,7 @@
         <v>44834</v>
       </c>
     </row>
-    <row r="639" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A639" s="1">
         <v>44841</v>
       </c>
@@ -12674,7 +12677,7 @@
         <v>44841</v>
       </c>
     </row>
-    <row r="640" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A640" s="1">
         <v>44848</v>
       </c>
@@ -12682,7 +12685,7 @@
         <v>44848</v>
       </c>
     </row>
-    <row r="641" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A641" s="1">
         <v>44855</v>
       </c>
@@ -12690,7 +12693,7 @@
         <v>44855</v>
       </c>
     </row>
-    <row r="642" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A642" s="1">
         <v>44862</v>
       </c>
@@ -12698,7 +12701,7 @@
         <v>44862</v>
       </c>
     </row>
-    <row r="643" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A643" s="1">
         <v>44869</v>
       </c>
@@ -12706,7 +12709,7 @@
         <v>44869</v>
       </c>
     </row>
-    <row r="644" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A644" s="1">
         <v>44876</v>
       </c>
@@ -12714,7 +12717,7 @@
         <v>44876</v>
       </c>
     </row>
-    <row r="645" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A645" s="1">
         <v>44883</v>
       </c>
@@ -12722,7 +12725,7 @@
         <v>44883</v>
       </c>
     </row>
-    <row r="646" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A646" s="1">
         <v>44890</v>
       </c>
@@ -12730,7 +12733,7 @@
         <v>44890</v>
       </c>
     </row>
-    <row r="647" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A647" s="1">
         <v>44897</v>
       </c>
@@ -12738,7 +12741,7 @@
         <v>44897</v>
       </c>
     </row>
-    <row r="648" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A648" s="1">
         <v>44904</v>
       </c>
@@ -12746,7 +12749,7 @@
         <v>44904</v>
       </c>
     </row>
-    <row r="649" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A649" s="1">
         <v>44911</v>
       </c>
@@ -12754,7 +12757,7 @@
         <v>44911</v>
       </c>
     </row>
-    <row r="650" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A650" s="1">
         <v>44918</v>
       </c>
@@ -12762,7 +12765,7 @@
         <v>44918</v>
       </c>
     </row>
-    <row r="651" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A651" s="1">
         <v>44925</v>
       </c>
@@ -12770,7 +12773,7 @@
         <v>44925</v>
       </c>
     </row>
-    <row r="652" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A652" s="1">
         <v>44932</v>
       </c>
@@ -12778,7 +12781,7 @@
         <v>44932</v>
       </c>
     </row>
-    <row r="653" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A653" s="1">
         <v>44939</v>
       </c>
@@ -12786,7 +12789,7 @@
         <v>44939</v>
       </c>
     </row>
-    <row r="654" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A654" s="1">
         <v>44946</v>
       </c>
@@ -12794,7 +12797,7 @@
         <v>44946</v>
       </c>
     </row>
-    <row r="655" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A655" s="1">
         <v>44953</v>
       </c>
@@ -12802,7 +12805,7 @@
         <v>44953</v>
       </c>
     </row>
-    <row r="656" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A656" s="1">
         <v>44960</v>
       </c>
@@ -12810,7 +12813,7 @@
         <v>44960</v>
       </c>
     </row>
-    <row r="657" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A657" s="1">
         <v>44967</v>
       </c>
@@ -12818,7 +12821,7 @@
         <v>44967</v>
       </c>
     </row>
-    <row r="658" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A658" s="1">
         <v>44974</v>
       </c>
@@ -12826,7 +12829,7 @@
         <v>44974</v>
       </c>
     </row>
-    <row r="659" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A659" s="1">
         <v>44981</v>
       </c>
@@ -12834,7 +12837,7 @@
         <v>44981</v>
       </c>
     </row>
-    <row r="660" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A660" s="1">
         <v>44988</v>
       </c>
@@ -12842,7 +12845,7 @@
         <v>44988</v>
       </c>
     </row>
-    <row r="661" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A661" s="1">
         <v>44995</v>
       </c>
@@ -12850,7 +12853,7 @@
         <v>44995</v>
       </c>
     </row>
-    <row r="662" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A662" s="1">
         <v>45002</v>
       </c>
@@ -12858,7 +12861,7 @@
         <v>45002</v>
       </c>
     </row>
-    <row r="663" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A663" s="1">
         <v>45009</v>
       </c>
@@ -12866,7 +12869,7 @@
         <v>45009</v>
       </c>
     </row>
-    <row r="664" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A664" s="1">
         <v>45016</v>
       </c>
@@ -12874,7 +12877,7 @@
         <v>45016</v>
       </c>
     </row>
-    <row r="665" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A665" s="1">
         <v>45023</v>
       </c>
@@ -12882,7 +12885,7 @@
         <v>45023</v>
       </c>
     </row>
-    <row r="666" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A666" s="1">
         <v>45030</v>
       </c>
@@ -12890,7 +12893,7 @@
         <v>45030</v>
       </c>
     </row>
-    <row r="667" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A667" s="1">
         <v>45037</v>
       </c>
@@ -12898,7 +12901,7 @@
         <v>45037</v>
       </c>
     </row>
-    <row r="668" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A668" s="1">
         <v>45044</v>
       </c>
@@ -12906,7 +12909,7 @@
         <v>45044</v>
       </c>
     </row>
-    <row r="669" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A669" s="1">
         <v>45051</v>
       </c>
@@ -12914,7 +12917,7 @@
         <v>45051</v>
       </c>
     </row>
-    <row r="670" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A670" s="1">
         <v>45058</v>
       </c>
@@ -12922,7 +12925,7 @@
         <v>45058</v>
       </c>
     </row>
-    <row r="671" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A671" s="1">
         <v>45065</v>
       </c>
@@ -12930,7 +12933,7 @@
         <v>45065</v>
       </c>
     </row>
-    <row r="672" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A672" s="1">
         <v>45072</v>
       </c>
@@ -12938,7 +12941,7 @@
         <v>45072</v>
       </c>
     </row>
-    <row r="673" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A673" s="1">
         <v>45079</v>
       </c>
@@ -12946,7 +12949,7 @@
         <v>45079</v>
       </c>
     </row>
-    <row r="674" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A674" s="1">
         <v>45086</v>
       </c>
@@ -12954,7 +12957,7 @@
         <v>45086</v>
       </c>
     </row>
-    <row r="675" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A675" s="1">
         <v>45093</v>
       </c>
@@ -12962,7 +12965,7 @@
         <v>45093</v>
       </c>
     </row>
-    <row r="676" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A676" s="1">
         <v>45100</v>
       </c>
@@ -12970,7 +12973,7 @@
         <v>45100</v>
       </c>
     </row>
-    <row r="677" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A677" s="1">
         <v>45107</v>
       </c>
@@ -12978,7 +12981,7 @@
         <v>45107</v>
       </c>
     </row>
-    <row r="678" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A678" s="1">
         <v>45114</v>
       </c>
@@ -12986,7 +12989,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="679" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A679" s="1">
         <v>45121</v>
       </c>
@@ -12994,7 +12997,7 @@
         <v>45121</v>
       </c>
     </row>
-    <row r="680" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A680" s="1">
         <v>45128</v>
       </c>
@@ -13002,7 +13005,7 @@
         <v>45128</v>
       </c>
     </row>
-    <row r="681" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A681" s="1">
         <v>45135</v>
       </c>
@@ -13010,7 +13013,7 @@
         <v>45135</v>
       </c>
     </row>
-    <row r="682" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A682" s="1">
         <v>45142</v>
       </c>
@@ -13018,7 +13021,7 @@
         <v>45142</v>
       </c>
     </row>
-    <row r="683" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A683" s="1">
         <v>45149</v>
       </c>
@@ -13026,7 +13029,7 @@
         <v>45149</v>
       </c>
     </row>
-    <row r="684" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A684" s="1">
         <v>45156</v>
       </c>
@@ -13034,7 +13037,7 @@
         <v>45156</v>
       </c>
     </row>
-    <row r="685" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A685" s="1">
         <v>45163</v>
       </c>
@@ -13042,7 +13045,7 @@
         <v>45163</v>
       </c>
     </row>
-    <row r="686" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A686" s="1">
         <v>45170</v>
       </c>
@@ -13050,7 +13053,7 @@
         <v>45170</v>
       </c>
     </row>
-    <row r="687" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A687" s="1">
         <v>45177</v>
       </c>
@@ -13058,7 +13061,7 @@
         <v>45177</v>
       </c>
     </row>
-    <row r="688" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A688" s="1">
         <v>45184</v>
       </c>
@@ -13066,7 +13069,7 @@
         <v>45184</v>
       </c>
     </row>
-    <row r="689" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A689" s="1">
         <v>45191</v>
       </c>
@@ -13074,7 +13077,7 @@
         <v>45191</v>
       </c>
     </row>
-    <row r="690" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A690" s="1">
         <v>45198</v>
       </c>
@@ -13082,7 +13085,7 @@
         <v>45198</v>
       </c>
     </row>
-    <row r="691" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A691" s="1">
         <v>45205</v>
       </c>
@@ -13090,7 +13093,7 @@
         <v>45205</v>
       </c>
     </row>
-    <row r="692" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A692" s="1">
         <v>45212</v>
       </c>
@@ -13098,7 +13101,7 @@
         <v>45212</v>
       </c>
     </row>
-    <row r="693" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A693" s="1">
         <v>45219</v>
       </c>
@@ -13106,7 +13109,7 @@
         <v>45219</v>
       </c>
     </row>
-    <row r="694" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A694" s="1">
         <v>45226</v>
       </c>
@@ -13114,7 +13117,7 @@
         <v>45226</v>
       </c>
     </row>
-    <row r="695" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A695" s="1">
         <v>45233</v>
       </c>
@@ -13122,7 +13125,7 @@
         <v>45233</v>
       </c>
     </row>
-    <row r="696" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A696" s="1">
         <v>45240</v>
       </c>
@@ -13130,7 +13133,7 @@
         <v>45240</v>
       </c>
     </row>
-    <row r="697" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A697" s="1">
         <v>45247</v>
       </c>
@@ -13138,7 +13141,7 @@
         <v>45247</v>
       </c>
     </row>
-    <row r="698" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A698" s="1">
         <v>45254</v>
       </c>
@@ -13146,7 +13149,7 @@
         <v>45254</v>
       </c>
     </row>
-    <row r="699" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A699" s="1">
         <v>45261</v>
       </c>
@@ -13154,7 +13157,7 @@
         <v>45261</v>
       </c>
     </row>
-    <row r="700" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A700" s="1">
         <v>45268</v>
       </c>
@@ -13162,7 +13165,7 @@
         <v>45268</v>
       </c>
     </row>
-    <row r="701" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A701" s="1">
         <v>45275</v>
       </c>
@@ -13170,7 +13173,7 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="702" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A702" s="1">
         <v>45282</v>
       </c>
@@ -13178,7 +13181,7 @@
         <v>45282</v>
       </c>
     </row>
-    <row r="703" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A703" s="1">
         <v>45289</v>
       </c>
@@ -13186,7 +13189,7 @@
         <v>45289</v>
       </c>
     </row>
-    <row r="704" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A704" s="1">
         <v>45296</v>
       </c>
@@ -13194,7 +13197,7 @@
         <v>45296</v>
       </c>
     </row>
-    <row r="705" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A705" s="1">
         <v>45303</v>
       </c>
@@ -13202,7 +13205,7 @@
         <v>45303</v>
       </c>
     </row>
-    <row r="706" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A706" s="1">
         <v>45310</v>
       </c>
@@ -13210,7 +13213,7 @@
         <v>45310</v>
       </c>
     </row>
-    <row r="707" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A707" s="1">
         <v>45317</v>
       </c>
@@ -13218,7 +13221,7 @@
         <v>45317</v>
       </c>
     </row>
-    <row r="708" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A708" s="1">
         <v>45324</v>
       </c>
@@ -13226,7 +13229,7 @@
         <v>45324</v>
       </c>
     </row>
-    <row r="709" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A709" s="1">
         <v>45331</v>
       </c>
@@ -13234,7 +13237,7 @@
         <v>45331</v>
       </c>
     </row>
-    <row r="710" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A710" s="1">
         <v>45338</v>
       </c>
@@ -13242,7 +13245,7 @@
         <v>45338</v>
       </c>
     </row>
-    <row r="711" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A711" s="1">
         <v>45345</v>
       </c>
@@ -13250,7 +13253,7 @@
         <v>45345</v>
       </c>
     </row>
-    <row r="712" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A712" s="1">
         <v>45352</v>
       </c>
@@ -13258,7 +13261,7 @@
         <v>45352</v>
       </c>
     </row>
-    <row r="713" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A713" s="1">
         <v>45359</v>
       </c>
@@ -13266,7 +13269,7 @@
         <v>45359</v>
       </c>
     </row>
-    <row r="714" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A714" s="1">
         <v>45366</v>
       </c>
@@ -13274,7 +13277,7 @@
         <v>45366</v>
       </c>
     </row>
-    <row r="715" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A715" s="1">
         <v>45373</v>
       </c>
@@ -13282,7 +13285,7 @@
         <v>45373</v>
       </c>
     </row>
-    <row r="716" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A716" s="1">
         <v>45380</v>
       </c>
@@ -13290,7 +13293,7 @@
         <v>45380</v>
       </c>
     </row>
-    <row r="717" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A717" s="1">
         <v>45387</v>
       </c>
@@ -13298,7 +13301,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="718" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A718" s="1">
         <v>45394</v>
       </c>
@@ -13306,7 +13309,7 @@
         <v>45394</v>
       </c>
     </row>
-    <row r="719" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A719" s="1">
         <v>45401</v>
       </c>
@@ -13314,7 +13317,7 @@
         <v>45401</v>
       </c>
     </row>
-    <row r="720" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A720" s="1">
         <v>45408</v>
       </c>
@@ -13322,7 +13325,7 @@
         <v>45408</v>
       </c>
     </row>
-    <row r="721" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A721" s="1">
         <v>45415</v>
       </c>
@@ -13330,7 +13333,7 @@
         <v>45415</v>
       </c>
     </row>
-    <row r="722" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A722" s="1">
         <v>45422</v>
       </c>
@@ -13338,7 +13341,7 @@
         <v>45422</v>
       </c>
     </row>
-    <row r="723" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A723" s="1">
         <v>45429</v>
       </c>
@@ -13346,7 +13349,7 @@
         <v>45429</v>
       </c>
     </row>
-    <row r="724" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A724" s="1">
         <v>45436</v>
       </c>
@@ -13354,7 +13357,7 @@
         <v>45436</v>
       </c>
     </row>
-    <row r="725" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A725" s="1">
         <v>45443</v>
       </c>
@@ -13362,7 +13365,7 @@
         <v>45443</v>
       </c>
     </row>
-    <row r="726" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A726" s="1">
         <v>45450</v>
       </c>
@@ -13370,7 +13373,7 @@
         <v>45450</v>
       </c>
     </row>
-    <row r="727" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A727" s="1">
         <v>45457</v>
       </c>
@@ -13378,7 +13381,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="728" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A728" s="1">
         <v>45464</v>
       </c>
@@ -13389,15 +13392,18 @@
         <v>1627.4</v>
       </c>
     </row>
-    <row r="729" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A729" s="1">
         <v>45471</v>
       </c>
       <c r="B729" s="1">
         <v>45471</v>
       </c>
-    </row>
-    <row r="730" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E729" s="13">
+        <v>1712.39</v>
+      </c>
+    </row>
+    <row r="730" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A730" s="1">
         <v>45478</v>
       </c>
@@ -13405,7 +13411,7 @@
         <v>45478</v>
       </c>
     </row>
-    <row r="731" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A731" s="1">
         <v>45485</v>
       </c>
@@ -13413,7 +13419,7 @@
         <v>45485</v>
       </c>
     </row>
-    <row r="732" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A732" s="1">
         <v>45492</v>
       </c>
@@ -13421,7 +13427,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="733" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A733" s="1">
         <v>45499</v>
       </c>
@@ -13429,7 +13435,7 @@
         <v>45499</v>
       </c>
     </row>
-    <row r="734" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A734" s="1">
         <v>45506</v>
       </c>
@@ -13437,7 +13443,7 @@
         <v>45506</v>
       </c>
     </row>
-    <row r="735" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A735" s="1">
         <v>45513</v>
       </c>
@@ -13445,7 +13451,7 @@
         <v>45513</v>
       </c>
     </row>
-    <row r="736" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A736" s="1">
         <v>45520</v>
       </c>
@@ -13453,7 +13459,7 @@
         <v>45520</v>
       </c>
     </row>
-    <row r="737" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A737" s="1">
         <v>45527</v>
       </c>
@@ -13461,7 +13467,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="738" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A738" s="1">
         <v>45534</v>
       </c>
@@ -13469,7 +13475,7 @@
         <v>45534</v>
       </c>
     </row>
-    <row r="739" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A739" s="1">
         <v>45541</v>
       </c>
@@ -13477,7 +13483,7 @@
         <v>45541</v>
       </c>
     </row>
-    <row r="740" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A740" s="1">
         <v>45548</v>
       </c>
@@ -13485,7 +13491,7 @@
         <v>45548</v>
       </c>
     </row>
-    <row r="741" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A741" s="1">
         <v>45555</v>
       </c>
@@ -13493,7 +13499,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="742" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A742" s="1">
         <v>45562</v>
       </c>
@@ -13501,7 +13507,7 @@
         <v>45562</v>
       </c>
     </row>
-    <row r="743" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A743" s="1">
         <v>45569</v>
       </c>
@@ -13509,7 +13515,7 @@
         <v>45569</v>
       </c>
     </row>
-    <row r="744" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A744" s="1">
         <v>45576</v>
       </c>
@@ -13517,7 +13523,7 @@
         <v>45576</v>
       </c>
     </row>
-    <row r="745" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A745" s="1">
         <v>45583</v>
       </c>
@@ -13525,7 +13531,7 @@
         <v>45583</v>
       </c>
     </row>
-    <row r="746" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A746" s="1">
         <v>45590</v>
       </c>
@@ -13533,7 +13539,7 @@
         <v>45590</v>
       </c>
     </row>
-    <row r="747" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A747" s="1">
         <v>45597</v>
       </c>
@@ -13541,7 +13547,7 @@
         <v>45597</v>
       </c>
     </row>
-    <row r="748" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A748" s="1">
         <v>45604</v>
       </c>
@@ -13549,7 +13555,7 @@
         <v>45604</v>
       </c>
     </row>
-    <row r="749" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A749" s="1">
         <v>45611</v>
       </c>
@@ -13557,7 +13563,7 @@
         <v>45611</v>
       </c>
     </row>
-    <row r="750" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A750" s="1">
         <v>45618</v>
       </c>
@@ -13565,7 +13571,7 @@
         <v>45618</v>
       </c>
     </row>
-    <row r="751" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A751" s="1">
         <v>45625</v>
       </c>
@@ -13573,7 +13579,7 @@
         <v>45625</v>
       </c>
     </row>
-    <row r="752" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A752" s="1">
         <v>45632</v>
       </c>
@@ -13581,7 +13587,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="753" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A753" s="1">
         <v>45639</v>
       </c>
@@ -13589,7 +13595,7 @@
         <v>45639</v>
       </c>
     </row>
-    <row r="754" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A754" s="1">
         <v>45646</v>
       </c>
@@ -13597,7 +13603,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="755" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A755" s="1">
         <v>45653</v>
       </c>
@@ -13605,7 +13611,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="756" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A756" s="1">
         <v>45660</v>
       </c>
@@ -13613,7 +13619,7 @@
         <v>45660</v>
       </c>
     </row>
-    <row r="757" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A757" s="1">
         <v>45667</v>
       </c>
@@ -13621,7 +13627,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="758" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A758" s="1">
         <v>45674</v>
       </c>
@@ -13629,7 +13635,7 @@
         <v>45674</v>
       </c>
     </row>
-    <row r="759" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A759" s="1">
         <v>45681</v>
       </c>
@@ -13637,7 +13643,7 @@
         <v>45681</v>
       </c>
     </row>
-    <row r="760" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A760" s="1">
         <v>45688</v>
       </c>
@@ -13645,7 +13651,7 @@
         <v>45688</v>
       </c>
     </row>
-    <row r="761" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A761" s="1">
         <v>45695</v>
       </c>
@@ -13653,7 +13659,7 @@
         <v>45695</v>
       </c>
     </row>
-    <row r="762" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A762" s="1">
         <v>45702</v>
       </c>
@@ -13661,7 +13667,7 @@
         <v>45702</v>
       </c>
     </row>
-    <row r="763" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A763" s="1">
         <v>45709</v>
       </c>
@@ -13669,7 +13675,7 @@
         <v>45709</v>
       </c>
     </row>
-    <row r="764" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A764" s="1">
         <v>45716</v>
       </c>
@@ -13677,7 +13683,7 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="765" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A765" s="1">
         <v>45723</v>
       </c>
@@ -13685,7 +13691,7 @@
         <v>45723</v>
       </c>
     </row>
-    <row r="766" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A766" s="1">
         <v>45730</v>
       </c>
@@ -13693,7 +13699,7 @@
         <v>45730</v>
       </c>
     </row>
-    <row r="767" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A767" s="1">
         <v>45737</v>
       </c>
@@ -13701,7 +13707,7 @@
         <v>45737</v>
       </c>
     </row>
-    <row r="768" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A768" s="1">
         <v>45744</v>
       </c>
@@ -13709,7 +13715,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="769" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A769" s="1">
         <v>45751</v>
       </c>
@@ -13717,7 +13723,7 @@
         <v>45751</v>
       </c>
     </row>
-    <row r="770" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A770" s="1">
         <v>45758</v>
       </c>
@@ -13725,7 +13731,7 @@
         <v>45758</v>
       </c>
     </row>
-    <row r="771" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A771" s="1">
         <v>45765</v>
       </c>
@@ -13733,7 +13739,7 @@
         <v>45765</v>
       </c>
     </row>
-    <row r="772" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A772" s="1">
         <v>45772</v>
       </c>
@@ -13741,7 +13747,7 @@
         <v>45772</v>
       </c>
     </row>
-    <row r="773" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A773" s="1">
         <v>45779</v>
       </c>
@@ -13749,7 +13755,7 @@
         <v>45779</v>
       </c>
     </row>
-    <row r="774" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A774" s="1">
         <v>45786</v>
       </c>
@@ -13757,7 +13763,7 @@
         <v>45786</v>
       </c>
     </row>
-    <row r="775" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A775" s="1">
         <v>45793</v>
       </c>
@@ -13765,7 +13771,7 @@
         <v>45793</v>
       </c>
     </row>
-    <row r="776" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A776" s="1">
         <v>45800</v>
       </c>
@@ -13773,7 +13779,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="777" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A777" s="1">
         <v>45807</v>
       </c>
@@ -13781,7 +13787,7 @@
         <v>45807</v>
       </c>
     </row>
-    <row r="778" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A778" s="1">
         <v>45814</v>
       </c>
@@ -13789,7 +13795,7 @@
         <v>45814</v>
       </c>
     </row>
-    <row r="779" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A779" s="1">
         <v>45821</v>
       </c>
@@ -13797,7 +13803,7 @@
         <v>45821</v>
       </c>
     </row>
-    <row r="780" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A780" s="1">
         <v>45828</v>
       </c>
@@ -13808,7 +13814,7 @@
         <v>2158.19</v>
       </c>
     </row>
-    <row r="781" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A781" s="1">
         <v>45835</v>
       </c>
@@ -13819,7 +13825,7 @@
         <v>2158.19</v>
       </c>
     </row>
-    <row r="782" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A782" s="1">
         <v>45842</v>
       </c>
@@ -13827,7 +13833,7 @@
         <v>45842</v>
       </c>
     </row>
-    <row r="783" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A783" s="1">
         <v>45849</v>
       </c>
@@ -13835,7 +13841,7 @@
         <v>45849</v>
       </c>
     </row>
-    <row r="784" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A784" s="1">
         <v>45856</v>
       </c>
@@ -13843,7 +13849,7 @@
         <v>45856</v>
       </c>
     </row>
-    <row r="785" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A785" s="1">
         <v>45863</v>
       </c>
@@ -13851,7 +13857,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="786" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A786" s="1">
         <v>45870</v>
       </c>
@@ -13859,7 +13865,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="787" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A787" s="1">
         <v>45877</v>
       </c>
@@ -13867,7 +13873,7 @@
         <v>45877</v>
       </c>
     </row>
-    <row r="788" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A788" s="1">
         <v>45884</v>
       </c>
@@ -13875,7 +13881,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="789" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A789" s="1">
         <v>45891</v>
       </c>
@@ -13883,7 +13889,7 @@
         <v>45891</v>
       </c>
     </row>
-    <row r="790" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A790" s="1">
         <v>45898</v>
       </c>
@@ -13891,7 +13897,7 @@
         <v>45898</v>
       </c>
     </row>
-    <row r="791" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A791" s="1">
         <v>45905</v>
       </c>
@@ -13899,7 +13905,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="792" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A792" s="1">
         <v>45912</v>
       </c>
@@ -13907,7 +13913,7 @@
         <v>45912</v>
       </c>
     </row>
-    <row r="793" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A793" s="1">
         <v>45919</v>
       </c>
@@ -13915,7 +13921,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="794" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A794" s="1">
         <v>45926</v>
       </c>
@@ -13923,7 +13929,7 @@
         <v>45926</v>
       </c>
     </row>
-    <row r="795" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A795" s="1">
         <v>45933</v>
       </c>
@@ -13931,7 +13937,7 @@
         <v>45933</v>
       </c>
     </row>
-    <row r="796" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A796" s="1">
         <v>45940</v>
       </c>
@@ -13939,7 +13945,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="797" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A797" s="1">
         <v>45947</v>
       </c>
@@ -13947,7 +13953,7 @@
         <v>45947</v>
       </c>
     </row>
-    <row r="798" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A798" s="1">
         <v>45954</v>
       </c>
@@ -13955,7 +13961,7 @@
         <v>45954</v>
       </c>
     </row>
-    <row r="799" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A799" s="1">
         <v>45961</v>
       </c>
@@ -13963,7 +13969,7 @@
         <v>45961</v>
       </c>
     </row>
-    <row r="800" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A800" s="1">
         <v>45968</v>
       </c>
@@ -13971,7 +13977,7 @@
         <v>45968</v>
       </c>
     </row>
-    <row r="801" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A801" s="1">
         <v>45975</v>
       </c>
@@ -13979,7 +13985,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="802" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A802" s="1">
         <v>45982</v>
       </c>
@@ -13987,7 +13993,7 @@
         <v>45982</v>
       </c>
     </row>
-    <row r="803" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A803" s="1">
         <v>45989</v>
       </c>
@@ -13995,7 +14001,7 @@
         <v>45989</v>
       </c>
     </row>
-    <row r="804" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A804" s="1">
         <v>45996</v>
       </c>
@@ -14003,7 +14009,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="805" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A805" s="1">
         <v>46003</v>
       </c>
@@ -14011,7 +14017,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="806" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A806" s="1">
         <v>46010</v>
       </c>
@@ -14019,7 +14025,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="807" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A807" s="1">
         <v>46017</v>
       </c>
@@ -14042,7 +14048,7 @@
       <c r="N807" s="10"/>
       <c r="O807" s="10"/>
     </row>
-    <row r="808" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A808" s="1">
         <v>46024</v>
       </c>
@@ -14085,7 +14091,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="809" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A809" s="1">
         <v>46031</v>
       </c>
@@ -14128,7 +14134,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="810" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A810" s="1">
         <v>46038</v>
       </c>
@@ -14171,7 +14177,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="811" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A811" s="1">
         <v>46045</v>
       </c>
@@ -14214,7 +14220,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="812" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A812" s="1">
         <v>46052</v>
       </c>
@@ -14257,7 +14263,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="813" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A813" s="1">
         <v>46059</v>
       </c>
@@ -14300,7 +14306,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="814" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A814" s="1">
         <v>46066</v>
       </c>
@@ -14343,7 +14349,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="815" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A815" s="1">
         <v>46073</v>
       </c>
@@ -14386,7 +14392,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="816" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A816" s="1">
         <v>46080</v>
       </c>
@@ -14429,7 +14435,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="817" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A817" s="1">
         <v>46087</v>
       </c>
@@ -14472,7 +14478,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="818" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A818" s="1">
         <v>46094</v>
       </c>
@@ -14515,7 +14521,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="819" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A819" s="1">
         <v>46101</v>
       </c>
@@ -14558,7 +14564,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="820" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A820" s="1">
         <v>46108</v>
       </c>
@@ -14601,7 +14607,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="821" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A821" s="1">
         <v>46115</v>
       </c>
@@ -14644,7 +14650,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="822" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A822" s="1">
         <v>46122</v>
       </c>
@@ -14667,7 +14673,7 @@
       <c r="N822" s="3"/>
       <c r="O822" s="3"/>
     </row>
-    <row r="823" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A823" s="1">
         <v>46129</v>
       </c>
@@ -14690,7 +14696,7 @@
       <c r="N823" s="3"/>
       <c r="O823" s="3"/>
     </row>
-    <row r="824" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A824" s="1">
         <v>46136</v>
       </c>
@@ -14713,7 +14719,7 @@
       <c r="N824" s="3"/>
       <c r="O824" s="3"/>
     </row>
-    <row r="825" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A825" s="1">
         <v>46143</v>
       </c>
@@ -14756,7 +14762,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="826" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A826" s="1">
         <v>46150</v>
       </c>
@@ -14799,7 +14805,7 @@
         <v>76000</v>
       </c>
     </row>
-    <row r="827" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A827" s="1">
         <v>46157</v>
       </c>
@@ -14842,7 +14848,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="828" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A828" s="1">
         <v>46164</v>
       </c>
@@ -14885,7 +14891,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="829" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A829" s="1">
         <v>46171</v>
       </c>
@@ -14928,7 +14934,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="830" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A830" s="1">
         <v>46178</v>
       </c>
@@ -14969,7 +14975,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="831" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A831" s="1">
         <v>46185</v>
       </c>
@@ -15010,7 +15016,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="832" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A832" s="1">
         <v>46192</v>
       </c>
@@ -15059,7 +15065,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02768588-2FF0-42C1-8A18-87D4CAFE9D17}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -15069,12 +15075,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A6084AF-43C5-4F58-881A-79CFC1D1F25A}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" s="8" t="s">
         <v>15</v>
       </c>
@@ -15082,7 +15088,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" s="8" t="s">
         <v>17</v>
       </c>

--- a/data/freight/HARPEX.xlsx
+++ b/data/freight/HARPEX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/freight/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82C67B9-2401-7145-B87A-A45AFC3761B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9B7534-9BBB-4666-A7E9-4A64AB9BFD16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25700" yWindow="3980" windowWidth="23260" windowHeight="14860" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
   <sheets>
     <sheet name="HARPEX" sheetId="1" r:id="rId1"/>
@@ -2761,6 +2761,9 @@
                 <c:pt idx="830">
                   <c:v>46192</c:v>
                 </c:pt>
+                <c:pt idx="831">
+                  <c:v>46199</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4631,6 +4634,9 @@
                   <c:v>2323.69</c:v>
                 </c:pt>
                 <c:pt idx="830">
+                  <c:v>2326.67</c:v>
+                </c:pt>
+                <c:pt idx="831">
                   <c:v>2326.67</c:v>
                 </c:pt>
               </c:numCache>
@@ -5741,18 +5747,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
-  <dimension ref="A1:P832"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:P833"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.36328125" style="16" customWidth="1"/>
     <col min="4" max="4" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="15" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.36328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="15" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -5800,7 +5806,7 @@
       </c>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>40383</v>
       </c>
@@ -5811,7 +5817,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>40390</v>
       </c>
@@ -5822,7 +5828,7 @@
         <v>705.88</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>40397</v>
       </c>
@@ -5833,7 +5839,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>40404</v>
       </c>
@@ -5844,7 +5850,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>40411</v>
       </c>
@@ -5855,7 +5861,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>40418</v>
       </c>
@@ -5866,7 +5872,7 @@
         <v>742.34</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>40425</v>
       </c>
@@ -5877,7 +5883,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>40432</v>
       </c>
@@ -5888,7 +5894,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>40439</v>
       </c>
@@ -5899,7 +5905,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>40446</v>
       </c>
@@ -5910,7 +5916,7 @@
         <v>763.05</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>40453</v>
       </c>
@@ -5921,7 +5927,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>40460</v>
       </c>
@@ -5932,7 +5938,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>40467</v>
       </c>
@@ -5943,7 +5949,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>40474</v>
       </c>
@@ -5954,7 +5960,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>40481</v>
       </c>
@@ -5965,7 +5971,7 @@
         <v>686.83</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>40488</v>
       </c>
@@ -5976,7 +5982,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>40495</v>
       </c>
@@ -5987,7 +5993,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>40502</v>
       </c>
@@ -5998,7 +6004,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>40509</v>
       </c>
@@ -6009,7 +6015,7 @@
         <v>613.5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>40516</v>
       </c>
@@ -6020,7 +6026,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>40523</v>
       </c>
@@ -6031,7 +6037,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>40530</v>
       </c>
@@ -6042,7 +6048,7 @@
         <v>669.84</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>40537</v>
       </c>
@@ -6053,7 +6059,7 @@
         <v>679.37</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>40544</v>
       </c>
@@ -6064,7 +6070,7 @@
         <v>696.35</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>40551</v>
       </c>
@@ -6075,7 +6081,7 @@
         <v>706.3</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>40558</v>
       </c>
@@ -6086,7 +6092,7 @@
         <v>719.55</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>40565</v>
       </c>
@@ -6097,7 +6103,7 @@
         <v>747.31</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>40572</v>
       </c>
@@ -6108,7 +6114,7 @@
         <v>764.29</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>40579</v>
       </c>
@@ -6119,7 +6125,7 @@
         <v>782.1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>40586</v>
       </c>
@@ -6130,7 +6136,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>40593</v>
       </c>
@@ -6141,7 +6147,7 @@
         <v>849.63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>40600</v>
       </c>
@@ -6152,7 +6158,7 @@
         <v>861.23</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>40607</v>
       </c>
@@ -6163,7 +6169,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>40614</v>
       </c>
@@ -6174,7 +6180,7 @@
         <v>879.04</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>40621</v>
       </c>
@@ -6185,7 +6191,7 @@
         <v>882.35</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>40628</v>
       </c>
@@ -6196,7 +6202,7 @@
         <v>900.99</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>40635</v>
       </c>
@@ -6207,7 +6213,7 @@
         <v>892.29</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>40642</v>
       </c>
@@ -6218,7 +6224,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>40649</v>
       </c>
@@ -6229,7 +6235,7 @@
         <v>888.15</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>40656</v>
       </c>
@@ -6240,7 +6246,7 @@
         <v>879.87</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>40663</v>
       </c>
@@ -6251,7 +6257,7 @@
         <v>875.72</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>40670</v>
       </c>
@@ -6262,7 +6268,7 @@
         <v>874.48</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>40677</v>
       </c>
@@ -6273,7 +6279,7 @@
         <v>877.38</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>40684</v>
       </c>
@@ -6284,7 +6290,7 @@
         <v>876.14</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>40691</v>
       </c>
@@ -6295,7 +6301,7 @@
         <v>870.34</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>40698</v>
       </c>
@@ -6306,7 +6312,7 @@
         <v>865.37</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>40705</v>
       </c>
@@ -6317,7 +6323,7 @@
         <v>856.67</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>40712</v>
       </c>
@@ -6328,7 +6334,7 @@
         <v>847.14</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>40719</v>
       </c>
@@ -6339,7 +6345,7 @@
         <v>831.4</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>40726</v>
       </c>
@@ -6350,7 +6356,7 @@
         <v>820.22</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>40733</v>
       </c>
@@ -6361,7 +6367,7 @@
         <v>808.62</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>40740</v>
       </c>
@@ -6372,7 +6378,7 @@
         <v>775.06</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>40747</v>
       </c>
@@ -6383,7 +6389,7 @@
         <v>741.51</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>40754</v>
       </c>
@@ -6394,7 +6400,7 @@
         <v>719.97</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>40761</v>
       </c>
@@ -6405,7 +6411,7 @@
         <v>709.2</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>40768</v>
       </c>
@@ -6416,7 +6422,7 @@
         <v>671.91</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>40775</v>
       </c>
@@ -6427,7 +6433,7 @@
         <v>666.11</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>40782</v>
       </c>
@@ -6438,7 +6444,7 @@
         <v>657.83</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>40789</v>
       </c>
@@ -6449,7 +6455,7 @@
         <v>630.9</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>40796</v>
       </c>
@@ -6460,7 +6466,7 @@
         <v>621.38</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>40803</v>
       </c>
@@ -6471,7 +6477,7 @@
         <v>616.4</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>40810</v>
       </c>
@@ -6482,7 +6488,7 @@
         <v>555.1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>40817</v>
       </c>
@@ -6493,7 +6499,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>40824</v>
       </c>
@@ -6504,7 +6510,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>40831</v>
       </c>
@@ -6515,7 +6521,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>40838</v>
       </c>
@@ -6526,7 +6532,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>40845</v>
       </c>
@@ -6537,7 +6543,7 @@
         <v>445.32</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>40852</v>
       </c>
@@ -6548,7 +6554,7 @@
         <v>438.28</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>40859</v>
       </c>
@@ -6559,7 +6565,7 @@
         <v>437.45</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>40866</v>
       </c>
@@ -6570,7 +6576,7 @@
         <v>420.05</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>40873</v>
       </c>
@@ -6581,7 +6587,7 @@
         <v>417.98</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>40880</v>
       </c>
@@ -6592,7 +6598,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>40887</v>
       </c>
@@ -6603,7 +6609,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>40894</v>
       </c>
@@ -6614,7 +6620,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>40901</v>
       </c>
@@ -6625,7 +6631,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>40908</v>
       </c>
@@ -6636,7 +6642,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>40915</v>
       </c>
@@ -6647,7 +6653,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>40922</v>
       </c>
@@ -6658,7 +6664,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>40929</v>
       </c>
@@ -6669,7 +6675,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>40936</v>
       </c>
@@ -6680,7 +6686,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>40942</v>
       </c>
@@ -6691,7 +6697,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>40943</v>
       </c>
@@ -6702,7 +6708,7 @@
         <v>389.81</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>40950</v>
       </c>
@@ -6713,7 +6719,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>40957</v>
       </c>
@@ -6724,7 +6730,7 @@
         <v>375.31</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>40964</v>
       </c>
@@ -6735,7 +6741,7 @@
         <v>376.14</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>40978</v>
       </c>
@@ -6746,7 +6752,7 @@
         <v>384.84</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>40985</v>
       </c>
@@ -6757,7 +6763,7 @@
         <v>393.12</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>40992</v>
       </c>
@@ -6768,7 +6774,7 @@
         <v>396.02</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>40999</v>
       </c>
@@ -6779,7 +6785,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>41006</v>
       </c>
@@ -6790,7 +6796,7 @@
         <v>394.78</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>41013</v>
       </c>
@@ -6801,7 +6807,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>41020</v>
       </c>
@@ -6812,7 +6818,7 @@
         <v>416.32</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>41027</v>
       </c>
@@ -6823,7 +6829,7 @@
         <v>428.33</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>41034</v>
       </c>
@@ -6834,7 +6840,7 @@
         <v>440.35</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>41041</v>
       </c>
@@ -6845,7 +6851,7 @@
         <v>444.9</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>41048</v>
       </c>
@@ -6856,7 +6862,7 @@
         <v>457.33</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>41055</v>
       </c>
@@ -6867,7 +6873,7 @@
         <v>458.99</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>41062</v>
       </c>
@@ -6878,7 +6884,7 @@
         <v>456.92</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>41069</v>
       </c>
@@ -6889,7 +6895,7 @@
         <v>451.12</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>41076</v>
       </c>
@@ -6900,7 +6906,7 @@
         <v>446.98</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>41083</v>
       </c>
@@ -6911,7 +6917,7 @@
         <v>437.86</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>41090</v>
       </c>
@@ -6922,7 +6928,7 @@
         <v>434.96</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>41097</v>
       </c>
@@ -6933,7 +6939,7 @@
         <v>430.41</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>41104</v>
       </c>
@@ -6944,7 +6950,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>41111</v>
       </c>
@@ -6955,7 +6961,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>41118</v>
       </c>
@@ -6966,7 +6972,7 @@
         <v>413.84</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>41125</v>
       </c>
@@ -6977,7 +6983,7 @@
         <v>399.75</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>41132</v>
       </c>
@@ -6988,7 +6994,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>41139</v>
       </c>
@@ -6999,7 +7005,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>41146</v>
       </c>
@@ -7010,7 +7016,7 @@
         <v>396.44</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>41153</v>
       </c>
@@ -7021,7 +7027,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>41160</v>
       </c>
@@ -7032,7 +7038,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>41167</v>
       </c>
@@ -7043,7 +7049,7 @@
         <v>386.08</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>41174</v>
       </c>
@@ -7054,7 +7060,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>41181</v>
       </c>
@@ -7065,7 +7071,7 @@
         <v>377.8</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>41188</v>
       </c>
@@ -7076,7 +7082,7 @@
         <v>373.65</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>41195</v>
       </c>
@@ -7087,7 +7093,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>41202</v>
       </c>
@@ -7098,7 +7104,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>41209</v>
       </c>
@@ -7109,7 +7115,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>41216</v>
       </c>
@@ -7120,7 +7126,7 @@
         <v>367.44</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>41223</v>
       </c>
@@ -7131,7 +7137,7 @@
         <v>366.61</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>41230</v>
       </c>
@@ -7142,7 +7148,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>41237</v>
       </c>
@@ -7153,7 +7159,7 @@
         <v>362.88</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>41244</v>
       </c>
@@ -7164,7 +7170,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>41251</v>
       </c>
@@ -7175,7 +7181,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>41258</v>
       </c>
@@ -7186,7 +7192,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>41265</v>
       </c>
@@ -7197,7 +7203,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>41272</v>
       </c>
@@ -7208,7 +7214,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>41279</v>
       </c>
@@ -7219,7 +7225,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>41286</v>
       </c>
@@ -7230,7 +7236,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>41293</v>
       </c>
@@ -7241,7 +7247,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>41300</v>
       </c>
@@ -7252,7 +7258,7 @@
         <v>359.15</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>41307</v>
       </c>
@@ -7263,7 +7269,7 @@
         <v>366.2</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>41314</v>
       </c>
@@ -7274,7 +7280,7 @@
         <v>369.93</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>41321</v>
       </c>
@@ -7285,7 +7291,7 @@
         <v>372.41</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>41328</v>
       </c>
@@ -7296,7 +7302,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>41335</v>
       </c>
@@ -7307,7 +7313,7 @@
         <v>376.97</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>41342</v>
       </c>
@@ -7318,7 +7324,7 @@
         <v>379.45</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>41349</v>
       </c>
@@ -7329,7 +7335,7 @@
         <v>382.35</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>41356</v>
       </c>
@@ -7340,7 +7346,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>41363</v>
       </c>
@@ -7351,7 +7357,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>41370</v>
       </c>
@@ -7362,7 +7368,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>41377</v>
       </c>
@@ -7373,7 +7379,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>41384</v>
       </c>
@@ -7384,7 +7390,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>41391</v>
       </c>
@@ -7395,7 +7401,7 @@
         <v>395.61</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>41398</v>
       </c>
@@ -7406,7 +7412,7 @@
         <v>396.85</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>41405</v>
       </c>
@@ -7417,7 +7423,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>41412</v>
       </c>
@@ -7428,7 +7434,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>41419</v>
       </c>
@@ -7439,7 +7445,7 @@
         <v>398.09</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>41426</v>
       </c>
@@ -7450,7 +7456,7 @@
         <v>401.41</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>41433</v>
       </c>
@@ -7461,7 +7467,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>41440</v>
       </c>
@@ -7472,7 +7478,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>41447</v>
       </c>
@@ -7483,7 +7489,7 @@
         <v>400.58</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>41454</v>
       </c>
@@ -7494,7 +7500,7 @@
         <v>401.82</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>41461</v>
       </c>
@@ -7505,7 +7511,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>41468</v>
       </c>
@@ -7516,7 +7522,7 @@
         <v>398.51</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>41475</v>
       </c>
@@ -7527,7 +7533,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>41482</v>
       </c>
@@ -7538,7 +7544,7 @@
         <v>400.99</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>41489</v>
       </c>
@@ -7549,7 +7555,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>41496</v>
       </c>
@@ -7560,7 +7566,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>41503</v>
       </c>
@@ -7571,7 +7577,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>41510</v>
       </c>
@@ -7582,7 +7588,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>41517</v>
       </c>
@@ -7593,7 +7599,7 @@
         <v>404.72</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>41524</v>
       </c>
@@ -7604,7 +7610,7 @@
         <v>405.55</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>41531</v>
       </c>
@@ -7615,7 +7621,7 @@
         <v>403.07</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>41538</v>
       </c>
@@ -7626,7 +7632,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>41545</v>
       </c>
@@ -7637,7 +7643,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>41552</v>
       </c>
@@ -7648,7 +7654,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>41559</v>
       </c>
@@ -7659,7 +7665,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>41566</v>
       </c>
@@ -7670,7 +7676,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>41573</v>
       </c>
@@ -7681,7 +7687,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>41580</v>
       </c>
@@ -7692,7 +7698,7 @@
         <v>400.17</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>41587</v>
       </c>
@@ -7703,7 +7709,7 @@
         <v>398.92</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>41594</v>
       </c>
@@ -7714,7 +7720,7 @@
         <v>397.68</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>41601</v>
       </c>
@@ -7725,7 +7731,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>41608</v>
       </c>
@@ -7736,7 +7742,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>41615</v>
       </c>
@@ -7747,7 +7753,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>41622</v>
       </c>
@@ -7758,7 +7764,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>41629</v>
       </c>
@@ -7769,7 +7775,7 @@
         <v>390.64</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>41636</v>
       </c>
@@ -7780,7 +7786,7 @@
         <v>390.22</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>41643</v>
       </c>
@@ -7791,7 +7797,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>41650</v>
       </c>
@@ -7802,7 +7808,7 @@
         <v>391.88</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>41657</v>
       </c>
@@ -7813,7 +7819,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>41664</v>
       </c>
@@ -7824,7 +7830,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>41671</v>
       </c>
@@ -7835,7 +7841,7 @@
         <v>388.57</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>41678</v>
       </c>
@@ -7846,7 +7852,7 @@
         <v>387.74</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>41685</v>
       </c>
@@ -7857,7 +7863,7 @@
         <v>386.91</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>41692</v>
       </c>
@@ -7868,7 +7874,7 @@
         <v>385.25</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>41699</v>
       </c>
@@ -7879,7 +7885,7 @@
         <v>384.42</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>41706</v>
       </c>
@@ -7890,7 +7896,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>41713</v>
       </c>
@@ -7901,7 +7907,7 @@
         <v>382.77</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>41720</v>
       </c>
@@ -7912,7 +7918,7 @@
         <v>380.7</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>41727</v>
       </c>
@@ -7923,7 +7929,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>41734</v>
       </c>
@@ -7934,7 +7940,7 @@
         <v>378.21</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>41741</v>
       </c>
@@ -7945,7 +7951,7 @@
         <v>386.5</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>41748</v>
       </c>
@@ -7956,7 +7962,7 @@
         <v>392.71</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>41755</v>
       </c>
@@ -7967,7 +7973,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>41762</v>
       </c>
@@ -7978,7 +7984,7 @@
         <v>393.54</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>41769</v>
       </c>
@@ -7989,7 +7995,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>41776</v>
       </c>
@@ -8000,7 +8006,7 @@
         <v>399.34</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>41783</v>
       </c>
@@ -8011,7 +8017,7 @@
         <v>402.65</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>41790</v>
       </c>
@@ -8022,7 +8028,7 @@
         <v>403.89</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>41797</v>
       </c>
@@ -8033,7 +8039,7 @@
         <v>406.79</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>41804</v>
       </c>
@@ -8044,7 +8050,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>41811</v>
       </c>
@@ -8055,7 +8061,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>41818</v>
       </c>
@@ -8066,7 +8072,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>41825</v>
       </c>
@@ -8077,7 +8083,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>41832</v>
       </c>
@@ -8088,7 +8094,7 @@
         <v>409.28</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>41839</v>
       </c>
@@ -8099,7 +8105,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>41846</v>
       </c>
@@ -8110,7 +8116,7 @@
         <v>405.97</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>41853</v>
       </c>
@@ -8121,7 +8127,7 @@
         <v>407.21</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>41860</v>
       </c>
@@ -8132,7 +8138,7 @@
         <v>406.38</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>41867</v>
       </c>
@@ -8143,7 +8149,7 @@
         <v>409.69</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>41874</v>
       </c>
@@ -8154,7 +8160,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>41881</v>
       </c>
@@ -8165,7 +8171,7 @@
         <v>410.52</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>41888</v>
       </c>
@@ -8176,7 +8182,7 @@
         <v>412.59</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>41895</v>
       </c>
@@ -8187,7 +8193,7 @@
         <v>412.18</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>41902</v>
       </c>
@@ -8198,7 +8204,7 @@
         <v>422.54</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>41909</v>
       </c>
@@ -8209,7 +8215,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>41916</v>
       </c>
@@ -8220,7 +8226,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>41923</v>
       </c>
@@ -8231,7 +8237,7 @@
         <v>424.61</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>41930</v>
       </c>
@@ -8242,7 +8248,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>41937</v>
       </c>
@@ -8253,7 +8259,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>41944</v>
       </c>
@@ -8264,7 +8270,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>41951</v>
       </c>
@@ -8275,7 +8281,7 @@
         <v>421.29</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>41958</v>
       </c>
@@ -8286,7 +8292,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>41965</v>
       </c>
@@ -8297,7 +8303,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>41972</v>
       </c>
@@ -8308,7 +8314,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>41979</v>
       </c>
@@ -8319,7 +8325,7 @@
         <v>421.71</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>41986</v>
       </c>
@@ -8330,7 +8336,7 @@
         <v>422.12</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>41993</v>
       </c>
@@ -8341,7 +8347,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>42000</v>
       </c>
@@ -8352,7 +8358,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>42007</v>
       </c>
@@ -8363,7 +8369,7 @@
         <v>422.95</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>42014</v>
       </c>
@@ -8374,7 +8380,7 @@
         <v>435.38</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>42021</v>
       </c>
@@ -8385,7 +8391,7 @@
         <v>441.59</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>42028</v>
       </c>
@@ -8396,7 +8402,7 @@
         <v>455.26</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>42035</v>
       </c>
@@ -8407,7 +8413,7 @@
         <v>461.47</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>42042</v>
       </c>
@@ -8418,7 +8424,7 @@
         <v>477.63</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>42049</v>
       </c>
@@ -8429,7 +8435,7 @@
         <v>483.84</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>42056</v>
       </c>
@@ -8440,7 +8446,7 @@
         <v>494.2</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>42063</v>
       </c>
@@ -8451,7 +8457,7 @@
         <v>496.27</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
         <v>42070</v>
       </c>
@@ -8462,7 +8468,7 @@
         <v>502.49</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A244" s="1">
         <v>42077</v>
       </c>
@@ -8473,7 +8479,7 @@
         <v>504.14</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A245" s="1">
         <v>42084</v>
       </c>
@@ -8484,7 +8490,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
         <v>42091</v>
       </c>
@@ -8495,7 +8501,7 @@
         <v>561.72</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
         <v>42098</v>
       </c>
@@ -8506,7 +8512,7 @@
         <v>596.11</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A248" s="1">
         <v>42105</v>
       </c>
@@ -8517,7 +8523,7 @@
         <v>614.75</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A249" s="1">
         <v>42112</v>
       </c>
@@ -8528,7 +8534,7 @@
         <v>612.67999999999995</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A250" s="1">
         <v>42119</v>
       </c>
@@ -8539,7 +8545,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A251" s="1">
         <v>42126</v>
       </c>
@@ -8550,7 +8556,7 @@
         <v>619.72</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
         <v>42133</v>
       </c>
@@ -8561,7 +8567,7 @@
         <v>626.76</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>42140</v>
       </c>
@@ -8572,7 +8578,7 @@
         <v>640.02</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>42147</v>
       </c>
@@ -8583,7 +8589,7 @@
         <v>642.91999999999996</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A255" s="1">
         <v>42154</v>
       </c>
@@ -8594,7 +8600,7 @@
         <v>644.57000000000005</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A256" s="1">
         <v>42161</v>
       </c>
@@ -8605,7 +8611,7 @@
         <v>643.74</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A257" s="1">
         <v>42168</v>
       </c>
@@ -8616,7 +8622,7 @@
         <v>645.82000000000005</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A258" s="1">
         <v>42175</v>
       </c>
@@ -8627,7 +8633,7 @@
         <v>639.6</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A259" s="1">
         <v>42182</v>
       </c>
@@ -8638,7 +8644,7 @@
         <v>633.39</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A260" s="1">
         <v>42189</v>
       </c>
@@ -8649,7 +8655,7 @@
         <v>630.07000000000005</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A261" s="1">
         <v>42196</v>
       </c>
@@ -8660,7 +8666,7 @@
         <v>620.13</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A262" s="1">
         <v>42203</v>
       </c>
@@ -8671,7 +8677,7 @@
         <v>617.65</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A263" s="1">
         <v>42210</v>
       </c>
@@ -8682,7 +8688,7 @@
         <v>600.25</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A264" s="1">
         <v>42217</v>
       </c>
@@ -8693,7 +8699,7 @@
         <v>577.04999999999995</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A265" s="1">
         <v>42224</v>
       </c>
@@ -8704,7 +8710,7 @@
         <v>560.07000000000005</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A266" s="1">
         <v>42231</v>
       </c>
@@ -8715,7 +8721,7 @@
         <v>558.82000000000005</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A267" s="1">
         <v>42238</v>
       </c>
@@ -8726,7 +8732,7 @@
         <v>550.12</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A268" s="1">
         <v>42245</v>
       </c>
@@ -8737,7 +8743,7 @@
         <v>545.98</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A269" s="1">
         <v>42252</v>
       </c>
@@ -8748,7 +8754,7 @@
         <v>541.01</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A270" s="1">
         <v>42259</v>
       </c>
@@ -8759,7 +8765,7 @@
         <v>527.75</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A271" s="1">
         <v>42266</v>
       </c>
@@ -8770,7 +8776,7 @@
         <v>512.84</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A272" s="1">
         <v>42273</v>
       </c>
@@ -8781,7 +8787,7 @@
         <v>491.3</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A273" s="1">
         <v>42280</v>
       </c>
@@ -8792,7 +8798,7 @@
         <v>477.22</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A274" s="1">
         <v>42287</v>
       </c>
@@ -8803,7 +8809,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A275" s="1">
         <v>42294</v>
       </c>
@@ -8814,7 +8820,7 @@
         <v>438.69</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A276" s="1">
         <v>42301</v>
       </c>
@@ -8825,7 +8831,7 @@
         <v>415.08</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A277" s="1">
         <v>42308</v>
       </c>
@@ -8836,7 +8842,7 @@
         <v>395.19</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A278" s="1">
         <v>42315</v>
       </c>
@@ -8847,7 +8853,7 @@
         <v>394.37</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A279" s="1">
         <v>42322</v>
       </c>
@@ -8858,7 +8864,7 @@
         <v>388.98</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A280" s="1">
         <v>42329</v>
       </c>
@@ -8869,7 +8875,7 @@
         <v>385.67</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A281" s="1">
         <v>42336</v>
       </c>
@@ -8880,7 +8886,7 @@
         <v>380.28</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A282" s="1">
         <v>42343</v>
       </c>
@@ -8891,7 +8897,7 @@
         <v>371.17</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A283" s="1">
         <v>42350</v>
       </c>
@@ -8902,7 +8908,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A284" s="1">
         <v>42357</v>
       </c>
@@ -8913,7 +8919,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A285" s="1">
         <v>42364</v>
       </c>
@@ -8924,7 +8930,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A286" s="1">
         <v>42371</v>
       </c>
@@ -8935,7 +8941,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A287" s="1">
         <v>42378</v>
       </c>
@@ -8946,7 +8952,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A288" s="1">
         <v>42385</v>
       </c>
@@ -8957,7 +8963,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A289" s="1">
         <v>42392</v>
       </c>
@@ -8968,7 +8974,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A290" s="1">
         <v>42399</v>
       </c>
@@ -8979,7 +8985,7 @@
         <v>363.71</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A291" s="1">
         <v>42406</v>
       </c>
@@ -8990,7 +8996,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A292" s="1">
         <v>42413</v>
       </c>
@@ -9001,7 +9007,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A293" s="1">
         <v>42420</v>
       </c>
@@ -9012,7 +9018,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A294" s="1">
         <v>42427</v>
       </c>
@@ -9023,7 +9029,7 @@
         <v>365.78</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A295" s="1">
         <v>42434</v>
       </c>
@@ -9034,7 +9040,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A296" s="1">
         <v>42441</v>
       </c>
@@ -9045,7 +9051,7 @@
         <v>364.95</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A297" s="1">
         <v>42448</v>
       </c>
@@ -9056,7 +9062,7 @@
         <v>364.13</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A298" s="1">
         <v>42455</v>
       </c>
@@ -9067,7 +9073,7 @@
         <v>363.3</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A299" s="1">
         <v>42462</v>
       </c>
@@ -9078,7 +9084,7 @@
         <v>362.47</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A300" s="1">
         <v>42469</v>
       </c>
@@ -9089,7 +9095,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A301" s="1">
         <v>42476</v>
       </c>
@@ -9100,7 +9106,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A302" s="1">
         <v>42483</v>
       </c>
@@ -9111,7 +9117,7 @@
         <v>357.91</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A303" s="1">
         <v>42490</v>
       </c>
@@ -9122,7 +9128,7 @@
         <v>358.74</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A304" s="1">
         <v>42497</v>
       </c>
@@ -9133,7 +9139,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A305" s="1">
         <v>42504</v>
       </c>
@@ -9144,7 +9150,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A306" s="1">
         <v>42511</v>
       </c>
@@ -9155,7 +9161,7 @@
         <v>359.98</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A307" s="1">
         <v>42518</v>
       </c>
@@ -9166,7 +9172,7 @@
         <v>356.67</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A308" s="1">
         <v>42525</v>
       </c>
@@ -9177,7 +9183,7 @@
         <v>355.84</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A309" s="1">
         <v>42532</v>
       </c>
@@ -9188,7 +9194,7 @@
         <v>354.6</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A310" s="1">
         <v>42539</v>
       </c>
@@ -9199,7 +9205,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A311" s="1">
         <v>42546</v>
       </c>
@@ -9210,7 +9216,7 @@
         <v>352.53</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A312" s="1">
         <v>42553</v>
       </c>
@@ -9221,7 +9227,7 @@
         <v>351.7</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A313" s="1">
         <v>42560</v>
       </c>
@@ -9232,7 +9238,7 @@
         <v>348.8</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A314" s="1">
         <v>42567</v>
       </c>
@@ -9243,7 +9249,7 @@
         <v>347.56</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A315" s="1">
         <v>42574</v>
       </c>
@@ -9254,7 +9260,7 @@
         <v>345.9</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A316" s="1">
         <v>42581</v>
       </c>
@@ -9265,7 +9271,7 @@
         <v>345.07</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A317" s="1">
         <v>42588</v>
       </c>
@@ -9276,7 +9282,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A318" s="1">
         <v>42595</v>
       </c>
@@ -9287,7 +9293,7 @@
         <v>342.17</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A319" s="1">
         <v>42602</v>
       </c>
@@ -9298,7 +9304,7 @@
         <v>341.76</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A320" s="1">
         <v>42609</v>
       </c>
@@ -9309,7 +9315,7 @@
         <v>337.2</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A321" s="1">
         <v>42616</v>
       </c>
@@ -9320,7 +9326,7 @@
         <v>331.4</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A322" s="1">
         <v>42623</v>
       </c>
@@ -9331,7 +9337,7 @@
         <v>330.99</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A323" s="1">
         <v>42630</v>
       </c>
@@ -9342,7 +9348,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A324" s="1">
         <v>42637</v>
       </c>
@@ -9353,7 +9359,7 @@
         <v>328.09</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A325" s="1">
         <v>42644</v>
       </c>
@@ -9364,7 +9370,7 @@
         <v>328.5</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A326" s="1">
         <v>42651</v>
       </c>
@@ -9375,7 +9381,7 @@
         <v>326.01</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A327" s="1">
         <v>42658</v>
       </c>
@@ -9386,7 +9392,7 @@
         <v>324.77</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A328" s="1">
         <v>42665</v>
       </c>
@@ -9397,7 +9403,7 @@
         <v>322.7</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A329" s="1">
         <v>42672</v>
       </c>
@@ -9408,7 +9414,7 @@
         <v>319.39</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A330" s="1">
         <v>42679</v>
       </c>
@@ -9419,7 +9425,7 @@
         <v>318.56</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A331" s="1">
         <v>42686</v>
       </c>
@@ -9430,7 +9436,7 @@
         <v>317.32</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A332" s="1">
         <v>42693</v>
       </c>
@@ -9441,7 +9447,7 @@
         <v>316.49</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A333" s="1">
         <v>42700</v>
       </c>
@@ -9452,7 +9458,7 @@
         <v>316.07</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A334" s="1">
         <v>42707</v>
       </c>
@@ -9463,7 +9469,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A335" s="1">
         <v>42714</v>
       </c>
@@ -9474,7 +9480,7 @@
         <v>314.83</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A336" s="1">
         <v>42721</v>
       </c>
@@ -9485,7 +9491,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A337" s="1">
         <v>42728</v>
       </c>
@@ -9496,7 +9502,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A338" s="1">
         <v>42735</v>
       </c>
@@ -9507,7 +9513,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A339" s="1">
         <v>42742</v>
       </c>
@@ -9518,7 +9524,7 @@
         <v>316.39</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A340" s="1">
         <v>42749</v>
       </c>
@@ -9529,7 +9535,7 @@
         <v>319.07</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A341" s="1">
         <v>42756</v>
       </c>
@@ -9540,7 +9546,7 @@
         <v>320.56</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A342" s="1">
         <v>42763</v>
       </c>
@@ -9551,7 +9557,7 @@
         <v>322.35000000000002</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A343" s="1">
         <v>42770</v>
       </c>
@@ -9562,7 +9568,7 @@
         <v>323.83999999999997</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A344" s="1">
         <v>42777</v>
       </c>
@@ -9573,7 +9579,7 @@
         <v>325.33</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A345" s="1">
         <v>42784</v>
       </c>
@@ -9584,7 +9590,7 @@
         <v>330.4</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A346" s="1">
         <v>42791</v>
       </c>
@@ -9595,7 +9601,7 @@
         <v>343.52</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A347" s="1">
         <v>42798</v>
       </c>
@@ -9606,7 +9612,7 @@
         <v>351.87</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A348" s="1">
         <v>42805</v>
       </c>
@@ -9617,7 +9623,7 @@
         <v>389.44</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A349" s="1">
         <v>42812</v>
       </c>
@@ -9628,7 +9634,7 @@
         <v>404.35</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A350" s="1">
         <v>42819</v>
       </c>
@@ -9639,7 +9645,7 @@
         <v>438.94</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A351" s="1">
         <v>42826</v>
       </c>
@@ -9650,7 +9656,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A352" s="1">
         <v>42833</v>
       </c>
@@ -9661,7 +9667,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A353" s="1">
         <v>42840</v>
       </c>
@@ -9672,7 +9678,7 @@
         <v>516.77</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A354" s="1">
         <v>42847</v>
       </c>
@@ -9683,7 +9689,7 @@
         <v>522.14</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A355" s="1">
         <v>42854</v>
       </c>
@@ -9694,7 +9700,7 @@
         <v>523.33000000000004</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A356" s="1">
         <v>42861</v>
       </c>
@@ -9705,7 +9711,7 @@
         <v>533.47</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A357" s="1">
         <v>42868</v>
       </c>
@@ -9716,7 +9722,7 @@
         <v>533.16999999999996</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A358" s="1">
         <v>42875</v>
       </c>
@@ -9727,7 +9733,7 @@
         <v>500.37</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A359" s="1">
         <v>42882</v>
       </c>
@@ -9738,7 +9744,7 @@
         <v>483.97</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A360" s="1">
         <v>42889</v>
       </c>
@@ -9749,7 +9755,7 @@
         <v>458.92</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A361" s="1">
         <v>42896</v>
       </c>
@@ -9760,7 +9766,7 @@
         <v>443.72</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A362" s="1">
         <v>42903</v>
       </c>
@@ -9771,7 +9777,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A363" s="1">
         <v>42910</v>
       </c>
@@ -9782,7 +9788,7 @@
         <v>438.35</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A364" s="1">
         <v>42917</v>
       </c>
@@ -9793,7 +9799,7 @@
         <v>439.54</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A365" s="1">
         <v>42924</v>
       </c>
@@ -9804,7 +9810,7 @@
         <v>435.96</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A366" s="1">
         <v>42931</v>
       </c>
@@ -9815,7 +9821,7 @@
         <v>445.8</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A367" s="1">
         <v>42938</v>
       </c>
@@ -9826,7 +9832,7 @@
         <v>470.25</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A368" s="1">
         <v>42945</v>
       </c>
@@ -9837,7 +9843,7 @@
         <v>472.04</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A369" s="1">
         <v>42952</v>
       </c>
@@ -9848,7 +9854,7 @@
         <v>481.88</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A370" s="1">
         <v>42959</v>
       </c>
@@ -9859,7 +9865,7 @@
         <v>486.66</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A371" s="1">
         <v>42966</v>
       </c>
@@ -9870,7 +9876,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A372" s="1">
         <v>42973</v>
       </c>
@@ -9881,7 +9887,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A373" s="1">
         <v>42980</v>
       </c>
@@ -9892,7 +9898,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A374" s="1">
         <v>42987</v>
       </c>
@@ -9903,7 +9909,7 @@
         <v>515.88</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A375" s="1">
         <v>42994</v>
       </c>
@@ -9914,7 +9920,7 @@
         <v>517.07000000000005</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A376" s="1">
         <v>43001</v>
       </c>
@@ -9925,7 +9931,7 @@
         <v>513.79</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A377" s="1">
         <v>43008</v>
       </c>
@@ -9936,7 +9942,7 @@
         <v>506.34</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A378" s="1">
         <v>43015</v>
       </c>
@@ -9947,7 +9953,7 @@
         <v>507.53</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A379" s="1">
         <v>43022</v>
       </c>
@@ -9958,7 +9964,7 @@
         <v>505.14</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A380" s="1">
         <v>43029</v>
       </c>
@@ -9969,7 +9975,7 @@
         <v>494.11</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A381" s="1">
         <v>43036</v>
       </c>
@@ -9980,7 +9986,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A382" s="1">
         <v>43043</v>
       </c>
@@ -9991,7 +9997,7 @@
         <v>473.24</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A383" s="1">
         <v>43050</v>
       </c>
@@ -10002,7 +10008,7 @@
         <v>473.83</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A384" s="1">
         <v>43057</v>
       </c>
@@ -10013,7 +10019,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A385" s="1">
         <v>43064</v>
       </c>
@@ -10024,7 +10030,7 @@
         <v>477.71</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A386" s="1">
         <v>43071</v>
       </c>
@@ -10035,7 +10041,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A387" s="1">
         <v>43078</v>
       </c>
@@ -10046,7 +10052,7 @@
         <v>477.41</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A388" s="1">
         <v>43085</v>
       </c>
@@ -10057,7 +10063,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A389" s="1">
         <v>43092</v>
       </c>
@@ -10068,7 +10074,7 @@
         <v>482.78</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A390" s="1">
         <v>43099</v>
       </c>
@@ -10079,7 +10085,7 @@
         <v>483.08</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A391" s="1">
         <v>43106</v>
       </c>
@@ -10090,7 +10096,7 @@
         <v>485.16</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A392" s="1">
         <v>43113</v>
       </c>
@@ -10101,7 +10107,7 @@
         <v>489.34</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A393" s="1">
         <v>43120</v>
       </c>
@@ -10112,7 +10118,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A394" s="1">
         <v>43127</v>
       </c>
@@ -10123,7 +10129,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A395" s="1">
         <v>43134</v>
       </c>
@@ -10134,7 +10140,7 @@
         <v>504.25</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A396" s="1">
         <v>43141</v>
       </c>
@@ -10145,7 +10151,7 @@
         <v>520.35</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A397" s="1">
         <v>43148</v>
       </c>
@@ -10156,7 +10162,7 @@
         <v>526.02</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A398" s="1">
         <v>43155</v>
       </c>
@@ -10167,7 +10173,7 @@
         <v>542.41999999999996</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A399" s="1">
         <v>43162</v>
       </c>
@@ -10178,7 +10184,7 @@
         <v>548.98</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A400" s="1">
         <v>43169</v>
       </c>
@@ -10189,7 +10195,7 @@
         <v>579.69000000000005</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A401" s="1">
         <v>43176</v>
       </c>
@@ -10200,7 +10206,7 @@
         <v>597.88</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A402" s="1">
         <v>43183</v>
       </c>
@@ -10211,7 +10217,7 @@
         <v>635.16</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A403" s="1">
         <v>43190</v>
       </c>
@@ -10222,7 +10228,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A404" s="1">
         <v>43197</v>
       </c>
@@ -10233,7 +10239,7 @@
         <v>645.59</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A405" s="1">
         <v>43204</v>
       </c>
@@ -10244,7 +10250,7 @@
         <v>642.61</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A406" s="1">
         <v>43211</v>
       </c>
@@ -10255,7 +10261,7 @@
         <v>646.19000000000005</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A407" s="1">
         <v>43218</v>
       </c>
@@ -10266,7 +10272,7 @@
         <v>652.45000000000005</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A408" s="1">
         <v>43225</v>
       </c>
@@ -10277,7 +10283,7 @@
         <v>653.64</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A409" s="1">
         <v>43232</v>
       </c>
@@ -10288,7 +10294,7 @@
         <v>656.63</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A410" s="1">
         <v>43239</v>
       </c>
@@ -10299,7 +10305,7 @@
         <v>661.1</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A411" s="1">
         <v>43245</v>
       </c>
@@ -10310,7 +10316,7 @@
         <v>670.64</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A412" s="1">
         <v>43252</v>
       </c>
@@ -10321,7 +10327,7 @@
         <v>673.62</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A413" s="1">
         <v>43259</v>
       </c>
@@ -10332,7 +10338,7 @@
         <v>676.61</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A414" s="1">
         <v>43266</v>
       </c>
@@ -10343,7 +10349,7 @@
         <v>678.1</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A415" s="1">
         <v>43273</v>
       </c>
@@ -10354,7 +10360,7 @@
         <v>676.9</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A416" s="1">
         <v>43280</v>
       </c>
@@ -10365,7 +10371,7 @@
         <v>672.73</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A417" s="1">
         <v>43287</v>
       </c>
@@ -10376,7 +10382,7 @@
         <v>668.26</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A418" s="1">
         <v>43294</v>
       </c>
@@ -10387,7 +10393,7 @@
         <v>652.15</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A419" s="1">
         <v>43301</v>
       </c>
@@ -10398,7 +10404,7 @@
         <v>628.6</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A420" s="1">
         <v>43308</v>
       </c>
@@ -10409,7 +10415,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A421" s="1">
         <v>43315</v>
       </c>
@@ -10420,7 +10426,7 @@
         <v>594.6</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A422" s="1">
         <v>43322</v>
       </c>
@@ -10431,7 +10437,7 @@
         <v>584.16999999999996</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A423" s="1">
         <v>43329</v>
       </c>
@@ -10442,7 +10448,7 @@
         <v>582.97</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A424" s="1">
         <v>43336</v>
       </c>
@@ -10453,7 +10459,7 @@
         <v>577.01</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A425" s="1">
         <v>43343</v>
       </c>
@@ -10464,7 +10470,7 @@
         <v>568.05999999999995</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A426" s="1">
         <v>43350</v>
       </c>
@@ -10475,7 +10481,7 @@
         <v>550.77</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A427" s="1">
         <v>43357</v>
       </c>
@@ -10486,7 +10492,7 @@
         <v>548.08000000000004</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A428" s="1">
         <v>43364</v>
       </c>
@@ -10497,7 +10503,7 @@
         <v>538.54</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A429" s="1">
         <v>43371</v>
       </c>
@@ -10508,7 +10514,7 @@
         <v>534.37</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A430" s="1">
         <v>43378</v>
       </c>
@@ -10519,7 +10525,7 @@
         <v>532.28</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A431" s="1">
         <v>43385</v>
       </c>
@@ -10530,7 +10536,7 @@
         <v>524.23</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A432" s="1">
         <v>43392</v>
       </c>
@@ -10541,7 +10547,7 @@
         <v>516.17999999999995</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A433" s="1">
         <v>43399</v>
       </c>
@@ -10552,7 +10558,7 @@
         <v>509.62</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A434" s="1">
         <v>43406</v>
       </c>
@@ -10563,7 +10569,7 @@
         <v>503.06</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A435" s="1">
         <v>43413</v>
       </c>
@@ -10574,7 +10580,7 @@
         <v>499.48</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A436" s="1">
         <v>43420</v>
       </c>
@@ -10585,7 +10591,7 @@
         <v>501.57</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A437" s="1">
         <v>43427</v>
       </c>
@@ -10596,7 +10602,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A438" s="1">
         <v>43434</v>
       </c>
@@ -10607,7 +10613,7 @@
         <v>502.16</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A439" s="1">
         <v>43441</v>
       </c>
@@ -10618,7 +10624,7 @@
         <v>498.58</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A440" s="1">
         <v>43448</v>
       </c>
@@ -10629,7 +10635,7 @@
         <v>495.6</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A441" s="1">
         <v>43455</v>
       </c>
@@ -10640,7 +10646,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A442" s="1">
         <v>43462</v>
       </c>
@@ -10651,7 +10657,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A443" s="1">
         <v>43469</v>
       </c>
@@ -10662,7 +10668,7 @@
         <v>485.46</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A444" s="1">
         <v>43476</v>
       </c>
@@ -10673,7 +10679,7 @@
         <v>478.01</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A445" s="1">
         <v>43483</v>
       </c>
@@ -10684,7 +10690,7 @@
         <v>474.43</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A446" s="1">
         <v>43490</v>
       </c>
@@ -10695,7 +10701,7 @@
         <v>481.29</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A447" s="1">
         <v>43497</v>
       </c>
@@ -10706,7 +10712,7 @@
         <v>492.02</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A448" s="1">
         <v>43504</v>
       </c>
@@ -10717,7 +10723,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A449" s="1">
         <v>43511</v>
       </c>
@@ -10728,7 +10734,7 @@
         <v>499.18</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A450" s="1">
         <v>43518</v>
       </c>
@@ -10739,7 +10745,7 @@
         <v>502.46</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A451" s="1">
         <v>43525</v>
       </c>
@@ -10750,7 +10756,7 @@
         <v>527.80999999999995</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A452" s="1">
         <v>43532</v>
       </c>
@@ -10761,7 +10767,7 @@
         <v>543.01</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A453" s="1">
         <v>43539</v>
       </c>
@@ -10772,7 +10778,7 @@
         <v>552.55999999999995</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A454" s="1">
         <v>43546</v>
       </c>
@@ -10783,7 +10789,7 @@
         <v>560.61</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A455" s="1">
         <v>43553</v>
       </c>
@@ -10794,7 +10800,7 @@
         <v>565.67999999999995</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A456" s="1">
         <v>43560</v>
       </c>
@@ -10805,7 +10811,7 @@
         <v>576.11</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A457" s="1">
         <v>43567</v>
       </c>
@@ -10816,7 +10822,7 @@
         <v>581.48</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A458" s="1">
         <v>43574</v>
       </c>
@@ -10827,7 +10833,7 @@
         <v>585.05999999999995</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A459" s="1">
         <v>43581</v>
       </c>
@@ -10838,7 +10844,7 @@
         <v>585.66</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A460" s="1">
         <v>43588</v>
       </c>
@@ -10849,7 +10855,7 @@
         <v>586.25</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A461" s="1">
         <v>43595</v>
       </c>
@@ -10860,7 +10866,7 @@
         <v>586.85</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A462" s="1">
         <v>43602</v>
       </c>
@@ -10871,7 +10877,7 @@
         <v>596.09</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A463" s="1">
         <v>43609</v>
       </c>
@@ -10882,7 +10888,7 @@
         <v>599.08000000000004</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A464" s="1">
         <v>43616</v>
       </c>
@@ -10893,7 +10899,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A465" s="1">
         <v>43623</v>
       </c>
@@ -10904,7 +10910,7 @@
         <v>603.25</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A466" s="1">
         <v>43630</v>
       </c>
@@ -10915,7 +10921,7 @@
         <v>603.85</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A467" s="1">
         <v>43637</v>
       </c>
@@ -10926,7 +10932,7 @@
         <v>603.54999999999995</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A468" s="1">
         <v>43644</v>
       </c>
@@ -10937,7 +10943,7 @@
         <v>611.6</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A469" s="1">
         <v>43651</v>
       </c>
@@ -10948,7 +10954,7 @@
         <v>618.76</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A470" s="1">
         <v>43658</v>
       </c>
@@ -10959,7 +10965,7 @@
         <v>629.19000000000005</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A471" s="1">
         <v>43665</v>
       </c>
@@ -10970,7 +10976,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A472" s="1">
         <v>43672</v>
       </c>
@@ -10981,7 +10987,7 @@
         <v>666.77</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A473" s="1">
         <v>43679</v>
       </c>
@@ -10992,7 +10998,7 @@
         <v>670.94</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A474" s="1">
         <v>43686</v>
       </c>
@@ -11003,7 +11009,7 @@
         <v>681.97</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A475" s="1">
         <v>43693</v>
       </c>
@@ -11014,7 +11020,7 @@
         <v>690.02</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A476" s="1">
         <v>43700</v>
       </c>
@@ -11025,7 +11031,7 @@
         <v>696.88</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A477" s="1">
         <v>43707</v>
       </c>
@@ -11036,7 +11042,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A478" s="1">
         <v>43714</v>
       </c>
@@ -11047,7 +11053,7 @@
         <v>718.65</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A479" s="1">
         <v>43721</v>
       </c>
@@ -11058,7 +11064,7 @@
         <v>723.42</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A480" s="1">
         <v>43728</v>
       </c>
@@ -11069,7 +11075,7 @@
         <v>724.62</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A481" s="1">
         <v>43735</v>
       </c>
@@ -11080,7 +11086,7 @@
         <v>726.4</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A482" s="1">
         <v>43742</v>
       </c>
@@ -11091,7 +11097,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A483" s="1">
         <v>43749</v>
       </c>
@@ -11102,7 +11108,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A484" s="1">
         <v>43756</v>
       </c>
@@ -11113,7 +11119,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A485" s="1">
         <v>43763</v>
       </c>
@@ -11124,7 +11130,7 @@
         <v>723.72</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A486" s="1">
         <v>43770</v>
       </c>
@@ -11135,7 +11141,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A487" s="1">
         <v>43777</v>
       </c>
@@ -11146,7 +11152,7 @@
         <v>714.18</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A488" s="1">
         <v>43784</v>
       </c>
@@ -11157,7 +11163,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A489" s="1">
         <v>43791</v>
       </c>
@@ -11168,7 +11174,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A490" s="1">
         <v>43798</v>
       </c>
@@ -11179,7 +11185,7 @@
         <v>717.46</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A491" s="1">
         <v>43805</v>
       </c>
@@ -11190,7 +11196,7 @@
         <v>716.27</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A492" s="1">
         <v>43812</v>
       </c>
@@ -11201,7 +11207,7 @@
         <v>715.67</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A493" s="1">
         <v>43819</v>
       </c>
@@ -11212,7 +11218,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A494" s="1">
         <v>43826</v>
       </c>
@@ -11223,7 +11229,7 @@
         <v>712.99</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A495" s="1">
         <v>43833</v>
       </c>
@@ -11234,7 +11240,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A496" s="1">
         <v>43840</v>
       </c>
@@ -11245,7 +11251,7 @@
         <v>712.69</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A497" s="1">
         <v>43847</v>
       </c>
@@ -11256,7 +11262,7 @@
         <v>711.49</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A498" s="1">
         <v>43854</v>
       </c>
@@ -11267,7 +11273,7 @@
         <v>708.51</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A499" s="1">
         <v>43861</v>
       </c>
@@ -11278,7 +11284,7 @@
         <v>705.53</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A500" s="1">
         <v>43868</v>
       </c>
@@ -11289,7 +11295,7 @@
         <v>701.95</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A501" s="1">
         <v>43875</v>
       </c>
@@ -11300,7 +11306,7 @@
         <v>691.52</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A502" s="1">
         <v>43882</v>
       </c>
@@ -11311,7 +11317,7 @@
         <v>680.48</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A503" s="1">
         <v>43889</v>
       </c>
@@ -11322,7 +11328,7 @@
         <v>668.85</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A504" s="1">
         <v>43896</v>
       </c>
@@ -11333,7 +11339,7 @@
         <v>651.26</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A505" s="1">
         <v>43903</v>
       </c>
@@ -11344,7 +11350,7 @@
         <v>638.14</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A506" s="1">
         <v>43910</v>
       </c>
@@ -11355,7 +11361,7 @@
         <v>631.58000000000004</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A507" s="1">
         <v>43917</v>
       </c>
@@ -11366,7 +11372,7 @@
         <v>616.07000000000005</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A508" s="1">
         <v>43924</v>
       </c>
@@ -11377,7 +11383,7 @@
         <v>613.09</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A509" s="1">
         <v>43931</v>
       </c>
@@ -11388,7 +11394,7 @@
         <v>601.46</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A510" s="1">
         <v>43938</v>
       </c>
@@ -11399,7 +11405,7 @@
         <v>572.83000000000004</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A511" s="1">
         <v>43945</v>
       </c>
@@ -11410,7 +11416,7 @@
         <v>549.87</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A512" s="1">
         <v>43952</v>
       </c>
@@ -11421,7 +11427,7 @@
         <v>528.70000000000005</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A513" s="1">
         <v>43959</v>
       </c>
@@ -11432,7 +11438,7 @@
         <v>507.83</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A514" s="1">
         <v>43966</v>
       </c>
@@ -11443,7 +11449,7 @@
         <v>491.43</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A515" s="1">
         <v>43973</v>
       </c>
@@ -11454,7 +11460,7 @@
         <v>479.2</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A516" s="1">
         <v>43980</v>
       </c>
@@ -11465,7 +11471,7 @@
         <v>452.36</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A517" s="1">
         <v>43987</v>
       </c>
@@ -11476,7 +11482,7 @@
         <v>434.17</v>
       </c>
     </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A518" s="1">
         <v>43994</v>
       </c>
@@ -11487,7 +11493,7 @@
         <v>412.11</v>
       </c>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A519" s="1">
         <v>44001</v>
       </c>
@@ -11498,7 +11504,7 @@
         <v>418.96</v>
       </c>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A520" s="1">
         <v>44008</v>
       </c>
@@ -11509,7 +11515,7 @@
         <v>431.79</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A521" s="1">
         <v>44015</v>
       </c>
@@ -11520,7 +11526,7 @@
         <v>439.84</v>
       </c>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A522" s="1">
         <v>44022</v>
       </c>
@@ -11531,7 +11537,7 @@
         <v>444.91</v>
       </c>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A523" s="1">
         <v>44029</v>
       </c>
@@ -11542,7 +11548,7 @@
         <v>463.1</v>
       </c>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A524" s="1">
         <v>44036</v>
       </c>
@@ -11553,7 +11559,7 @@
         <v>484.87</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A525" s="1">
         <v>44043</v>
       </c>
@@ -11564,7 +11570,7 @@
         <v>521.54</v>
       </c>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A526" s="1">
         <v>44050</v>
       </c>
@@ -11575,7 +11581,7 @@
         <v>556.13</v>
       </c>
     </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A527" s="1">
         <v>44057</v>
       </c>
@@ -11586,7 +11592,7 @@
         <v>596.69000000000005</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A528" s="1">
         <v>44064</v>
       </c>
@@ -11597,7 +11603,7 @@
         <v>627.11</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A529" s="1">
         <v>44071</v>
       </c>
@@ -11608,7 +11614,7 @@
         <v>665.87</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A530" s="1">
         <v>44078</v>
       </c>
@@ -11619,7 +11625,7 @@
         <v>671.83</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A531" s="1">
         <v>44085</v>
       </c>
@@ -11630,7 +11636,7 @@
         <v>678.4</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A532" s="1">
         <v>44092</v>
       </c>
@@ -11641,7 +11647,7 @@
         <v>691.81</v>
       </c>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A533" s="1">
         <v>44099</v>
       </c>
@@ -11652,7 +11658,7 @@
         <v>703.74</v>
       </c>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A534" s="1">
         <v>44106</v>
       </c>
@@ -11663,7 +11669,7 @@
         <v>714.77</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A535" s="1">
         <v>44113</v>
       </c>
@@ -11674,7 +11680,7 @@
         <v>754.14</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A536" s="1">
         <v>44120</v>
       </c>
@@ -11685,7 +11691,7 @@
         <v>783.96</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A537" s="1">
         <v>44127</v>
       </c>
@@ -11696,7 +11702,7 @@
         <v>820.04</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A538" s="1">
         <v>44134</v>
       </c>
@@ -11707,7 +11713,7 @@
         <v>881.17</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A539" s="1">
         <v>44141</v>
       </c>
@@ -11718,7 +11724,7 @@
         <v>910.09</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A540" s="1">
         <v>44148</v>
       </c>
@@ -11729,7 +11735,7 @@
         <v>947.07</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A541" s="1">
         <v>44155</v>
       </c>
@@ -11740,7 +11746,7 @@
         <v>978.68</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A542" s="1">
         <v>44162</v>
       </c>
@@ -11751,7 +11757,7 @@
         <v>1009.39</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A543" s="1">
         <v>44169</v>
       </c>
@@ -11762,7 +11768,7 @@
         <v>1016.25</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A544" s="1">
         <v>44176</v>
       </c>
@@ -11773,7 +11779,7 @@
         <v>1020.13</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A545" s="1">
         <v>44183</v>
       </c>
@@ -11784,7 +11790,7 @@
         <v>1032.06</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A546" s="1">
         <v>44190</v>
       </c>
@@ -11795,7 +11801,7 @@
         <v>1036.23</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A547" s="1">
         <v>44197</v>
       </c>
@@ -11806,7 +11812,7 @@
         <v>1038.02</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A548" s="1">
         <v>44204</v>
       </c>
@@ -11817,7 +11823,7 @@
         <v>1069.6300000000001</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A549" s="1">
         <v>44211</v>
       </c>
@@ -11828,7 +11834,7 @@
         <v>1094.3800000000001</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A550" s="1">
         <v>44218</v>
       </c>
@@ -11839,7 +11845,7 @@
         <v>1112.8699999999999</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A551" s="1">
         <v>44225</v>
       </c>
@@ -11850,7 +11856,7 @@
         <v>1154.32</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A552" s="1">
         <v>44232</v>
       </c>
@@ -11861,7 +11867,7 @@
         <v>1202.03</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A553" s="1">
         <v>44239</v>
       </c>
@@ -11872,7 +11878,7 @@
         <v>1228.27</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A554" s="1">
         <v>44246</v>
       </c>
@@ -11883,7 +11889,7 @@
         <v>1262.26</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A555" s="1">
         <v>44253</v>
       </c>
@@ -11894,7 +11900,7 @@
         <v>1278.3599999999999</v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A556" s="1">
         <v>44260</v>
       </c>
@@ -11905,7 +11911,7 @@
         <v>1323.39</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A557" s="1">
         <v>44267</v>
       </c>
@@ -11916,7 +11922,7 @@
         <v>1387.21</v>
       </c>
     </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A558" s="1">
         <v>44274</v>
       </c>
@@ -11927,7 +11933,7 @@
         <v>1442.97</v>
       </c>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A559" s="1">
         <v>44281</v>
       </c>
@@ -11938,7 +11944,7 @@
         <v>1454.3</v>
       </c>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A560" s="1">
         <v>44288</v>
       </c>
@@ -11949,7 +11955,7 @@
         <v>1492.47</v>
       </c>
     </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A561" s="1">
         <v>44295</v>
       </c>
@@ -11960,7 +11966,7 @@
         <v>1559.56</v>
       </c>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A562" s="1">
         <v>44302</v>
       </c>
@@ -11971,7 +11977,7 @@
         <v>1650.51</v>
       </c>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A563" s="1">
         <v>44309</v>
       </c>
@@ -11982,7 +11988,7 @@
         <v>1680.33</v>
       </c>
     </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A564" s="1">
         <v>44316</v>
       </c>
@@ -11993,7 +11999,7 @@
         <v>1707.47</v>
       </c>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A565" s="1">
         <v>44323</v>
       </c>
@@ -12004,7 +12010,7 @@
         <v>1777.25</v>
       </c>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A566" s="1">
         <v>44330</v>
       </c>
@@ -12015,7 +12021,7 @@
         <v>1837.48</v>
       </c>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A567" s="1">
         <v>44337</v>
       </c>
@@ -12026,7 +12032,7 @@
         <v>1890.86</v>
       </c>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A568" s="1">
         <v>44344</v>
       </c>
@@ -12037,7 +12043,7 @@
         <v>1940.66</v>
       </c>
     </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A569" s="1">
         <v>44351</v>
       </c>
@@ -12048,7 +12054,7 @@
         <v>1986.58</v>
       </c>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A570" s="1">
         <v>44358</v>
       </c>
@@ -12059,7 +12065,7 @@
         <v>2033.69</v>
       </c>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A571" s="1">
         <v>44365</v>
       </c>
@@ -12070,7 +12076,7 @@
         <v>2117.19</v>
       </c>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A572" s="1">
         <v>44372</v>
       </c>
@@ -12081,7 +12087,7 @@
         <v>2212.31</v>
       </c>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A573" s="1">
         <v>44379</v>
       </c>
@@ -12092,7 +12098,7 @@
         <v>2406.44</v>
       </c>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A574" s="1">
         <v>44386</v>
       </c>
@@ -12103,7 +12109,7 @@
         <v>2695.69</v>
       </c>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A575" s="1">
         <v>44393</v>
       </c>
@@ -12114,7 +12120,7 @@
         <v>3023.7</v>
       </c>
     </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A576" s="1">
         <v>44400</v>
       </c>
@@ -12125,7 +12131,7 @@
         <v>3142.98</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A577" s="1">
         <v>44407</v>
       </c>
@@ -12136,7 +12142,7 @@
         <v>3301.03</v>
       </c>
     </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A578" s="1">
         <v>44414</v>
       </c>
@@ -12147,7 +12153,7 @@
         <v>3548.53</v>
       </c>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A579" s="1">
         <v>44421</v>
       </c>
@@ -12158,7 +12164,7 @@
         <v>3554.49</v>
       </c>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A580" s="1">
         <v>44428</v>
       </c>
@@ -12169,7 +12175,7 @@
         <v>3560.46</v>
       </c>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A581" s="1">
         <v>44435</v>
       </c>
@@ -12180,7 +12186,7 @@
         <v>3599.22</v>
       </c>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A582" s="1">
         <v>44442</v>
       </c>
@@ -12191,7 +12197,7 @@
         <v>3694.64</v>
       </c>
     </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A583" s="1">
         <v>44449</v>
       </c>
@@ -12202,7 +12208,7 @@
         <v>3822.87</v>
       </c>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A584" s="1">
         <v>44456</v>
       </c>
@@ -12213,7 +12219,7 @@
         <v>3928.73</v>
       </c>
     </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A585" s="1">
         <v>44463</v>
       </c>
@@ -12224,7 +12230,7 @@
         <v>3980.91</v>
       </c>
     </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A586" s="1">
         <v>44470</v>
       </c>
@@ -12235,7 +12241,7 @@
         <v>3989.86</v>
       </c>
     </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A587" s="1">
         <v>44477</v>
       </c>
@@ -12246,7 +12252,7 @@
         <v>3995.82</v>
       </c>
     </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A588" s="1">
         <v>44484</v>
       </c>
@@ -12257,7 +12263,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A589" s="1">
         <v>44491</v>
       </c>
@@ -12268,7 +12274,7 @@
         <v>3998.8</v>
       </c>
     </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A590" s="1">
         <v>44498</v>
       </c>
@@ -12279,7 +12285,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A591" s="1">
         <v>44505</v>
       </c>
@@ -12290,7 +12296,7 @@
         <v>3936.18</v>
       </c>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A592" s="1">
         <v>44512</v>
       </c>
@@ -12301,7 +12307,7 @@
         <v>3852.69</v>
       </c>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" s="1">
         <v>44519</v>
       </c>
@@ -12309,7 +12315,7 @@
         <v>44519</v>
       </c>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" s="1">
         <v>44526</v>
       </c>
@@ -12317,7 +12323,7 @@
         <v>44526</v>
       </c>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" s="1">
         <v>44533</v>
       </c>
@@ -12325,7 +12331,7 @@
         <v>44533</v>
       </c>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" s="1">
         <v>44540</v>
       </c>
@@ -12333,7 +12339,7 @@
         <v>44540</v>
       </c>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" s="1">
         <v>44547</v>
       </c>
@@ -12341,7 +12347,7 @@
         <v>44547</v>
       </c>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" s="1">
         <v>44554</v>
       </c>
@@ -12349,7 +12355,7 @@
         <v>44554</v>
       </c>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" s="1">
         <v>44561</v>
       </c>
@@ -12357,7 +12363,7 @@
         <v>44561</v>
       </c>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" s="1">
         <v>44568</v>
       </c>
@@ -12365,7 +12371,7 @@
         <v>44568</v>
       </c>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" s="1">
         <v>44575</v>
       </c>
@@ -12373,7 +12379,7 @@
         <v>44575</v>
       </c>
     </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" s="1">
         <v>44582</v>
       </c>
@@ -12381,7 +12387,7 @@
         <v>44582</v>
       </c>
     </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" s="1">
         <v>44589</v>
       </c>
@@ -12389,7 +12395,7 @@
         <v>44589</v>
       </c>
     </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" s="1">
         <v>44596</v>
       </c>
@@ -12397,7 +12403,7 @@
         <v>44596</v>
       </c>
     </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" s="1">
         <v>44603</v>
       </c>
@@ -12405,7 +12411,7 @@
         <v>44603</v>
       </c>
     </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" s="1">
         <v>44610</v>
       </c>
@@ -12413,7 +12419,7 @@
         <v>44610</v>
       </c>
     </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" s="1">
         <v>44617</v>
       </c>
@@ -12421,7 +12427,7 @@
         <v>44617</v>
       </c>
     </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" s="1">
         <v>44624</v>
       </c>
@@ -12429,7 +12435,7 @@
         <v>44624</v>
       </c>
     </row>
-    <row r="609" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" s="1">
         <v>44631</v>
       </c>
@@ -12437,7 +12443,7 @@
         <v>44631</v>
       </c>
     </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" s="1">
         <v>44638</v>
       </c>
@@ -12445,7 +12451,7 @@
         <v>44638</v>
       </c>
     </row>
-    <row r="611" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" s="1">
         <v>44645</v>
       </c>
@@ -12453,7 +12459,7 @@
         <v>44645</v>
       </c>
     </row>
-    <row r="612" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" s="1">
         <v>44652</v>
       </c>
@@ -12461,7 +12467,7 @@
         <v>44652</v>
       </c>
     </row>
-    <row r="613" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" s="1">
         <v>44659</v>
       </c>
@@ -12469,7 +12475,7 @@
         <v>44659</v>
       </c>
     </row>
-    <row r="614" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" s="1">
         <v>44666</v>
       </c>
@@ -12477,7 +12483,7 @@
         <v>44666</v>
       </c>
     </row>
-    <row r="615" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" s="1">
         <v>44673</v>
       </c>
@@ -12485,7 +12491,7 @@
         <v>44673</v>
       </c>
     </row>
-    <row r="616" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" s="1">
         <v>44680</v>
       </c>
@@ -12493,7 +12499,7 @@
         <v>44680</v>
       </c>
     </row>
-    <row r="617" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" s="1">
         <v>44687</v>
       </c>
@@ -12501,7 +12507,7 @@
         <v>44687</v>
       </c>
     </row>
-    <row r="618" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" s="1">
         <v>44694</v>
       </c>
@@ -12509,7 +12515,7 @@
         <v>44694</v>
       </c>
     </row>
-    <row r="619" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" s="1">
         <v>44701</v>
       </c>
@@ -12517,7 +12523,7 @@
         <v>44701</v>
       </c>
     </row>
-    <row r="620" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" s="1">
         <v>44708</v>
       </c>
@@ -12525,7 +12531,7 @@
         <v>44708</v>
       </c>
     </row>
-    <row r="621" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" s="1">
         <v>44715</v>
       </c>
@@ -12533,7 +12539,7 @@
         <v>44715</v>
       </c>
     </row>
-    <row r="622" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" s="1">
         <v>44722</v>
       </c>
@@ -12541,7 +12547,7 @@
         <v>44722</v>
       </c>
     </row>
-    <row r="623" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" s="1">
         <v>44729</v>
       </c>
@@ -12549,7 +12555,7 @@
         <v>44729</v>
       </c>
     </row>
-    <row r="624" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" s="1">
         <v>44736</v>
       </c>
@@ -12557,7 +12563,7 @@
         <v>44736</v>
       </c>
     </row>
-    <row r="625" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" s="1">
         <v>44743</v>
       </c>
@@ -12565,7 +12571,7 @@
         <v>44743</v>
       </c>
     </row>
-    <row r="626" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" s="1">
         <v>44750</v>
       </c>
@@ -12573,7 +12579,7 @@
         <v>44750</v>
       </c>
     </row>
-    <row r="627" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" s="1">
         <v>44757</v>
       </c>
@@ -12581,7 +12587,7 @@
         <v>44757</v>
       </c>
     </row>
-    <row r="628" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" s="1">
         <v>44764</v>
       </c>
@@ -12589,7 +12595,7 @@
         <v>44764</v>
       </c>
     </row>
-    <row r="629" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" s="1">
         <v>44771</v>
       </c>
@@ -12597,7 +12603,7 @@
         <v>44771</v>
       </c>
     </row>
-    <row r="630" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" s="1">
         <v>44778</v>
       </c>
@@ -12605,7 +12611,7 @@
         <v>44778</v>
       </c>
     </row>
-    <row r="631" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" s="1">
         <v>44785</v>
       </c>
@@ -12613,7 +12619,7 @@
         <v>44785</v>
       </c>
     </row>
-    <row r="632" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" s="1">
         <v>44792</v>
       </c>
@@ -12621,7 +12627,7 @@
         <v>44792</v>
       </c>
     </row>
-    <row r="633" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" s="1">
         <v>44799</v>
       </c>
@@ -12629,7 +12635,7 @@
         <v>44799</v>
       </c>
     </row>
-    <row r="634" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" s="1">
         <v>44806</v>
       </c>
@@ -12637,7 +12643,7 @@
         <v>44806</v>
       </c>
     </row>
-    <row r="635" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" s="1">
         <v>44813</v>
       </c>
@@ -12645,7 +12651,7 @@
         <v>44813</v>
       </c>
     </row>
-    <row r="636" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" s="1">
         <v>44820</v>
       </c>
@@ -12653,7 +12659,7 @@
         <v>44820</v>
       </c>
     </row>
-    <row r="637" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" s="1">
         <v>44827</v>
       </c>
@@ -12661,7 +12667,7 @@
         <v>44827</v>
       </c>
     </row>
-    <row r="638" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638" s="1">
         <v>44834</v>
       </c>
@@ -12669,7 +12675,7 @@
         <v>44834</v>
       </c>
     </row>
-    <row r="639" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" s="1">
         <v>44841</v>
       </c>
@@ -12677,7 +12683,7 @@
         <v>44841</v>
       </c>
     </row>
-    <row r="640" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" s="1">
         <v>44848</v>
       </c>
@@ -12685,7 +12691,7 @@
         <v>44848</v>
       </c>
     </row>
-    <row r="641" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" s="1">
         <v>44855</v>
       </c>
@@ -12693,7 +12699,7 @@
         <v>44855</v>
       </c>
     </row>
-    <row r="642" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" s="1">
         <v>44862</v>
       </c>
@@ -12701,7 +12707,7 @@
         <v>44862</v>
       </c>
     </row>
-    <row r="643" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643" s="1">
         <v>44869</v>
       </c>
@@ -12709,7 +12715,7 @@
         <v>44869</v>
       </c>
     </row>
-    <row r="644" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" s="1">
         <v>44876</v>
       </c>
@@ -12717,7 +12723,7 @@
         <v>44876</v>
       </c>
     </row>
-    <row r="645" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" s="1">
         <v>44883</v>
       </c>
@@ -12725,7 +12731,7 @@
         <v>44883</v>
       </c>
     </row>
-    <row r="646" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" s="1">
         <v>44890</v>
       </c>
@@ -12733,7 +12739,7 @@
         <v>44890</v>
       </c>
     </row>
-    <row r="647" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" s="1">
         <v>44897</v>
       </c>
@@ -12741,7 +12747,7 @@
         <v>44897</v>
       </c>
     </row>
-    <row r="648" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" s="1">
         <v>44904</v>
       </c>
@@ -12749,7 +12755,7 @@
         <v>44904</v>
       </c>
     </row>
-    <row r="649" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" s="1">
         <v>44911</v>
       </c>
@@ -12757,7 +12763,7 @@
         <v>44911</v>
       </c>
     </row>
-    <row r="650" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" s="1">
         <v>44918</v>
       </c>
@@ -12765,7 +12771,7 @@
         <v>44918</v>
       </c>
     </row>
-    <row r="651" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" s="1">
         <v>44925</v>
       </c>
@@ -12773,7 +12779,7 @@
         <v>44925</v>
       </c>
     </row>
-    <row r="652" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" s="1">
         <v>44932</v>
       </c>
@@ -12781,7 +12787,7 @@
         <v>44932</v>
       </c>
     </row>
-    <row r="653" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" s="1">
         <v>44939</v>
       </c>
@@ -12789,7 +12795,7 @@
         <v>44939</v>
       </c>
     </row>
-    <row r="654" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654" s="1">
         <v>44946</v>
       </c>
@@ -12797,7 +12803,7 @@
         <v>44946</v>
       </c>
     </row>
-    <row r="655" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655" s="1">
         <v>44953</v>
       </c>
@@ -12805,7 +12811,7 @@
         <v>44953</v>
       </c>
     </row>
-    <row r="656" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656" s="1">
         <v>44960</v>
       </c>
@@ -12813,7 +12819,7 @@
         <v>44960</v>
       </c>
     </row>
-    <row r="657" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A657" s="1">
         <v>44967</v>
       </c>
@@ -12821,7 +12827,7 @@
         <v>44967</v>
       </c>
     </row>
-    <row r="658" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658" s="1">
         <v>44974</v>
       </c>
@@ -12829,7 +12835,7 @@
         <v>44974</v>
       </c>
     </row>
-    <row r="659" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659" s="1">
         <v>44981</v>
       </c>
@@ -12837,7 +12843,7 @@
         <v>44981</v>
       </c>
     </row>
-    <row r="660" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" s="1">
         <v>44988</v>
       </c>
@@ -12845,7 +12851,7 @@
         <v>44988</v>
       </c>
     </row>
-    <row r="661" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A661" s="1">
         <v>44995</v>
       </c>
@@ -12853,7 +12859,7 @@
         <v>44995</v>
       </c>
     </row>
-    <row r="662" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A662" s="1">
         <v>45002</v>
       </c>
@@ -12861,7 +12867,7 @@
         <v>45002</v>
       </c>
     </row>
-    <row r="663" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663" s="1">
         <v>45009</v>
       </c>
@@ -12869,7 +12875,7 @@
         <v>45009</v>
       </c>
     </row>
-    <row r="664" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664" s="1">
         <v>45016</v>
       </c>
@@ -12877,7 +12883,7 @@
         <v>45016</v>
       </c>
     </row>
-    <row r="665" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A665" s="1">
         <v>45023</v>
       </c>
@@ -12885,7 +12891,7 @@
         <v>45023</v>
       </c>
     </row>
-    <row r="666" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A666" s="1">
         <v>45030</v>
       </c>
@@ -12893,7 +12899,7 @@
         <v>45030</v>
       </c>
     </row>
-    <row r="667" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A667" s="1">
         <v>45037</v>
       </c>
@@ -12901,7 +12907,7 @@
         <v>45037</v>
       </c>
     </row>
-    <row r="668" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A668" s="1">
         <v>45044</v>
       </c>
@@ -12909,7 +12915,7 @@
         <v>45044</v>
       </c>
     </row>
-    <row r="669" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A669" s="1">
         <v>45051</v>
       </c>
@@ -12917,7 +12923,7 @@
         <v>45051</v>
       </c>
     </row>
-    <row r="670" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A670" s="1">
         <v>45058</v>
       </c>
@@ -12925,7 +12931,7 @@
         <v>45058</v>
       </c>
     </row>
-    <row r="671" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671" s="1">
         <v>45065</v>
       </c>
@@ -12933,7 +12939,7 @@
         <v>45065</v>
       </c>
     </row>
-    <row r="672" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A672" s="1">
         <v>45072</v>
       </c>
@@ -12941,7 +12947,7 @@
         <v>45072</v>
       </c>
     </row>
-    <row r="673" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A673" s="1">
         <v>45079</v>
       </c>
@@ -12949,7 +12955,7 @@
         <v>45079</v>
       </c>
     </row>
-    <row r="674" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A674" s="1">
         <v>45086</v>
       </c>
@@ -12957,7 +12963,7 @@
         <v>45086</v>
       </c>
     </row>
-    <row r="675" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A675" s="1">
         <v>45093</v>
       </c>
@@ -12965,7 +12971,7 @@
         <v>45093</v>
       </c>
     </row>
-    <row r="676" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A676" s="1">
         <v>45100</v>
       </c>
@@ -12973,7 +12979,7 @@
         <v>45100</v>
       </c>
     </row>
-    <row r="677" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A677" s="1">
         <v>45107</v>
       </c>
@@ -12981,7 +12987,7 @@
         <v>45107</v>
       </c>
     </row>
-    <row r="678" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A678" s="1">
         <v>45114</v>
       </c>
@@ -12989,7 +12995,7 @@
         <v>45114</v>
       </c>
     </row>
-    <row r="679" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A679" s="1">
         <v>45121</v>
       </c>
@@ -12997,7 +13003,7 @@
         <v>45121</v>
       </c>
     </row>
-    <row r="680" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A680" s="1">
         <v>45128</v>
       </c>
@@ -13005,7 +13011,7 @@
         <v>45128</v>
       </c>
     </row>
-    <row r="681" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A681" s="1">
         <v>45135</v>
       </c>
@@ -13013,7 +13019,7 @@
         <v>45135</v>
       </c>
     </row>
-    <row r="682" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A682" s="1">
         <v>45142</v>
       </c>
@@ -13021,7 +13027,7 @@
         <v>45142</v>
       </c>
     </row>
-    <row r="683" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A683" s="1">
         <v>45149</v>
       </c>
@@ -13029,7 +13035,7 @@
         <v>45149</v>
       </c>
     </row>
-    <row r="684" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A684" s="1">
         <v>45156</v>
       </c>
@@ -13037,7 +13043,7 @@
         <v>45156</v>
       </c>
     </row>
-    <row r="685" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A685" s="1">
         <v>45163</v>
       </c>
@@ -13045,7 +13051,7 @@
         <v>45163</v>
       </c>
     </row>
-    <row r="686" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A686" s="1">
         <v>45170</v>
       </c>
@@ -13053,7 +13059,7 @@
         <v>45170</v>
       </c>
     </row>
-    <row r="687" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A687" s="1">
         <v>45177</v>
       </c>
@@ -13061,7 +13067,7 @@
         <v>45177</v>
       </c>
     </row>
-    <row r="688" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A688" s="1">
         <v>45184</v>
       </c>
@@ -13069,7 +13075,7 @@
         <v>45184</v>
       </c>
     </row>
-    <row r="689" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A689" s="1">
         <v>45191</v>
       </c>
@@ -13077,7 +13083,7 @@
         <v>45191</v>
       </c>
     </row>
-    <row r="690" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A690" s="1">
         <v>45198</v>
       </c>
@@ -13085,7 +13091,7 @@
         <v>45198</v>
       </c>
     </row>
-    <row r="691" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A691" s="1">
         <v>45205</v>
       </c>
@@ -13093,7 +13099,7 @@
         <v>45205</v>
       </c>
     </row>
-    <row r="692" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A692" s="1">
         <v>45212</v>
       </c>
@@ -13101,7 +13107,7 @@
         <v>45212</v>
       </c>
     </row>
-    <row r="693" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A693" s="1">
         <v>45219</v>
       </c>
@@ -13109,7 +13115,7 @@
         <v>45219</v>
       </c>
     </row>
-    <row r="694" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A694" s="1">
         <v>45226</v>
       </c>
@@ -13117,7 +13123,7 @@
         <v>45226</v>
       </c>
     </row>
-    <row r="695" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A695" s="1">
         <v>45233</v>
       </c>
@@ -13125,7 +13131,7 @@
         <v>45233</v>
       </c>
     </row>
-    <row r="696" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A696" s="1">
         <v>45240</v>
       </c>
@@ -13133,7 +13139,7 @@
         <v>45240</v>
       </c>
     </row>
-    <row r="697" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A697" s="1">
         <v>45247</v>
       </c>
@@ -13141,7 +13147,7 @@
         <v>45247</v>
       </c>
     </row>
-    <row r="698" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A698" s="1">
         <v>45254</v>
       </c>
@@ -13149,7 +13155,7 @@
         <v>45254</v>
       </c>
     </row>
-    <row r="699" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A699" s="1">
         <v>45261</v>
       </c>
@@ -13157,7 +13163,7 @@
         <v>45261</v>
       </c>
     </row>
-    <row r="700" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A700" s="1">
         <v>45268</v>
       </c>
@@ -13165,7 +13171,7 @@
         <v>45268</v>
       </c>
     </row>
-    <row r="701" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A701" s="1">
         <v>45275</v>
       </c>
@@ -13173,7 +13179,7 @@
         <v>45275</v>
       </c>
     </row>
-    <row r="702" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A702" s="1">
         <v>45282</v>
       </c>
@@ -13181,7 +13187,7 @@
         <v>45282</v>
       </c>
     </row>
-    <row r="703" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A703" s="1">
         <v>45289</v>
       </c>
@@ -13189,7 +13195,7 @@
         <v>45289</v>
       </c>
     </row>
-    <row r="704" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A704" s="1">
         <v>45296</v>
       </c>
@@ -13197,7 +13203,7 @@
         <v>45296</v>
       </c>
     </row>
-    <row r="705" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A705" s="1">
         <v>45303</v>
       </c>
@@ -13205,7 +13211,7 @@
         <v>45303</v>
       </c>
     </row>
-    <row r="706" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A706" s="1">
         <v>45310</v>
       </c>
@@ -13213,7 +13219,7 @@
         <v>45310</v>
       </c>
     </row>
-    <row r="707" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A707" s="1">
         <v>45317</v>
       </c>
@@ -13221,7 +13227,7 @@
         <v>45317</v>
       </c>
     </row>
-    <row r="708" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A708" s="1">
         <v>45324</v>
       </c>
@@ -13229,7 +13235,7 @@
         <v>45324</v>
       </c>
     </row>
-    <row r="709" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A709" s="1">
         <v>45331</v>
       </c>
@@ -13237,7 +13243,7 @@
         <v>45331</v>
       </c>
     </row>
-    <row r="710" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A710" s="1">
         <v>45338</v>
       </c>
@@ -13245,7 +13251,7 @@
         <v>45338</v>
       </c>
     </row>
-    <row r="711" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A711" s="1">
         <v>45345</v>
       </c>
@@ -13253,7 +13259,7 @@
         <v>45345</v>
       </c>
     </row>
-    <row r="712" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A712" s="1">
         <v>45352</v>
       </c>
@@ -13261,7 +13267,7 @@
         <v>45352</v>
       </c>
     </row>
-    <row r="713" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A713" s="1">
         <v>45359</v>
       </c>
@@ -13269,7 +13275,7 @@
         <v>45359</v>
       </c>
     </row>
-    <row r="714" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A714" s="1">
         <v>45366</v>
       </c>
@@ -13277,7 +13283,7 @@
         <v>45366</v>
       </c>
     </row>
-    <row r="715" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A715" s="1">
         <v>45373</v>
       </c>
@@ -13285,7 +13291,7 @@
         <v>45373</v>
       </c>
     </row>
-    <row r="716" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A716" s="1">
         <v>45380</v>
       </c>
@@ -13293,7 +13299,7 @@
         <v>45380</v>
       </c>
     </row>
-    <row r="717" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A717" s="1">
         <v>45387</v>
       </c>
@@ -13301,7 +13307,7 @@
         <v>45387</v>
       </c>
     </row>
-    <row r="718" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A718" s="1">
         <v>45394</v>
       </c>
@@ -13309,7 +13315,7 @@
         <v>45394</v>
       </c>
     </row>
-    <row r="719" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A719" s="1">
         <v>45401</v>
       </c>
@@ -13317,7 +13323,7 @@
         <v>45401</v>
       </c>
     </row>
-    <row r="720" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A720" s="1">
         <v>45408</v>
       </c>
@@ -13325,7 +13331,7 @@
         <v>45408</v>
       </c>
     </row>
-    <row r="721" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A721" s="1">
         <v>45415</v>
       </c>
@@ -13333,7 +13339,7 @@
         <v>45415</v>
       </c>
     </row>
-    <row r="722" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A722" s="1">
         <v>45422</v>
       </c>
@@ -13341,7 +13347,7 @@
         <v>45422</v>
       </c>
     </row>
-    <row r="723" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A723" s="1">
         <v>45429</v>
       </c>
@@ -13349,7 +13355,7 @@
         <v>45429</v>
       </c>
     </row>
-    <row r="724" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A724" s="1">
         <v>45436</v>
       </c>
@@ -13357,7 +13363,7 @@
         <v>45436</v>
       </c>
     </row>
-    <row r="725" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A725" s="1">
         <v>45443</v>
       </c>
@@ -13365,7 +13371,7 @@
         <v>45443</v>
       </c>
     </row>
-    <row r="726" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A726" s="1">
         <v>45450</v>
       </c>
@@ -13373,7 +13379,7 @@
         <v>45450</v>
       </c>
     </row>
-    <row r="727" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A727" s="1">
         <v>45457</v>
       </c>
@@ -13381,7 +13387,7 @@
         <v>45457</v>
       </c>
     </row>
-    <row r="728" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A728" s="1">
         <v>45464</v>
       </c>
@@ -13392,7 +13398,7 @@
         <v>1627.4</v>
       </c>
     </row>
-    <row r="729" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A729" s="1">
         <v>45471</v>
       </c>
@@ -13403,7 +13409,7 @@
         <v>1712.39</v>
       </c>
     </row>
-    <row r="730" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A730" s="1">
         <v>45478</v>
       </c>
@@ -13411,7 +13417,7 @@
         <v>45478</v>
       </c>
     </row>
-    <row r="731" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A731" s="1">
         <v>45485</v>
       </c>
@@ -13419,7 +13425,7 @@
         <v>45485</v>
       </c>
     </row>
-    <row r="732" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A732" s="1">
         <v>45492</v>
       </c>
@@ -13427,7 +13433,7 @@
         <v>45492</v>
       </c>
     </row>
-    <row r="733" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A733" s="1">
         <v>45499</v>
       </c>
@@ -13435,7 +13441,7 @@
         <v>45499</v>
       </c>
     </row>
-    <row r="734" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A734" s="1">
         <v>45506</v>
       </c>
@@ -13443,7 +13449,7 @@
         <v>45506</v>
       </c>
     </row>
-    <row r="735" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A735" s="1">
         <v>45513</v>
       </c>
@@ -13451,7 +13457,7 @@
         <v>45513</v>
       </c>
     </row>
-    <row r="736" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A736" s="1">
         <v>45520</v>
       </c>
@@ -13459,7 +13465,7 @@
         <v>45520</v>
       </c>
     </row>
-    <row r="737" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A737" s="1">
         <v>45527</v>
       </c>
@@ -13467,7 +13473,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="738" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A738" s="1">
         <v>45534</v>
       </c>
@@ -13475,7 +13481,7 @@
         <v>45534</v>
       </c>
     </row>
-    <row r="739" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A739" s="1">
         <v>45541</v>
       </c>
@@ -13483,7 +13489,7 @@
         <v>45541</v>
       </c>
     </row>
-    <row r="740" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A740" s="1">
         <v>45548</v>
       </c>
@@ -13491,7 +13497,7 @@
         <v>45548</v>
       </c>
     </row>
-    <row r="741" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A741" s="1">
         <v>45555</v>
       </c>
@@ -13499,7 +13505,7 @@
         <v>45555</v>
       </c>
     </row>
-    <row r="742" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A742" s="1">
         <v>45562</v>
       </c>
@@ -13507,7 +13513,7 @@
         <v>45562</v>
       </c>
     </row>
-    <row r="743" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A743" s="1">
         <v>45569</v>
       </c>
@@ -13515,7 +13521,7 @@
         <v>45569</v>
       </c>
     </row>
-    <row r="744" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A744" s="1">
         <v>45576</v>
       </c>
@@ -13523,7 +13529,7 @@
         <v>45576</v>
       </c>
     </row>
-    <row r="745" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A745" s="1">
         <v>45583</v>
       </c>
@@ -13531,7 +13537,7 @@
         <v>45583</v>
       </c>
     </row>
-    <row r="746" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A746" s="1">
         <v>45590</v>
       </c>
@@ -13539,7 +13545,7 @@
         <v>45590</v>
       </c>
     </row>
-    <row r="747" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A747" s="1">
         <v>45597</v>
       </c>
@@ -13547,7 +13553,7 @@
         <v>45597</v>
       </c>
     </row>
-    <row r="748" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A748" s="1">
         <v>45604</v>
       </c>
@@ -13555,7 +13561,7 @@
         <v>45604</v>
       </c>
     </row>
-    <row r="749" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A749" s="1">
         <v>45611</v>
       </c>
@@ -13563,7 +13569,7 @@
         <v>45611</v>
       </c>
     </row>
-    <row r="750" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A750" s="1">
         <v>45618</v>
       </c>
@@ -13571,7 +13577,7 @@
         <v>45618</v>
       </c>
     </row>
-    <row r="751" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A751" s="1">
         <v>45625</v>
       </c>
@@ -13579,7 +13585,7 @@
         <v>45625</v>
       </c>
     </row>
-    <row r="752" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A752" s="1">
         <v>45632</v>
       </c>
@@ -13587,7 +13593,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="753" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A753" s="1">
         <v>45639</v>
       </c>
@@ -13595,7 +13601,7 @@
         <v>45639</v>
       </c>
     </row>
-    <row r="754" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A754" s="1">
         <v>45646</v>
       </c>
@@ -13603,7 +13609,7 @@
         <v>45646</v>
       </c>
     </row>
-    <row r="755" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A755" s="1">
         <v>45653</v>
       </c>
@@ -13611,7 +13617,7 @@
         <v>45653</v>
       </c>
     </row>
-    <row r="756" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A756" s="1">
         <v>45660</v>
       </c>
@@ -13619,7 +13625,7 @@
         <v>45660</v>
       </c>
     </row>
-    <row r="757" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A757" s="1">
         <v>45667</v>
       </c>
@@ -13627,7 +13633,7 @@
         <v>45667</v>
       </c>
     </row>
-    <row r="758" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A758" s="1">
         <v>45674</v>
       </c>
@@ -13635,7 +13641,7 @@
         <v>45674</v>
       </c>
     </row>
-    <row r="759" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A759" s="1">
         <v>45681</v>
       </c>
@@ -13643,7 +13649,7 @@
         <v>45681</v>
       </c>
     </row>
-    <row r="760" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A760" s="1">
         <v>45688</v>
       </c>
@@ -13651,7 +13657,7 @@
         <v>45688</v>
       </c>
     </row>
-    <row r="761" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A761" s="1">
         <v>45695</v>
       </c>
@@ -13659,7 +13665,7 @@
         <v>45695</v>
       </c>
     </row>
-    <row r="762" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A762" s="1">
         <v>45702</v>
       </c>
@@ -13667,7 +13673,7 @@
         <v>45702</v>
       </c>
     </row>
-    <row r="763" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A763" s="1">
         <v>45709</v>
       </c>
@@ -13675,7 +13681,7 @@
         <v>45709</v>
       </c>
     </row>
-    <row r="764" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A764" s="1">
         <v>45716</v>
       </c>
@@ -13683,7 +13689,7 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="765" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A765" s="1">
         <v>45723</v>
       </c>
@@ -13691,7 +13697,7 @@
         <v>45723</v>
       </c>
     </row>
-    <row r="766" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A766" s="1">
         <v>45730</v>
       </c>
@@ -13699,7 +13705,7 @@
         <v>45730</v>
       </c>
     </row>
-    <row r="767" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A767" s="1">
         <v>45737</v>
       </c>
@@ -13707,7 +13713,7 @@
         <v>45737</v>
       </c>
     </row>
-    <row r="768" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A768" s="1">
         <v>45744</v>
       </c>
@@ -13715,7 +13721,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="769" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A769" s="1">
         <v>45751</v>
       </c>
@@ -13723,7 +13729,7 @@
         <v>45751</v>
       </c>
     </row>
-    <row r="770" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A770" s="1">
         <v>45758</v>
       </c>
@@ -13731,7 +13737,7 @@
         <v>45758</v>
       </c>
     </row>
-    <row r="771" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A771" s="1">
         <v>45765</v>
       </c>
@@ -13739,7 +13745,7 @@
         <v>45765</v>
       </c>
     </row>
-    <row r="772" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A772" s="1">
         <v>45772</v>
       </c>
@@ -13747,7 +13753,7 @@
         <v>45772</v>
       </c>
     </row>
-    <row r="773" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A773" s="1">
         <v>45779</v>
       </c>
@@ -13755,7 +13761,7 @@
         <v>45779</v>
       </c>
     </row>
-    <row r="774" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A774" s="1">
         <v>45786</v>
       </c>
@@ -13763,7 +13769,7 @@
         <v>45786</v>
       </c>
     </row>
-    <row r="775" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A775" s="1">
         <v>45793</v>
       </c>
@@ -13771,7 +13777,7 @@
         <v>45793</v>
       </c>
     </row>
-    <row r="776" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A776" s="1">
         <v>45800</v>
       </c>
@@ -13779,7 +13785,7 @@
         <v>45800</v>
       </c>
     </row>
-    <row r="777" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A777" s="1">
         <v>45807</v>
       </c>
@@ -13787,7 +13793,7 @@
         <v>45807</v>
       </c>
     </row>
-    <row r="778" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A778" s="1">
         <v>45814</v>
       </c>
@@ -13795,7 +13801,7 @@
         <v>45814</v>
       </c>
     </row>
-    <row r="779" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A779" s="1">
         <v>45821</v>
       </c>
@@ -13803,7 +13809,7 @@
         <v>45821</v>
       </c>
     </row>
-    <row r="780" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A780" s="1">
         <v>45828</v>
       </c>
@@ -13814,7 +13820,7 @@
         <v>2158.19</v>
       </c>
     </row>
-    <row r="781" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A781" s="1">
         <v>45835</v>
       </c>
@@ -13825,7 +13831,7 @@
         <v>2158.19</v>
       </c>
     </row>
-    <row r="782" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A782" s="1">
         <v>45842</v>
       </c>
@@ -13833,7 +13839,7 @@
         <v>45842</v>
       </c>
     </row>
-    <row r="783" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A783" s="1">
         <v>45849</v>
       </c>
@@ -13841,7 +13847,7 @@
         <v>45849</v>
       </c>
     </row>
-    <row r="784" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A784" s="1">
         <v>45856</v>
       </c>
@@ -13849,7 +13855,7 @@
         <v>45856</v>
       </c>
     </row>
-    <row r="785" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A785" s="1">
         <v>45863</v>
       </c>
@@ -13857,7 +13863,7 @@
         <v>45863</v>
       </c>
     </row>
-    <row r="786" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A786" s="1">
         <v>45870</v>
       </c>
@@ -13865,7 +13871,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="787" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A787" s="1">
         <v>45877</v>
       </c>
@@ -13873,7 +13879,7 @@
         <v>45877</v>
       </c>
     </row>
-    <row r="788" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A788" s="1">
         <v>45884</v>
       </c>
@@ -13881,7 +13887,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="789" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A789" s="1">
         <v>45891</v>
       </c>
@@ -13889,7 +13895,7 @@
         <v>45891</v>
       </c>
     </row>
-    <row r="790" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A790" s="1">
         <v>45898</v>
       </c>
@@ -13897,7 +13903,7 @@
         <v>45898</v>
       </c>
     </row>
-    <row r="791" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A791" s="1">
         <v>45905</v>
       </c>
@@ -13905,7 +13911,7 @@
         <v>45905</v>
       </c>
     </row>
-    <row r="792" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A792" s="1">
         <v>45912</v>
       </c>
@@ -13913,7 +13919,7 @@
         <v>45912</v>
       </c>
     </row>
-    <row r="793" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A793" s="1">
         <v>45919</v>
       </c>
@@ -13921,7 +13927,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="794" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A794" s="1">
         <v>45926</v>
       </c>
@@ -13929,7 +13935,7 @@
         <v>45926</v>
       </c>
     </row>
-    <row r="795" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A795" s="1">
         <v>45933</v>
       </c>
@@ -13937,7 +13943,7 @@
         <v>45933</v>
       </c>
     </row>
-    <row r="796" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A796" s="1">
         <v>45940</v>
       </c>
@@ -13945,7 +13951,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="797" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A797" s="1">
         <v>45947</v>
       </c>
@@ -13953,7 +13959,7 @@
         <v>45947</v>
       </c>
     </row>
-    <row r="798" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A798" s="1">
         <v>45954</v>
       </c>
@@ -13961,7 +13967,7 @@
         <v>45954</v>
       </c>
     </row>
-    <row r="799" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A799" s="1">
         <v>45961</v>
       </c>
@@ -13969,7 +13975,7 @@
         <v>45961</v>
       </c>
     </row>
-    <row r="800" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A800" s="1">
         <v>45968</v>
       </c>
@@ -13977,7 +13983,7 @@
         <v>45968</v>
       </c>
     </row>
-    <row r="801" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A801" s="1">
         <v>45975</v>
       </c>
@@ -13985,7 +13991,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="802" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A802" s="1">
         <v>45982</v>
       </c>
@@ -13993,7 +13999,7 @@
         <v>45982</v>
       </c>
     </row>
-    <row r="803" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A803" s="1">
         <v>45989</v>
       </c>
@@ -14001,7 +14007,7 @@
         <v>45989</v>
       </c>
     </row>
-    <row r="804" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A804" s="1">
         <v>45996</v>
       </c>
@@ -14009,7 +14015,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="805" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A805" s="1">
         <v>46003</v>
       </c>
@@ -14017,7 +14023,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="806" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A806" s="1">
         <v>46010</v>
       </c>
@@ -14025,7 +14031,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="807" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A807" s="1">
         <v>46017</v>
       </c>
@@ -14048,7 +14054,7 @@
       <c r="N807" s="10"/>
       <c r="O807" s="10"/>
     </row>
-    <row r="808" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A808" s="1">
         <v>46024</v>
       </c>
@@ -14091,7 +14097,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="809" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A809" s="1">
         <v>46031</v>
       </c>
@@ -14134,7 +14140,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="810" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A810" s="1">
         <v>46038</v>
       </c>
@@ -14177,7 +14183,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="811" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A811" s="1">
         <v>46045</v>
       </c>
@@ -14220,7 +14226,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="812" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A812" s="1">
         <v>46052</v>
       </c>
@@ -14263,7 +14269,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="813" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A813" s="1">
         <v>46059</v>
       </c>
@@ -14306,7 +14312,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="814" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A814" s="1">
         <v>46066</v>
       </c>
@@ -14349,7 +14355,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="815" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A815" s="1">
         <v>46073</v>
       </c>
@@ -14392,7 +14398,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="816" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A816" s="1">
         <v>46080</v>
       </c>
@@ -14435,7 +14441,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="817" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A817" s="1">
         <v>46087</v>
       </c>
@@ -14478,7 +14484,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="818" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A818" s="1">
         <v>46094</v>
       </c>
@@ -14521,7 +14527,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="819" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A819" s="1">
         <v>46101</v>
       </c>
@@ -14564,7 +14570,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="820" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A820" s="1">
         <v>46108</v>
       </c>
@@ -14607,7 +14613,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="821" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A821" s="1">
         <v>46115</v>
       </c>
@@ -14650,7 +14656,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="822" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A822" s="1">
         <v>46122</v>
       </c>
@@ -14673,7 +14679,7 @@
       <c r="N822" s="3"/>
       <c r="O822" s="3"/>
     </row>
-    <row r="823" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A823" s="1">
         <v>46129</v>
       </c>
@@ -14696,7 +14702,7 @@
       <c r="N823" s="3"/>
       <c r="O823" s="3"/>
     </row>
-    <row r="824" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A824" s="1">
         <v>46136</v>
       </c>
@@ -14719,7 +14725,7 @@
       <c r="N824" s="3"/>
       <c r="O824" s="3"/>
     </row>
-    <row r="825" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A825" s="1">
         <v>46143</v>
       </c>
@@ -14762,7 +14768,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="826" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A826" s="1">
         <v>46150</v>
       </c>
@@ -14805,7 +14811,7 @@
         <v>76000</v>
       </c>
     </row>
-    <row r="827" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A827" s="1">
         <v>46157</v>
       </c>
@@ -14848,7 +14854,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="828" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A828" s="1">
         <v>46164</v>
       </c>
@@ -14891,7 +14897,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="829" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A829" s="1">
         <v>46171</v>
       </c>
@@ -14934,7 +14940,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="830" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A830" s="1">
         <v>46178</v>
       </c>
@@ -14975,7 +14981,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="831" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A831" s="1">
         <v>46185</v>
       </c>
@@ -15016,7 +15022,7 @@
         <v>78000</v>
       </c>
     </row>
-    <row r="832" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A832" s="1">
         <v>46192</v>
       </c>
@@ -15054,6 +15060,47 @@
         <v>71000</v>
       </c>
       <c r="O832" s="4">
+        <v>78000</v>
+      </c>
+    </row>
+    <row r="833" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A833" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B833" s="1">
+        <v>46199</v>
+      </c>
+      <c r="E833" s="13">
+        <v>2326.67</v>
+      </c>
+      <c r="F833" s="4">
+        <v>11250</v>
+      </c>
+      <c r="G833" s="4">
+        <v>17750</v>
+      </c>
+      <c r="H833" s="4">
+        <v>30000</v>
+      </c>
+      <c r="I833" s="4">
+        <v>33500</v>
+      </c>
+      <c r="J833" s="4">
+        <v>38000</v>
+      </c>
+      <c r="K833" s="4">
+        <v>40000</v>
+      </c>
+      <c r="L833" s="4">
+        <v>46000</v>
+      </c>
+      <c r="M833" s="4">
+        <v>57000</v>
+      </c>
+      <c r="N833" s="4">
+        <v>71000</v>
+      </c>
+      <c r="O833" s="4">
         <v>78000</v>
       </c>
     </row>
@@ -15065,7 +15112,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02768588-2FF0-42C1-8A18-87D4CAFE9D17}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -15075,12 +15122,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A6084AF-43C5-4F58-881A-79CFC1D1F25A}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="8" t="s">
         <v>15</v>
       </c>
@@ -15088,7 +15135,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B3" s="8" t="s">
         <v>17</v>
       </c>
